--- a/publishing/accessibility/springer_alt_text_inventory.xlsx
+++ b/publishing/accessibility/springer_alt_text_inventory.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rba95e2d5e3cc4d47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alt Text" sheetId="2" r:id="R82e5d891620a4e72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guidance" sheetId="3" r:id="R0914918296d94ed1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R279a70114db8440e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alt Text" sheetId="2" r:id="Rad8424983bb046fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guidance" sheetId="3" r:id="Rb26aced4ff684dd3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -169,12 +169,58 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="dk1"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="accent1"/>
-        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
+                <a:satMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
+                <a:satMod val="110000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="12700">
@@ -277,7 +323,7 @@
         <x:v>Generated at UTC</x:v>
       </x:c>
       <x:c r="B2" s="4" t="n">
-        <x:v>46186.70651364583</x:v>
+        <x:v>46188.45159912037</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -6107,16 +6153,16 @@
         <x:v>Six-layer architecture for data engineering agents</x:v>
       </x:c>
       <x:c r="K84" s="4" t="str">
-        <x:v>docs/images/part10/ai_agent_decision_workflow_ch31_01.png</x:v>
+        <x:v>docs/images/part10/ai_agent_decision_workflow_ch31_01.svg</x:v>
       </x:c>
       <x:c r="L84" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M84" s="4" t="str">
-        <x:v>2732x1534</x:v>
+        <x:v>16x7.2999997</x:v>
       </x:c>
       <x:c r="N84" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O84" s="4" t="str">
         <x:v>Six-layer architecture for data engineering agents.</x:v>
@@ -6171,16 +6217,16 @@
         <x:v>Human-AI collaboration flow by risk level</x:v>
       </x:c>
       <x:c r="K85" s="4" t="str">
-        <x:v>docs/images/part10/ai_agent_decision_workflow_ch31_02.png</x:v>
+        <x:v>docs/images/part10/ai_agent_decision_workflow_ch31_02.svg</x:v>
       </x:c>
       <x:c r="L85" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M85" s="4" t="str">
-        <x:v>2732x1534</x:v>
+        <x:v>16.510416x9.617118</x:v>
       </x:c>
       <x:c r="N85" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O85" s="4" t="str">
         <x:v>Human-AI collaboration flow by risk level.</x:v>
@@ -6233,16 +6279,16 @@
         <x:v>Unified architecture for four-source collection agents</x:v>
       </x:c>
       <x:c r="K86" s="4" t="str">
-        <x:v>docs/images/part10/ai_agent_decision_workflow_ch32_01.png</x:v>
+        <x:v>docs/images/part10/ai_agent_decision_workflow_ch32_01.svg</x:v>
       </x:c>
       <x:c r="L86" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M86" s="4" t="str">
-        <x:v>2732x1534</x:v>
+        <x:v>100x100</x:v>
       </x:c>
       <x:c r="N86" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O86" s="4" t="str">
         <x:v>Unified architecture for four-source collection agents.</x:v>
@@ -6297,16 +6343,16 @@
         <x:v>Parsing exception handling decision flow</x:v>
       </x:c>
       <x:c r="K87" s="4" t="str">
-        <x:v>docs/images/part10/ai_agent_decision_workflow_ch32_02.png</x:v>
+        <x:v>docs/images/part10/ai_agent_decision_workflow_ch32_02.svg</x:v>
       </x:c>
       <x:c r="L87" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M87" s="4" t="str">
-        <x:v>2732x1534</x:v>
+        <x:v>20.2x11</x:v>
       </x:c>
       <x:c r="N87" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O87" s="4" t="str">
         <x:v>Parsing exception handling decision flow.</x:v>
@@ -6359,16 +6405,16 @@
         <x:v>Tiered quality filtering pipeline</x:v>
       </x:c>
       <x:c r="K88" s="4" t="str">
-        <x:v>docs/images/part10/ai_agent_decision_workflow_ch32_03.png</x:v>
+        <x:v>docs/images/part10/ai_agent_decision_workflow_ch32_03.svg</x:v>
       </x:c>
       <x:c r="L88" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M88" s="4" t="str">
-        <x:v>2732x1534</x:v>
+        <x:v>23.80315x11.692913</x:v>
       </x:c>
       <x:c r="N88" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O88" s="4" t="str">
         <x:v>Tiered quality filtering pipeline.</x:v>
@@ -6423,16 +6469,16 @@
         <x:v>Four dimensions of labeling-assistance agents</x:v>
       </x:c>
       <x:c r="K89" s="4" t="str">
-        <x:v>docs/images/part10/ai_agent_decision_workflow_ch33_01.png</x:v>
+        <x:v>docs/images/part10/ai_agent_decision_workflow_ch33_01.svg</x:v>
       </x:c>
       <x:c r="L89" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M89" s="4" t="str">
-        <x:v>2732x1534</x:v>
+        <x:v>23.80315x11.692913</x:v>
       </x:c>
       <x:c r="N89" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O89" s="4" t="str">
         <x:v>Four dimensions of labeling-assistance agents.</x:v>
@@ -6485,16 +6531,16 @@
         <x:v>Synthetic data agent closed-loop pipeline</x:v>
       </x:c>
       <x:c r="K90" s="4" t="str">
-        <x:v>docs/images/part10/ai_agent_decision_workflow_ch33_02.png</x:v>
+        <x:v>docs/images/part10/ai_agent_decision_workflow_ch33_02.svg</x:v>
       </x:c>
       <x:c r="L90" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M90" s="4" t="str">
-        <x:v>2732x1534</x:v>
+        <x:v>23.80315x11.692913</x:v>
       </x:c>
       <x:c r="N90" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O90" s="4" t="str">
         <x:v>Synthetic data agent closed-loop pipeline.</x:v>
@@ -6549,16 +6595,16 @@
         <x:v>Alert-to-root-cause agent flow</x:v>
       </x:c>
       <x:c r="K91" s="4" t="str">
-        <x:v>docs/images/part10/ai_agent_decision_workflow_ch34_01.png</x:v>
+        <x:v>docs/images/part10/ai_agent_decision_workflow_ch34_01.svg</x:v>
       </x:c>
       <x:c r="L91" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M91" s="4" t="str">
-        <x:v>2732x1534</x:v>
+        <x:v>23.80315x11.692913</x:v>
       </x:c>
       <x:c r="N91" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O91" s="4" t="str">
         <x:v>Alert-to-root-cause agent flow.</x:v>
@@ -6611,16 +6657,16 @@
         <x:v>Rollback approval workflow</x:v>
       </x:c>
       <x:c r="K92" s="4" t="str">
-        <x:v>docs/images/part10/ai_agent_decision_workflow_ch34_02.png</x:v>
+        <x:v>docs/images/part10/ai_agent_decision_workflow_ch34_02.svg</x:v>
       </x:c>
       <x:c r="L92" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M92" s="4" t="str">
-        <x:v>2732x1534</x:v>
+        <x:v>23.80315x11.692913</x:v>
       </x:c>
       <x:c r="N92" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O92" s="4" t="str">
         <x:v>Rollback approval workflow.</x:v>
@@ -6675,16 +6721,16 @@
         <x:v>Pipeline self-healing decision flow</x:v>
       </x:c>
       <x:c r="K93" s="4" t="str">
-        <x:v>docs/images/part10/ai_agent_decision_workflow_ch34_03.png</x:v>
+        <x:v>docs/images/part10/ai_agent_decision_workflow_ch34_03.svg</x:v>
       </x:c>
       <x:c r="L93" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M93" s="4" t="str">
-        <x:v>2732x1534</x:v>
+        <x:v>23.80315x11.692913</x:v>
       </x:c>
       <x:c r="N93" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O93" s="4" t="str">
         <x:v>Pipeline self-healing decision flow.</x:v>
@@ -6739,16 +6785,16 @@
         <x:v>Layered approval flow for agent permissions</x:v>
       </x:c>
       <x:c r="K94" s="4" t="str">
-        <x:v>docs/images/part10/ai_agent_decision_workflow_ch35_01.png</x:v>
+        <x:v>docs/images/part10/ai_agent_decision_workflow_ch35_01.svg</x:v>
       </x:c>
       <x:c r="L94" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M94" s="4" t="str">
-        <x:v>2732x1534</x:v>
+        <x:v>23.80315x11.692913</x:v>
       </x:c>
       <x:c r="N94" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O94" s="4" t="str">
         <x:v>Layered approval flow for agent permissions.</x:v>
@@ -6801,16 +6847,16 @@
         <x:v>Layered prompt injection defense flow</x:v>
       </x:c>
       <x:c r="K95" s="4" t="str">
-        <x:v>docs/images/part10/ai_agent_decision_workflow_ch35_02.png</x:v>
+        <x:v>docs/images/part10/ai_agent_decision_workflow_ch35_02.svg</x:v>
       </x:c>
       <x:c r="L95" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M95" s="4" t="str">
-        <x:v>1773x2364</x:v>
+        <x:v>10.5x15.5</x:v>
       </x:c>
       <x:c r="N95" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O95" s="4" t="str">
         <x:v>Layered prompt injection defense flow.</x:v>
@@ -6863,16 +6909,16 @@
         <x:v>Agent security incident response flow</x:v>
       </x:c>
       <x:c r="K96" s="4" t="str">
-        <x:v>docs/images/part10/ai_agent_decision_workflow_ch35_03.png</x:v>
+        <x:v>docs/images/part10/ai_agent_decision_workflow_ch35_03.svg</x:v>
       </x:c>
       <x:c r="L96" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M96" s="4" t="str">
-        <x:v>1773x2364</x:v>
+        <x:v>11.010417x11.388889</x:v>
       </x:c>
       <x:c r="N96" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O96" s="4" t="str">
         <x:v>Agent security incident response flow.</x:v>
@@ -6980,13 +7026,13 @@
         <x:v>237</x:v>
       </x:c>
       <x:c r="H98" s="4" t="str">
-        <x:v>36-4</x:v>
+        <x:v>36-2</x:v>
       </x:c>
       <x:c r="I98" s="4" t="str">
-        <x:v>Figure 36-4: Risk matrix formed by data level, purpose, and processing action</x:v>
+        <x:v>Figure 36-2: Risk matrix formed by data level, purpose, and processing action</x:v>
       </x:c>
       <x:c r="J98" s="4" t="str">
-        <x:v>Figure 36-4: Risk matrix formed by data level, purpose, and processing action</x:v>
+        <x:v>Figure 36-2: Risk matrix formed by data level, purpose, and processing action</x:v>
       </x:c>
       <x:c r="K98" s="4" t="str">
         <x:v>docs/images/part11/图36_4_数据分级用途和处理动作构成的风险矩阵图.svg</x:v>
@@ -7015,10 +7061,10 @@
       <x:c r="S98" s="4" t="str"/>
       <x:c r="T98" s="4" t="str"/>
       <x:c r="U98" s="4" t="str">
-        <x:v>图36-4：数据分级、用途和处理动作构成的风险矩阵图</x:v>
+        <x:v>图36-2：数据分级、用途和处理动作构成的风险矩阵图</x:v>
       </x:c>
       <x:c r="V98" s="4" t="str">
-        <x:v>图36-4：数据分级、用途和处理动作构成的风险矩阵图</x:v>
+        <x:v>图36-2：数据分级、用途和处理动作构成的风险矩阵图</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -7044,13 +7090,13 @@
         <x:v>440</x:v>
       </x:c>
       <x:c r="H99" s="4" t="str">
-        <x:v>36-5</x:v>
+        <x:v>36-3</x:v>
       </x:c>
       <x:c r="I99" s="4" t="str">
-        <x:v>Figure 36-5: Compliance gate flow from data onboarding to model training</x:v>
+        <x:v>Figure 36-3: Compliance gate flow from data onboarding to model training</x:v>
       </x:c>
       <x:c r="J99" s="4" t="str">
-        <x:v>Figure 36-5: Compliance gate flow from data onboarding to model training</x:v>
+        <x:v>Figure 36-3: Compliance gate flow from data onboarding to model training</x:v>
       </x:c>
       <x:c r="K99" s="4" t="str">
         <x:v>docs/images/part11/图36_5_从数据接入到模型训练的合规门禁流程图.svg</x:v>
@@ -7077,10 +7123,10 @@
       <x:c r="S99" s="4" t="str"/>
       <x:c r="T99" s="4" t="str"/>
       <x:c r="U99" s="4" t="str">
-        <x:v>图36-5：从数据接入到模型训练的合规门禁流程图</x:v>
+        <x:v>图36-3：从数据接入到模型训练的合规门禁流程图</x:v>
       </x:c>
       <x:c r="V99" s="4" t="str">
-        <x:v>图36-5：从数据接入到模型训练的合规门禁流程图</x:v>
+        <x:v>图36-3：从数据接入到模型训练的合规门禁流程图</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -7106,13 +7152,13 @@
         <x:v>455</x:v>
       </x:c>
       <x:c r="H100" s="4" t="str">
-        <x:v>36-3</x:v>
+        <x:v>36-4</x:v>
       </x:c>
       <x:c r="I100" s="4" t="str">
-        <x:v>Figure 36-3: Privacy specification and policy generation flow</x:v>
+        <x:v>Figure 36-4: Privacy specification and policy generation flow</x:v>
       </x:c>
       <x:c r="J100" s="4" t="str">
-        <x:v>Figure 36-3: Privacy specification and policy generation flow</x:v>
+        <x:v>Figure 36-4: Privacy specification and policy generation flow</x:v>
       </x:c>
       <x:c r="K100" s="4" t="str">
         <x:v>docs/images/part11/图36_3_P09隐私规格与策略生成流程图.svg</x:v>
@@ -7139,10 +7185,10 @@
       <x:c r="S100" s="4" t="str"/>
       <x:c r="T100" s="4" t="str"/>
       <x:c r="U100" s="4" t="str">
-        <x:v>图36-3：隐私规格与策略生成流程图</x:v>
+        <x:v>图36-4：隐私规格与策略生成流程图</x:v>
       </x:c>
       <x:c r="V100" s="4" t="str">
-        <x:v>图36-3：隐私规格与策略生成流程图</x:v>
+        <x:v>图36-4：隐私规格与策略生成流程图</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -7168,13 +7214,13 @@
         <x:v>470</x:v>
       </x:c>
       <x:c r="H101" s="4" t="str">
-        <x:v>36-2</x:v>
+        <x:v>36-5</x:v>
       </x:c>
       <x:c r="I101" s="4" t="str">
-        <x:v>Figure 36-2: Data compliance lifecycle from business initiation to automated blocking and audit</x:v>
+        <x:v>Figure 36-5: Data compliance lifecycle from business initiation to automated blocking and audit</x:v>
       </x:c>
       <x:c r="J101" s="4" t="str">
-        <x:v>Figure 36-2: Engineering approval flow for DPIA and RoPA</x:v>
+        <x:v>Figure 36-5: Engineering approval flow for DPIA and RoPA</x:v>
       </x:c>
       <x:c r="K101" s="4" t="str">
         <x:v>docs/images/part11/图36_2_DPIA与RoPA工程化审批流.svg</x:v>
@@ -7201,10 +7247,10 @@
       <x:c r="S101" s="4" t="str"/>
       <x:c r="T101" s="4" t="str"/>
       <x:c r="U101" s="4" t="str">
-        <x:v>图36-2：数据合规生命周期 —— 从业务立项到下线的自动化拦截与审计流程</x:v>
+        <x:v>图36-5：数据合规生命周期 —— 从业务立项到下线的自动化拦截与审计流程</x:v>
       </x:c>
       <x:c r="V101" s="4" t="str">
-        <x:v>图36-2：DPIA与RoPA工程化审批流</x:v>
+        <x:v>图36-5：DPIA与RoPA工程化审批流</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -9987,7 +10033,7 @@
         <x:v>docs/en/part13/ch44_pretrain_recipes.md</x:v>
       </x:c>
       <x:c r="G146" s="4" t="n">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H146" s="4" t="str">
         <x:v>44-1</x:v>
@@ -9999,16 +10045,16 @@
         <x:v>Figure 44-1: Data Recipe Funnel</x:v>
       </x:c>
       <x:c r="K146" s="4" t="str">
-        <x:v>docs/images/part13/ch44_01_data_recipe_funnel_en.png</x:v>
+        <x:v>docs/images/part13/ch44_01_data_recipe_funnel_en.svg</x:v>
       </x:c>
       <x:c r="L146" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M146" s="4" t="str">
-        <x:v>2970x2371</x:v>
+        <x:v>800x600</x:v>
       </x:c>
       <x:c r="N146" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O146" s="4" t="str">
         <x:v>&lt;div align="center"&lt;bFigure 44-1: Data Recipe Funnel&lt;/b&lt;/div.</x:v>
@@ -10049,7 +10095,7 @@
         <x:v>docs/en/part13/ch44_pretrain_recipes.md</x:v>
       </x:c>
       <x:c r="G147" s="4" t="n">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H147" s="4" t="str">
         <x:v>44-2</x:v>
@@ -10061,16 +10107,16 @@
         <x:v>Figure 44-2: Data Transparency Spectrum for Large Language Models</x:v>
       </x:c>
       <x:c r="K147" s="4" t="str">
-        <x:v>docs/images/part13/ch44_02_data_transparency_spectrum_en.png</x:v>
+        <x:v>docs/images/part13/ch44_02_data_transparency_spectrum_en.svg</x:v>
       </x:c>
       <x:c r="L147" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M147" s="4" t="str">
-        <x:v>3570x1470</x:v>
+        <x:v>900x450</x:v>
       </x:c>
       <x:c r="N147" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O147" s="4" t="str">
         <x:v>&lt;div align="center"&lt;bFigure 44-2: Data Transparency Spectrum for Large Language Models&lt;/b&lt;/div.</x:v>
@@ -10111,7 +10157,7 @@
         <x:v>docs/en/part13/ch44_pretrain_recipes.md</x:v>
       </x:c>
       <x:c r="G148" s="4" t="n">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H148" s="4" t="str">
         <x:v>44-3</x:v>
@@ -10173,7 +10219,7 @@
         <x:v>docs/en/part13/ch44_pretrain_recipes.md</x:v>
       </x:c>
       <x:c r="G149" s="4" t="n">
-        <x:v>91</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H149" s="4" t="str">
         <x:v>44-4</x:v>
@@ -10185,16 +10231,16 @@
         <x:v>Figure 44-4: Estimated Data Mixture Ratios — Pie Chart Comparison Across Three Models</x:v>
       </x:c>
       <x:c r="K149" s="4" t="str">
-        <x:v>docs/images/part13/ch44_04_models_pie_chart_en.png</x:v>
+        <x:v>docs/images/part13/ch44_04_models_pie_chart_en.svg</x:v>
       </x:c>
       <x:c r="L149" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M149" s="4" t="str">
-        <x:v>4770x1864</x:v>
+        <x:v>1100x460</x:v>
       </x:c>
       <x:c r="N149" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O149" s="4" t="str">
         <x:v>&lt;div align="center"&lt;bFigure 44-4: Estimated Data Mixture Ratios — Pie Chart Comparison Across Three Models&lt;/b&lt;/div.</x:v>
@@ -10237,7 +10283,7 @@
         <x:v>docs/en/part13/ch44_pretrain_recipes.md</x:v>
       </x:c>
       <x:c r="G150" s="4" t="n">
-        <x:v>257</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="H150" s="4" t="str">
         <x:v>44-5</x:v>
@@ -10249,16 +10295,16 @@
         <x:v>Figure 44-5: Llama-3 Annealing Phase Data Composition Timeline (Curriculum Learning Schedule)</x:v>
       </x:c>
       <x:c r="K150" s="4" t="str">
-        <x:v>docs/images/part13/ch44_05_llama3_annealing_schedule_en.png</x:v>
+        <x:v>docs/images/part13/ch44_05_llama3_annealing_schedule_en.svg</x:v>
       </x:c>
       <x:c r="L150" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M150" s="4" t="str">
-        <x:v>2960x1772</x:v>
+        <x:v>1000x600</x:v>
       </x:c>
       <x:c r="N150" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O150" s="4" t="str">
         <x:v>&lt;div align="center"&lt;bFigure 44-5: Llama-3 Annealing Phase Data Composition Timeline (Curriculum Learning Schedule)&lt;/b&lt;/div.</x:v>
@@ -10311,16 +10357,16 @@
         <x:v>Figure 45-1: Schematic of the LLM Three-Stage Post-Training Pipeline</x:v>
       </x:c>
       <x:c r="K151" s="4" t="str">
-        <x:v>docs/images/part13/ch45_01_posttrain_three_stage_pipeline.png</x:v>
+        <x:v>docs/images/part13/ch45_01_posttrain_three_stage_pipeline.svg</x:v>
       </x:c>
       <x:c r="L151" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M151" s="4" t="str">
-        <x:v>2816x1425</x:v>
+        <x:v>100x100</x:v>
       </x:c>
       <x:c r="N151" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O151" s="4" t="str">
         <x:v>Data flow relationships among SFT, Preference Alignment, and Online Continuous Optimization.</x:v>
@@ -10373,16 +10419,16 @@
         <x:v>Figure 45-2: Pipeline Comparison of the Three SFT Synthesis Schools: Self-Instruct, Evol-Instruct, and Magpie</x:v>
       </x:c>
       <x:c r="K152" s="4" t="str">
-        <x:v>docs/images/part13/ch45_02_sft_synthesis_pipelines.png</x:v>
+        <x:v>docs/images/part13/ch45_02_sft_synthesis_pipelines.svg</x:v>
       </x:c>
       <x:c r="L152" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M152" s="4" t="str">
-        <x:v>2816x1454</x:v>
+        <x:v>100x100</x:v>
       </x:c>
       <x:c r="N152" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O152" s="4" t="str">
         <x:v>Data entry points, generation methods, and quality control checkpoints for the three SFT synthesis approaches.</x:v>
@@ -10435,16 +10481,16 @@
         <x:v>Figure 45-3: Tülu-3 Three-Stage Data Flow and Scale Schematic</x:v>
       </x:c>
       <x:c r="K153" s="4" t="str">
-        <x:v>docs/images/part13/ch45_03_tulu3_posttrain_flow.png</x:v>
+        <x:v>docs/images/part13/ch45_03_tulu3_posttrain_flow.svg</x:v>
       </x:c>
       <x:c r="L153" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M153" s="4" t="str">
-        <x:v>2816x1536</x:v>
+        <x:v>100x100</x:v>
       </x:c>
       <x:c r="N153" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O153" s="4" t="str">
         <x:v>Data flow and stage relationships in Tülu-3 from SFT-Mix and DPO mix to RLVR.</x:v>
@@ -10497,16 +10543,16 @@
         <x:v>Figure 46-1: The four stages of the R1-style reasoning data flywheel</x:v>
       </x:c>
       <x:c r="K154" s="4" t="str">
-        <x:v>docs/images/part13/ch46_01_r1_reasoning_flywheel.png</x:v>
+        <x:v>docs/images/part13/ch46_01_r1_reasoning_flywheel.svg</x:v>
       </x:c>
       <x:c r="L154" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M154" s="4" t="str">
-        <x:v>2816x1536</x:v>
+        <x:v>100x100</x:v>
       </x:c>
       <x:c r="N154" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O154" s="4" t="str">
         <x:v>The data feedback relationships among cold-start SFT, large-scale RL, rejection sampling, and second-round SFT.</x:v>
@@ -10559,16 +10605,16 @@
         <x:v>Figure 46-2: Reward signal and verifier architecture for reasoning data</x:v>
       </x:c>
       <x:c r="K155" s="4" t="str">
-        <x:v>docs/images/part13/ch46_02_reward_verifier_architecture.png</x:v>
+        <x:v>docs/images/part13/ch46_02_reward_verifier_architecture.svg</x:v>
       </x:c>
       <x:c r="L155" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M155" s="4" t="str">
-        <x:v>2816x1349</x:v>
+        <x:v>100x100</x:v>
       </x:c>
       <x:c r="N155" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O155" s="4" t="str">
         <x:v>The relationship among rule-based rewards, model-based rewards, and human audits.</x:v>
@@ -10621,16 +10667,16 @@
         <x:v>Figure 46-3: Long-CoT data sample cross-section</x:v>
       </x:c>
       <x:c r="K156" s="4" t="str">
-        <x:v>docs/images/part13/ch46_03_long_cot_trace_patterns.png</x:v>
+        <x:v>docs/images/part13/ch46_03_long_cot_trace_patterns.svg</x:v>
       </x:c>
       <x:c r="L156" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M156" s="4" t="str">
-        <x:v>2816x1395</x:v>
+        <x:v>100x100</x:v>
       </x:c>
       <x:c r="N156" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O156" s="4" t="str">
         <x:v>A cross-section of a Long-CoT data sample illustrating three reasoning trajectory patterns: Reflection, Verification, and Backtrack.</x:v>
@@ -10671,7 +10717,7 @@
         <x:v>docs/en/part13/ch47_vlm_data_recipes.md</x:v>
       </x:c>
       <x:c r="G157" s="4" t="n">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="H157" s="4" t="str">
         <x:v>47-1</x:v>
@@ -10733,7 +10779,7 @@
         <x:v>docs/en/part13/ch47_vlm_data_recipes.md</x:v>
       </x:c>
       <x:c r="G158" s="4" t="n">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H158" s="4" t="str">
         <x:v>47-2</x:v>
@@ -10745,16 +10791,16 @@
         <x:v>Figure 47-2: VLM Three-Stage Data Engineering Pipeline</x:v>
       </x:c>
       <x:c r="K158" s="4" t="str">
-        <x:v>docs/images/part13/ch47_02_vlm_three_stages_en.png</x:v>
+        <x:v>docs/images/part13/ch47_02_vlm_three_stages_en.svg</x:v>
       </x:c>
       <x:c r="L158" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M158" s="4" t="str">
-        <x:v>1024x1024</x:v>
+        <x:v>900x660</x:v>
       </x:c>
       <x:c r="N158" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O158" s="4" t="str">
         <x:v>&lt;div align="center"&lt;bFigure 47-2: VLM Three-Stage Data Pipeline&lt;/b&lt;/div.</x:v>
@@ -10797,7 +10843,7 @@
         <x:v>docs/en/part13/ch47_vlm_data_recipes.md</x:v>
       </x:c>
       <x:c r="G159" s="4" t="n">
-        <x:v>116</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="H159" s="4" t="str">
         <x:v>47-3</x:v>
@@ -10809,16 +10855,16 @@
         <x:v>Figure 47-3: Native vs. Dynamic Resolution Data Pipeline Comparison</x:v>
       </x:c>
       <x:c r="K159" s="4" t="str">
-        <x:v>docs/images/part13/ch47_03_resolution_handling_en.png</x:v>
+        <x:v>docs/images/part13/ch47_03_resolution_handling_en.svg</x:v>
       </x:c>
       <x:c r="L159" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M159" s="4" t="str">
-        <x:v>1024x1024</x:v>
+        <x:v>800x750</x:v>
       </x:c>
       <x:c r="N159" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O159" s="4" t="str">
         <x:v>&lt;div align="center"&lt;bFigure 47-3: Native vs. Dynamic Resolution Data Pipeline Comparison&lt;/b&lt;/div.</x:v>
@@ -10861,7 +10907,7 @@
         <x:v>docs/en/part13/ch47_vlm_data_recipes.md</x:v>
       </x:c>
       <x:c r="G160" s="4" t="n">
-        <x:v>147</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="H160" s="4" t="str">
         <x:v>47-4</x:v>
@@ -10873,16 +10919,16 @@
         <x:v>Figure 47-4: Multimodal Instruction Synthesis Pipeline</x:v>
       </x:c>
       <x:c r="K160" s="4" t="str">
-        <x:v>docs/images/part13/ch47_04_instruction_synthesis_en.png</x:v>
+        <x:v>docs/images/part13/ch47_04_instruction_synthesis_en.svg</x:v>
       </x:c>
       <x:c r="L160" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M160" s="4" t="str">
-        <x:v>1024x1024</x:v>
+        <x:v>1000x800</x:v>
       </x:c>
       <x:c r="N160" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O160" s="4" t="str">
         <x:v>&lt;div align="center"&lt;bFigure 47-4: Multimodal Instruction Synthesis Pipeline&lt;/b&lt;/div.</x:v>
@@ -11129,16 +11175,16 @@
         <x:v>Figure P01-1</x:v>
       </x:c>
       <x:c r="K164" s="4" t="str">
-        <x:v>docs/images/part14/p01_01_mini_c4_pipeline_overview.png</x:v>
+        <x:v>docs/images/part14/p01/p01_01_mini_c4_pipeline_overview.svg</x:v>
       </x:c>
       <x:c r="L164" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M164" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>900x355</x:v>
       </x:c>
       <x:c r="N164" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O164" s="4" t="str">
         <x:v>Mini-C4 Data Pipeline Overview.</x:v>
@@ -11193,16 +11239,16 @@
         <x:v>Figure P01-2</x:v>
       </x:c>
       <x:c r="K165" s="4" t="str">
-        <x:v>docs/images/part14/p01_02_warc_to_text.png</x:v>
+        <x:v>docs/images/part14/p01/p01_02_warc_to_text.svg</x:v>
       </x:c>
       <x:c r="L165" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M165" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N165" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O165" s="4" t="str">
         <x:v>Parsing Path from WARC to Body Text.</x:v>
@@ -11255,16 +11301,16 @@
         <x:v>Figure P01-3</x:v>
       </x:c>
       <x:c r="K166" s="4" t="str">
-        <x:v>docs/images/part14/p01_03_cleaning_rules.png</x:v>
+        <x:v>docs/images/part14/p01/p01_03_cleaning_rules.svg</x:v>
       </x:c>
       <x:c r="L166" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M166" s="4" t="str">
-        <x:v>1800x1344</x:v>
+        <x:v>900x672</x:v>
       </x:c>
       <x:c r="N166" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O166" s="4" t="str">
         <x:v>Heuristic Cleaning Rules Illustration.</x:v>
@@ -11317,16 +11363,16 @@
         <x:v>Figure P01-4</x:v>
       </x:c>
       <x:c r="K167" s="4" t="str">
-        <x:v>docs/images/part14/p01_04_dedup_minhash_lsh.png</x:v>
+        <x:v>docs/images/part14/p01/p01_04_dedup_minhash_lsh.svg</x:v>
       </x:c>
       <x:c r="L167" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M167" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N167" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O167" s="4" t="str">
         <x:v>MinHash + LSH Deduplication Approach.</x:v>
@@ -11379,16 +11425,16 @@
         <x:v>Figure P01-5</x:v>
       </x:c>
       <x:c r="K168" s="4" t="str">
-        <x:v>docs/images/part14/p01_05_language_split.png</x:v>
+        <x:v>docs/images/part14/p01/p01_05_language_split.svg</x:v>
       </x:c>
       <x:c r="L168" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M168" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N168" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O168" s="4" t="str">
         <x:v>Language Splitting and Branch Processing.</x:v>
@@ -11441,16 +11487,16 @@
         <x:v>Figure P01-6</x:v>
       </x:c>
       <x:c r="K169" s="4" t="str">
-        <x:v>docs/images/part14/p01_06_quality_filter.png</x:v>
+        <x:v>docs/images/part14/p01/p01_06_quality_filter.svg</x:v>
       </x:c>
       <x:c r="L169" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M169" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>960.12x540</x:v>
       </x:c>
       <x:c r="N169" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O169" s="4" t="str">
         <x:v>Quality Filtering Decision Illustration.</x:v>
@@ -11503,16 +11549,16 @@
         <x:v>Figure P01-7</x:v>
       </x:c>
       <x:c r="K170" s="4" t="str">
-        <x:v>docs/images/part14/p01_07_three_iterations.png</x:v>
+        <x:v>docs/images/part14/p01/p01_07_three_iterations.svg</x:v>
       </x:c>
       <x:c r="L170" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M170" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N170" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O170" s="4" t="str">
         <x:v>Three-Round Experimental Iteration Path.</x:v>
@@ -11565,7 +11611,7 @@
         <x:v>Figure P01-8</x:v>
       </x:c>
       <x:c r="K171" s="4" t="str">
-        <x:v>docs/images/part14/p01_08_funnel.png</x:v>
+        <x:v>docs/images/part14/p01/p01_08_funnel.svg</x:v>
       </x:c>
       <x:c r="L171" s="4" t="str">
         <x:v>yes</x:v>
@@ -11574,7 +11620,7 @@
         <x:v>1800x1005</x:v>
       </x:c>
       <x:c r="N171" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O171" s="4" t="str">
         <x:v>Data Retention Funnel. --- Figure P01-8: Data Retention Funnel The final retention funnel obtained by this project is as follows:.</x:v>
@@ -11627,16 +11673,16 @@
         <x:v>Figure P01-9</x:v>
       </x:c>
       <x:c r="K172" s="4" t="str">
-        <x:v>docs/images/part14/p01_09_cost_breakdown.png</x:v>
+        <x:v>docs/images/part14/p01/p01_09_cost_breakdown.svg</x:v>
       </x:c>
       <x:c r="L172" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M172" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>960.12x540</x:v>
       </x:c>
       <x:c r="N172" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O172" s="4" t="str">
         <x:v>Resource and Cost Breakdown.</x:v>
@@ -11689,16 +11735,16 @@
         <x:v>Figure P01-10</x:v>
       </x:c>
       <x:c r="K173" s="4" t="str">
-        <x:v>docs/images/part14/p01_10_validation_loop.png</x:v>
+        <x:v>docs/images/part14/p01/p01_10_validation_loop.svg</x:v>
       </x:c>
       <x:c r="L173" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M173" s="4" t="str">
-        <x:v>2048x2048</x:v>
+        <x:v>1024x1024</x:v>
       </x:c>
       <x:c r="N173" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O173" s="4" t="str">
         <x:v>Project Validation Loop. Figure P01-10: Project Validation Loop If a data engineering project has only output files and no inspection mechanism, it is actually difficult to say whether it is truly correct.</x:v>
@@ -11751,16 +11797,16 @@
         <x:v>Figure P01-11</x:v>
       </x:c>
       <x:c r="K174" s="4" t="str">
-        <x:v>docs/images/part14/p01_11_methodology_summary.png</x:v>
+        <x:v>docs/images/part14/p01/p01_11_methodology_summary.svg</x:v>
       </x:c>
       <x:c r="L174" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M174" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N174" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O174" s="4" t="str">
         <x:v>Mini-C4 Engineering Methodology Summary.</x:v>
@@ -11813,16 +11859,16 @@
         <x:v>Figure P02-1</x:v>
       </x:c>
       <x:c r="K175" s="4" t="str">
-        <x:v>docs/images/part14/p02_01_legal_sft_factory_overview.png</x:v>
+        <x:v>docs/images/part14/p02/p02_01_legal_sft_factory_overview.svg</x:v>
       </x:c>
       <x:c r="L175" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M175" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N175" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O175" s="4" t="str">
         <x:v>Legal-Domain SFT Data Factory Overview.</x:v>
@@ -11875,16 +11921,16 @@
         <x:v>Figure P02-2</x:v>
       </x:c>
       <x:c r="K176" s="4" t="str">
-        <x:v>docs/images/part14/p02_02_roles_and_responsibilities.png</x:v>
+        <x:v>docs/images/part14/p02/p02_02_roles_and_responsibilities.svg</x:v>
       </x:c>
       <x:c r="L176" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M176" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N176" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O176" s="4" t="str">
         <x:v>Legal SFT Data Factory Role Assignment Diagram.</x:v>
@@ -11937,16 +11983,16 @@
         <x:v>Figure P02-3</x:v>
       </x:c>
       <x:c r="K177" s="4" t="str">
-        <x:v>docs/images/part14/p02_03_pdf_cleaning_pipeline.png</x:v>
+        <x:v>docs/images/part14/p02/p02_03_pdf_cleaning_pipeline.svg</x:v>
       </x:c>
       <x:c r="L177" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M177" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N177" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O177" s="4" t="str">
         <x:v>Legal PDF Intelligent Cleaning Pipeline Diagram.</x:v>
@@ -12001,16 +12047,16 @@
         <x:v>Figure P02-4</x:v>
       </x:c>
       <x:c r="K178" s="4" t="str">
-        <x:v>docs/images/part14/p02_04_cleaning_examples.png</x:v>
+        <x:v>docs/images/part14/p02/p02_04_cleaning_examples.svg</x:v>
       </x:c>
       <x:c r="L178" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M178" s="4" t="str">
-        <x:v>1800x1344</x:v>
+        <x:v>900x672</x:v>
       </x:c>
       <x:c r="N178" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O178" s="4" t="str">
         <x:v>Examples of Embedded Page Number Removal and Chinese Word-Break Repair.</x:v>
@@ -12063,16 +12109,16 @@
         <x:v>Figure P02-5</x:v>
       </x:c>
       <x:c r="K179" s="4" t="str">
-        <x:v>docs/images/part14/p02_05_seed_schema.png</x:v>
+        <x:v>docs/images/part14/p02/p02_05_seed_schema.svg</x:v>
       </x:c>
       <x:c r="L179" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M179" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N179" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O179" s="4" t="str">
         <x:v>Legal Seed Sample Schema Diagram.</x:v>
@@ -12127,16 +12173,16 @@
         <x:v>Figure P02-6</x:v>
       </x:c>
       <x:c r="K180" s="4" t="str">
-        <x:v>docs/images/part14/p02_06_task_taxonomy.png</x:v>
+        <x:v>docs/images/part14/p02/p02_06_task_taxonomy.svg</x:v>
       </x:c>
       <x:c r="L180" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M180" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N180" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O180" s="4" t="str">
         <x:v>Legal Task Taxonomy Stratification Diagram.</x:v>
@@ -12189,16 +12235,16 @@
         <x:v>Figure P02-7</x:v>
       </x:c>
       <x:c r="K181" s="4" t="str">
-        <x:v>docs/images/part14/p02_07_task_vs_domain_distribution.png</x:v>
+        <x:v>docs/images/part14/p02/p02_07_task_vs_domain_distribution.svg</x:v>
       </x:c>
       <x:c r="L181" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M181" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N181" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O181" s="4" t="str">
         <x:v>Task Distribution vs. Legal Domain Coverage Comparison Chart.</x:v>
@@ -12253,16 +12299,16 @@
         <x:v>Figure P02-8</x:v>
       </x:c>
       <x:c r="K182" s="4" t="str">
-        <x:v>docs/images/part14/p02_08_weighted_task_sampling.png</x:v>
+        <x:v>docs/images/part14/p02/p02_08_weighted_task_sampling.svg</x:v>
       </x:c>
       <x:c r="L182" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M182" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N182" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O182" s="4" t="str">
         <x:v>Weighted Roulette Task Sampling Diagram.</x:v>
@@ -12315,16 +12361,16 @@
         <x:v>Figure P02-9</x:v>
       </x:c>
       <x:c r="K183" s="4" t="str">
-        <x:v>docs/images/part14/p02_09_cot_structure.png</x:v>
+        <x:v>docs/images/part14/p02/p02_09_cot_structure.svg</x:v>
       </x:c>
       <x:c r="L183" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M183" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N183" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O183" s="4" t="str">
         <x:v>CoT Structure Diagram for Case Analysis Tasks.</x:v>
@@ -12377,16 +12423,16 @@
         <x:v>Figure P02-10</x:v>
       </x:c>
       <x:c r="K184" s="4" t="str">
-        <x:v>docs/images/part14/p02_10_preference_and_review.png</x:v>
+        <x:v>docs/images/part14/p02/p02_10_preference_and_review.svg</x:v>
       </x:c>
       <x:c r="L184" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M184" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N184" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O184" s="4" t="str">
         <x:v>Relationship Between Preference Pairs and Review Records.</x:v>
@@ -12439,16 +12485,16 @@
         <x:v>Figure P02-11</x:v>
       </x:c>
       <x:c r="K185" s="4" t="str">
-        <x:v>docs/images/part14/p02_11_risk_refusal_flow.png</x:v>
+        <x:v>docs/images/part14/p02/p02_11_risk_refusal_flow.svg</x:v>
       </x:c>
       <x:c r="L185" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M185" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N185" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O185" s="4" t="str">
         <x:v>Legal Scenario Risk Refusal Routing Diagram.</x:v>
@@ -12501,16 +12547,16 @@
         <x:v>Figure P02-12</x:v>
       </x:c>
       <x:c r="K186" s="4" t="str">
-        <x:v>docs/images/part14/p02_12_qa_loop.png</x:v>
+        <x:v>docs/images/part14/p02/p02_12_qa_loop.svg</x:v>
       </x:c>
       <x:c r="L186" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M186" s="4" t="str">
-        <x:v>1800x982</x:v>
+        <x:v>900x491</x:v>
       </x:c>
       <x:c r="N186" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O186" s="4" t="str">
         <x:v>QA Review Closed-Loop Diagram.</x:v>
@@ -12563,16 +12609,16 @@
         <x:v>Figure P02-13</x:v>
       </x:c>
       <x:c r="K187" s="4" t="str">
-        <x:v>docs/images/part14/p02_13_qa_decision_table.png</x:v>
+        <x:v>docs/images/part14/p02/p02_13_qa_decision_table.svg</x:v>
       </x:c>
       <x:c r="L187" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M187" s="4" t="str">
-        <x:v>1800x982</x:v>
+        <x:v>900x491</x:v>
       </x:c>
       <x:c r="N187" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O187" s="4" t="str">
         <x:v>QA Accept / Revise / Reject Decision Table.</x:v>
@@ -12625,16 +12671,16 @@
         <x:v>Figure P02-14</x:v>
       </x:c>
       <x:c r="K188" s="4" t="str">
-        <x:v>docs/images/part14/p02_14_human_in_the_loop.png</x:v>
+        <x:v>docs/images/part14/p02/p02_14_human_in_the_loop.svg</x:v>
       </x:c>
       <x:c r="L188" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M188" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N188" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O188" s="4" t="str">
         <x:v>Human-in-the-Loop and Vendor Tiered Review Diagram.</x:v>
@@ -12687,16 +12733,16 @@
         <x:v>Figure P02-15</x:v>
       </x:c>
       <x:c r="K189" s="4" t="str">
-        <x:v>docs/images/part14/p02_15_training_artifacts.png</x:v>
+        <x:v>docs/images/part14/p02/p02_15_training_artifacts.svg</x:v>
       </x:c>
       <x:c r="L189" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M189" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N189" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O189" s="4" t="str">
         <x:v>Training Packaging and Delivery Interface Diagram.</x:v>
@@ -12749,16 +12795,16 @@
         <x:v>Figure P02-16</x:v>
       </x:c>
       <x:c r="K190" s="4" t="str">
-        <x:v>docs/images/part14/p02_16_metrics_dashboard.png</x:v>
+        <x:v>docs/images/part14/p02/p02_16_metrics_dashboard.svg</x:v>
       </x:c>
       <x:c r="L190" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M190" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N190" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O190" s="4" t="str">
         <x:v>P02 Core Metrics Dashboard.</x:v>
@@ -12811,16 +12857,16 @@
         <x:v>Figure P02-17</x:v>
       </x:c>
       <x:c r="K191" s="4" t="str">
-        <x:v>docs/images/part14/p02_17_eval_sampling_protocol.png</x:v>
+        <x:v>docs/images/part14/p02/p02_17_eval_sampling_protocol.svg</x:v>
       </x:c>
       <x:c r="L191" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M191" s="4" t="str">
-        <x:v>1800x982</x:v>
+        <x:v>1380x752</x:v>
       </x:c>
       <x:c r="N191" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O191" s="4" t="str">
         <x:v>50-Sample Validation Protocol Diagram.</x:v>
@@ -12873,16 +12919,16 @@
         <x:v>Figure P02-18</x:v>
       </x:c>
       <x:c r="K192" s="4" t="str">
-        <x:v>docs/images/part14/p02_18_version_timeline.png</x:v>
+        <x:v>docs/images/part14/p02/p02_18_version_timeline.svg</x:v>
       </x:c>
       <x:c r="L192" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M192" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>1377x768</x:v>
       </x:c>
       <x:c r="N192" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O192" s="4" t="str">
         <x:v>P02 Version Evolution Roadmap.</x:v>
@@ -12935,16 +12981,16 @@
         <x:v>Figure P02-19</x:v>
       </x:c>
       <x:c r="K193" s="4" t="str">
-        <x:v>docs/images/part14/p02_19_validation_chain.png</x:v>
+        <x:v>docs/images/part14/p02/p02_19_validation_chain.svg</x:v>
       </x:c>
       <x:c r="L193" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M193" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N193" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O193" s="4" t="str">
         <x:v>Code–Artifact–Report Consistency Validation Diagram.</x:v>
@@ -12997,16 +13043,16 @@
         <x:v>Figure P02-20</x:v>
       </x:c>
       <x:c r="K194" s="4" t="str">
-        <x:v>docs/images/part14/p02_20_cross_domain_transfer.png</x:v>
+        <x:v>docs/images/part14/p02/p02_20_cross_domain_transfer.svg</x:v>
       </x:c>
       <x:c r="L194" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M194" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>1377x768</x:v>
       </x:c>
       <x:c r="N194" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O194" s="4" t="str">
         <x:v>Cross-Industry Transfer Methodology Chain Diagram.</x:v>
@@ -18351,16 +18397,16 @@
         <x:v>Mini-DeepSeek Data Pipeline</x:v>
       </x:c>
       <x:c r="K280" s="4" t="str">
-        <x:v>docs/images/part14/p11_mini_deepseek_arch_en.png</x:v>
+        <x:v>docs/images/part14/p11_mini_deepseek_arch_en.svg</x:v>
       </x:c>
       <x:c r="L280" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M280" s="4" t="str">
-        <x:v>1024x1024</x:v>
+        <x:v>950x500</x:v>
       </x:c>
       <x:c r="N280" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O280" s="4" t="str">
         <x:v>Mini-DeepSeek Multi-Source Pre-Training Data Pipeline Architecture.</x:v>
@@ -18477,16 +18523,16 @@
         <x:v>Multimodal Instruction Factory</x:v>
       </x:c>
       <x:c r="K282" s="4" t="str">
-        <x:v>docs/images/part14/p13_mm_instruction_factory_arch_en.png</x:v>
+        <x:v>docs/images/part14/p13_mm_instruction_factory_arch_en.svg</x:v>
       </x:c>
       <x:c r="L282" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M282" s="4" t="str">
-        <x:v>1024x1024</x:v>
+        <x:v>1000x730</x:v>
       </x:c>
       <x:c r="N282" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O282" s="4" t="str">
         <x:v>Qwen-VL-style multimodal instruction synthesis pipeline.</x:v>

--- a/publishing/accessibility/springer_alt_text_inventory.xlsx
+++ b/publishing/accessibility/springer_alt_text_inventory.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R1fcb29f994d34ff4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alt Text" sheetId="2" r:id="R858b4d3cac164c28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guidance" sheetId="3" r:id="R5ef60f777a8e461f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R50897c53eebd4ad1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alt Text" sheetId="2" r:id="R8e0e361ff63d43a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guidance" sheetId="3" r:id="Rc2b21ba1b0184d40"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -323,7 +323,7 @@
         <x:v>Generated at UTC</x:v>
       </x:c>
       <x:c r="B2" s="4" t="n">
-        <x:v>46195.457691574076</x:v>
+        <x:v>46195.60789384259</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -339,7 +339,7 @@
         <x:v>Total image rows</x:v>
       </x:c>
       <x:c r="B4" s="4" t="n">
-        <x:v>288</x:v>
+        <x:v>291</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -711,7 +711,7 @@
         <x:v>Ch41</x:v>
       </x:c>
       <x:c r="B51" s="4" t="n">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -8305,7 +8305,7 @@
         <x:v>Figure 38-1 FineWeb MinHash deduplication and PII-processing flow</x:v>
       </x:c>
       <x:c r="K118" s="4" t="str">
-        <x:v>docs/images/part12/ch41_01_fineweb_minhash_pii_flow_en.svg</x:v>
+        <x:v>docs/images/part12/ch38_01_fineweb_minhash_pii_flow_en.svg</x:v>
       </x:c>
       <x:c r="L118" s="4" t="str">
         <x:v>yes</x:v>
@@ -8367,7 +8367,7 @@
         <x:v>Figure 38-2 FineWeb data-processing-choice ablation loop</x:v>
       </x:c>
       <x:c r="K119" s="4" t="str">
-        <x:v>docs/images/part12/ch41_02_fineweb_ablation_loop_en.svg</x:v>
+        <x:v>docs/images/part12/ch38_02_fineweb_ablation_loop_en.svg</x:v>
       </x:c>
       <x:c r="L119" s="4" t="str">
         <x:v>yes</x:v>
@@ -8429,7 +8429,7 @@
         <x:v>Figure 38-3 Dolma transparent-corpus evidence chain</x:v>
       </x:c>
       <x:c r="K120" s="4" t="str">
-        <x:v>docs/images/part12/ch42_01_dolma_evidence_chain_en.svg</x:v>
+        <x:v>docs/images/part12/ch38_03_dolma_evidence_chain_en.svg</x:v>
       </x:c>
       <x:c r="L120" s="4" t="str">
         <x:v>yes</x:v>
@@ -8491,7 +8491,7 @@
         <x:v>Figure 38-4 Dolma source mix and training-diagnosis loop</x:v>
       </x:c>
       <x:c r="K121" s="4" t="str">
-        <x:v>docs/images/part12/ch42_02_dolma_source_mix_diagnosis_en.svg</x:v>
+        <x:v>docs/images/part12/ch38_04_dolma_source_mix_diagnosis_en.svg</x:v>
       </x:c>
       <x:c r="L121" s="4" t="str">
         <x:v>yes</x:v>
@@ -8553,7 +8553,7 @@
         <x:v>Figure 39-1 Multi-channel schema for LAION-5B image-text candidate records</x:v>
       </x:c>
       <x:c r="K122" s="4" t="str">
-        <x:v>docs/images/part12/ch43_01_laion_multichannel_schema_en.svg</x:v>
+        <x:v>docs/images/part12/ch39_01_laion_multichannel_schema_en.svg</x:v>
       </x:c>
       <x:c r="L122" s="4" t="str">
         <x:v>yes</x:v>
@@ -8617,7 +8617,7 @@
         <x:v>Figure 39-2 Image-text candidate-pool quality evaluation and closed-loop repair</x:v>
       </x:c>
       <x:c r="K123" s="4" t="str">
-        <x:v>docs/images/part12/ch43_02_laion_quality_datacomp_loop_en.svg</x:v>
+        <x:v>docs/images/part12/ch39_02_laion_quality_datacomp_loop_en.svg</x:v>
       </x:c>
       <x:c r="L123" s="4" t="str">
         <x:v>yes</x:v>
@@ -8679,7 +8679,7 @@
         <x:v>Figure 40-1: Schema-to-JSON mapping</x:v>
       </x:c>
       <x:c r="K124" s="4" t="str">
-        <x:v>docs/images/part12/ch38_01_schema_decomposition_en.png</x:v>
+        <x:v>docs/images/part12/ch40_01_schema_decomposition_en.png</x:v>
       </x:c>
       <x:c r="L124" s="4" t="str">
         <x:v>yes</x:v>
@@ -8743,7 +8743,7 @@
         <x:v>Figure 40-2: StructBill-CN construction pipeline</x:v>
       </x:c>
       <x:c r="K125" s="4" t="str">
-        <x:v>docs/images/part12/ch38_02_dataset_construction_pipeline_en.png</x:v>
+        <x:v>docs/images/part12/ch40_02_dataset_construction_pipeline_en.png</x:v>
       </x:c>
       <x:c r="L125" s="4" t="str">
         <x:v>yes</x:v>
@@ -8807,7 +8807,7 @@
         <x:v>Figure 40-3: Logic-consistency validation</x:v>
       </x:c>
       <x:c r="K126" s="4" t="str">
-        <x:v>docs/images/part12/ch38_03_structural_consistency_validation_en.png</x:v>
+        <x:v>docs/images/part12/ch40_03_structural_consistency_validation_en.png</x:v>
       </x:c>
       <x:c r="L126" s="4" t="str">
         <x:v>yes</x:v>
@@ -8860,7 +8860,7 @@
         <x:v>505</x:v>
       </x:c>
       <x:c r="H127" s="4" t="str">
-        <x:v>38-4</x:v>
+        <x:v>40-4</x:v>
       </x:c>
       <x:c r="I127" s="4" t="str">
         <x:v>From a data engineering perspective, the sample schema of STB includes at least the following fields and validation rules</x:v>
@@ -8869,13 +8869,13 @@
         <x:v>Figure 40-4: Three synchronized supervision signals in a table sample</x:v>
       </x:c>
       <x:c r="K127" s="4" t="str">
-        <x:v>docs/images/part12/ch38_04_supervision_schema.png</x:v>
+        <x:v>docs/images/part12/ch40_04_supervision_schema_en.png</x:v>
       </x:c>
       <x:c r="L127" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M127" s="4" t="str">
-        <x:v>1653x952</x:v>
+        <x:v>1653x951</x:v>
       </x:c>
       <x:c r="N127" s="4" t="str">
         <x:v>png</x:v>
@@ -8933,7 +8933,7 @@
         <x:v>Figure 40-5: Four-stage SparseTable-Bench construction pipeline</x:v>
       </x:c>
       <x:c r="K128" s="4" t="str">
-        <x:v>docs/images/part12/ch38_05_stb_pipeline.png</x:v>
+        <x:v>docs/images/part12/ch40_05_stb_pipeline_en.png</x:v>
       </x:c>
       <x:c r="L128" s="4" t="str">
         <x:v>yes</x:v>
@@ -8988,7 +8988,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="H129" s="4" t="str">
-        <x:v>38-6</x:v>
+        <x:v>40-6</x:v>
       </x:c>
       <x:c r="I129" s="4" t="str">
         <x:v>The occlusion strategy of STB-Mask-Stress is column-aware. The workflow can be summarized as follows. 1. Parse the original table structure to obtain the row-column index, header/body membership, and bounding box of each cell. 2. Randomly select a subset of columns as occlusion candidates</x:v>
@@ -8997,7 +8997,7 @@
         <x:v>Figure 40-6: STB-Mask-Stress occlusion generation and evaluation workflow</x:v>
       </x:c>
       <x:c r="K129" s="4" t="str">
-        <x:v>docs/images/part12/ch38_06_mask_stress_flow.png</x:v>
+        <x:v>docs/images/part12/ch40_06_mask_stress_flow_en.png</x:v>
       </x:c>
       <x:c r="L129" s="4" t="str">
         <x:v>yes</x:v>
@@ -9061,7 +9061,7 @@
         <x:v>Figure 41-1: Domain distribution in the multi-chart infographic reasoning dataset</x:v>
       </x:c>
       <x:c r="K130" s="4" t="str">
-        <x:v>docs/images/part12/ch39_01_domain_distribution_en.png</x:v>
+        <x:v>docs/images/part12/ch41_01_domain_distribution_en.png</x:v>
       </x:c>
       <x:c r="L130" s="4" t="str">
         <x:v>yes</x:v>
@@ -9125,7 +9125,7 @@
         <x:v>Figure 41-2: Chart type distribution</x:v>
       </x:c>
       <x:c r="K131" s="4" t="str">
-        <x:v>docs/images/part12/ch39_02_chart_type_distribution_en.png</x:v>
+        <x:v>docs/images/part12/ch41_02_chart_type_distribution_en.png</x:v>
       </x:c>
       <x:c r="L131" s="4" t="str">
         <x:v>yes</x:v>
@@ -9189,7 +9189,7 @@
         <x:v>Figure 41-3: Question type distribution</x:v>
       </x:c>
       <x:c r="K132" s="4" t="str">
-        <x:v>docs/images/part12/ch39_03_question_type_distribution_en.png</x:v>
+        <x:v>docs/images/part12/ch41_03_question_type_distribution_en.png</x:v>
       </x:c>
       <x:c r="L132" s="4" t="str">
         <x:v>yes</x:v>
@@ -9241,31 +9241,31 @@
         <x:v>docs/en/part12/ch41_visual_reasoning_tool_data_engineering.md</x:v>
       </x:c>
       <x:c r="G133" s="4" t="n">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H133" s="4" t="str">
         <x:v>41-4</x:v>
       </x:c>
       <x:c r="I133" s="4" t="str">
-        <x:v>Figure 41-4. Example of a multi-chart infographic sample from the dataset (Shark Attacks), consisting of four distinct subcharts covering three categories of statistics: historical shark-attack county ranking in the United States, state-level shark attacks in the last ten years, and average annual accidental deaths in the United States</x:v>
+        <x:v>Shark-attack infographic subfigure 1 showing historical U.S. county rankings</x:v>
       </x:c>
       <x:c r="J133" s="4" t="str">
-        <x:v>Figure 41-4: Shark-attack compound infographic example</x:v>
+        <x:v>Shark-attack infographic subfigure 1 showing historical U.S. county rankings</x:v>
       </x:c>
       <x:c r="K133" s="4" t="str">
-        <x:v>docs/images/part12/ch39_04_shark_attack_infographic.jpg</x:v>
+        <x:v>docs/images/part12/ch41_04_shark_attack_infographic_1.jpg</x:v>
       </x:c>
       <x:c r="L133" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M133" s="4" t="str">
-        <x:v>800x4073</x:v>
+        <x:v>800x982</x:v>
       </x:c>
       <x:c r="N133" s="4" t="str">
         <x:v>jpg</x:v>
       </x:c>
       <x:c r="O133" s="4" t="str">
-        <x:v>. Example of a multi-chart infographic sample from the dataset (Shark Attacks), consisting of four distinct subcharts covering three categories of statistics: historical shark-attack county ranking in the United States, state-level shark attacks in the last ten years, and average annual accidental deaths in the United States.</x:v>
+        <x:v>Shark-attack infographic subfigure 1 showing historical U.S. county rankings.</x:v>
       </x:c>
       <x:c r="P133" s="4" t="str"/>
       <x:c r="Q133" s="4" t="str">
@@ -9277,10 +9277,10 @@
       <x:c r="S133" s="4" t="str"/>
       <x:c r="T133" s="4" t="str"/>
       <x:c r="U133" s="4" t="str">
-        <x:v>Figure 41-4：多图表信息图样本（鲨鱼袭击）。该信息图包含四个独立子图，内容涉及美国历史累计鲨鱼袭击县域排行榜、美国近 10 年各州鲨鱼袭击汇总统计、全美年均意外死亡人数统计</x:v>
+        <x:v>图41-4子图1：鲨鱼袭击信息图中的美国历史县域排行部分</x:v>
       </x:c>
       <x:c r="V133" s="4" t="str">
-        <x:v>图41-4：多图表信息图样本（鲨鱼袭击）</x:v>
+        <x:v>图41-4子图1：鲨鱼袭击信息图中的美国历史县域排行部分</x:v>
       </x:c>
     </x:row>
     <x:row r="134">
@@ -9303,35 +9303,33 @@
         <x:v>docs/en/part12/ch41_visual_reasoning_tool_data_engineering.md</x:v>
       </x:c>
       <x:c r="G134" s="4" t="n">
-        <x:v>150</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="H134" s="4" t="str">
-        <x:v>41-5</x:v>
+        <x:v>41-4</x:v>
       </x:c>
       <x:c r="I134" s="4" t="str">
-        <x:v>Figure 41-5. Overview of the four-stage data construction pipeline for the Multi-Chart Infographic Reasoning Dataset: collecting and filtering real compound infographics, manually partitioning subchart regions, designing layered question chains, and cross-checking answers</x:v>
+        <x:v>Shark-attack infographic subfigure 2 showing state-level attacks in the last ten years</x:v>
       </x:c>
       <x:c r="J134" s="4" t="str">
-        <x:v>Figure 41-5: Multi-chart infographic dataset construction pipeline</x:v>
+        <x:v>Shark-attack infographic subfigure 2 showing state-level attacks in the last ten years</x:v>
       </x:c>
       <x:c r="K134" s="4" t="str">
-        <x:v>docs/images/part12/ch39_05_multichart_dataset_pipeline_en.png</x:v>
+        <x:v>docs/images/part12/ch41_04_shark_attack_infographic_2.jpg</x:v>
       </x:c>
       <x:c r="L134" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M134" s="4" t="str">
-        <x:v>2158x1648</x:v>
+        <x:v>800x719</x:v>
       </x:c>
       <x:c r="N134" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>jpg</x:v>
       </x:c>
       <x:c r="O134" s="4" t="str">
-        <x:v>. Overview of the four-stage data construction pipeline for the Multi-Chart Infographic Reasoning Dataset: collecting and filtering real compound infographics, manually partitioning subchart regions, designing layered question chains, and cross-checking answers.</x:v>
-      </x:c>
-      <x:c r="P134" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Chapter 41: Visual Reasoning Data Engineering: Chart Evidence, Medical Images, and Tool-Call Trajectories; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>Shark-attack infographic subfigure 2 showing state-level attacks in the last ten years.</x:v>
+      </x:c>
+      <x:c r="P134" s="4" t="str"/>
       <x:c r="Q134" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -9341,10 +9339,10 @@
       <x:c r="S134" s="4" t="str"/>
       <x:c r="T134" s="4" t="str"/>
       <x:c r="U134" s="4" t="str">
-        <x:v>Figure 41-5：多图标信息图推理数据集四阶段构建流水线图。该流水线包括原始信息图爬取筛选、多子图区域人工划分、链式问题分层设计、答案人工核验标注四大工序</x:v>
+        <x:v>图41-4子图2：鲨鱼袭击信息图中的近十年州级袭击统计部分</x:v>
       </x:c>
       <x:c r="V134" s="4" t="str">
-        <x:v>图41-5：多图标信息图推理数据集四阶段构建流水线图</x:v>
+        <x:v>图41-4子图2：鲨鱼袭击信息图中的近十年州级袭击统计部分</x:v>
       </x:c>
     </x:row>
     <x:row r="135">
@@ -9367,31 +9365,31 @@
         <x:v>docs/en/part12/ch41_visual_reasoning_tool_data_engineering.md</x:v>
       </x:c>
       <x:c r="G135" s="4" t="n">
-        <x:v>442</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="H135" s="4" t="str">
-        <x:v>41-6</x:v>
+        <x:v>41-4</x:v>
       </x:c>
       <x:c r="I135" s="4" t="str">
-        <x:v>Figure 41-6: Conceptual construction flow for MedImage-ToolVQA. The key point is not script order, but how the evidence chain and behavior chain are preserved across stages</x:v>
+        <x:v>Shark-attack infographic subfigure 3 showing fatal attack annotation and related context</x:v>
       </x:c>
       <x:c r="J135" s="4" t="str">
-        <x:v>Figure 41-6: MedImage-ToolVQA conceptual construction flow</x:v>
+        <x:v>Shark-attack infographic subfigure 3 showing fatal attack annotation and related context</x:v>
       </x:c>
       <x:c r="K135" s="4" t="str">
-        <x:v>docs/images/part12/ch41_02_medimage_tool_vqa_pipeline_en.svg</x:v>
+        <x:v>docs/images/part12/ch41_04_shark_attack_infographic_3.jpg</x:v>
       </x:c>
       <x:c r="L135" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M135" s="4" t="str">
-        <x:v>2200x1050</x:v>
+        <x:v>800x1276</x:v>
       </x:c>
       <x:c r="N135" s="4" t="str">
-        <x:v>svg</x:v>
+        <x:v>jpg</x:v>
       </x:c>
       <x:c r="O135" s="4" t="str">
-        <x:v>Conceptual construction flow for MedImage-ToolVQA. The key point is not script order, but how the evidence chain and behavior chain are preserved across stages.</x:v>
+        <x:v>Shark-attack infographic subfigure 3 showing fatal attack annotation and related context.</x:v>
       </x:c>
       <x:c r="P135" s="4" t="str"/>
       <x:c r="Q135" s="4" t="str">
@@ -9403,10 +9401,10 @@
       <x:c r="S135" s="4" t="str"/>
       <x:c r="T135" s="4" t="str"/>
       <x:c r="U135" s="4" t="str">
-        <x:v>图41-6：MedImage-ToolVQA 数据构建概念流程。流程的重点不是脚本顺序，而是证据链和行为链如何在各阶段被保留下来</x:v>
+        <x:v>图41-4子图3：鲨鱼袭击信息图中的致命袭击备注与上下文部分</x:v>
       </x:c>
       <x:c r="V135" s="4" t="str">
-        <x:v>图41-6：MedImage-ToolVQA 数据构建概念流程</x:v>
+        <x:v>图41-4子图3：鲨鱼袭击信息图中的致命袭击备注与上下文部分</x:v>
       </x:c>
     </x:row>
     <x:row r="136">
@@ -9429,31 +9427,31 @@
         <x:v>docs/en/part12/ch41_visual_reasoning_tool_data_engineering.md</x:v>
       </x:c>
       <x:c r="G136" s="4" t="n">
-        <x:v>484</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="H136" s="4" t="str">
-        <x:v>41-7</x:v>
+        <x:v>41-4</x:v>
       </x:c>
       <x:c r="I136" s="4" t="str">
-        <x:v>Figure 41-7: Multi-turn structure of a tool-call trajectory. Tool observations return as new image inputs; the model must continue reasoning from the observation image rather than merely produce a formally correct call</x:v>
+        <x:v>&lt;/div Figure 41-4. Example of a multi-chart infographic sample from the dataset (Shark Attacks), consisting of four distinct subcharts covering three categories of statistics: historical shark-attack county ranking in the United States, state-level shark attacks in the last ten years, and average annual accidental deaths in the United States. The original figure is vertically elongated and hard to read as a whole; it is thus divided into horizontally aligned subfigures</x:v>
       </x:c>
       <x:c r="J136" s="4" t="str">
-        <x:v>Figure 41-7: Multi-turn structure of tool-call trajectories</x:v>
+        <x:v>Shark-attack infographic subfigure 4 comparing average annual accidental deaths</x:v>
       </x:c>
       <x:c r="K136" s="4" t="str">
-        <x:v>docs/images/part12/ch41_03_tool_trajectory_structure_en.svg</x:v>
+        <x:v>docs/images/part12/ch41_04_shark_attack_infographic_4.jpg</x:v>
       </x:c>
       <x:c r="L136" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M136" s="4" t="str">
-        <x:v>1900x1120</x:v>
+        <x:v>800x1067</x:v>
       </x:c>
       <x:c r="N136" s="4" t="str">
-        <x:v>svg</x:v>
+        <x:v>jpg</x:v>
       </x:c>
       <x:c r="O136" s="4" t="str">
-        <x:v>Multi-turn structure of a tool-call trajectory. Tool observations return as new image inputs; the model must continue reasoning from the observation image rather than merely produce a formally correct call.</x:v>
+        <x:v>&lt;/div Figure 41-4. Example of a multi-chart infographic sample from the dataset (Shark Attacks), consisting of four distinct subcharts covering three categories of statistics: historical shark-attack county ranking in the United States, state-level shark attacks in the last ten years, and average annual accidental deaths in the United States. The original figure is vertically elongated and hard to read as a whole; it is thus divided into horizontally aligned subfigures.</x:v>
       </x:c>
       <x:c r="P136" s="4" t="str"/>
       <x:c r="Q136" s="4" t="str">
@@ -9465,10 +9463,10 @@
       <x:c r="S136" s="4" t="str"/>
       <x:c r="T136" s="4" t="str"/>
       <x:c r="U136" s="4" t="str">
-        <x:v>图41-7：工具调用多轮轨迹结构。工具观察以新的图像输入形式返回，模型必须基于观察图继续推理，而非仅生成一个形式正确的调用</x:v>
+        <x:v>&lt;/div 图 41-4：多图表信息图样本（鲨鱼袭击）。该信息图包含四个独立子图，内容涉及美国历史累计鲨鱼袭击县域排行榜、美国近 10 年各州鲨鱼袭击汇总统计、全美年均意外死亡人数统计。原图纵向幅面远大于横向幅面，直接呈现可读性不佳，故拆解为多张子图横向排布展示</x:v>
       </x:c>
       <x:c r="V136" s="4" t="str">
-        <x:v>图41-7：工具调用多轮轨迹结构</x:v>
+        <x:v>图41-4子图4：鲨鱼袭击信息图中的年均意外死亡对比部分</x:v>
       </x:c>
     </x:row>
     <x:row r="137">
@@ -9491,33 +9489,35 @@
         <x:v>docs/en/part12/ch41_visual_reasoning_tool_data_engineering.md</x:v>
       </x:c>
       <x:c r="G137" s="4" t="n">
-        <x:v>561</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="H137" s="4" t="str">
-        <x:v>41-8</x:v>
+        <x:v>41-5</x:v>
       </x:c>
       <x:c r="I137" s="4" t="str">
-        <x:v>Figure 41-8: Bbox is a structured field and should be recoverable as reviewable visual evidence</x:v>
+        <x:v>Figure 41-5. Overview of the four-stage data construction pipeline for the Multi-Chart Infographic Reasoning Dataset: collecting and filtering real compound infographics, manually partitioning subchart regions, designing layered question chains, and cross-checking answers</x:v>
       </x:c>
       <x:c r="J137" s="4" t="str">
-        <x:v>Figure 41-8: Real image and bbox evidence in the SFT schema</x:v>
+        <x:v>Figure 41-5: Multi-chart infographic dataset construction pipeline</x:v>
       </x:c>
       <x:c r="K137" s="4" t="str">
-        <x:v>docs/images/part12/ch41_05_sft_schema_real_bbox_example_en.svg</x:v>
+        <x:v>docs/images/part12/ch41_05_multichart_dataset_pipeline_en.png</x:v>
       </x:c>
       <x:c r="L137" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M137" s="4" t="str">
-        <x:v>2100x980</x:v>
+        <x:v>2158x1648</x:v>
       </x:c>
       <x:c r="N137" s="4" t="str">
-        <x:v>svg</x:v>
+        <x:v>png</x:v>
       </x:c>
       <x:c r="O137" s="4" t="str">
-        <x:v>Bbox is a structured field and should be recoverable as reviewable visual evidence.</x:v>
-      </x:c>
-      <x:c r="P137" s="4" t="str"/>
+        <x:v>. Overview of the four-stage data construction pipeline for the Multi-Chart Infographic Reasoning Dataset: collecting and filtering real compound infographics, manually partitioning subchart regions, designing layered question chains, and cross-checking answers.</x:v>
+      </x:c>
+      <x:c r="P137" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Chapter 41: Visual Reasoning Data Engineering: Chart Evidence, Medical Images, and Tool-Call Trajectories; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q137" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -9527,10 +9527,10 @@
       <x:c r="S137" s="4" t="str"/>
       <x:c r="T137" s="4" t="str"/>
       <x:c r="U137" s="4" t="str">
-        <x:v>图41-8：SFT schema 中的真实图像与 bbox 证据。bbox 是训练记录中的结构化字段，同时也应能被还原为可复查的可视化证据</x:v>
+        <x:v>Figure 41-5：多图标信息图推理数据集四阶段构建流水线图。该流水线包括原始信息图爬取筛选、多子图区域人工划分、链式问题分层设计、答案人工核验标注四大工序</x:v>
       </x:c>
       <x:c r="V137" s="4" t="str">
-        <x:v>图41-8：SFT schema 中的真实图像与 bbox 证据</x:v>
+        <x:v>图41-5：多图标信息图推理数据集四阶段构建流水线图</x:v>
       </x:c>
     </x:row>
     <x:row r="138">
@@ -9553,31 +9553,31 @@
         <x:v>docs/en/part12/ch41_visual_reasoning_tool_data_engineering.md</x:v>
       </x:c>
       <x:c r="G138" s="4" t="n">
-        <x:v>696</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="H138" s="4" t="str">
-        <x:v>41-9</x:v>
+        <x:v>41-6</x:v>
       </x:c>
       <x:c r="I138" s="4" t="str">
-        <x:v>Figure 41-9: Quality-control and human-review gates. Medical image tool-use data needs to check answer, evidence, and behavior together; automated validation and human review should complement each other</x:v>
+        <x:v>Figure 41-6: Conceptual construction flow for MedImage-ToolVQA. The key point is not script order, but how the evidence chain and behavior chain are preserved across stages</x:v>
       </x:c>
       <x:c r="J138" s="4" t="str">
-        <x:v>Figure 41-9: Quality-control and human-review gates</x:v>
+        <x:v>Figure 41-6: MedImage-ToolVQA conceptual construction flow</x:v>
       </x:c>
       <x:c r="K138" s="4" t="str">
-        <x:v>docs/images/part12/ch41_04_quality_review_gate_en.svg</x:v>
+        <x:v>docs/images/part12/ch41_06_medimage_tool_vqa_pipeline_en.svg</x:v>
       </x:c>
       <x:c r="L138" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M138" s="4" t="str">
-        <x:v>2000x1120</x:v>
+        <x:v>2200x1050</x:v>
       </x:c>
       <x:c r="N138" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O138" s="4" t="str">
-        <x:v>Quality-control and human-review gates. Medical image tool-use data needs to check answer, evidence, and behavior together; automated validation and human review should complement each other.</x:v>
+        <x:v>Conceptual construction flow for MedImage-ToolVQA. The key point is not script order, but how the evidence chain and behavior chain are preserved across stages.</x:v>
       </x:c>
       <x:c r="P138" s="4" t="str"/>
       <x:c r="Q138" s="4" t="str">
@@ -9589,10 +9589,10 @@
       <x:c r="S138" s="4" t="str"/>
       <x:c r="T138" s="4" t="str"/>
       <x:c r="U138" s="4" t="str">
-        <x:v>图41-9：质量控制与人工复核门禁。医学图像工具调用数据需要同时检查答案、证据和行为，自动校验与人工复核应形成互补</x:v>
+        <x:v>图41-6：MedImage-ToolVQA 数据构建概念流程。流程的重点不是脚本顺序，而是证据链和行为链如何在各阶段被保留下来</x:v>
       </x:c>
       <x:c r="V138" s="4" t="str">
-        <x:v>图41-9：质量控制与人工复核门禁</x:v>
+        <x:v>图41-6：MedImage-ToolVQA 数据构建概念流程</x:v>
       </x:c>
     </x:row>
     <x:row r="139">
@@ -9606,44 +9606,42 @@
         <x:v>Part 12: Specialized Datasets and Multimodal Data Engineering Practice</x:v>
       </x:c>
       <x:c r="D139" s="4" t="str">
-        <x:v>Ch42</x:v>
+        <x:v>Ch41</x:v>
       </x:c>
       <x:c r="E139" s="4" t="str">
-        <x:v>Chapter 42: Speech and Audio Data Engineering: Interaction Control, Style Labels, and Safety Boundaries</x:v>
+        <x:v>Chapter 41: Visual Reasoning Data Engineering: Chart Evidence, Medical Images, and Tool-Call Trajectories</x:v>
       </x:c>
       <x:c r="F139" s="4" t="str">
-        <x:v>docs/en/part12/ch42_speech_audio_interaction_data_engineering.md</x:v>
+        <x:v>docs/en/part12/ch41_visual_reasoning_tool_data_engineering.md</x:v>
       </x:c>
       <x:c r="G139" s="4" t="n">
-        <x:v>70</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="H139" s="4" t="str">
-        <x:v>42-1</x:v>
+        <x:v>41-7</x:v>
       </x:c>
       <x:c r="I139" s="4" t="str">
-        <x:v>Figure 42-1: Dual-channel schema for semantic response and style control. The semantic channel answers "what to say," the style channel answers "with which voice and emotion to say it," and the acoustic supervision channel binds both to audio files, speech tokens, and sampling configuration</x:v>
+        <x:v>Figure 41-7: Multi-turn structure of a tool-call trajectory. Tool observations return as new image inputs; the model must continue reasoning from the observation image rather than merely produce a formally correct call</x:v>
       </x:c>
       <x:c r="J139" s="4" t="str">
-        <x:v>Figure 42-1: Dual-channel schema for semantic response and style control</x:v>
+        <x:v>Figure 41-7: Multi-turn structure of tool-call trajectories</x:v>
       </x:c>
       <x:c r="K139" s="4" t="str">
-        <x:v>docs/images/part12/ch42_fig02_dual_channel_schema.svg</x:v>
+        <x:v>docs/images/part12/ch41_07_tool_trajectory_structure_en.svg</x:v>
       </x:c>
       <x:c r="L139" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M139" s="4" t="str">
-        <x:v>1280x560</x:v>
+        <x:v>1900x1120</x:v>
       </x:c>
       <x:c r="N139" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O139" s="4" t="str">
-        <x:v>Dual-channel schema for semantic response and style control. The semantic channel answers "what to say," the style channel answers "with which voice and emotion to say it," and the acoustic supervision channel binds both to audio files, speech tokens, and sampling configuration.</x:v>
-      </x:c>
-      <x:c r="P139" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Chapter 42: Speech and Audio Data Engineering: Interaction Control, Style Labels, and Safety Boundaries; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>Multi-turn structure of a tool-call trajectory. Tool observations return as new image inputs; the model must continue reasoning from the observation image rather than merely produce a formally correct call.</x:v>
+      </x:c>
+      <x:c r="P139" s="4" t="str"/>
       <x:c r="Q139" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -9653,10 +9651,10 @@
       <x:c r="S139" s="4" t="str"/>
       <x:c r="T139" s="4" t="str"/>
       <x:c r="U139" s="4" t="str">
-        <x:v>图42-1：语义响应与风格控制双通道 schema。语义通道回答“说什么”，风格通道回答“用什么声音和情绪说”，声学监督通道把二者绑定到音频文件、speech token 和采样配置</x:v>
+        <x:v>图41-7：工具调用多轮轨迹结构。工具观察以新的图像输入形式返回，模型必须基于观察图继续推理，而非仅生成一个形式正确的调用</x:v>
       </x:c>
       <x:c r="V139" s="4" t="str">
-        <x:v>图42-1：语义响应与风格控制双通道 schema</x:v>
+        <x:v>图41-7：工具调用多轮轨迹结构</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
@@ -9670,44 +9668,42 @@
         <x:v>Part 12: Specialized Datasets and Multimodal Data Engineering Practice</x:v>
       </x:c>
       <x:c r="D140" s="4" t="str">
-        <x:v>Ch42</x:v>
+        <x:v>Ch41</x:v>
       </x:c>
       <x:c r="E140" s="4" t="str">
-        <x:v>Chapter 42: Speech and Audio Data Engineering: Interaction Control, Style Labels, and Safety Boundaries</x:v>
+        <x:v>Chapter 41: Visual Reasoning Data Engineering: Chart Evidence, Medical Images, and Tool-Call Trajectories</x:v>
       </x:c>
       <x:c r="F140" s="4" t="str">
-        <x:v>docs/en/part12/ch42_speech_audio_interaction_data_engineering.md</x:v>
+        <x:v>docs/en/part12/ch41_visual_reasoning_tool_data_engineering.md</x:v>
       </x:c>
       <x:c r="G140" s="4" t="n">
-        <x:v>271</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="H140" s="4" t="str">
-        <x:v>42-2</x:v>
+        <x:v>41-8</x:v>
       </x:c>
       <x:c r="I140" s="4" t="str">
-        <x:v>Figure 42-2: VoiceStyleControl data construction pipeline. Text conversation or style content is first assigned speaker and emotion conditions, then audio is generated or collected through the authorized reference voice pool, and finally the samples are tokenized, quality-checked, balanced, and packaged</x:v>
+        <x:v>Figure 41-8: Bbox is a structured field and should be recoverable as reviewable visual evidence</x:v>
       </x:c>
       <x:c r="J140" s="4" t="str">
-        <x:v>Figure 42-2: VoiceStyleControl data construction pipeline</x:v>
+        <x:v>Figure 41-8: Real image and bbox evidence in the SFT schema</x:v>
       </x:c>
       <x:c r="K140" s="4" t="str">
-        <x:v>docs/images/part12/ch42_fig01_data_pipeline.svg</x:v>
+        <x:v>docs/images/part12/ch41_08_sft_schema_real_bbox_example_en.svg</x:v>
       </x:c>
       <x:c r="L140" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M140" s="4" t="str">
-        <x:v>1320x380</x:v>
+        <x:v>2100x980</x:v>
       </x:c>
       <x:c r="N140" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O140" s="4" t="str">
-        <x:v>VoiceStyleControl data construction pipeline. Text conversation or style content is first assigned speaker and emotion conditions, then audio is generated or collected through the authorized reference voice pool, and finally the samples are tokenized, quality-checked, balanced, and packaged.</x:v>
-      </x:c>
-      <x:c r="P140" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Chapter 42: Speech and Audio Data Engineering: Interaction Control, Style Labels, and Safety Boundaries; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>Bbox is a structured field and should be recoverable as reviewable visual evidence.</x:v>
+      </x:c>
+      <x:c r="P140" s="4" t="str"/>
       <x:c r="Q140" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -9717,10 +9713,10 @@
       <x:c r="S140" s="4" t="str"/>
       <x:c r="T140" s="4" t="str"/>
       <x:c r="U140" s="4" t="str">
-        <x:v>图42-2：VoiceStyleControl 数据构建流水线。文本对话或风格内容先被赋予 speaker 与 emotion 条件，再通过授权参考语音池生成或采集音频，最后经过 token 化、质检、配平和封装</x:v>
+        <x:v>图41-8：SFT schema 中的真实图像与 bbox 证据。bbox 是训练记录中的结构化字段，同时也应能被还原为可复查的可视化证据</x:v>
       </x:c>
       <x:c r="V140" s="4" t="str">
-        <x:v>图42-2：VoiceStyleControl 数据构建流水线</x:v>
+        <x:v>图41-8：SFT schema 中的真实图像与 bbox 证据</x:v>
       </x:c>
     </x:row>
     <x:row r="141">
@@ -9734,40 +9730,40 @@
         <x:v>Part 12: Specialized Datasets and Multimodal Data Engineering Practice</x:v>
       </x:c>
       <x:c r="D141" s="4" t="str">
-        <x:v>Ch42</x:v>
+        <x:v>Ch41</x:v>
       </x:c>
       <x:c r="E141" s="4" t="str">
-        <x:v>Chapter 42: Speech and Audio Data Engineering: Interaction Control, Style Labels, and Safety Boundaries</x:v>
+        <x:v>Chapter 41: Visual Reasoning Data Engineering: Chart Evidence, Medical Images, and Tool-Call Trajectories</x:v>
       </x:c>
       <x:c r="F141" s="4" t="str">
-        <x:v>docs/en/part12/ch42_speech_audio_interaction_data_engineering.md</x:v>
+        <x:v>docs/en/part12/ch41_visual_reasoning_tool_data_engineering.md</x:v>
       </x:c>
       <x:c r="G141" s="4" t="n">
-        <x:v>365</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="H141" s="4" t="str">
-        <x:v>42-3</x:v>
+        <x:v>41-9</x:v>
       </x:c>
       <x:c r="I141" s="4" t="str">
-        <x:v>Figure 42-3: Quality assessment and data flywheel closed loop. Automated validation, reverse ASR, style assessment, and manual sampling together form a defective-sample queue that feeds back into re-synthesis, re-annotation, downweighting, or removal</x:v>
+        <x:v>Figure 41-9: Quality-control and human-review gates. Medical image tool-use data needs to check answer, evidence, and behavior together; automated validation and human review should complement each other</x:v>
       </x:c>
       <x:c r="J141" s="4" t="str">
-        <x:v>Figure 42-3: Quality assessment and data flywheel closed loop</x:v>
+        <x:v>Figure 41-9: Quality-control and human-review gates</x:v>
       </x:c>
       <x:c r="K141" s="4" t="str">
-        <x:v>docs/images/part12/ch42_fig03_quality_loop.svg</x:v>
+        <x:v>docs/images/part12/ch41_09_quality_review_gate_en.svg</x:v>
       </x:c>
       <x:c r="L141" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M141" s="4" t="str">
-        <x:v>1120x430</x:v>
+        <x:v>2000x1120</x:v>
       </x:c>
       <x:c r="N141" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O141" s="4" t="str">
-        <x:v>Quality assessment and data flywheel closed loop. Automated validation, reverse ASR, style assessment, and manual sampling together form a defective-sample queue that feeds back into re-synthesis, re-annotation, downweighting, or removal.</x:v>
+        <x:v>Quality-control and human-review gates. Medical image tool-use data needs to check answer, evidence, and behavior together; automated validation and human review should complement each other.</x:v>
       </x:c>
       <x:c r="P141" s="4" t="str"/>
       <x:c r="Q141" s="4" t="str">
@@ -9779,10 +9775,10 @@
       <x:c r="S141" s="4" t="str"/>
       <x:c r="T141" s="4" t="str"/>
       <x:c r="U141" s="4" t="str">
-        <x:v>图42-3：质量评估与数据飞轮闭环。自动校验、反向 ASR、风格评估和人工抽检共同形成问题样本队列，再回流到重合成、重标注、降权或剔除</x:v>
+        <x:v>图41-9：质量控制与人工复核门禁。医学图像工具调用数据需要同时检查答案、证据和行为，自动校验与人工复核应形成互补</x:v>
       </x:c>
       <x:c r="V141" s="4" t="str">
-        <x:v>图42-3：质量评估与数据飞轮闭环</x:v>
+        <x:v>图41-9：质量控制与人工复核门禁</x:v>
       </x:c>
     </x:row>
     <x:row r="142">
@@ -9796,42 +9792,44 @@
         <x:v>Part 12: Specialized Datasets and Multimodal Data Engineering Practice</x:v>
       </x:c>
       <x:c r="D142" s="4" t="str">
-        <x:v>Ch43</x:v>
+        <x:v>Ch42</x:v>
       </x:c>
       <x:c r="E142" s="4" t="str">
-        <x:v>Chapter 43: Reasoning Trace Data Engineering: Long-Chain Compression, Implicit Computation, and Supervision Masks</x:v>
+        <x:v>Chapter 42: Speech and Audio Data Engineering: Interaction Control, Style Labels, and Safety Boundaries</x:v>
       </x:c>
       <x:c r="F142" s="4" t="str">
-        <x:v>docs/en/part12/ch43_reasoning_trace_compression_data_engineering.md</x:v>
+        <x:v>docs/en/part12/ch42_speech_audio_interaction_data_engineering.md</x:v>
       </x:c>
       <x:c r="G142" s="4" t="n">
-        <x:v>33</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H142" s="4" t="str">
-        <x:v>43-1</x:v>
+        <x:v>42-1</x:v>
       </x:c>
       <x:c r="I142" s="4" t="str">
-        <x:v>Figure 43-1: Latent-Switch-69K distills reasoning traces from Dolci-Think-SFT-32B into solution intuitions, compressed CoT, latent budgets, student sequences, and mask-aligned SFT records</x:v>
+        <x:v>Figure 42-1: Dual-channel schema for semantic response and style control. The semantic channel answers "what to say," the style channel answers "with which voice and emotion to say it," and the acoustic supervision channel binds both to audio files, speech tokens, and sampling configuration</x:v>
       </x:c>
       <x:c r="J142" s="4" t="str">
-        <x:v>Figure 43-1: Latent-Switch-69K Construction Pipeline</x:v>
+        <x:v>Figure 42-1: Dual-channel schema for semantic response and style control</x:v>
       </x:c>
       <x:c r="K142" s="4" t="str">
-        <x:v>docs/images/part12/ch43_latent_switch_pipeline.svg</x:v>
+        <x:v>docs/images/part12/ch42_01_dual_channel_schema_en.svg</x:v>
       </x:c>
       <x:c r="L142" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M142" s="4" t="str">
-        <x:v>1502.114x436.48425</x:v>
+        <x:v>1280x560</x:v>
       </x:c>
       <x:c r="N142" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O142" s="4" t="str">
-        <x:v>Latent-Switch-69K distills reasoning traces from Dolci-Think-SFT-32B into solution intuitions, compressed CoT, latent budgets, student sequences, and mask-aligned SFT records.</x:v>
-      </x:c>
-      <x:c r="P142" s="4" t="str"/>
+        <x:v>Dual-channel schema for semantic response and style control. The semantic channel answers "what to say," the style channel answers "with which voice and emotion to say it," and the acoustic supervision channel binds both to audio files, speech tokens, and sampling configuration.</x:v>
+      </x:c>
+      <x:c r="P142" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Chapter 42: Speech and Audio Data Engineering: Interaction Control, Style Labels, and Safety Boundaries; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q142" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -9841,10 +9839,10 @@
       <x:c r="S142" s="4" t="str"/>
       <x:c r="T142" s="4" t="str"/>
       <x:c r="U142" s="4" t="str">
-        <x:v>图43-1：Latent-Switch-69K 将 Dolci-Think-SFT-32B 的推理轨迹蒸馏为 solution intuition、压缩 CoT、latent budget、student sequence 和 mask 对齐后的 SFT 记录</x:v>
+        <x:v>图42-1：语义响应与风格控制双通道 schema。语义通道回答“说什么”，风格通道回答“用什么声音和情绪说”，声学监督通道把二者绑定到音频文件、speech token 和采样配置</x:v>
       </x:c>
       <x:c r="V142" s="4" t="str">
-        <x:v>图43-1：Latent-Switch-69K 构建流水线图</x:v>
+        <x:v>图42-1：语义响应与风格控制双通道 schema</x:v>
       </x:c>
     </x:row>
     <x:row r="143">
@@ -9858,42 +9856,44 @@
         <x:v>Part 12: Specialized Datasets and Multimodal Data Engineering Practice</x:v>
       </x:c>
       <x:c r="D143" s="4" t="str">
-        <x:v>Ch43</x:v>
+        <x:v>Ch42</x:v>
       </x:c>
       <x:c r="E143" s="4" t="str">
-        <x:v>Chapter 43: Reasoning Trace Data Engineering: Long-Chain Compression, Implicit Computation, and Supervision Masks</x:v>
+        <x:v>Chapter 42: Speech and Audio Data Engineering: Interaction Control, Style Labels, and Safety Boundaries</x:v>
       </x:c>
       <x:c r="F143" s="4" t="str">
-        <x:v>docs/en/part12/ch43_reasoning_trace_compression_data_engineering.md</x:v>
+        <x:v>docs/en/part12/ch42_speech_audio_interaction_data_engineering.md</x:v>
       </x:c>
       <x:c r="G143" s="4" t="n">
-        <x:v>58</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="H143" s="4" t="str">
-        <x:v>43-2</x:v>
+        <x:v>42-2</x:v>
       </x:c>
       <x:c r="I143" s="4" t="str">
-        <x:v>Figure 43-2: The final training set contains 69,745 samples; mathematics, code, and precise instruction-following data account for a large share</x:v>
+        <x:v>Figure 42-2: VoiceStyleControl data construction pipeline. Text conversation or style content is first assigned speaker and emotion conditions, then audio is generated or collected through the authorized reference voice pool, and finally the samples are tokenized, quality-checked, balanced, and packaged</x:v>
       </x:c>
       <x:c r="J143" s="4" t="str">
-        <x:v>Figure 43-2: Latent-Switch-69K Data Sources and Domain Composition</x:v>
+        <x:v>Figure 42-2: VoiceStyleControl data construction pipeline</x:v>
       </x:c>
       <x:c r="K143" s="4" t="str">
-        <x:v>docs/images/part12/ch40_05_dataset_composition.png</x:v>
+        <x:v>docs/images/part12/ch42_02_voice_style_data_pipeline_en.svg</x:v>
       </x:c>
       <x:c r="L143" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M143" s="4" t="str">
-        <x:v>2304x1052</x:v>
+        <x:v>1320x380</x:v>
       </x:c>
       <x:c r="N143" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O143" s="4" t="str">
-        <x:v>The final training set contains 69,745 samples; mathematics, code, and precise instruction-following data account for a large share.</x:v>
-      </x:c>
-      <x:c r="P143" s="4" t="str"/>
+        <x:v>VoiceStyleControl data construction pipeline. Text conversation or style content is first assigned speaker and emotion conditions, then audio is generated or collected through the authorized reference voice pool, and finally the samples are tokenized, quality-checked, balanced, and packaged.</x:v>
+      </x:c>
+      <x:c r="P143" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Chapter 42: Speech and Audio Data Engineering: Interaction Control, Style Labels, and Safety Boundaries; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q143" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -9903,10 +9903,10 @@
       <x:c r="S143" s="4" t="str"/>
       <x:c r="T143" s="4" t="str"/>
       <x:c r="U143" s="4" t="str">
-        <x:v>图43-2：最终训练集包含 69,745 条样本，来源中数学、代码和精确指令类数据占比较高</x:v>
+        <x:v>图42-2：VoiceStyleControl 数据构建流水线。文本对话或风格内容先被赋予 speaker 与 emotion 条件，再通过授权参考语音池生成或采集音频，最后经过 token 化、质检、配平和封装</x:v>
       </x:c>
       <x:c r="V143" s="4" t="str">
-        <x:v>图43-2：Latent-Switch-69K 数据来源与领域组成</x:v>
+        <x:v>图42-2：VoiceStyleControl 数据构建流水线</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
@@ -9920,40 +9920,40 @@
         <x:v>Part 12: Specialized Datasets and Multimodal Data Engineering Practice</x:v>
       </x:c>
       <x:c r="D144" s="4" t="str">
-        <x:v>Ch43</x:v>
+        <x:v>Ch42</x:v>
       </x:c>
       <x:c r="E144" s="4" t="str">
-        <x:v>Chapter 43: Reasoning Trace Data Engineering: Long-Chain Compression, Implicit Computation, and Supervision Masks</x:v>
+        <x:v>Chapter 42: Speech and Audio Data Engineering: Interaction Control, Style Labels, and Safety Boundaries</x:v>
       </x:c>
       <x:c r="F144" s="4" t="str">
-        <x:v>docs/en/part12/ch43_reasoning_trace_compression_data_engineering.md</x:v>
+        <x:v>docs/en/part12/ch42_speech_audio_interaction_data_engineering.md</x:v>
       </x:c>
       <x:c r="G144" s="4" t="n">
-        <x:v>183</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="H144" s="4" t="str">
-        <x:v>43-3</x:v>
+        <x:v>42-3</x:v>
       </x:c>
       <x:c r="I144" s="4" t="str">
-        <x:v>Figure 43-3: The extensive visible reasoning in the source trace is split into two types of signal: solution intuition is used to estimate the latent budget, and the compressed CoT is used for explicit verification and answer supervision</x:v>
+        <x:v>Figure 42-3: Quality assessment and data flywheel closed loop. Automated validation, reverse ASR, style assessment, and manual sampling together form a defective-sample queue that feeds back into re-synthesis, re-annotation, downweighting, or removal</x:v>
       </x:c>
       <x:c r="J144" s="4" t="str">
-        <x:v>Figure 43-3: Comparison of Original CoT, Compressed CoT, and Latent Placeholders</x:v>
+        <x:v>Figure 42-3: Quality assessment and data flywheel closed loop</x:v>
       </x:c>
       <x:c r="K144" s="4" t="str">
-        <x:v>docs/images/part12/ch43_cot_latent_comparison.svg</x:v>
+        <x:v>docs/images/part12/ch42_03_quality_loop_en.svg</x:v>
       </x:c>
       <x:c r="L144" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M144" s="4" t="str">
-        <x:v>1342.4434x565.25885</x:v>
+        <x:v>1120x430</x:v>
       </x:c>
       <x:c r="N144" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O144" s="4" t="str">
-        <x:v>The extensive visible reasoning in the source trace is split into two types of signal: solution intuition is used to estimate the latent budget, and the compressed CoT is used for explicit verification and answer supervision.</x:v>
+        <x:v>Quality assessment and data flywheel closed loop. Automated validation, reverse ASR, style assessment, and manual sampling together form a defective-sample queue that feeds back into re-synthesis, re-annotation, downweighting, or removal.</x:v>
       </x:c>
       <x:c r="P144" s="4" t="str"/>
       <x:c r="Q144" s="4" t="str">
@@ -9965,10 +9965,10 @@
       <x:c r="S144" s="4" t="str"/>
       <x:c r="T144" s="4" t="str"/>
       <x:c r="U144" s="4" t="str">
-        <x:v>图43-3：source trace 中的大量可见推理被拆成两类信号：solution intuition 用于估计 latent budget，压缩 CoT 用于显式验证和答案监督</x:v>
+        <x:v>图42-3：质量评估与数据飞轮闭环。自动校验、反向 ASR、风格评估和人工抽检共同形成问题样本队列，再回流到重合成、重标注、降权或剔除</x:v>
       </x:c>
       <x:c r="V144" s="4" t="str">
-        <x:v>图43-3：原始 CoT、压缩 CoT 与 latent placeholder 对比</x:v>
+        <x:v>图42-3：质量评估与数据飞轮闭环</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
@@ -9991,35 +9991,33 @@
         <x:v>docs/en/part12/ch43_reasoning_trace_compression_data_engineering.md</x:v>
       </x:c>
       <x:c r="G145" s="4" t="n">
-        <x:v>196</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H145" s="4" t="str">
-        <x:v>43-4</x:v>
+        <x:v>43-1</x:v>
       </x:c>
       <x:c r="I145" s="4" t="str">
-        <x:v>Figure 43-4: This figure shows the distributions of source CoT length, distilled CoT length, intuition length, ground truth length, and compression ratio</x:v>
+        <x:v>Figure 43-1: Latent-Switch-69K distills reasoning traces from Dolci-Think-SFT-32B into solution intuitions, compressed CoT, latent budgets, student sequences, and mask-aligned SFT records</x:v>
       </x:c>
       <x:c r="J145" s="4" t="str">
-        <x:v>Figure 43-4: Distributions of Original and Distilled Reasoning Length and Compression Ratio</x:v>
+        <x:v>Figure 43-1: Latent-Switch-69K Construction Pipeline</x:v>
       </x:c>
       <x:c r="K145" s="4" t="str">
-        <x:v>docs/images/part12/ch40_07_token_compression_distribution.png</x:v>
+        <x:v>docs/images/part12/ch43_01_latent_switch_pipeline.svg</x:v>
       </x:c>
       <x:c r="L145" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M145" s="4" t="str">
-        <x:v>2304x422</x:v>
+        <x:v>1502.114x436.48425</x:v>
       </x:c>
       <x:c r="N145" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O145" s="4" t="str">
-        <x:v>This figure shows the distributions of source CoT length, distilled CoT length, intuition length, ground truth length, and compression ratio.</x:v>
-      </x:c>
-      <x:c r="P145" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Chapter 43: Reasoning Trace Data Engineering: Long-Chain Compression, Implicit Computation, and Supervision Masks; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>Latent-Switch-69K distills reasoning traces from Dolci-Think-SFT-32B into solution intuitions, compressed CoT, latent budgets, student sequences, and mask-aligned SFT records.</x:v>
+      </x:c>
+      <x:c r="P145" s="4" t="str"/>
       <x:c r="Q145" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -10029,10 +10027,10 @@
       <x:c r="S145" s="4" t="str"/>
       <x:c r="T145" s="4" t="str"/>
       <x:c r="U145" s="4" t="str">
-        <x:v>图43-4：本图展示了 source CoT length、distilled CoT length、insight length、ground truth length 和 compression ratio 的分布</x:v>
+        <x:v>图43-1：Latent-Switch-69K 将 Dolci-Think-SFT-32B 的推理轨迹蒸馏为 solution intuition、压缩 CoT、latent budget、student sequence 和 mask 对齐后的 SFT 记录</x:v>
       </x:c>
       <x:c r="V145" s="4" t="str">
-        <x:v>图43-4：原始与蒸馏后推理长度及压缩率统计</x:v>
+        <x:v>图43-1：Latent-Switch-69K 构建流水线图</x:v>
       </x:c>
     </x:row>
     <x:row r="146">
@@ -10055,31 +10053,31 @@
         <x:v>docs/en/part12/ch43_reasoning_trace_compression_data_engineering.md</x:v>
       </x:c>
       <x:c r="G146" s="4" t="n">
-        <x:v>343</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H146" s="4" t="str">
-        <x:v>43-5</x:v>
+        <x:v>43-2</x:v>
       </x:c>
       <x:c r="I146" s="4" t="str">
-        <x:v>Figure 43-5: Prompt and latent interior tokens are masked from ordinary CE; latent boundaries, explicit CoT, answers, and end tokens are controlled by different weights and masks</x:v>
+        <x:v>Figure 43-2: The final training set contains 69,745 samples; mathematics, code, and precise instruction-following data account for a large share</x:v>
       </x:c>
       <x:c r="J146" s="4" t="str">
-        <x:v>Figure 43-5: Supervision Mask Schematic</x:v>
+        <x:v>Figure 43-2: Latent-Switch-69K Data Sources and Domain Composition</x:v>
       </x:c>
       <x:c r="K146" s="4" t="str">
-        <x:v>docs/images/part12/ch43_supervision_mask.svg</x:v>
+        <x:v>docs/images/part12/ch43_02_dataset_composition.png</x:v>
       </x:c>
       <x:c r="L146" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M146" s="4" t="str">
-        <x:v>1473.5x791.87109</x:v>
+        <x:v>2304x1052</x:v>
       </x:c>
       <x:c r="N146" s="4" t="str">
-        <x:v>svg</x:v>
+        <x:v>png</x:v>
       </x:c>
       <x:c r="O146" s="4" t="str">
-        <x:v>Prompt and latent interior tokens are masked from ordinary CE; latent boundaries, explicit CoT, answers, and end tokens are controlled by different weights and masks.</x:v>
+        <x:v>The final training set contains 69,745 samples; mathematics, code, and precise instruction-following data account for a large share.</x:v>
       </x:c>
       <x:c r="P146" s="4" t="str"/>
       <x:c r="Q146" s="4" t="str">
@@ -10091,10 +10089,10 @@
       <x:c r="S146" s="4" t="str"/>
       <x:c r="T146" s="4" t="str"/>
       <x:c r="U146" s="4" t="str">
-        <x:v>图43-5：prompt 与 latent interior 被普通 CE mask 掉；latent 边界、显式 CoT、答案和结束 token 由不同权重和 mask 控制</x:v>
+        <x:v>图43-2：最终训练集包含 69,745 条样本，来源中数学、代码和精确指令类数据占比较高</x:v>
       </x:c>
       <x:c r="V146" s="4" t="str">
-        <x:v>图43-5：Supervision mask 示意图</x:v>
+        <x:v>图43-2：Latent-Switch-69K 数据来源与领域组成</x:v>
       </x:c>
     </x:row>
     <x:row r="147">
@@ -10105,43 +10103,43 @@
         <x:v>en</x:v>
       </x:c>
       <x:c r="C147" s="4" t="str">
-        <x:v>Part 13: Open-source LLM Data Engineering Recipes and Paradigms</x:v>
+        <x:v>Part 12: Specialized Datasets and Multimodal Data Engineering Practice</x:v>
       </x:c>
       <x:c r="D147" s="4" t="str">
-        <x:v>Ch44</x:v>
+        <x:v>Ch43</x:v>
       </x:c>
       <x:c r="E147" s="4" t="str">
-        <x:v>Chapter 44: LLM Pre-training Data Engineering in Practice</x:v>
+        <x:v>Chapter 43: Reasoning Trace Data Engineering: Long-Chain Compression, Implicit Computation, and Supervision Masks</x:v>
       </x:c>
       <x:c r="F147" s="4" t="str">
-        <x:v>docs/en/part13/ch44_pretrain_recipes.md</x:v>
+        <x:v>docs/en/part12/ch43_reasoning_trace_compression_data_engineering.md</x:v>
       </x:c>
       <x:c r="G147" s="4" t="n">
-        <x:v>39</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="H147" s="4" t="str">
-        <x:v>44-1</x:v>
+        <x:v>43-3</x:v>
       </x:c>
       <x:c r="I147" s="4" t="str">
-        <x:v>&lt;div align="center"&lt;bFigure 44-1: Data Recipe Funnel&lt;/b&lt;/div</x:v>
+        <x:v>Figure 43-3: The extensive visible reasoning in the source trace is split into two types of signal: solution intuition is used to estimate the latent budget, and the compressed CoT is used for explicit verification and answer supervision</x:v>
       </x:c>
       <x:c r="J147" s="4" t="str">
-        <x:v>Figure 44-1: Data Recipe Funnel</x:v>
+        <x:v>Figure 43-3: Comparison of Original CoT, Compressed CoT, and Latent Placeholders</x:v>
       </x:c>
       <x:c r="K147" s="4" t="str">
-        <x:v>docs/images/part13/ch44_01_data_recipe_funnel_en.svg</x:v>
+        <x:v>docs/images/part12/ch43_03_cot_latent_comparison.svg</x:v>
       </x:c>
       <x:c r="L147" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M147" s="4" t="str">
-        <x:v>800x600</x:v>
+        <x:v>1342.4434x565.25885</x:v>
       </x:c>
       <x:c r="N147" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O147" s="4" t="str">
-        <x:v>&lt;div align="center"&lt;bFigure 44-1: Data Recipe Funnel&lt;/b&lt;/div.</x:v>
+        <x:v>The extensive visible reasoning in the source trace is split into two types of signal: solution intuition is used to estimate the latent budget, and the compressed CoT is used for explicit verification and answer supervision.</x:v>
       </x:c>
       <x:c r="P147" s="4" t="str"/>
       <x:c r="Q147" s="4" t="str">
@@ -10153,10 +10151,10 @@
       <x:c r="S147" s="4" t="str"/>
       <x:c r="T147" s="4" t="str"/>
       <x:c r="U147" s="4" t="str">
-        <x:v>&lt;div align="center"&lt;b图44-1：数据配方漏斗 (Data Recipe Funnel)&lt;/b&lt;/div</x:v>
+        <x:v>图43-3：source trace 中的大量可见推理被拆成两类信号：solution intuition 用于估计 latent budget，压缩 CoT 用于显式验证和答案监督</x:v>
       </x:c>
       <x:c r="V147" s="4" t="str">
-        <x:v>图44-1：数据配方漏斗 (Data Recipe Funnel)</x:v>
+        <x:v>图43-3：原始 CoT、压缩 CoT 与 latent placeholder 对比</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
@@ -10167,45 +10165,47 @@
         <x:v>en</x:v>
       </x:c>
       <x:c r="C148" s="4" t="str">
-        <x:v>Part 13: Open-source LLM Data Engineering Recipes and Paradigms</x:v>
+        <x:v>Part 12: Specialized Datasets and Multimodal Data Engineering Practice</x:v>
       </x:c>
       <x:c r="D148" s="4" t="str">
-        <x:v>Ch44</x:v>
+        <x:v>Ch43</x:v>
       </x:c>
       <x:c r="E148" s="4" t="str">
-        <x:v>Chapter 44: LLM Pre-training Data Engineering in Practice</x:v>
+        <x:v>Chapter 43: Reasoning Trace Data Engineering: Long-Chain Compression, Implicit Computation, and Supervision Masks</x:v>
       </x:c>
       <x:c r="F148" s="4" t="str">
-        <x:v>docs/en/part13/ch44_pretrain_recipes.md</x:v>
+        <x:v>docs/en/part12/ch43_reasoning_trace_compression_data_engineering.md</x:v>
       </x:c>
       <x:c r="G148" s="4" t="n">
-        <x:v>51</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="H148" s="4" t="str">
-        <x:v>44-2</x:v>
+        <x:v>43-4</x:v>
       </x:c>
       <x:c r="I148" s="4" t="str">
-        <x:v>&lt;div align="center"&lt;bFigure 44-2: Data Transparency Spectrum for Large Language Models&lt;/b&lt;/div</x:v>
+        <x:v>Figure 43-4: This figure shows the distributions of source CoT length, distilled CoT length, intuition length, ground truth length, and compression ratio</x:v>
       </x:c>
       <x:c r="J148" s="4" t="str">
-        <x:v>Figure 44-2: Data Transparency Spectrum for Large Language Models</x:v>
+        <x:v>Figure 43-4: Distributions of Original and Distilled Reasoning Length and Compression Ratio</x:v>
       </x:c>
       <x:c r="K148" s="4" t="str">
-        <x:v>docs/images/part13/ch44_02_data_transparency_spectrum_en.svg</x:v>
+        <x:v>docs/images/part12/ch43_04_token_compression_distribution.png</x:v>
       </x:c>
       <x:c r="L148" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M148" s="4" t="str">
-        <x:v>900x450</x:v>
+        <x:v>2304x422</x:v>
       </x:c>
       <x:c r="N148" s="4" t="str">
-        <x:v>svg</x:v>
+        <x:v>png</x:v>
       </x:c>
       <x:c r="O148" s="4" t="str">
-        <x:v>&lt;div align="center"&lt;bFigure 44-2: Data Transparency Spectrum for Large Language Models&lt;/b&lt;/div.</x:v>
-      </x:c>
-      <x:c r="P148" s="4" t="str"/>
+        <x:v>This figure shows the distributions of source CoT length, distilled CoT length, intuition length, ground truth length, and compression ratio.</x:v>
+      </x:c>
+      <x:c r="P148" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Chapter 43: Reasoning Trace Data Engineering: Long-Chain Compression, Implicit Computation, and Supervision Masks; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q148" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -10215,10 +10215,10 @@
       <x:c r="S148" s="4" t="str"/>
       <x:c r="T148" s="4" t="str"/>
       <x:c r="U148" s="4" t="str">
-        <x:v>&lt;div align="center"&lt;b图44-2：大模型数据透明度光谱 (Data Transparency Spectrum)&lt;/b&lt;/div</x:v>
+        <x:v>图43-4：本图展示了 source CoT length、distilled CoT length、insight length、ground truth length 和 compression ratio 的分布</x:v>
       </x:c>
       <x:c r="V148" s="4" t="str">
-        <x:v>图44-2：大模型数据透明度光谱 (Data Transparency Spectrum)</x:v>
+        <x:v>图43-4：原始与蒸馏后推理长度及压缩率统计</x:v>
       </x:c>
     </x:row>
     <x:row r="149">
@@ -10229,43 +10229,43 @@
         <x:v>en</x:v>
       </x:c>
       <x:c r="C149" s="4" t="str">
-        <x:v>Part 13: Open-source LLM Data Engineering Recipes and Paradigms</x:v>
+        <x:v>Part 12: Specialized Datasets and Multimodal Data Engineering Practice</x:v>
       </x:c>
       <x:c r="D149" s="4" t="str">
-        <x:v>Ch44</x:v>
+        <x:v>Ch43</x:v>
       </x:c>
       <x:c r="E149" s="4" t="str">
-        <x:v>Chapter 44: LLM Pre-training Data Engineering in Practice</x:v>
+        <x:v>Chapter 43: Reasoning Trace Data Engineering: Long-Chain Compression, Implicit Computation, and Supervision Masks</x:v>
       </x:c>
       <x:c r="F149" s="4" t="str">
-        <x:v>docs/en/part13/ch44_pretrain_recipes.md</x:v>
+        <x:v>docs/en/part12/ch43_reasoning_trace_compression_data_engineering.md</x:v>
       </x:c>
       <x:c r="G149" s="4" t="n">
-        <x:v>56</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="H149" s="4" t="str">
-        <x:v>44-3</x:v>
+        <x:v>43-5</x:v>
       </x:c>
       <x:c r="I149" s="4" t="str">
-        <x:v>&lt;div align="center"&lt;bFigure 44-3: Hierarchical Map of Pretraining Data Sources (redrawn from the foundational figure in Chapter 4)&lt;/b&lt;/div</x:v>
+        <x:v>Figure 43-5: Prompt and latent interior tokens are masked from ordinary CE; latent boundaries, explicit CoT, answers, and end tokens are controlled by different weights and masks</x:v>
       </x:c>
       <x:c r="J149" s="4" t="str">
-        <x:v>Figure 44-3: Hierarchical Map of Pretraining Data Sources</x:v>
+        <x:v>Figure 43-5: Supervision Mask Schematic</x:v>
       </x:c>
       <x:c r="K149" s="4" t="str">
-        <x:v>docs/images/part13/ch44_03_pretrain_data_source_map.png</x:v>
+        <x:v>docs/images/part12/ch43_05_supervision_mask.svg</x:v>
       </x:c>
       <x:c r="L149" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M149" s="4" t="str">
-        <x:v>1024x1024</x:v>
+        <x:v>1473.5x791.87109</x:v>
       </x:c>
       <x:c r="N149" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O149" s="4" t="str">
-        <x:v>&lt;div align="center"&lt;bFigure 44-3: Hierarchical Map of Pretraining Data Sources (redrawn from the foundational figure in Chapter 4)&lt;/b&lt;/div.</x:v>
+        <x:v>Prompt and latent interior tokens are masked from ordinary CE; latent boundaries, explicit CoT, answers, and end tokens are controlled by different weights and masks.</x:v>
       </x:c>
       <x:c r="P149" s="4" t="str"/>
       <x:c r="Q149" s="4" t="str">
@@ -10277,10 +10277,10 @@
       <x:c r="S149" s="4" t="str"/>
       <x:c r="T149" s="4" t="str"/>
       <x:c r="U149" s="4" t="str">
-        <x:v>&lt;div align="center"&lt;b图44-3：预训练数据源分层地图（改绘自第4章基础图）&lt;/b&lt;/div</x:v>
+        <x:v>图43-5：prompt 与 latent interior 被普通 CE mask 掉；latent 边界、显式 CoT、答案和结束 token 由不同权重和 mask 控制</x:v>
       </x:c>
       <x:c r="V149" s="4" t="str">
-        <x:v>图44-3：预训练数据源分层地图</x:v>
+        <x:v>图43-5：Supervision mask 示意图</x:v>
       </x:c>
     </x:row>
     <x:row r="150">
@@ -10303,35 +10303,33 @@
         <x:v>docs/en/part13/ch44_pretrain_recipes.md</x:v>
       </x:c>
       <x:c r="G150" s="4" t="n">
-        <x:v>87</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H150" s="4" t="str">
-        <x:v>44-4</x:v>
+        <x:v>44-1</x:v>
       </x:c>
       <x:c r="I150" s="4" t="str">
-        <x:v>&lt;div align="center"&lt;bFigure 44-4: Estimated Data Mixture Ratios — Pie Chart Comparison Across Three Models&lt;/b&lt;/div</x:v>
+        <x:v>&lt;div align="center"&lt;bFigure 44-1: Data Recipe Funnel&lt;/b&lt;/div</x:v>
       </x:c>
       <x:c r="J150" s="4" t="str">
-        <x:v>Figure 44-4: Estimated Data Mixture Ratios — Pie Chart Comparison Across Three Models</x:v>
+        <x:v>Figure 44-1: Data Recipe Funnel</x:v>
       </x:c>
       <x:c r="K150" s="4" t="str">
-        <x:v>docs/images/part13/ch44_04_models_pie_chart_en.svg</x:v>
+        <x:v>docs/images/part13/ch44_01_data_recipe_funnel_en.svg</x:v>
       </x:c>
       <x:c r="L150" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M150" s="4" t="str">
-        <x:v>1100x460</x:v>
+        <x:v>800x600</x:v>
       </x:c>
       <x:c r="N150" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O150" s="4" t="str">
-        <x:v>&lt;div align="center"&lt;bFigure 44-4: Estimated Data Mixture Ratios — Pie Chart Comparison Across Three Models&lt;/b&lt;/div.</x:v>
-      </x:c>
-      <x:c r="P150" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Chapter 44: LLM Pre-training Data Engineering in Practice; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>&lt;div align="center"&lt;bFigure 44-1: Data Recipe Funnel&lt;/b&lt;/div.</x:v>
+      </x:c>
+      <x:c r="P150" s="4" t="str"/>
       <x:c r="Q150" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -10341,10 +10339,10 @@
       <x:c r="S150" s="4" t="str"/>
       <x:c r="T150" s="4" t="str"/>
       <x:c r="U150" s="4" t="str">
-        <x:v>&lt;div align="center"&lt;b图44-4：三模型数据组成饼图对比 (Estimated Data Mixture Ratios)&lt;/b&lt;/div</x:v>
+        <x:v>&lt;div align="center"&lt;b图44-1：数据配方漏斗 (Data Recipe Funnel)&lt;/b&lt;/div</x:v>
       </x:c>
       <x:c r="V150" s="4" t="str">
-        <x:v>图44-4：三模型数据组成饼图对比 (Estimated Data Mixture Ratios)</x:v>
+        <x:v>图44-1：数据配方漏斗 (Data Recipe Funnel)</x:v>
       </x:c>
     </x:row>
     <x:row r="151">
@@ -10367,31 +10365,31 @@
         <x:v>docs/en/part13/ch44_pretrain_recipes.md</x:v>
       </x:c>
       <x:c r="G151" s="4" t="n">
-        <x:v>253</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H151" s="4" t="str">
-        <x:v>44-5</x:v>
+        <x:v>44-2</x:v>
       </x:c>
       <x:c r="I151" s="4" t="str">
-        <x:v>&lt;div align="center"&lt;bFigure 44-5: Llama-3 Annealing Phase Data Composition Timeline (Curriculum Learning Schedule)&lt;/b&lt;/div</x:v>
+        <x:v>&lt;div align="center"&lt;bFigure 44-2: Data Transparency Spectrum for Large Language Models&lt;/b&lt;/div</x:v>
       </x:c>
       <x:c r="J151" s="4" t="str">
-        <x:v>Figure 44-5: Llama-3 Annealing Phase Data Composition Timeline (Curriculum Learning Schedule)</x:v>
+        <x:v>Figure 44-2: Data Transparency Spectrum for Large Language Models</x:v>
       </x:c>
       <x:c r="K151" s="4" t="str">
-        <x:v>docs/images/part13/ch44_05_llama3_annealing_schedule_en.svg</x:v>
+        <x:v>docs/images/part13/ch44_02_data_transparency_spectrum_en.svg</x:v>
       </x:c>
       <x:c r="L151" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M151" s="4" t="str">
-        <x:v>1000x600</x:v>
+        <x:v>900x450</x:v>
       </x:c>
       <x:c r="N151" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O151" s="4" t="str">
-        <x:v>&lt;div align="center"&lt;bFigure 44-5: Llama-3 Annealing Phase Data Composition Timeline (Curriculum Learning Schedule)&lt;/b&lt;/div.</x:v>
+        <x:v>&lt;div align="center"&lt;bFigure 44-2: Data Transparency Spectrum for Large Language Models&lt;/b&lt;/div.</x:v>
       </x:c>
       <x:c r="P151" s="4" t="str"/>
       <x:c r="Q151" s="4" t="str">
@@ -10403,10 +10401,10 @@
       <x:c r="S151" s="4" t="str"/>
       <x:c r="T151" s="4" t="str"/>
       <x:c r="U151" s="4" t="str">
-        <x:v>&lt;div align="center"&lt;b图44-5：Llama-3 退火期数据组成时间轴 (Curriculum Learning Schedule)&lt;/b&lt;/div</x:v>
+        <x:v>&lt;div align="center"&lt;b图44-2：大模型数据透明度光谱 (Data Transparency Spectrum)&lt;/b&lt;/div</x:v>
       </x:c>
       <x:c r="V151" s="4" t="str">
-        <x:v>图44-5：Llama-3 退火期数据组成时间轴 (Curriculum Learning Schedule)</x:v>
+        <x:v>图44-2：大模型数据透明度光谱 (Data Transparency Spectrum)</x:v>
       </x:c>
     </x:row>
     <x:row r="152">
@@ -10420,40 +10418,40 @@
         <x:v>Part 13: Open-source LLM Data Engineering Recipes and Paradigms</x:v>
       </x:c>
       <x:c r="D152" s="4" t="str">
-        <x:v>Ch45</x:v>
+        <x:v>Ch44</x:v>
       </x:c>
       <x:c r="E152" s="4" t="str">
-        <x:v>Chapter 45: LLM Post-training Data Engineering: SFT and Preference Alignment</x:v>
+        <x:v>Chapter 44: LLM Pre-training Data Engineering in Practice</x:v>
       </x:c>
       <x:c r="F152" s="4" t="str">
-        <x:v>docs/en/part13/ch45_posttrain_recipes.md</x:v>
+        <x:v>docs/en/part13/ch44_pretrain_recipes.md</x:v>
       </x:c>
       <x:c r="G152" s="4" t="n">
-        <x:v>64</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H152" s="4" t="str">
-        <x:v>45-1</x:v>
+        <x:v>44-3</x:v>
       </x:c>
       <x:c r="I152" s="4" t="str">
-        <x:v>Figure 45-1: Data flow relationships among SFT, Preference Alignment, and Online Continuous Optimization</x:v>
+        <x:v>&lt;div align="center"&lt;bFigure 44-3: Hierarchical Map of Pretraining Data Sources (redrawn from the foundational figure in Chapter 4)&lt;/b&lt;/div</x:v>
       </x:c>
       <x:c r="J152" s="4" t="str">
-        <x:v>Figure 45-1: Schematic of the LLM Three-Stage Post-Training Pipeline</x:v>
+        <x:v>Figure 44-3: Hierarchical Map of Pretraining Data Sources</x:v>
       </x:c>
       <x:c r="K152" s="4" t="str">
-        <x:v>docs/images/part13/ch45_01_posttrain_three_stage_pipeline.svg</x:v>
+        <x:v>docs/images/part13/ch44_03_pretrain_data_source_map.png</x:v>
       </x:c>
       <x:c r="L152" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M152" s="4" t="str">
-        <x:v>1672x941</x:v>
+        <x:v>1024x1024</x:v>
       </x:c>
       <x:c r="N152" s="4" t="str">
-        <x:v>svg</x:v>
+        <x:v>png</x:v>
       </x:c>
       <x:c r="O152" s="4" t="str">
-        <x:v>Data flow relationships among SFT, Preference Alignment, and Online Continuous Optimization.</x:v>
+        <x:v>&lt;div align="center"&lt;bFigure 44-3: Hierarchical Map of Pretraining Data Sources (redrawn from the foundational figure in Chapter 4)&lt;/b&lt;/div.</x:v>
       </x:c>
       <x:c r="P152" s="4" t="str"/>
       <x:c r="Q152" s="4" t="str">
@@ -10465,10 +10463,10 @@
       <x:c r="S152" s="4" t="str"/>
       <x:c r="T152" s="4" t="str"/>
       <x:c r="U152" s="4" t="str">
-        <x:v>图45-1：SFT、偏好对齐与在线持续优化之间的数据流动关系</x:v>
+        <x:v>&lt;div align="center"&lt;b图44-3：预训练数据源分层地图（改绘自第4章基础图）&lt;/b&lt;/div</x:v>
       </x:c>
       <x:c r="V152" s="4" t="str">
-        <x:v>图45-1：LLM 后训练三阶段流水线示意图</x:v>
+        <x:v>图44-3：预训练数据源分层地图</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
@@ -10482,42 +10480,44 @@
         <x:v>Part 13: Open-source LLM Data Engineering Recipes and Paradigms</x:v>
       </x:c>
       <x:c r="D153" s="4" t="str">
-        <x:v>Ch45</x:v>
+        <x:v>Ch44</x:v>
       </x:c>
       <x:c r="E153" s="4" t="str">
-        <x:v>Chapter 45: LLM Post-training Data Engineering: SFT and Preference Alignment</x:v>
+        <x:v>Chapter 44: LLM Pre-training Data Engineering in Practice</x:v>
       </x:c>
       <x:c r="F153" s="4" t="str">
-        <x:v>docs/en/part13/ch45_posttrain_recipes.md</x:v>
+        <x:v>docs/en/part13/ch44_pretrain_recipes.md</x:v>
       </x:c>
       <x:c r="G153" s="4" t="n">
-        <x:v>142</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H153" s="4" t="str">
-        <x:v>45-2</x:v>
+        <x:v>44-4</x:v>
       </x:c>
       <x:c r="I153" s="4" t="str">
-        <x:v>Figure 45-2: Data entry points, generation methods, and quality control checkpoints for the three SFT synthesis approaches</x:v>
+        <x:v>&lt;div align="center"&lt;bFigure 44-4: Estimated Data Mixture Ratios — Pie Chart Comparison Across Three Models&lt;/b&lt;/div</x:v>
       </x:c>
       <x:c r="J153" s="4" t="str">
-        <x:v>Figure 45-2: Pipeline Comparison of the Three SFT Synthesis Schools: Self-Instruct, Evol-Instruct, and Magpie</x:v>
+        <x:v>Figure 44-4: Estimated Data Mixture Ratios — Pie Chart Comparison Across Three Models</x:v>
       </x:c>
       <x:c r="K153" s="4" t="str">
-        <x:v>docs/images/part13/ch45_02_sft_synthesis_pipelines.svg</x:v>
+        <x:v>docs/images/part13/ch44_04_models_pie_chart_en.svg</x:v>
       </x:c>
       <x:c r="L153" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M153" s="4" t="str">
-        <x:v>1672x941</x:v>
+        <x:v>1100x460</x:v>
       </x:c>
       <x:c r="N153" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O153" s="4" t="str">
-        <x:v>Data entry points, generation methods, and quality control checkpoints for the three SFT synthesis approaches.</x:v>
-      </x:c>
-      <x:c r="P153" s="4" t="str"/>
+        <x:v>&lt;div align="center"&lt;bFigure 44-4: Estimated Data Mixture Ratios — Pie Chart Comparison Across Three Models&lt;/b&lt;/div.</x:v>
+      </x:c>
+      <x:c r="P153" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Chapter 44: LLM Pre-training Data Engineering in Practice; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q153" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -10527,10 +10527,10 @@
       <x:c r="S153" s="4" t="str"/>
       <x:c r="T153" s="4" t="str"/>
       <x:c r="U153" s="4" t="str">
-        <x:v>图45-2：三类 SFT 合成路线的数据入口、生成方式与质检位置</x:v>
+        <x:v>&lt;div align="center"&lt;b图44-4：三模型数据组成饼图对比 (Estimated Data Mixture Ratios)&lt;/b&lt;/div</x:v>
       </x:c>
       <x:c r="V153" s="4" t="str">
-        <x:v>图45-2：Self-Instruct、Evol-Instruct 与 Magpie 三流派 pipeline 对比</x:v>
+        <x:v>图44-4：三模型数据组成饼图对比 (Estimated Data Mixture Ratios)</x:v>
       </x:c>
     </x:row>
     <x:row r="154">
@@ -10544,40 +10544,40 @@
         <x:v>Part 13: Open-source LLM Data Engineering Recipes and Paradigms</x:v>
       </x:c>
       <x:c r="D154" s="4" t="str">
-        <x:v>Ch45</x:v>
+        <x:v>Ch44</x:v>
       </x:c>
       <x:c r="E154" s="4" t="str">
-        <x:v>Chapter 45: LLM Post-training Data Engineering: SFT and Preference Alignment</x:v>
+        <x:v>Chapter 44: LLM Pre-training Data Engineering in Practice</x:v>
       </x:c>
       <x:c r="F154" s="4" t="str">
-        <x:v>docs/en/part13/ch45_posttrain_recipes.md</x:v>
+        <x:v>docs/en/part13/ch44_pretrain_recipes.md</x:v>
       </x:c>
       <x:c r="G154" s="4" t="n">
-        <x:v>237</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="H154" s="4" t="str">
-        <x:v>45-3</x:v>
+        <x:v>44-5</x:v>
       </x:c>
       <x:c r="I154" s="4" t="str">
-        <x:v>Figure 45-3: Data flow and stage relationships in Tülu-3 from SFT-Mix and DPO mix to RLVR</x:v>
+        <x:v>&lt;div align="center"&lt;bFigure 44-5: Llama-3 Annealing Phase Data Composition Timeline (Curriculum Learning Schedule)&lt;/b&lt;/div</x:v>
       </x:c>
       <x:c r="J154" s="4" t="str">
-        <x:v>Figure 45-3: Tülu-3 Three-Stage Data Flow and Scale Schematic</x:v>
+        <x:v>Figure 44-5: Llama-3 Annealing Phase Data Composition Timeline (Curriculum Learning Schedule)</x:v>
       </x:c>
       <x:c r="K154" s="4" t="str">
-        <x:v>docs/images/part13/ch45_03_tulu3_posttrain_flow.svg</x:v>
+        <x:v>docs/images/part13/ch44_05_llama3_annealing_schedule_en.svg</x:v>
       </x:c>
       <x:c r="L154" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M154" s="4" t="str">
-        <x:v>1672x941</x:v>
+        <x:v>1000x600</x:v>
       </x:c>
       <x:c r="N154" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O154" s="4" t="str">
-        <x:v>Data flow and stage relationships in Tülu-3 from SFT-Mix and DPO mix to RLVR.</x:v>
+        <x:v>&lt;div align="center"&lt;bFigure 44-5: Llama-3 Annealing Phase Data Composition Timeline (Curriculum Learning Schedule)&lt;/b&lt;/div.</x:v>
       </x:c>
       <x:c r="P154" s="4" t="str"/>
       <x:c r="Q154" s="4" t="str">
@@ -10589,10 +10589,10 @@
       <x:c r="S154" s="4" t="str"/>
       <x:c r="T154" s="4" t="str"/>
       <x:c r="U154" s="4" t="str">
-        <x:v>图45-3：Tülu-3 从 SFT-Mix、DPO mix 到 RLVR 的数据流与阶段关系</x:v>
+        <x:v>&lt;div align="center"&lt;b图44-5：Llama-3 退火期数据组成时间轴 (Curriculum Learning Schedule)&lt;/b&lt;/div</x:v>
       </x:c>
       <x:c r="V154" s="4" t="str">
-        <x:v>图45-3：Tülu-3 三阶段数据流与规模示意</x:v>
+        <x:v>图44-5：Llama-3 退火期数据组成时间轴 (Curriculum Learning Schedule)</x:v>
       </x:c>
     </x:row>
     <x:row r="155">
@@ -10606,28 +10606,28 @@
         <x:v>Part 13: Open-source LLM Data Engineering Recipes and Paradigms</x:v>
       </x:c>
       <x:c r="D155" s="4" t="str">
-        <x:v>Ch46</x:v>
+        <x:v>Ch45</x:v>
       </x:c>
       <x:c r="E155" s="4" t="str">
-        <x:v>Chapter 46: Reasoning Models and RL Data Engineering: R1 / QwQ Paradigm</x:v>
+        <x:v>Chapter 45: LLM Post-training Data Engineering: SFT and Preference Alignment</x:v>
       </x:c>
       <x:c r="F155" s="4" t="str">
-        <x:v>docs/en/part13/ch46_rl_reasoning_data.md</x:v>
+        <x:v>docs/en/part13/ch45_posttrain_recipes.md</x:v>
       </x:c>
       <x:c r="G155" s="4" t="n">
-        <x:v>73</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H155" s="4" t="str">
-        <x:v>46-1</x:v>
+        <x:v>45-1</x:v>
       </x:c>
       <x:c r="I155" s="4" t="str">
-        <x:v>Figure 46-1: The data feedback relationships among cold-start SFT, large-scale RL, rejection sampling, and second-round SFT</x:v>
+        <x:v>Figure 45-1: Data flow relationships among SFT, Preference Alignment, and Online Continuous Optimization</x:v>
       </x:c>
       <x:c r="J155" s="4" t="str">
-        <x:v>Figure 46-1: The four stages of the R1-style reasoning data flywheel</x:v>
+        <x:v>Figure 45-1: Schematic of the LLM Three-Stage Post-Training Pipeline</x:v>
       </x:c>
       <x:c r="K155" s="4" t="str">
-        <x:v>docs/images/part13/ch46_01_r1_reasoning_flywheel.svg</x:v>
+        <x:v>docs/images/part13/ch45_01_posttrain_three_stage_pipeline.svg</x:v>
       </x:c>
       <x:c r="L155" s="4" t="str">
         <x:v>yes</x:v>
@@ -10639,7 +10639,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O155" s="4" t="str">
-        <x:v>The data feedback relationships among cold-start SFT, large-scale RL, rejection sampling, and second-round SFT.</x:v>
+        <x:v>Data flow relationships among SFT, Preference Alignment, and Online Continuous Optimization.</x:v>
       </x:c>
       <x:c r="P155" s="4" t="str"/>
       <x:c r="Q155" s="4" t="str">
@@ -10651,10 +10651,10 @@
       <x:c r="S155" s="4" t="str"/>
       <x:c r="T155" s="4" t="str"/>
       <x:c r="U155" s="4" t="str">
-        <x:v>图46-1：冷启动 SFT、大规模 RL、拒绝采样与二轮 SFT 之间的数据回流关系</x:v>
+        <x:v>图45-1：SFT、偏好对齐与在线持续优化之间的数据流动关系</x:v>
       </x:c>
       <x:c r="V155" s="4" t="str">
-        <x:v>图46-1：R1 风格推理数据飞轮四阶段</x:v>
+        <x:v>图45-1：LLM 后训练三阶段流水线示意图</x:v>
       </x:c>
     </x:row>
     <x:row r="156">
@@ -10668,28 +10668,28 @@
         <x:v>Part 13: Open-source LLM Data Engineering Recipes and Paradigms</x:v>
       </x:c>
       <x:c r="D156" s="4" t="str">
-        <x:v>Ch46</x:v>
+        <x:v>Ch45</x:v>
       </x:c>
       <x:c r="E156" s="4" t="str">
-        <x:v>Chapter 46: Reasoning Models and RL Data Engineering: R1 / QwQ Paradigm</x:v>
+        <x:v>Chapter 45: LLM Post-training Data Engineering: SFT and Preference Alignment</x:v>
       </x:c>
       <x:c r="F156" s="4" t="str">
-        <x:v>docs/en/part13/ch46_rl_reasoning_data.md</x:v>
+        <x:v>docs/en/part13/ch45_posttrain_recipes.md</x:v>
       </x:c>
       <x:c r="G156" s="4" t="n">
-        <x:v>180</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="H156" s="4" t="str">
-        <x:v>46-2</x:v>
+        <x:v>45-2</x:v>
       </x:c>
       <x:c r="I156" s="4" t="str">
-        <x:v>Figure 46-2: The relationship among rule-based rewards, model-based rewards, and human audits</x:v>
+        <x:v>Figure 45-2: Data entry points, generation methods, and quality control checkpoints for the three SFT synthesis approaches</x:v>
       </x:c>
       <x:c r="J156" s="4" t="str">
-        <x:v>Figure 46-2: Reward signal and verifier architecture for reasoning data</x:v>
+        <x:v>Figure 45-2: Pipeline Comparison of the Three SFT Synthesis Schools: Self-Instruct, Evol-Instruct, and Magpie</x:v>
       </x:c>
       <x:c r="K156" s="4" t="str">
-        <x:v>docs/images/part13/ch46_02_reward_verifier_architecture.svg</x:v>
+        <x:v>docs/images/part13/ch45_02_sft_synthesis_pipelines.svg</x:v>
       </x:c>
       <x:c r="L156" s="4" t="str">
         <x:v>yes</x:v>
@@ -10701,7 +10701,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O156" s="4" t="str">
-        <x:v>The relationship among rule-based rewards, model-based rewards, and human audits.</x:v>
+        <x:v>Data entry points, generation methods, and quality control checkpoints for the three SFT synthesis approaches.</x:v>
       </x:c>
       <x:c r="P156" s="4" t="str"/>
       <x:c r="Q156" s="4" t="str">
@@ -10713,10 +10713,10 @@
       <x:c r="S156" s="4" t="str"/>
       <x:c r="T156" s="4" t="str"/>
       <x:c r="U156" s="4" t="str">
-        <x:v>图46-2：rule-based reward、model-based reward 与人工审计之间的关系</x:v>
+        <x:v>图45-2：三类 SFT 合成路线的数据入口、生成方式与质检位置</x:v>
       </x:c>
       <x:c r="V156" s="4" t="str">
-        <x:v>图46-2：推理数据奖励信号与验证器结构</x:v>
+        <x:v>图45-2：Self-Instruct、Evol-Instruct 与 Magpie 三流派 pipeline 对比</x:v>
       </x:c>
     </x:row>
     <x:row r="157">
@@ -10730,28 +10730,28 @@
         <x:v>Part 13: Open-source LLM Data Engineering Recipes and Paradigms</x:v>
       </x:c>
       <x:c r="D157" s="4" t="str">
-        <x:v>Ch46</x:v>
+        <x:v>Ch45</x:v>
       </x:c>
       <x:c r="E157" s="4" t="str">
-        <x:v>Chapter 46: Reasoning Models and RL Data Engineering: R1 / QwQ Paradigm</x:v>
+        <x:v>Chapter 45: LLM Post-training Data Engineering: SFT and Preference Alignment</x:v>
       </x:c>
       <x:c r="F157" s="4" t="str">
-        <x:v>docs/en/part13/ch46_rl_reasoning_data.md</x:v>
+        <x:v>docs/en/part13/ch45_posttrain_recipes.md</x:v>
       </x:c>
       <x:c r="G157" s="4" t="n">
-        <x:v>225</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="H157" s="4" t="str">
-        <x:v>46-3</x:v>
+        <x:v>45-3</x:v>
       </x:c>
       <x:c r="I157" s="4" t="str">
-        <x:v>Figure 46-3: A cross-section of a Long-CoT data sample illustrating three reasoning trajectory patterns: Reflection, Verification, and Backtrack</x:v>
+        <x:v>Figure 45-3: Data flow and stage relationships in Tülu-3 from SFT-Mix and DPO mix to RLVR</x:v>
       </x:c>
       <x:c r="J157" s="4" t="str">
-        <x:v>Figure 46-3: Long-CoT data sample cross-section</x:v>
+        <x:v>Figure 45-3: Tülu-3 Three-Stage Data Flow and Scale Schematic</x:v>
       </x:c>
       <x:c r="K157" s="4" t="str">
-        <x:v>docs/images/part13/ch46_03_long_cot_trace_patterns.svg</x:v>
+        <x:v>docs/images/part13/ch45_03_tulu3_posttrain_flow.svg</x:v>
       </x:c>
       <x:c r="L157" s="4" t="str">
         <x:v>yes</x:v>
@@ -10763,7 +10763,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O157" s="4" t="str">
-        <x:v>A cross-section of a Long-CoT data sample illustrating three reasoning trajectory patterns: Reflection, Verification, and Backtrack.</x:v>
+        <x:v>Data flow and stage relationships in Tülu-3 from SFT-Mix and DPO mix to RLVR.</x:v>
       </x:c>
       <x:c r="P157" s="4" t="str"/>
       <x:c r="Q157" s="4" t="str">
@@ -10775,10 +10775,10 @@
       <x:c r="S157" s="4" t="str"/>
       <x:c r="T157" s="4" t="str"/>
       <x:c r="U157" s="4" t="str">
-        <x:v>图46-3：Long-CoT 数据样例剖面，展示 Reflection、Verification 与 Backtrack 三种推理轨迹模式</x:v>
+        <x:v>图45-3：Tülu-3 从 SFT-Mix、DPO mix 到 RLVR 的数据流与阶段关系</x:v>
       </x:c>
       <x:c r="V157" s="4" t="str">
-        <x:v>图46-3：Long-CoT 数据样例剖面</x:v>
+        <x:v>图45-3：Tülu-3 三阶段数据流与规模示意</x:v>
       </x:c>
     </x:row>
     <x:row r="158">
@@ -10792,40 +10792,40 @@
         <x:v>Part 13: Open-source LLM Data Engineering Recipes and Paradigms</x:v>
       </x:c>
       <x:c r="D158" s="4" t="str">
-        <x:v>Ch47</x:v>
+        <x:v>Ch46</x:v>
       </x:c>
       <x:c r="E158" s="4" t="str">
-        <x:v>Chapter 47: VLM Data Recipes from Pre-training to Visual Alignment</x:v>
+        <x:v>Chapter 46: Reasoning Models and RL Data Engineering: R1 / QwQ Paradigm</x:v>
       </x:c>
       <x:c r="F158" s="4" t="str">
-        <x:v>docs/en/part13/ch47_vlm_data_recipes.md</x:v>
+        <x:v>docs/en/part13/ch46_rl_reasoning_data.md</x:v>
       </x:c>
       <x:c r="G158" s="4" t="n">
-        <x:v>37</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H158" s="4" t="str">
-        <x:v>47-1</x:v>
+        <x:v>46-1</x:v>
       </x:c>
       <x:c r="I158" s="4" t="str">
-        <x:v>&lt;div align="center"&lt;bFigure 47-1: Multimodal Data Engineering Panorama (adapted from Chapter 8 base figure)&lt;/b&lt;/div</x:v>
+        <x:v>Figure 46-1: The data feedback relationships among cold-start SFT, large-scale RL, rejection sampling, and second-round SFT</x:v>
       </x:c>
       <x:c r="J158" s="4" t="str">
-        <x:v>Figure 47-1: Multimodal Data Engineering Panorama</x:v>
+        <x:v>Figure 46-1: The four stages of the R1-style reasoning data flywheel</x:v>
       </x:c>
       <x:c r="K158" s="4" t="str">
-        <x:v>docs/images/part13/ch47_01_multimodal_data_panorama.png</x:v>
+        <x:v>docs/images/part13/ch46_01_r1_reasoning_flywheel.svg</x:v>
       </x:c>
       <x:c r="L158" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M158" s="4" t="str">
-        <x:v>1024x1024</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N158" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O158" s="4" t="str">
-        <x:v>&lt;div align="center"&lt;bFigure 47-1: Multimodal Data Engineering Panorama (adapted from Chapter 8 base figure)&lt;/b&lt;/div.</x:v>
+        <x:v>The data feedback relationships among cold-start SFT, large-scale RL, rejection sampling, and second-round SFT.</x:v>
       </x:c>
       <x:c r="P158" s="4" t="str"/>
       <x:c r="Q158" s="4" t="str">
@@ -10837,10 +10837,10 @@
       <x:c r="S158" s="4" t="str"/>
       <x:c r="T158" s="4" t="str"/>
       <x:c r="U158" s="4" t="str">
-        <x:v>&lt;div align="center"&lt;b图47-1：多模态数据工程全景图（改绘自第8章基础图）&lt;/b&lt;/div</x:v>
+        <x:v>图46-1：冷启动 SFT、大规模 RL、拒绝采样与二轮 SFT 之间的数据回流关系</x:v>
       </x:c>
       <x:c r="V158" s="4" t="str">
-        <x:v>图47-1：多模态数据工程全景图</x:v>
+        <x:v>图46-1：R1 风格推理数据飞轮四阶段</x:v>
       </x:c>
     </x:row>
     <x:row r="159">
@@ -10854,44 +10854,42 @@
         <x:v>Part 13: Open-source LLM Data Engineering Recipes and Paradigms</x:v>
       </x:c>
       <x:c r="D159" s="4" t="str">
-        <x:v>Ch47</x:v>
+        <x:v>Ch46</x:v>
       </x:c>
       <x:c r="E159" s="4" t="str">
-        <x:v>Chapter 47: VLM Data Recipes from Pre-training to Visual Alignment</x:v>
+        <x:v>Chapter 46: Reasoning Models and RL Data Engineering: R1 / QwQ Paradigm</x:v>
       </x:c>
       <x:c r="F159" s="4" t="str">
-        <x:v>docs/en/part13/ch47_vlm_data_recipes.md</x:v>
+        <x:v>docs/en/part13/ch46_rl_reasoning_data.md</x:v>
       </x:c>
       <x:c r="G159" s="4" t="n">
-        <x:v>47</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="H159" s="4" t="str">
-        <x:v>47-2</x:v>
+        <x:v>46-2</x:v>
       </x:c>
       <x:c r="I159" s="4" t="str">
-        <x:v>&lt;div align="center"&lt;bFigure 47-2: VLM Three-Stage Data Pipeline&lt;/b&lt;/div</x:v>
+        <x:v>Figure 46-2: The relationship among rule-based rewards, model-based rewards, and human audits</x:v>
       </x:c>
       <x:c r="J159" s="4" t="str">
-        <x:v>Figure 47-2: VLM Three-Stage Data Engineering Pipeline</x:v>
+        <x:v>Figure 46-2: Reward signal and verifier architecture for reasoning data</x:v>
       </x:c>
       <x:c r="K159" s="4" t="str">
-        <x:v>docs/images/part13/ch47_02_vlm_three_stages_en.svg</x:v>
+        <x:v>docs/images/part13/ch46_02_reward_verifier_architecture.svg</x:v>
       </x:c>
       <x:c r="L159" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M159" s="4" t="str">
-        <x:v>900x660</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N159" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O159" s="4" t="str">
-        <x:v>&lt;div align="center"&lt;bFigure 47-2: VLM Three-Stage Data Pipeline&lt;/b&lt;/div.</x:v>
-      </x:c>
-      <x:c r="P159" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Chapter 47: VLM Data Recipes from Pre-training to Visual Alignment; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>The relationship among rule-based rewards, model-based rewards, and human audits.</x:v>
+      </x:c>
+      <x:c r="P159" s="4" t="str"/>
       <x:c r="Q159" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -10901,10 +10899,10 @@
       <x:c r="S159" s="4" t="str"/>
       <x:c r="T159" s="4" t="str"/>
       <x:c r="U159" s="4" t="str">
-        <x:v>&lt;div align="center"&lt;b图47-2：VLM 数据三阶段流水线 (3-Stage VLM Data Pipeline)&lt;/b&lt;/div</x:v>
+        <x:v>图46-2：rule-based reward、model-based reward 与人工审计之间的关系</x:v>
       </x:c>
       <x:c r="V159" s="4" t="str">
-        <x:v>图47-2：VLM 数据三阶段流水线 (3-Stage VLM Data Engineering Pipeline)</x:v>
+        <x:v>图46-2：推理数据奖励信号与验证器结构</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
@@ -10918,44 +10916,42 @@
         <x:v>Part 13: Open-source LLM Data Engineering Recipes and Paradigms</x:v>
       </x:c>
       <x:c r="D160" s="4" t="str">
-        <x:v>Ch47</x:v>
+        <x:v>Ch46</x:v>
       </x:c>
       <x:c r="E160" s="4" t="str">
-        <x:v>Chapter 47: VLM Data Recipes from Pre-training to Visual Alignment</x:v>
+        <x:v>Chapter 46: Reasoning Models and RL Data Engineering: R1 / QwQ Paradigm</x:v>
       </x:c>
       <x:c r="F160" s="4" t="str">
-        <x:v>docs/en/part13/ch47_vlm_data_recipes.md</x:v>
+        <x:v>docs/en/part13/ch46_rl_reasoning_data.md</x:v>
       </x:c>
       <x:c r="G160" s="4" t="n">
-        <x:v>114</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="H160" s="4" t="str">
-        <x:v>47-3</x:v>
+        <x:v>46-3</x:v>
       </x:c>
       <x:c r="I160" s="4" t="str">
-        <x:v>&lt;div align="center"&lt;bFigure 47-3: Native vs. Dynamic Resolution Data Pipeline Comparison&lt;/b&lt;/div</x:v>
+        <x:v>Figure 46-3: A cross-section of a Long-CoT data sample illustrating three reasoning trajectory patterns: Reflection, Verification, and Backtrack</x:v>
       </x:c>
       <x:c r="J160" s="4" t="str">
-        <x:v>Figure 47-3: Native vs. Dynamic Resolution Data Pipeline Comparison</x:v>
+        <x:v>Figure 46-3: Long-CoT data sample cross-section</x:v>
       </x:c>
       <x:c r="K160" s="4" t="str">
-        <x:v>docs/images/part13/ch47_03_resolution_handling_en.svg</x:v>
+        <x:v>docs/images/part13/ch46_03_long_cot_trace_patterns.svg</x:v>
       </x:c>
       <x:c r="L160" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M160" s="4" t="str">
-        <x:v>800x750</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N160" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O160" s="4" t="str">
-        <x:v>&lt;div align="center"&lt;bFigure 47-3: Native vs. Dynamic Resolution Data Pipeline Comparison&lt;/b&lt;/div.</x:v>
-      </x:c>
-      <x:c r="P160" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Chapter 47: VLM Data Recipes from Pre-training to Visual Alignment; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>A cross-section of a Long-CoT data sample illustrating three reasoning trajectory patterns: Reflection, Verification, and Backtrack.</x:v>
+      </x:c>
+      <x:c r="P160" s="4" t="str"/>
       <x:c r="Q160" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -10965,10 +10961,10 @@
       <x:c r="S160" s="4" t="str"/>
       <x:c r="T160" s="4" t="str"/>
       <x:c r="U160" s="4" t="str">
-        <x:v>&lt;div align="center"&lt;b图47-3：Native vs Dynamic Resolution 数据 pipeline 对比&lt;/b&lt;/div</x:v>
+        <x:v>图46-3：Long-CoT 数据样例剖面，展示 Reflection、Verification 与 Backtrack 三种推理轨迹模式</x:v>
       </x:c>
       <x:c r="V160" s="4" t="str">
-        <x:v>图47-3：Native vs Dynamic Resolution 数据 pipeline 对比 (Resolution Handling)</x:v>
+        <x:v>图46-3：Long-CoT 数据样例剖面</x:v>
       </x:c>
     </x:row>
     <x:row r="161">
@@ -10991,35 +10987,33 @@
         <x:v>docs/en/part13/ch47_vlm_data_recipes.md</x:v>
       </x:c>
       <x:c r="G161" s="4" t="n">
-        <x:v>145</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="H161" s="4" t="str">
-        <x:v>47-4</x:v>
+        <x:v>47-1</x:v>
       </x:c>
       <x:c r="I161" s="4" t="str">
-        <x:v>&lt;div align="center"&lt;bFigure 47-4: Multimodal Instruction Synthesis Pipeline&lt;/b&lt;/div</x:v>
+        <x:v>&lt;div align="center"&lt;bFigure 47-1: Multimodal Data Engineering Panorama (adapted from Chapter 8 base figure)&lt;/b&lt;/div</x:v>
       </x:c>
       <x:c r="J161" s="4" t="str">
-        <x:v>Figure 47-4: Multimodal Instruction Synthesis Pipeline</x:v>
+        <x:v>Figure 47-1: Multimodal Data Engineering Panorama</x:v>
       </x:c>
       <x:c r="K161" s="4" t="str">
-        <x:v>docs/images/part13/ch47_04_instruction_synthesis_en.svg</x:v>
+        <x:v>docs/images/part13/ch47_01_multimodal_data_panorama.png</x:v>
       </x:c>
       <x:c r="L161" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M161" s="4" t="str">
-        <x:v>1000x800</x:v>
+        <x:v>1024x1024</x:v>
       </x:c>
       <x:c r="N161" s="4" t="str">
-        <x:v>svg</x:v>
+        <x:v>png</x:v>
       </x:c>
       <x:c r="O161" s="4" t="str">
-        <x:v>&lt;div align="center"&lt;bFigure 47-4: Multimodal Instruction Synthesis Pipeline&lt;/b&lt;/div.</x:v>
-      </x:c>
-      <x:c r="P161" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Chapter 47: VLM Data Recipes from Pre-training to Visual Alignment; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>&lt;div align="center"&lt;bFigure 47-1: Multimodal Data Engineering Panorama (adapted from Chapter 8 base figure)&lt;/b&lt;/div.</x:v>
+      </x:c>
+      <x:c r="P161" s="4" t="str"/>
       <x:c r="Q161" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -11029,10 +11023,10 @@
       <x:c r="S161" s="4" t="str"/>
       <x:c r="T161" s="4" t="str"/>
       <x:c r="U161" s="4" t="str">
-        <x:v>&lt;div align="center"&lt;b图47-4：多模态指令合成 pipeline&lt;/b&lt;/div</x:v>
+        <x:v>&lt;div align="center"&lt;b图47-1：多模态数据工程全景图（改绘自第8章基础图）&lt;/b&lt;/div</x:v>
       </x:c>
       <x:c r="V161" s="4" t="str">
-        <x:v>图47-4：多模态指令合成 pipeline (Multi-modal Instruction Synthesis)</x:v>
+        <x:v>图47-1：多模态数据工程全景图</x:v>
       </x:c>
     </x:row>
     <x:row r="162">
@@ -11046,43 +11040,43 @@
         <x:v>Part 13: Open-source LLM Data Engineering Recipes and Paradigms</x:v>
       </x:c>
       <x:c r="D162" s="4" t="str">
-        <x:v>Ch48</x:v>
+        <x:v>Ch47</x:v>
       </x:c>
       <x:c r="E162" s="4" t="str">
-        <x:v>Chapter 48: Multimodal Generative Model Data Engineering: T2I and T2V Pipelines</x:v>
+        <x:v>Chapter 47: VLM Data Recipes from Pre-training to Visual Alignment</x:v>
       </x:c>
       <x:c r="F162" s="4" t="str">
-        <x:v>docs/en/part13/ch48_t2i_t2v.md</x:v>
+        <x:v>docs/en/part13/ch47_vlm_data_recipes.md</x:v>
       </x:c>
       <x:c r="G162" s="4" t="n">
-        <x:v>157</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H162" s="4" t="str">
-        <x:v>48-1</x:v>
+        <x:v>47-2</x:v>
       </x:c>
       <x:c r="I162" s="4" t="str">
-        <x:v>Figure 48-1: T2I Data Pipeline</x:v>
+        <x:v>&lt;div align="center"&lt;bFigure 47-2: VLM Three-Stage Data Pipeline&lt;/b&lt;/div</x:v>
       </x:c>
       <x:c r="J162" s="4" t="str">
-        <x:v>Figure 48-1: T2I Data Pipeline</x:v>
+        <x:v>Figure 47-2: VLM Three-Stage Data Engineering Pipeline</x:v>
       </x:c>
       <x:c r="K162" s="4" t="str">
-        <x:v>docs/images/part13/ch48_01_t2i_data_pipeline.svg</x:v>
+        <x:v>docs/images/part13/ch47_02_vlm_three_stages_en.svg</x:v>
       </x:c>
       <x:c r="L162" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M162" s="4" t="str">
-        <x:v>4349x2413</x:v>
+        <x:v>900x660</x:v>
       </x:c>
       <x:c r="N162" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O162" s="4" t="str">
-        <x:v>T2I Data Pipeline. More sophisticated systems additionally route samples by data source, aesthetic score, caption type, safety tier, presence of text, presence of human subjects, and presence of complex multi-subject scenes.</x:v>
+        <x:v>&lt;div align="center"&lt;bFigure 47-2: VLM Three-Stage Data Pipeline&lt;/b&lt;/div.</x:v>
       </x:c>
       <x:c r="P162" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Chapter 48: Multimodal Generative Model Data Engineering: T2I and T2V Pipelines; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+        <x:v>Review against the figure and surrounding text in Chapter 47: VLM Data Recipes from Pre-training to Visual Alignment; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
       </x:c>
       <x:c r="Q162" s="4" t="str">
         <x:v>no</x:v>
@@ -11093,10 +11087,10 @@
       <x:c r="S162" s="4" t="str"/>
       <x:c r="T162" s="4" t="str"/>
       <x:c r="U162" s="4" t="str">
-        <x:v>图48-1：T2I 数据流水线</x:v>
+        <x:v>&lt;div align="center"&lt;b图47-2：VLM 数据三阶段流水线 (3-Stage VLM Data Pipeline)&lt;/b&lt;/div</x:v>
       </x:c>
       <x:c r="V162" s="4" t="str">
-        <x:v>图48-1：T2I 数据流水线</x:v>
+        <x:v>图47-2：VLM 数据三阶段流水线 (3-Stage VLM Data Engineering Pipeline)</x:v>
       </x:c>
     </x:row>
     <x:row r="163">
@@ -11110,43 +11104,43 @@
         <x:v>Part 13: Open-source LLM Data Engineering Recipes and Paradigms</x:v>
       </x:c>
       <x:c r="D163" s="4" t="str">
-        <x:v>Ch48</x:v>
+        <x:v>Ch47</x:v>
       </x:c>
       <x:c r="E163" s="4" t="str">
-        <x:v>Chapter 48: Multimodal Generative Model Data Engineering: T2I and T2V Pipelines</x:v>
+        <x:v>Chapter 47: VLM Data Recipes from Pre-training to Visual Alignment</x:v>
       </x:c>
       <x:c r="F163" s="4" t="str">
-        <x:v>docs/en/part13/ch48_t2i_t2v.md</x:v>
+        <x:v>docs/en/part13/ch47_vlm_data_recipes.md</x:v>
       </x:c>
       <x:c r="G163" s="4" t="n">
-        <x:v>266</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="H163" s="4" t="str">
-        <x:v>48-2</x:v>
+        <x:v>47-3</x:v>
       </x:c>
       <x:c r="I163" s="4" t="str">
-        <x:v>Figure 48-2: T2V Data Pipeline</x:v>
+        <x:v>&lt;div align="center"&lt;bFigure 47-3: Native vs. Dynamic Resolution Data Pipeline Comparison&lt;/b&lt;/div</x:v>
       </x:c>
       <x:c r="J163" s="4" t="str">
-        <x:v>Figure 48-2: T2V Data Pipeline</x:v>
+        <x:v>Figure 47-3: Native vs. Dynamic Resolution Data Pipeline Comparison</x:v>
       </x:c>
       <x:c r="K163" s="4" t="str">
-        <x:v>docs/images/part13/ch48_02_t2v_data_pipeline.svg</x:v>
+        <x:v>docs/images/part13/ch47_03_resolution_handling_en.svg</x:v>
       </x:c>
       <x:c r="L163" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M163" s="4" t="str">
-        <x:v>5267x1397</x:v>
+        <x:v>800x750</x:v>
       </x:c>
       <x:c r="N163" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O163" s="4" t="str">
-        <x:v>T2V Data Pipeline. This reveals that a T2V data pipeline is not a linear "clean then output" process, but a progressively converging training organization system.</x:v>
+        <x:v>&lt;div align="center"&lt;bFigure 47-3: Native vs. Dynamic Resolution Data Pipeline Comparison&lt;/b&lt;/div.</x:v>
       </x:c>
       <x:c r="P163" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Chapter 48: Multimodal Generative Model Data Engineering: T2I and T2V Pipelines; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+        <x:v>Review against the figure and surrounding text in Chapter 47: VLM Data Recipes from Pre-training to Visual Alignment; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
       </x:c>
       <x:c r="Q163" s="4" t="str">
         <x:v>no</x:v>
@@ -11157,10 +11151,10 @@
       <x:c r="S163" s="4" t="str"/>
       <x:c r="T163" s="4" t="str"/>
       <x:c r="U163" s="4" t="str">
-        <x:v>图48-2：T2V 数据流水线</x:v>
+        <x:v>&lt;div align="center"&lt;b图47-3：Native vs Dynamic Resolution 数据 pipeline 对比&lt;/b&lt;/div</x:v>
       </x:c>
       <x:c r="V163" s="4" t="str">
-        <x:v>图48-2：T2V 数据流水线</x:v>
+        <x:v>图47-3：Native vs Dynamic Resolution 数据 pipeline 对比 (Resolution Handling)</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
@@ -11174,43 +11168,43 @@
         <x:v>Part 13: Open-source LLM Data Engineering Recipes and Paradigms</x:v>
       </x:c>
       <x:c r="D164" s="4" t="str">
-        <x:v>Ch48</x:v>
+        <x:v>Ch47</x:v>
       </x:c>
       <x:c r="E164" s="4" t="str">
-        <x:v>Chapter 48: Multimodal Generative Model Data Engineering: T2I and T2V Pipelines</x:v>
+        <x:v>Chapter 47: VLM Data Recipes from Pre-training to Visual Alignment</x:v>
       </x:c>
       <x:c r="F164" s="4" t="str">
-        <x:v>docs/en/part13/ch48_t2i_t2v.md</x:v>
+        <x:v>docs/en/part13/ch47_vlm_data_recipes.md</x:v>
       </x:c>
       <x:c r="G164" s="4" t="n">
-        <x:v>371</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="H164" s="4" t="str">
-        <x:v>48-3</x:v>
+        <x:v>47-4</x:v>
       </x:c>
       <x:c r="I164" s="4" t="str">
-        <x:v>Figure 48-3: Multi-Tier Aesthetic / Copyright / Safety Filtering Architecture</x:v>
+        <x:v>&lt;div align="center"&lt;bFigure 47-4: Multimodal Instruction Synthesis Pipeline&lt;/b&lt;/div</x:v>
       </x:c>
       <x:c r="J164" s="4" t="str">
-        <x:v>Figure 48-3: Multi-Tier Aesthetic / Copyright / Safety Filtering Architecture</x:v>
+        <x:v>Figure 47-4: Multimodal Instruction Synthesis Pipeline</x:v>
       </x:c>
       <x:c r="K164" s="4" t="str">
-        <x:v>docs/images/part13/ch48_03_multistage_filtering_architecture.svg</x:v>
+        <x:v>docs/images/part13/ch47_04_instruction_synthesis_en.svg</x:v>
       </x:c>
       <x:c r="L164" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M164" s="4" t="str">
-        <x:v>3193x3428</x:v>
+        <x:v>1000x800</x:v>
       </x:c>
       <x:c r="N164" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O164" s="4" t="str">
-        <x:v>Multi-Tier Aesthetic / Copyright / Safety Filtering Architecture.</x:v>
+        <x:v>&lt;div align="center"&lt;bFigure 47-4: Multimodal Instruction Synthesis Pipeline&lt;/b&lt;/div.</x:v>
       </x:c>
       <x:c r="P164" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Chapter 48: Multimodal Generative Model Data Engineering: T2I and T2V Pipelines; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+        <x:v>Review against the figure and surrounding text in Chapter 47: VLM Data Recipes from Pre-training to Visual Alignment; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
       </x:c>
       <x:c r="Q164" s="4" t="str">
         <x:v>no</x:v>
@@ -11221,10 +11215,10 @@
       <x:c r="S164" s="4" t="str"/>
       <x:c r="T164" s="4" t="str"/>
       <x:c r="U164" s="4" t="str">
-        <x:v>图48-3：美学/版权/安全多级过滤架构</x:v>
+        <x:v>&lt;div align="center"&lt;b图47-4：多模态指令合成 pipeline&lt;/b&lt;/div</x:v>
       </x:c>
       <x:c r="V164" s="4" t="str">
-        <x:v>图48-3：美学/版权/安全多级过滤架构</x:v>
+        <x:v>图47-4：多模态指令合成 pipeline (Multi-modal Instruction Synthesis)</x:v>
       </x:c>
     </x:row>
     <x:row r="165">
@@ -11235,46 +11229,46 @@
         <x:v>en</x:v>
       </x:c>
       <x:c r="C165" s="4" t="str">
-        <x:v>Part 14: Practical Projects</x:v>
+        <x:v>Part 13: Open-source LLM Data Engineering Recipes and Paradigms</x:v>
       </x:c>
       <x:c r="D165" s="4" t="str">
-        <x:v>P01</x:v>
+        <x:v>Ch48</x:v>
       </x:c>
       <x:c r="E165" s="4" t="str">
-        <x:v>Project 1: Building a Distributed Mini-C4 Data Pipeline with Ray</x:v>
+        <x:v>Chapter 48: Multimodal Generative Model Data Engineering: T2I and T2V Pipelines</x:v>
       </x:c>
       <x:c r="F165" s="4" t="str">
-        <x:v>docs/en/part14/p01_mini_c4.md</x:v>
+        <x:v>docs/en/part13/ch48_t2i_t2v.md</x:v>
       </x:c>
       <x:c r="G165" s="4" t="n">
-        <x:v>130</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="H165" s="4" t="str">
-        <x:v>P01-1</x:v>
+        <x:v>48-1</x:v>
       </x:c>
       <x:c r="I165" s="4" t="str">
-        <x:v>Figure P01-1: Mini-C4 Data Pipeline Overview</x:v>
+        <x:v>Figure 48-1: T2I Data Pipeline</x:v>
       </x:c>
       <x:c r="J165" s="4" t="str">
-        <x:v>Figure P01-1</x:v>
+        <x:v>Figure 48-1: T2I Data Pipeline</x:v>
       </x:c>
       <x:c r="K165" s="4" t="str">
-        <x:v>docs/images/part14/p01/p01_01_mini_c4_pipeline_overview.svg</x:v>
+        <x:v>docs/images/part13/ch48_01_t2i_data_pipeline.svg</x:v>
       </x:c>
       <x:c r="L165" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M165" s="4" t="str">
-        <x:v>900x355</x:v>
+        <x:v>4349x2413</x:v>
       </x:c>
       <x:c r="N165" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O165" s="4" t="str">
-        <x:v>Mini-C4 Data Pipeline Overview.</x:v>
+        <x:v>T2I Data Pipeline. More sophisticated systems additionally route samples by data source, aesthetic score, caption type, safety tier, presence of text, presence of human subjects, and presence of complex multi-subject scenes.</x:v>
       </x:c>
       <x:c r="P165" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Project 1: Building a Distributed Mini-C4 Data Pipeline with Ray; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+        <x:v>Review against the figure and surrounding text in Chapter 48: Multimodal Generative Model Data Engineering: T2I and T2V Pipelines; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
       </x:c>
       <x:c r="Q165" s="4" t="str">
         <x:v>no</x:v>
@@ -11285,10 +11279,10 @@
       <x:c r="S165" s="4" t="str"/>
       <x:c r="T165" s="4" t="str"/>
       <x:c r="U165" s="4" t="str">
-        <x:v>Figure P01-1：Mini-C4 数据流水线总览</x:v>
+        <x:v>图48-1：T2I 数据流水线</x:v>
       </x:c>
       <x:c r="V165" s="4" t="str">
-        <x:v>图 P01-1</x:v>
+        <x:v>图48-1：T2I 数据流水线</x:v>
       </x:c>
     </x:row>
     <x:row r="166">
@@ -11299,45 +11293,47 @@
         <x:v>en</x:v>
       </x:c>
       <x:c r="C166" s="4" t="str">
-        <x:v>Part 14: Practical Projects</x:v>
+        <x:v>Part 13: Open-source LLM Data Engineering Recipes and Paradigms</x:v>
       </x:c>
       <x:c r="D166" s="4" t="str">
-        <x:v>P01</x:v>
+        <x:v>Ch48</x:v>
       </x:c>
       <x:c r="E166" s="4" t="str">
-        <x:v>Project 1: Building a Distributed Mini-C4 Data Pipeline with Ray</x:v>
+        <x:v>Chapter 48: Multimodal Generative Model Data Engineering: T2I and T2V Pipelines</x:v>
       </x:c>
       <x:c r="F166" s="4" t="str">
-        <x:v>docs/en/part14/p01_mini_c4.md</x:v>
+        <x:v>docs/en/part13/ch48_t2i_t2v.md</x:v>
       </x:c>
       <x:c r="G166" s="4" t="n">
-        <x:v>228</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="H166" s="4" t="str">
-        <x:v>P01-2</x:v>
+        <x:v>48-2</x:v>
       </x:c>
       <x:c r="I166" s="4" t="str">
-        <x:v>Figure P01-2: Parsing Path from WARC to Body Text</x:v>
+        <x:v>Figure 48-2: T2V Data Pipeline</x:v>
       </x:c>
       <x:c r="J166" s="4" t="str">
-        <x:v>Figure P01-2</x:v>
+        <x:v>Figure 48-2: T2V Data Pipeline</x:v>
       </x:c>
       <x:c r="K166" s="4" t="str">
-        <x:v>docs/images/part14/p01/p01_02_warc_to_text.svg</x:v>
+        <x:v>docs/images/part13/ch48_02_t2v_data_pipeline.svg</x:v>
       </x:c>
       <x:c r="L166" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M166" s="4" t="str">
-        <x:v>900x503</x:v>
+        <x:v>5267x1397</x:v>
       </x:c>
       <x:c r="N166" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O166" s="4" t="str">
-        <x:v>Parsing Path from WARC to Body Text.</x:v>
-      </x:c>
-      <x:c r="P166" s="4" t="str"/>
+        <x:v>T2V Data Pipeline. This reveals that a T2V data pipeline is not a linear "clean then output" process, but a progressively converging training organization system.</x:v>
+      </x:c>
+      <x:c r="P166" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Chapter 48: Multimodal Generative Model Data Engineering: T2I and T2V Pipelines; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q166" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -11347,10 +11343,10 @@
       <x:c r="S166" s="4" t="str"/>
       <x:c r="T166" s="4" t="str"/>
       <x:c r="U166" s="4" t="str">
-        <x:v>Figure P01-2：WARC 到正文文本的解析路径</x:v>
+        <x:v>图48-2：T2V 数据流水线</x:v>
       </x:c>
       <x:c r="V166" s="4" t="str">
-        <x:v>图 P01-2</x:v>
+        <x:v>图48-2：T2V 数据流水线</x:v>
       </x:c>
     </x:row>
     <x:row r="167">
@@ -11361,45 +11357,47 @@
         <x:v>en</x:v>
       </x:c>
       <x:c r="C167" s="4" t="str">
-        <x:v>Part 14: Practical Projects</x:v>
+        <x:v>Part 13: Open-source LLM Data Engineering Recipes and Paradigms</x:v>
       </x:c>
       <x:c r="D167" s="4" t="str">
-        <x:v>P01</x:v>
+        <x:v>Ch48</x:v>
       </x:c>
       <x:c r="E167" s="4" t="str">
-        <x:v>Project 1: Building a Distributed Mini-C4 Data Pipeline with Ray</x:v>
+        <x:v>Chapter 48: Multimodal Generative Model Data Engineering: T2I and T2V Pipelines</x:v>
       </x:c>
       <x:c r="F167" s="4" t="str">
-        <x:v>docs/en/part14/p01_mini_c4.md</x:v>
+        <x:v>docs/en/part13/ch48_t2i_t2v.md</x:v>
       </x:c>
       <x:c r="G167" s="4" t="n">
-        <x:v>296</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="H167" s="4" t="str">
-        <x:v>P01-3</x:v>
+        <x:v>48-3</x:v>
       </x:c>
       <x:c r="I167" s="4" t="str">
-        <x:v>Figure P01-3: Heuristic Cleaning Rules Illustration</x:v>
+        <x:v>Figure 48-3: Multi-Tier Aesthetic / Copyright / Safety Filtering Architecture</x:v>
       </x:c>
       <x:c r="J167" s="4" t="str">
-        <x:v>Figure P01-3</x:v>
+        <x:v>Figure 48-3: Multi-Tier Aesthetic / Copyright / Safety Filtering Architecture</x:v>
       </x:c>
       <x:c r="K167" s="4" t="str">
-        <x:v>docs/images/part14/p01/p01_03_cleaning_rules.svg</x:v>
+        <x:v>docs/images/part13/ch48_03_multistage_filtering_architecture.svg</x:v>
       </x:c>
       <x:c r="L167" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M167" s="4" t="str">
-        <x:v>900x672</x:v>
+        <x:v>3193x3428</x:v>
       </x:c>
       <x:c r="N167" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O167" s="4" t="str">
-        <x:v>Heuristic Cleaning Rules Illustration.</x:v>
-      </x:c>
-      <x:c r="P167" s="4" t="str"/>
+        <x:v>Multi-Tier Aesthetic / Copyright / Safety Filtering Architecture.</x:v>
+      </x:c>
+      <x:c r="P167" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Chapter 48: Multimodal Generative Model Data Engineering: T2I and T2V Pipelines; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q167" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -11409,10 +11407,10 @@
       <x:c r="S167" s="4" t="str"/>
       <x:c r="T167" s="4" t="str"/>
       <x:c r="U167" s="4" t="str">
-        <x:v>Figure P01-3：启发式清洗规则示意</x:v>
+        <x:v>图48-3：美学/版权/安全多级过滤架构</x:v>
       </x:c>
       <x:c r="V167" s="4" t="str">
-        <x:v>图 P01-3</x:v>
+        <x:v>图48-3：美学/版权/安全多级过滤架构</x:v>
       </x:c>
     </x:row>
     <x:row r="168">
@@ -11435,33 +11433,35 @@
         <x:v>docs/en/part14/p01_mini_c4.md</x:v>
       </x:c>
       <x:c r="G168" s="4" t="n">
-        <x:v>385</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="H168" s="4" t="str">
-        <x:v>P01-4</x:v>
+        <x:v>P01-1</x:v>
       </x:c>
       <x:c r="I168" s="4" t="str">
-        <x:v>Figure P01-4: MinHash + LSH Deduplication Approach</x:v>
+        <x:v>Figure P01-1: Mini-C4 Data Pipeline Overview</x:v>
       </x:c>
       <x:c r="J168" s="4" t="str">
-        <x:v>Figure P01-4</x:v>
+        <x:v>Figure P01-1</x:v>
       </x:c>
       <x:c r="K168" s="4" t="str">
-        <x:v>docs/images/part14/p01/p01_04_dedup_minhash_lsh.svg</x:v>
+        <x:v>docs/images/part14/p01/p01_01_mini_c4_pipeline_overview.svg</x:v>
       </x:c>
       <x:c r="L168" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M168" s="4" t="str">
-        <x:v>900x503</x:v>
+        <x:v>900x355</x:v>
       </x:c>
       <x:c r="N168" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O168" s="4" t="str">
-        <x:v>MinHash + LSH Deduplication Approach.</x:v>
-      </x:c>
-      <x:c r="P168" s="4" t="str"/>
+        <x:v>Mini-C4 Data Pipeline Overview.</x:v>
+      </x:c>
+      <x:c r="P168" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Project 1: Building a Distributed Mini-C4 Data Pipeline with Ray; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q168" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -11471,10 +11471,10 @@
       <x:c r="S168" s="4" t="str"/>
       <x:c r="T168" s="4" t="str"/>
       <x:c r="U168" s="4" t="str">
-        <x:v>Figure P01-4：MinHash + LSH 去重思路</x:v>
+        <x:v>Figure P01-1：Mini-C4 数据流水线总览</x:v>
       </x:c>
       <x:c r="V168" s="4" t="str">
-        <x:v>图 P01-4</x:v>
+        <x:v>图 P01-1</x:v>
       </x:c>
     </x:row>
     <x:row r="169">
@@ -11497,19 +11497,19 @@
         <x:v>docs/en/part14/p01_mini_c4.md</x:v>
       </x:c>
       <x:c r="G169" s="4" t="n">
-        <x:v>480</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H169" s="4" t="str">
-        <x:v>P01-5</x:v>
+        <x:v>P01-2</x:v>
       </x:c>
       <x:c r="I169" s="4" t="str">
-        <x:v>Figure P01-5: Language Splitting and Branch Processing</x:v>
+        <x:v>Figure P01-2: Parsing Path from WARC to Body Text</x:v>
       </x:c>
       <x:c r="J169" s="4" t="str">
-        <x:v>Figure P01-5</x:v>
+        <x:v>Figure P01-2</x:v>
       </x:c>
       <x:c r="K169" s="4" t="str">
-        <x:v>docs/images/part14/p01/p01_05_language_split.svg</x:v>
+        <x:v>docs/images/part14/p01/p01_02_warc_to_text.svg</x:v>
       </x:c>
       <x:c r="L169" s="4" t="str">
         <x:v>yes</x:v>
@@ -11521,7 +11521,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O169" s="4" t="str">
-        <x:v>Language Splitting and Branch Processing.</x:v>
+        <x:v>Parsing Path from WARC to Body Text.</x:v>
       </x:c>
       <x:c r="P169" s="4" t="str"/>
       <x:c r="Q169" s="4" t="str">
@@ -11533,10 +11533,10 @@
       <x:c r="S169" s="4" t="str"/>
       <x:c r="T169" s="4" t="str"/>
       <x:c r="U169" s="4" t="str">
-        <x:v>Figure P01-5：语种拆分与分支处理</x:v>
+        <x:v>Figure P01-2：WARC 到正文文本的解析路径</x:v>
       </x:c>
       <x:c r="V169" s="4" t="str">
-        <x:v>图 P01-5</x:v>
+        <x:v>图 P01-2</x:v>
       </x:c>
     </x:row>
     <x:row r="170">
@@ -11559,31 +11559,31 @@
         <x:v>docs/en/part14/p01_mini_c4.md</x:v>
       </x:c>
       <x:c r="G170" s="4" t="n">
-        <x:v>515</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="H170" s="4" t="str">
-        <x:v>P01-6</x:v>
+        <x:v>P01-3</x:v>
       </x:c>
       <x:c r="I170" s="4" t="str">
-        <x:v>Figure P01-6: Quality Filtering Decision Illustration</x:v>
+        <x:v>Figure P01-3: Heuristic Cleaning Rules Illustration</x:v>
       </x:c>
       <x:c r="J170" s="4" t="str">
-        <x:v>Figure P01-6</x:v>
+        <x:v>Figure P01-3</x:v>
       </x:c>
       <x:c r="K170" s="4" t="str">
-        <x:v>docs/images/part14/p01/p01_06_quality_filter.svg</x:v>
+        <x:v>docs/images/part14/p01/p01_03_cleaning_rules.svg</x:v>
       </x:c>
       <x:c r="L170" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M170" s="4" t="str">
-        <x:v>960.12x540</x:v>
+        <x:v>900x672</x:v>
       </x:c>
       <x:c r="N170" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O170" s="4" t="str">
-        <x:v>Quality Filtering Decision Illustration.</x:v>
+        <x:v>Heuristic Cleaning Rules Illustration.</x:v>
       </x:c>
       <x:c r="P170" s="4" t="str"/>
       <x:c r="Q170" s="4" t="str">
@@ -11595,10 +11595,10 @@
       <x:c r="S170" s="4" t="str"/>
       <x:c r="T170" s="4" t="str"/>
       <x:c r="U170" s="4" t="str">
-        <x:v>Figure P01-6：质量过滤决策示意</x:v>
+        <x:v>Figure P01-3：启发式清洗规则示意</x:v>
       </x:c>
       <x:c r="V170" s="4" t="str">
-        <x:v>图 P01-6</x:v>
+        <x:v>图 P01-3</x:v>
       </x:c>
     </x:row>
     <x:row r="171">
@@ -11621,19 +11621,19 @@
         <x:v>docs/en/part14/p01_mini_c4.md</x:v>
       </x:c>
       <x:c r="G171" s="4" t="n">
-        <x:v>577</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="H171" s="4" t="str">
-        <x:v>P01-7</x:v>
+        <x:v>P01-4</x:v>
       </x:c>
       <x:c r="I171" s="4" t="str">
-        <x:v>Figure P01-7: Three-Round Experimental Iteration Path</x:v>
+        <x:v>Figure P01-4: MinHash + LSH Deduplication Approach</x:v>
       </x:c>
       <x:c r="J171" s="4" t="str">
-        <x:v>Figure P01-7</x:v>
+        <x:v>Figure P01-4</x:v>
       </x:c>
       <x:c r="K171" s="4" t="str">
-        <x:v>docs/images/part14/p01/p01_07_three_iterations.svg</x:v>
+        <x:v>docs/images/part14/p01/p01_04_dedup_minhash_lsh.svg</x:v>
       </x:c>
       <x:c r="L171" s="4" t="str">
         <x:v>yes</x:v>
@@ -11645,7 +11645,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O171" s="4" t="str">
-        <x:v>Three-Round Experimental Iteration Path.</x:v>
+        <x:v>MinHash + LSH Deduplication Approach.</x:v>
       </x:c>
       <x:c r="P171" s="4" t="str"/>
       <x:c r="Q171" s="4" t="str">
@@ -11657,10 +11657,10 @@
       <x:c r="S171" s="4" t="str"/>
       <x:c r="T171" s="4" t="str"/>
       <x:c r="U171" s="4" t="str">
-        <x:v>Figure P01-7：三轮实验迭代路径</x:v>
+        <x:v>Figure P01-4：MinHash + LSH 去重思路</x:v>
       </x:c>
       <x:c r="V171" s="4" t="str">
-        <x:v>图 P01-7</x:v>
+        <x:v>图 P01-4</x:v>
       </x:c>
     </x:row>
     <x:row r="172">
@@ -11683,31 +11683,31 @@
         <x:v>docs/en/part14/p01_mini_c4.md</x:v>
       </x:c>
       <x:c r="G172" s="4" t="n">
-        <x:v>694</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="H172" s="4" t="str">
-        <x:v>P01-8</x:v>
+        <x:v>P01-5</x:v>
       </x:c>
       <x:c r="I172" s="4" t="str">
-        <x:v>Figure P01-8: Data Retention Funnel</x:v>
+        <x:v>Figure P01-5: Language Splitting and Branch Processing</x:v>
       </x:c>
       <x:c r="J172" s="4" t="str">
-        <x:v>Figure P01-8</x:v>
+        <x:v>Figure P01-5</x:v>
       </x:c>
       <x:c r="K172" s="4" t="str">
-        <x:v>docs/images/part14/p01/p01_08_funnel.svg</x:v>
+        <x:v>docs/images/part14/p01/p01_05_language_split.svg</x:v>
       </x:c>
       <x:c r="L172" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M172" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N172" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O172" s="4" t="str">
-        <x:v>Data Retention Funnel. --- Figure P01-8: Data Retention Funnel.</x:v>
+        <x:v>Language Splitting and Branch Processing.</x:v>
       </x:c>
       <x:c r="P172" s="4" t="str"/>
       <x:c r="Q172" s="4" t="str">
@@ -11719,10 +11719,10 @@
       <x:c r="S172" s="4" t="str"/>
       <x:c r="T172" s="4" t="str"/>
       <x:c r="U172" s="4" t="str">
-        <x:v>Figure P01-8：数据留存漏斗</x:v>
+        <x:v>Figure P01-5：语种拆分与分支处理</x:v>
       </x:c>
       <x:c r="V172" s="4" t="str">
-        <x:v>图 P01-8</x:v>
+        <x:v>图 P01-5</x:v>
       </x:c>
     </x:row>
     <x:row r="173">
@@ -11745,19 +11745,19 @@
         <x:v>docs/en/part14/p01_mini_c4.md</x:v>
       </x:c>
       <x:c r="G173" s="4" t="n">
-        <x:v>741</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="H173" s="4" t="str">
-        <x:v>P01-9</x:v>
+        <x:v>P01-6</x:v>
       </x:c>
       <x:c r="I173" s="4" t="str">
-        <x:v>Figure P01-9: Resource and Cost Breakdown</x:v>
+        <x:v>Figure P01-6: Quality Filtering Decision Illustration</x:v>
       </x:c>
       <x:c r="J173" s="4" t="str">
-        <x:v>Figure P01-9</x:v>
+        <x:v>Figure P01-6</x:v>
       </x:c>
       <x:c r="K173" s="4" t="str">
-        <x:v>docs/images/part14/p01/p01_09_cost_breakdown.svg</x:v>
+        <x:v>docs/images/part14/p01/p01_06_quality_filter.svg</x:v>
       </x:c>
       <x:c r="L173" s="4" t="str">
         <x:v>yes</x:v>
@@ -11769,7 +11769,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O173" s="4" t="str">
-        <x:v>Resource and Cost Breakdown.</x:v>
+        <x:v>Quality Filtering Decision Illustration.</x:v>
       </x:c>
       <x:c r="P173" s="4" t="str"/>
       <x:c r="Q173" s="4" t="str">
@@ -11781,10 +11781,10 @@
       <x:c r="S173" s="4" t="str"/>
       <x:c r="T173" s="4" t="str"/>
       <x:c r="U173" s="4" t="str">
-        <x:v>Figure P01-9：资源与成本构成</x:v>
+        <x:v>Figure P01-6：质量过滤决策示意</x:v>
       </x:c>
       <x:c r="V173" s="4" t="str">
-        <x:v>图 P01-9</x:v>
+        <x:v>图 P01-6</x:v>
       </x:c>
     </x:row>
     <x:row r="174">
@@ -11807,31 +11807,31 @@
         <x:v>docs/en/part14/p01_mini_c4.md</x:v>
       </x:c>
       <x:c r="G174" s="4" t="n">
-        <x:v>772</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="H174" s="4" t="str">
-        <x:v>P01-10</x:v>
+        <x:v>P01-7</x:v>
       </x:c>
       <x:c r="I174" s="4" t="str">
-        <x:v>Figure P01-10: Project Validation Loop</x:v>
+        <x:v>Figure P01-7: Three-Round Experimental Iteration Path</x:v>
       </x:c>
       <x:c r="J174" s="4" t="str">
-        <x:v>Figure P01-10</x:v>
+        <x:v>Figure P01-7</x:v>
       </x:c>
       <x:c r="K174" s="4" t="str">
-        <x:v>docs/images/part14/p01/p01_10_validation_loop.svg</x:v>
+        <x:v>docs/images/part14/p01/p01_07_three_iterations.svg</x:v>
       </x:c>
       <x:c r="L174" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M174" s="4" t="str">
-        <x:v>1024x1024</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N174" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O174" s="4" t="str">
-        <x:v>Project Validation Loop. Figure P01-10: Project Validation Loop.</x:v>
+        <x:v>Three-Round Experimental Iteration Path.</x:v>
       </x:c>
       <x:c r="P174" s="4" t="str"/>
       <x:c r="Q174" s="4" t="str">
@@ -11843,10 +11843,10 @@
       <x:c r="S174" s="4" t="str"/>
       <x:c r="T174" s="4" t="str"/>
       <x:c r="U174" s="4" t="str">
-        <x:v>Figure P01-10：项目验证闭环</x:v>
+        <x:v>Figure P01-7：三轮实验迭代路径</x:v>
       </x:c>
       <x:c r="V174" s="4" t="str">
-        <x:v>图 P01-10</x:v>
+        <x:v>图 P01-7</x:v>
       </x:c>
     </x:row>
     <x:row r="175">
@@ -11869,31 +11869,31 @@
         <x:v>docs/en/part14/p01_mini_c4.md</x:v>
       </x:c>
       <x:c r="G175" s="4" t="n">
-        <x:v>895</x:v>
+        <x:v>694</x:v>
       </x:c>
       <x:c r="H175" s="4" t="str">
-        <x:v>P01-11</x:v>
+        <x:v>P01-8</x:v>
       </x:c>
       <x:c r="I175" s="4" t="str">
-        <x:v>Figure P01-11: Mini-C4 Engineering Methodology Summary</x:v>
+        <x:v>Figure P01-8: Data Retention Funnel</x:v>
       </x:c>
       <x:c r="J175" s="4" t="str">
-        <x:v>Figure P01-11</x:v>
+        <x:v>Figure P01-8</x:v>
       </x:c>
       <x:c r="K175" s="4" t="str">
-        <x:v>docs/images/part14/p01/p01_11_methodology_summary.svg</x:v>
+        <x:v>docs/images/part14/p01/p01_08_funnel.svg</x:v>
       </x:c>
       <x:c r="L175" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M175" s="4" t="str">
-        <x:v>900x503</x:v>
+        <x:v>1800x1005</x:v>
       </x:c>
       <x:c r="N175" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O175" s="4" t="str">
-        <x:v>Mini-C4 Engineering Methodology Summary.</x:v>
+        <x:v>Data Retention Funnel. --- Figure P01-8: Data Retention Funnel.</x:v>
       </x:c>
       <x:c r="P175" s="4" t="str"/>
       <x:c r="Q175" s="4" t="str">
@@ -11905,10 +11905,10 @@
       <x:c r="S175" s="4" t="str"/>
       <x:c r="T175" s="4" t="str"/>
       <x:c r="U175" s="4" t="str">
-        <x:v>Figure P01-11：Mini-C4 工程方法论总结</x:v>
+        <x:v>Figure P01-8：数据留存漏斗</x:v>
       </x:c>
       <x:c r="V175" s="4" t="str">
-        <x:v>图 P01-11</x:v>
+        <x:v>图 P01-8</x:v>
       </x:c>
     </x:row>
     <x:row r="176">
@@ -11922,40 +11922,40 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D176" s="4" t="str">
-        <x:v>P02</x:v>
+        <x:v>P01</x:v>
       </x:c>
       <x:c r="E176" s="4" t="str">
-        <x:v>Project 2: Vertical-domain Expert SFT for Law</x:v>
+        <x:v>Project 1: Building a Distributed Mini-C4 Data Pipeline with Ray</x:v>
       </x:c>
       <x:c r="F176" s="4" t="str">
-        <x:v>docs/en/part14/p02_legal_sft.md</x:v>
+        <x:v>docs/en/part14/p01_mini_c4.md</x:v>
       </x:c>
       <x:c r="G176" s="4" t="n">
-        <x:v>170</x:v>
+        <x:v>741</x:v>
       </x:c>
       <x:c r="H176" s="4" t="str">
-        <x:v>P02-1</x:v>
+        <x:v>P01-9</x:v>
       </x:c>
       <x:c r="I176" s="4" t="str">
-        <x:v>Figure P02-1: Legal-Domain SFT Data Factory Overview</x:v>
+        <x:v>Figure P01-9: Resource and Cost Breakdown</x:v>
       </x:c>
       <x:c r="J176" s="4" t="str">
-        <x:v>Figure P02-1</x:v>
+        <x:v>Figure P01-9</x:v>
       </x:c>
       <x:c r="K176" s="4" t="str">
-        <x:v>docs/images/part14/p02/p02_01_legal_sft_factory_overview.svg</x:v>
+        <x:v>docs/images/part14/p01/p01_09_cost_breakdown.svg</x:v>
       </x:c>
       <x:c r="L176" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M176" s="4" t="str">
-        <x:v>900x503</x:v>
+        <x:v>960.12x540</x:v>
       </x:c>
       <x:c r="N176" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O176" s="4" t="str">
-        <x:v>Legal-Domain SFT Data Factory Overview.</x:v>
+        <x:v>Resource and Cost Breakdown.</x:v>
       </x:c>
       <x:c r="P176" s="4" t="str"/>
       <x:c r="Q176" s="4" t="str">
@@ -11967,10 +11967,10 @@
       <x:c r="S176" s="4" t="str"/>
       <x:c r="T176" s="4" t="str"/>
       <x:c r="U176" s="4" t="str">
-        <x:v>Figure P02-1：法律领域 SFT 数据工厂总览</x:v>
+        <x:v>Figure P01-9：资源与成本构成</x:v>
       </x:c>
       <x:c r="V176" s="4" t="str">
-        <x:v>图 P02-1</x:v>
+        <x:v>图 P01-9</x:v>
       </x:c>
     </x:row>
     <x:row r="177">
@@ -11984,40 +11984,40 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D177" s="4" t="str">
-        <x:v>P02</x:v>
+        <x:v>P01</x:v>
       </x:c>
       <x:c r="E177" s="4" t="str">
-        <x:v>Project 2: Vertical-domain Expert SFT for Law</x:v>
+        <x:v>Project 1: Building a Distributed Mini-C4 Data Pipeline with Ray</x:v>
       </x:c>
       <x:c r="F177" s="4" t="str">
-        <x:v>docs/en/part14/p02_legal_sft.md</x:v>
+        <x:v>docs/en/part14/p01_mini_c4.md</x:v>
       </x:c>
       <x:c r="G177" s="4" t="n">
-        <x:v>248</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="H177" s="4" t="str">
-        <x:v>P02-2</x:v>
+        <x:v>P01-10</x:v>
       </x:c>
       <x:c r="I177" s="4" t="str">
-        <x:v>Figure P02-2: Legal SFT Data Factory Role Assignment Diagram</x:v>
+        <x:v>Figure P01-10: Project Validation Loop</x:v>
       </x:c>
       <x:c r="J177" s="4" t="str">
-        <x:v>Figure P02-2</x:v>
+        <x:v>Figure P01-10</x:v>
       </x:c>
       <x:c r="K177" s="4" t="str">
-        <x:v>docs/images/part14/p02/p02_02_roles_and_responsibilities.svg</x:v>
+        <x:v>docs/images/part14/p01/p01_10_validation_loop.svg</x:v>
       </x:c>
       <x:c r="L177" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M177" s="4" t="str">
-        <x:v>900x503</x:v>
+        <x:v>1024x1024</x:v>
       </x:c>
       <x:c r="N177" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O177" s="4" t="str">
-        <x:v>Legal SFT Data Factory Role Assignment Diagram.</x:v>
+        <x:v>Project Validation Loop. Figure P01-10: Project Validation Loop.</x:v>
       </x:c>
       <x:c r="P177" s="4" t="str"/>
       <x:c r="Q177" s="4" t="str">
@@ -12029,10 +12029,10 @@
       <x:c r="S177" s="4" t="str"/>
       <x:c r="T177" s="4" t="str"/>
       <x:c r="U177" s="4" t="str">
-        <x:v>Figure P02-2：法律 SFT 数据工厂角色分工图</x:v>
+        <x:v>Figure P01-10：项目验证闭环</x:v>
       </x:c>
       <x:c r="V177" s="4" t="str">
-        <x:v>图 P02-2</x:v>
+        <x:v>图 P01-10</x:v>
       </x:c>
     </x:row>
     <x:row r="178">
@@ -12046,28 +12046,28 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D178" s="4" t="str">
-        <x:v>P02</x:v>
+        <x:v>P01</x:v>
       </x:c>
       <x:c r="E178" s="4" t="str">
-        <x:v>Project 2: Vertical-domain Expert SFT for Law</x:v>
+        <x:v>Project 1: Building a Distributed Mini-C4 Data Pipeline with Ray</x:v>
       </x:c>
       <x:c r="F178" s="4" t="str">
-        <x:v>docs/en/part14/p02_legal_sft.md</x:v>
+        <x:v>docs/en/part14/p01_mini_c4.md</x:v>
       </x:c>
       <x:c r="G178" s="4" t="n">
-        <x:v>367</x:v>
+        <x:v>895</x:v>
       </x:c>
       <x:c r="H178" s="4" t="str">
-        <x:v>P02-3</x:v>
+        <x:v>P01-11</x:v>
       </x:c>
       <x:c r="I178" s="4" t="str">
-        <x:v>Figure P02-3: Legal PDF Intelligent Cleaning Pipeline Diagram</x:v>
+        <x:v>Figure P01-11: Mini-C4 Engineering Methodology Summary</x:v>
       </x:c>
       <x:c r="J178" s="4" t="str">
-        <x:v>Figure P02-3</x:v>
+        <x:v>Figure P01-11</x:v>
       </x:c>
       <x:c r="K178" s="4" t="str">
-        <x:v>docs/images/part14/p02/p02_03_pdf_cleaning_pipeline.svg</x:v>
+        <x:v>docs/images/part14/p01/p01_11_methodology_summary.svg</x:v>
       </x:c>
       <x:c r="L178" s="4" t="str">
         <x:v>yes</x:v>
@@ -12079,11 +12079,9 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O178" s="4" t="str">
-        <x:v>Legal PDF Intelligent Cleaning Pipeline Diagram.</x:v>
-      </x:c>
-      <x:c r="P178" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Project 2: Vertical-domain Expert SFT for Law; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>Mini-C4 Engineering Methodology Summary.</x:v>
+      </x:c>
+      <x:c r="P178" s="4" t="str"/>
       <x:c r="Q178" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -12093,10 +12091,10 @@
       <x:c r="S178" s="4" t="str"/>
       <x:c r="T178" s="4" t="str"/>
       <x:c r="U178" s="4" t="str">
-        <x:v>Figure P02-3：法律 PDF 智能清洗示意图</x:v>
+        <x:v>Figure P01-11：Mini-C4 工程方法论总结</x:v>
       </x:c>
       <x:c r="V178" s="4" t="str">
-        <x:v>图 P02-3</x:v>
+        <x:v>图 P01-11</x:v>
       </x:c>
     </x:row>
     <x:row r="179">
@@ -12119,31 +12117,31 @@
         <x:v>docs/en/part14/p02_legal_sft.md</x:v>
       </x:c>
       <x:c r="G179" s="4" t="n">
-        <x:v>370</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H179" s="4" t="str">
-        <x:v>P02-4</x:v>
+        <x:v>P02-1</x:v>
       </x:c>
       <x:c r="I179" s="4" t="str">
-        <x:v>Figure P02-4: Examples of Embedded Page Number Removal and Chinese Word-Break Repair</x:v>
+        <x:v>Figure P02-1: Legal-Domain SFT Data Factory Overview</x:v>
       </x:c>
       <x:c r="J179" s="4" t="str">
-        <x:v>Figure P02-4</x:v>
+        <x:v>Figure P02-1</x:v>
       </x:c>
       <x:c r="K179" s="4" t="str">
-        <x:v>docs/images/part14/p02/p02_04_cleaning_examples.svg</x:v>
+        <x:v>docs/images/part14/p02/p02_01_legal_sft_factory_overview.svg</x:v>
       </x:c>
       <x:c r="L179" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M179" s="4" t="str">
-        <x:v>900x672</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N179" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O179" s="4" t="str">
-        <x:v>Examples of Embedded Page Number Removal and Chinese Word-Break Repair.</x:v>
+        <x:v>Legal-Domain SFT Data Factory Overview.</x:v>
       </x:c>
       <x:c r="P179" s="4" t="str"/>
       <x:c r="Q179" s="4" t="str">
@@ -12155,10 +12153,10 @@
       <x:c r="S179" s="4" t="str"/>
       <x:c r="T179" s="4" t="str"/>
       <x:c r="U179" s="4" t="str">
-        <x:v>Figure P02-4：嵌入式页码与中文断词修复案例</x:v>
+        <x:v>Figure P02-1：法律领域 SFT 数据工厂总览</x:v>
       </x:c>
       <x:c r="V179" s="4" t="str">
-        <x:v>图 P02-4</x:v>
+        <x:v>图 P02-1</x:v>
       </x:c>
     </x:row>
     <x:row r="180">
@@ -12181,19 +12179,19 @@
         <x:v>docs/en/part14/p02_legal_sft.md</x:v>
       </x:c>
       <x:c r="G180" s="4" t="n">
-        <x:v>419</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="H180" s="4" t="str">
-        <x:v>P02-5</x:v>
+        <x:v>P02-2</x:v>
       </x:c>
       <x:c r="I180" s="4" t="str">
-        <x:v>Figure P02-5: Legal Seed Sample Schema Diagram</x:v>
+        <x:v>Figure P02-2: Legal SFT Data Factory Role Assignment Diagram</x:v>
       </x:c>
       <x:c r="J180" s="4" t="str">
-        <x:v>Figure P02-5</x:v>
+        <x:v>Figure P02-2</x:v>
       </x:c>
       <x:c r="K180" s="4" t="str">
-        <x:v>docs/images/part14/p02/p02_05_seed_schema.svg</x:v>
+        <x:v>docs/images/part14/p02/p02_02_roles_and_responsibilities.svg</x:v>
       </x:c>
       <x:c r="L180" s="4" t="str">
         <x:v>yes</x:v>
@@ -12205,11 +12203,9 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O180" s="4" t="str">
-        <x:v>Legal Seed Sample Schema Diagram.</x:v>
-      </x:c>
-      <x:c r="P180" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Project 2: Vertical-domain Expert SFT for Law; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>Legal SFT Data Factory Role Assignment Diagram.</x:v>
+      </x:c>
+      <x:c r="P180" s="4" t="str"/>
       <x:c r="Q180" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -12219,10 +12215,10 @@
       <x:c r="S180" s="4" t="str"/>
       <x:c r="T180" s="4" t="str"/>
       <x:c r="U180" s="4" t="str">
-        <x:v>Figure P02-5：法律种子样本 schema 示意图</x:v>
+        <x:v>Figure P02-2：法律 SFT 数据工厂角色分工图</x:v>
       </x:c>
       <x:c r="V180" s="4" t="str">
-        <x:v>图 P02-5</x:v>
+        <x:v>图 P02-2</x:v>
       </x:c>
     </x:row>
     <x:row r="181">
@@ -12245,19 +12241,19 @@
         <x:v>docs/en/part14/p02_legal_sft.md</x:v>
       </x:c>
       <x:c r="G181" s="4" t="n">
-        <x:v>475</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="H181" s="4" t="str">
-        <x:v>P02-6</x:v>
+        <x:v>P02-3</x:v>
       </x:c>
       <x:c r="I181" s="4" t="str">
-        <x:v>Figure P02-6: Legal Task Taxonomy Stratification Diagram</x:v>
+        <x:v>Figure P02-3: Legal PDF Intelligent Cleaning Pipeline Diagram</x:v>
       </x:c>
       <x:c r="J181" s="4" t="str">
-        <x:v>Figure P02-6</x:v>
+        <x:v>Figure P02-3</x:v>
       </x:c>
       <x:c r="K181" s="4" t="str">
-        <x:v>docs/images/part14/p02/p02_06_task_taxonomy.svg</x:v>
+        <x:v>docs/images/part14/p02/p02_03_pdf_cleaning_pipeline.svg</x:v>
       </x:c>
       <x:c r="L181" s="4" t="str">
         <x:v>yes</x:v>
@@ -12269,9 +12265,11 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O181" s="4" t="str">
-        <x:v>Legal Task Taxonomy Stratification Diagram.</x:v>
-      </x:c>
-      <x:c r="P181" s="4" t="str"/>
+        <x:v>Legal PDF Intelligent Cleaning Pipeline Diagram.</x:v>
+      </x:c>
+      <x:c r="P181" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Project 2: Vertical-domain Expert SFT for Law; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q181" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -12281,10 +12279,10 @@
       <x:c r="S181" s="4" t="str"/>
       <x:c r="T181" s="4" t="str"/>
       <x:c r="U181" s="4" t="str">
-        <x:v>Figure P02-6：法律任务体系分层图</x:v>
+        <x:v>Figure P02-3：法律 PDF 智能清洗示意图</x:v>
       </x:c>
       <x:c r="V181" s="4" t="str">
-        <x:v>图 P02-6</x:v>
+        <x:v>图 P02-3</x:v>
       </x:c>
     </x:row>
     <x:row r="182">
@@ -12307,35 +12305,33 @@
         <x:v>docs/en/part14/p02_legal_sft.md</x:v>
       </x:c>
       <x:c r="G182" s="4" t="n">
-        <x:v>502</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="H182" s="4" t="str">
-        <x:v>P02-7</x:v>
+        <x:v>P02-4</x:v>
       </x:c>
       <x:c r="I182" s="4" t="str">
-        <x:v>Figure P02-7: Task Distribution vs. Legal Domain Coverage Comparison Chart</x:v>
+        <x:v>Figure P02-4: Examples of Embedded Page Number Removal and Chinese Word-Break Repair</x:v>
       </x:c>
       <x:c r="J182" s="4" t="str">
-        <x:v>Figure P02-7</x:v>
+        <x:v>Figure P02-4</x:v>
       </x:c>
       <x:c r="K182" s="4" t="str">
-        <x:v>docs/images/part14/p02/p02_07_task_vs_domain_distribution.svg</x:v>
+        <x:v>docs/images/part14/p02/p02_04_cleaning_examples.svg</x:v>
       </x:c>
       <x:c r="L182" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M182" s="4" t="str">
-        <x:v>900x503</x:v>
+        <x:v>900x672</x:v>
       </x:c>
       <x:c r="N182" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O182" s="4" t="str">
-        <x:v>Task Distribution vs. Legal Domain Coverage Comparison Chart.</x:v>
-      </x:c>
-      <x:c r="P182" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Project 2: Vertical-domain Expert SFT for Law; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>Examples of Embedded Page Number Removal and Chinese Word-Break Repair.</x:v>
+      </x:c>
+      <x:c r="P182" s="4" t="str"/>
       <x:c r="Q182" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -12345,10 +12341,10 @@
       <x:c r="S182" s="4" t="str"/>
       <x:c r="T182" s="4" t="str"/>
       <x:c r="U182" s="4" t="str">
-        <x:v>Figure P02-7：任务分布与法域覆盖对照图</x:v>
+        <x:v>Figure P02-4：嵌入式页码与中文断词修复案例</x:v>
       </x:c>
       <x:c r="V182" s="4" t="str">
-        <x:v>图 P02-7</x:v>
+        <x:v>图 P02-4</x:v>
       </x:c>
     </x:row>
     <x:row r="183">
@@ -12371,19 +12367,19 @@
         <x:v>docs/en/part14/p02_legal_sft.md</x:v>
       </x:c>
       <x:c r="G183" s="4" t="n">
-        <x:v>536</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="H183" s="4" t="str">
-        <x:v>P02-8</x:v>
+        <x:v>P02-5</x:v>
       </x:c>
       <x:c r="I183" s="4" t="str">
-        <x:v>Figure P02-8: Weighted Roulette Task Sampling Diagram</x:v>
+        <x:v>Figure P02-5: Legal Seed Sample Schema Diagram</x:v>
       </x:c>
       <x:c r="J183" s="4" t="str">
-        <x:v>Figure P02-8</x:v>
+        <x:v>Figure P02-5</x:v>
       </x:c>
       <x:c r="K183" s="4" t="str">
-        <x:v>docs/images/part14/p02/p02_08_weighted_task_sampling.svg</x:v>
+        <x:v>docs/images/part14/p02/p02_05_seed_schema.svg</x:v>
       </x:c>
       <x:c r="L183" s="4" t="str">
         <x:v>yes</x:v>
@@ -12395,9 +12391,11 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O183" s="4" t="str">
-        <x:v>Weighted Roulette Task Sampling Diagram.</x:v>
-      </x:c>
-      <x:c r="P183" s="4" t="str"/>
+        <x:v>Legal Seed Sample Schema Diagram.</x:v>
+      </x:c>
+      <x:c r="P183" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Project 2: Vertical-domain Expert SFT for Law; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q183" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -12407,10 +12405,10 @@
       <x:c r="S183" s="4" t="str"/>
       <x:c r="T183" s="4" t="str"/>
       <x:c r="U183" s="4" t="str">
-        <x:v>Figure P02-8：加权轮盘赌任务采样示意图</x:v>
+        <x:v>Figure P02-5：法律种子样本 schema 示意图</x:v>
       </x:c>
       <x:c r="V183" s="4" t="str">
-        <x:v>图 P02-8</x:v>
+        <x:v>图 P02-5</x:v>
       </x:c>
     </x:row>
     <x:row r="184">
@@ -12433,19 +12431,19 @@
         <x:v>docs/en/part14/p02_legal_sft.md</x:v>
       </x:c>
       <x:c r="G184" s="4" t="n">
-        <x:v>574</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="H184" s="4" t="str">
-        <x:v>P02-9</x:v>
+        <x:v>P02-6</x:v>
       </x:c>
       <x:c r="I184" s="4" t="str">
-        <x:v>Figure P02-9: CoT Structure Diagram for Case Analysis Tasks</x:v>
+        <x:v>Figure P02-6: Legal Task Taxonomy Stratification Diagram</x:v>
       </x:c>
       <x:c r="J184" s="4" t="str">
-        <x:v>Figure P02-9</x:v>
+        <x:v>Figure P02-6</x:v>
       </x:c>
       <x:c r="K184" s="4" t="str">
-        <x:v>docs/images/part14/p02/p02_09_cot_structure.svg</x:v>
+        <x:v>docs/images/part14/p02/p02_06_task_taxonomy.svg</x:v>
       </x:c>
       <x:c r="L184" s="4" t="str">
         <x:v>yes</x:v>
@@ -12457,7 +12455,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O184" s="4" t="str">
-        <x:v>CoT Structure Diagram for Case Analysis Tasks.</x:v>
+        <x:v>Legal Task Taxonomy Stratification Diagram.</x:v>
       </x:c>
       <x:c r="P184" s="4" t="str"/>
       <x:c r="Q184" s="4" t="str">
@@ -12469,10 +12467,10 @@
       <x:c r="S184" s="4" t="str"/>
       <x:c r="T184" s="4" t="str"/>
       <x:c r="U184" s="4" t="str">
-        <x:v>Figure P02-9：案情分析类 CoT 结构示意图</x:v>
+        <x:v>Figure P02-6：法律任务体系分层图</x:v>
       </x:c>
       <x:c r="V184" s="4" t="str">
-        <x:v>图 P02-9</x:v>
+        <x:v>图 P02-6</x:v>
       </x:c>
     </x:row>
     <x:row r="185">
@@ -12495,19 +12493,19 @@
         <x:v>docs/en/part14/p02_legal_sft.md</x:v>
       </x:c>
       <x:c r="G185" s="4" t="n">
-        <x:v>613</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="H185" s="4" t="str">
-        <x:v>P02-10</x:v>
+        <x:v>P02-7</x:v>
       </x:c>
       <x:c r="I185" s="4" t="str">
-        <x:v>Figure P02-10: Relationship Between Preference Pairs and Review Records</x:v>
+        <x:v>Figure P02-7: Task Distribution vs. Legal Domain Coverage Comparison Chart</x:v>
       </x:c>
       <x:c r="J185" s="4" t="str">
-        <x:v>Figure P02-10</x:v>
+        <x:v>Figure P02-7</x:v>
       </x:c>
       <x:c r="K185" s="4" t="str">
-        <x:v>docs/images/part14/p02/p02_10_preference_and_review.svg</x:v>
+        <x:v>docs/images/part14/p02/p02_07_task_vs_domain_distribution.svg</x:v>
       </x:c>
       <x:c r="L185" s="4" t="str">
         <x:v>yes</x:v>
@@ -12519,9 +12517,11 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O185" s="4" t="str">
-        <x:v>Relationship Between Preference Pairs and Review Records.</x:v>
-      </x:c>
-      <x:c r="P185" s="4" t="str"/>
+        <x:v>Task Distribution vs. Legal Domain Coverage Comparison Chart.</x:v>
+      </x:c>
+      <x:c r="P185" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Project 2: Vertical-domain Expert SFT for Law; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q185" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -12531,10 +12531,10 @@
       <x:c r="S185" s="4" t="str"/>
       <x:c r="T185" s="4" t="str"/>
       <x:c r="U185" s="4" t="str">
-        <x:v>Figure P02-10：偏好对与评审记录关系图</x:v>
+        <x:v>Figure P02-7：任务分布与法域覆盖对照图</x:v>
       </x:c>
       <x:c r="V185" s="4" t="str">
-        <x:v>图 P02-10</x:v>
+        <x:v>图 P02-7</x:v>
       </x:c>
     </x:row>
     <x:row r="186">
@@ -12557,19 +12557,19 @@
         <x:v>docs/en/part14/p02_legal_sft.md</x:v>
       </x:c>
       <x:c r="G186" s="4" t="n">
-        <x:v>647</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="H186" s="4" t="str">
-        <x:v>P02-11</x:v>
+        <x:v>P02-8</x:v>
       </x:c>
       <x:c r="I186" s="4" t="str">
-        <x:v>Figure P02-11: Legal Scenario Risk Refusal Routing Diagram</x:v>
+        <x:v>Figure P02-8: Weighted Roulette Task Sampling Diagram</x:v>
       </x:c>
       <x:c r="J186" s="4" t="str">
-        <x:v>Figure P02-11</x:v>
+        <x:v>Figure P02-8</x:v>
       </x:c>
       <x:c r="K186" s="4" t="str">
-        <x:v>docs/images/part14/p02/p02_11_risk_refusal_flow.svg</x:v>
+        <x:v>docs/images/part14/p02/p02_08_weighted_task_sampling.svg</x:v>
       </x:c>
       <x:c r="L186" s="4" t="str">
         <x:v>yes</x:v>
@@ -12581,7 +12581,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O186" s="4" t="str">
-        <x:v>Legal Scenario Risk Refusal Routing Diagram.</x:v>
+        <x:v>Weighted Roulette Task Sampling Diagram.</x:v>
       </x:c>
       <x:c r="P186" s="4" t="str"/>
       <x:c r="Q186" s="4" t="str">
@@ -12593,10 +12593,10 @@
       <x:c r="S186" s="4" t="str"/>
       <x:c r="T186" s="4" t="str"/>
       <x:c r="U186" s="4" t="str">
-        <x:v>Figure P02-11：法律场景风险拒答分流图</x:v>
+        <x:v>Figure P02-8：加权轮盘赌任务采样示意图</x:v>
       </x:c>
       <x:c r="V186" s="4" t="str">
-        <x:v>图 P02-11</x:v>
+        <x:v>图 P02-8</x:v>
       </x:c>
     </x:row>
     <x:row r="187">
@@ -12619,31 +12619,31 @@
         <x:v>docs/en/part14/p02_legal_sft.md</x:v>
       </x:c>
       <x:c r="G187" s="4" t="n">
-        <x:v>695</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="H187" s="4" t="str">
-        <x:v>P02-12</x:v>
+        <x:v>P02-9</x:v>
       </x:c>
       <x:c r="I187" s="4" t="str">
-        <x:v>Figure P02-12: QA Review Closed-Loop Diagram</x:v>
+        <x:v>Figure P02-9: CoT Structure Diagram for Case Analysis Tasks</x:v>
       </x:c>
       <x:c r="J187" s="4" t="str">
-        <x:v>Figure P02-12</x:v>
+        <x:v>Figure P02-9</x:v>
       </x:c>
       <x:c r="K187" s="4" t="str">
-        <x:v>docs/images/part14/p02/p02_12_qa_loop.svg</x:v>
+        <x:v>docs/images/part14/p02/p02_09_cot_structure.svg</x:v>
       </x:c>
       <x:c r="L187" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M187" s="4" t="str">
-        <x:v>900x491</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N187" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O187" s="4" t="str">
-        <x:v>QA Review Closed-Loop Diagram.</x:v>
+        <x:v>CoT Structure Diagram for Case Analysis Tasks.</x:v>
       </x:c>
       <x:c r="P187" s="4" t="str"/>
       <x:c r="Q187" s="4" t="str">
@@ -12655,10 +12655,10 @@
       <x:c r="S187" s="4" t="str"/>
       <x:c r="T187" s="4" t="str"/>
       <x:c r="U187" s="4" t="str">
-        <x:v>Figure P02-12：QA 审核闭环图</x:v>
+        <x:v>Figure P02-9：案情分析类 CoT 结构示意图</x:v>
       </x:c>
       <x:c r="V187" s="4" t="str">
-        <x:v>图 P02-12</x:v>
+        <x:v>图 P02-9</x:v>
       </x:c>
     </x:row>
     <x:row r="188">
@@ -12681,31 +12681,31 @@
         <x:v>docs/en/part14/p02_legal_sft.md</x:v>
       </x:c>
       <x:c r="G188" s="4" t="n">
-        <x:v>698</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="H188" s="4" t="str">
-        <x:v>P02-13</x:v>
+        <x:v>P02-10</x:v>
       </x:c>
       <x:c r="I188" s="4" t="str">
-        <x:v>Figure P02-13: QA Accept / Revise / Reject Decision Table</x:v>
+        <x:v>Figure P02-10: Relationship Between Preference Pairs and Review Records</x:v>
       </x:c>
       <x:c r="J188" s="4" t="str">
-        <x:v>Figure P02-13</x:v>
+        <x:v>Figure P02-10</x:v>
       </x:c>
       <x:c r="K188" s="4" t="str">
-        <x:v>docs/images/part14/p02/p02_13_qa_decision_table.svg</x:v>
+        <x:v>docs/images/part14/p02/p02_10_preference_and_review.svg</x:v>
       </x:c>
       <x:c r="L188" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M188" s="4" t="str">
-        <x:v>900x491</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N188" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O188" s="4" t="str">
-        <x:v>QA Accept / Revise / Reject Decision Table.</x:v>
+        <x:v>Relationship Between Preference Pairs and Review Records.</x:v>
       </x:c>
       <x:c r="P188" s="4" t="str"/>
       <x:c r="Q188" s="4" t="str">
@@ -12717,10 +12717,10 @@
       <x:c r="S188" s="4" t="str"/>
       <x:c r="T188" s="4" t="str"/>
       <x:c r="U188" s="4" t="str">
-        <x:v>Figure P02-13：QA 接收/返工/拒收判定表</x:v>
+        <x:v>Figure P02-10：偏好对与评审记录关系图</x:v>
       </x:c>
       <x:c r="V188" s="4" t="str">
-        <x:v>图 P02-13</x:v>
+        <x:v>图 P02-10</x:v>
       </x:c>
     </x:row>
     <x:row r="189">
@@ -12743,19 +12743,19 @@
         <x:v>docs/en/part14/p02_legal_sft.md</x:v>
       </x:c>
       <x:c r="G189" s="4" t="n">
-        <x:v>734</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="H189" s="4" t="str">
-        <x:v>P02-14</x:v>
+        <x:v>P02-11</x:v>
       </x:c>
       <x:c r="I189" s="4" t="str">
-        <x:v>Figure P02-14: Human-in-the-Loop and Vendor Tiered Review Diagram</x:v>
+        <x:v>Figure P02-11: Legal Scenario Risk Refusal Routing Diagram</x:v>
       </x:c>
       <x:c r="J189" s="4" t="str">
-        <x:v>Figure P02-14</x:v>
+        <x:v>Figure P02-11</x:v>
       </x:c>
       <x:c r="K189" s="4" t="str">
-        <x:v>docs/images/part14/p02/p02_14_human_in_the_loop.svg</x:v>
+        <x:v>docs/images/part14/p02/p02_11_risk_refusal_flow.svg</x:v>
       </x:c>
       <x:c r="L189" s="4" t="str">
         <x:v>yes</x:v>
@@ -12767,7 +12767,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O189" s="4" t="str">
-        <x:v>Human-in-the-Loop and Vendor Tiered Review Diagram.</x:v>
+        <x:v>Legal Scenario Risk Refusal Routing Diagram.</x:v>
       </x:c>
       <x:c r="P189" s="4" t="str"/>
       <x:c r="Q189" s="4" t="str">
@@ -12779,10 +12779,10 @@
       <x:c r="S189" s="4" t="str"/>
       <x:c r="T189" s="4" t="str"/>
       <x:c r="U189" s="4" t="str">
-        <x:v>Figure P02-14：人机协同与供应商分层审核图</x:v>
+        <x:v>Figure P02-11：法律场景风险拒答分流图</x:v>
       </x:c>
       <x:c r="V189" s="4" t="str">
-        <x:v>图 P02-14</x:v>
+        <x:v>图 P02-11</x:v>
       </x:c>
     </x:row>
     <x:row r="190">
@@ -12805,31 +12805,31 @@
         <x:v>docs/en/part14/p02_legal_sft.md</x:v>
       </x:c>
       <x:c r="G190" s="4" t="n">
-        <x:v>771</x:v>
+        <x:v>695</x:v>
       </x:c>
       <x:c r="H190" s="4" t="str">
-        <x:v>P02-15</x:v>
+        <x:v>P02-12</x:v>
       </x:c>
       <x:c r="I190" s="4" t="str">
-        <x:v>Figure P02-15: Training Packaging and Delivery Interface Diagram</x:v>
+        <x:v>Figure P02-12: QA Review Closed-Loop Diagram</x:v>
       </x:c>
       <x:c r="J190" s="4" t="str">
-        <x:v>Figure P02-15</x:v>
+        <x:v>Figure P02-12</x:v>
       </x:c>
       <x:c r="K190" s="4" t="str">
-        <x:v>docs/images/part14/p02/p02_15_training_artifacts.svg</x:v>
+        <x:v>docs/images/part14/p02/p02_12_qa_loop.svg</x:v>
       </x:c>
       <x:c r="L190" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M190" s="4" t="str">
-        <x:v>900x503</x:v>
+        <x:v>900x491</x:v>
       </x:c>
       <x:c r="N190" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O190" s="4" t="str">
-        <x:v>Training Packaging and Delivery Interface Diagram.</x:v>
+        <x:v>QA Review Closed-Loop Diagram.</x:v>
       </x:c>
       <x:c r="P190" s="4" t="str"/>
       <x:c r="Q190" s="4" t="str">
@@ -12841,10 +12841,10 @@
       <x:c r="S190" s="4" t="str"/>
       <x:c r="T190" s="4" t="str"/>
       <x:c r="U190" s="4" t="str">
-        <x:v>Figure P02-15：训练封装与交付接口图</x:v>
+        <x:v>Figure P02-12：QA 审核闭环图</x:v>
       </x:c>
       <x:c r="V190" s="4" t="str">
-        <x:v>图 P02-15</x:v>
+        <x:v>图 P02-12</x:v>
       </x:c>
     </x:row>
     <x:row r="191">
@@ -12867,31 +12867,31 @@
         <x:v>docs/en/part14/p02_legal_sft.md</x:v>
       </x:c>
       <x:c r="G191" s="4" t="n">
-        <x:v>828</x:v>
+        <x:v>698</x:v>
       </x:c>
       <x:c r="H191" s="4" t="str">
-        <x:v>P02-16</x:v>
+        <x:v>P02-13</x:v>
       </x:c>
       <x:c r="I191" s="4" t="str">
-        <x:v>Figure P02-16: P02 Core Metrics Dashboard</x:v>
+        <x:v>Figure P02-13: QA Accept / Revise / Reject Decision Table</x:v>
       </x:c>
       <x:c r="J191" s="4" t="str">
-        <x:v>Figure P02-16</x:v>
+        <x:v>Figure P02-13</x:v>
       </x:c>
       <x:c r="K191" s="4" t="str">
-        <x:v>docs/images/part14/p02/p02_16_metrics_dashboard.svg</x:v>
+        <x:v>docs/images/part14/p02/p02_13_qa_decision_table.svg</x:v>
       </x:c>
       <x:c r="L191" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M191" s="4" t="str">
-        <x:v>900x503</x:v>
+        <x:v>900x491</x:v>
       </x:c>
       <x:c r="N191" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O191" s="4" t="str">
-        <x:v>P02 Core Metrics Dashboard.</x:v>
+        <x:v>QA Accept / Revise / Reject Decision Table.</x:v>
       </x:c>
       <x:c r="P191" s="4" t="str"/>
       <x:c r="Q191" s="4" t="str">
@@ -12903,10 +12903,10 @@
       <x:c r="S191" s="4" t="str"/>
       <x:c r="T191" s="4" t="str"/>
       <x:c r="U191" s="4" t="str">
-        <x:v>Figure P02-16：P02 核心指标总览图</x:v>
+        <x:v>Figure P02-13：QA 接收/返工/拒收判定表</x:v>
       </x:c>
       <x:c r="V191" s="4" t="str">
-        <x:v>图 P02-16</x:v>
+        <x:v>图 P02-13</x:v>
       </x:c>
     </x:row>
     <x:row r="192">
@@ -12929,31 +12929,31 @@
         <x:v>docs/en/part14/p02_legal_sft.md</x:v>
       </x:c>
       <x:c r="G192" s="4" t="n">
-        <x:v>912</x:v>
+        <x:v>734</x:v>
       </x:c>
       <x:c r="H192" s="4" t="str">
-        <x:v>P02-17</x:v>
+        <x:v>P02-14</x:v>
       </x:c>
       <x:c r="I192" s="4" t="str">
-        <x:v>Figure P02-17: 50-Sample Validation Protocol Diagram</x:v>
+        <x:v>Figure P02-14: Human-in-the-Loop and Vendor Tiered Review Diagram</x:v>
       </x:c>
       <x:c r="J192" s="4" t="str">
-        <x:v>Figure P02-17</x:v>
+        <x:v>Figure P02-14</x:v>
       </x:c>
       <x:c r="K192" s="4" t="str">
-        <x:v>docs/images/part14/p02/p02_17_eval_sampling_protocol.svg</x:v>
+        <x:v>docs/images/part14/p02/p02_14_human_in_the_loop.svg</x:v>
       </x:c>
       <x:c r="L192" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M192" s="4" t="str">
-        <x:v>1380x752</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N192" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O192" s="4" t="str">
-        <x:v>50-Sample Validation Protocol Diagram.</x:v>
+        <x:v>Human-in-the-Loop and Vendor Tiered Review Diagram.</x:v>
       </x:c>
       <x:c r="P192" s="4" t="str"/>
       <x:c r="Q192" s="4" t="str">
@@ -12965,10 +12965,10 @@
       <x:c r="S192" s="4" t="str"/>
       <x:c r="T192" s="4" t="str"/>
       <x:c r="U192" s="4" t="str">
-        <x:v>Figure P02-17：50 条抽样验证流程图</x:v>
+        <x:v>Figure P02-14：人机协同与供应商分层审核图</x:v>
       </x:c>
       <x:c r="V192" s="4" t="str">
-        <x:v>图 P02-17</x:v>
+        <x:v>图 P02-14</x:v>
       </x:c>
     </x:row>
     <x:row r="193">
@@ -12991,31 +12991,31 @@
         <x:v>docs/en/part14/p02_legal_sft.md</x:v>
       </x:c>
       <x:c r="G193" s="4" t="n">
-        <x:v>1011</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="H193" s="4" t="str">
-        <x:v>P02-18</x:v>
+        <x:v>P02-15</x:v>
       </x:c>
       <x:c r="I193" s="4" t="str">
-        <x:v>Figure P02-18: P02 Version Evolution Roadmap</x:v>
+        <x:v>Figure P02-15: Training Packaging and Delivery Interface Diagram</x:v>
       </x:c>
       <x:c r="J193" s="4" t="str">
-        <x:v>Figure P02-18</x:v>
+        <x:v>Figure P02-15</x:v>
       </x:c>
       <x:c r="K193" s="4" t="str">
-        <x:v>docs/images/part14/p02/p02_18_version_timeline.svg</x:v>
+        <x:v>docs/images/part14/p02/p02_15_training_artifacts.svg</x:v>
       </x:c>
       <x:c r="L193" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M193" s="4" t="str">
-        <x:v>1377x768</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N193" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O193" s="4" t="str">
-        <x:v>P02 Version Evolution Roadmap.</x:v>
+        <x:v>Training Packaging and Delivery Interface Diagram.</x:v>
       </x:c>
       <x:c r="P193" s="4" t="str"/>
       <x:c r="Q193" s="4" t="str">
@@ -13027,10 +13027,10 @@
       <x:c r="S193" s="4" t="str"/>
       <x:c r="T193" s="4" t="str"/>
       <x:c r="U193" s="4" t="str">
-        <x:v>Figure P02-18：P02 版本演进路线图</x:v>
+        <x:v>Figure P02-15：训练封装与交付接口图</x:v>
       </x:c>
       <x:c r="V193" s="4" t="str">
-        <x:v>图 P02-18</x:v>
+        <x:v>图 P02-15</x:v>
       </x:c>
     </x:row>
     <x:row r="194">
@@ -13053,19 +13053,19 @@
         <x:v>docs/en/part14/p02_legal_sft.md</x:v>
       </x:c>
       <x:c r="G194" s="4" t="n">
-        <x:v>1072</x:v>
+        <x:v>828</x:v>
       </x:c>
       <x:c r="H194" s="4" t="str">
-        <x:v>P02-19</x:v>
+        <x:v>P02-16</x:v>
       </x:c>
       <x:c r="I194" s="4" t="str">
-        <x:v>Figure P02-19: Code–Artifact–Report Consistency Validation Diagram</x:v>
+        <x:v>Figure P02-16: P02 Core Metrics Dashboard</x:v>
       </x:c>
       <x:c r="J194" s="4" t="str">
-        <x:v>Figure P02-19</x:v>
+        <x:v>Figure P02-16</x:v>
       </x:c>
       <x:c r="K194" s="4" t="str">
-        <x:v>docs/images/part14/p02/p02_19_validation_chain.svg</x:v>
+        <x:v>docs/images/part14/p02/p02_16_metrics_dashboard.svg</x:v>
       </x:c>
       <x:c r="L194" s="4" t="str">
         <x:v>yes</x:v>
@@ -13077,7 +13077,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O194" s="4" t="str">
-        <x:v>Code–Artifact–Report Consistency Validation Diagram.</x:v>
+        <x:v>P02 Core Metrics Dashboard.</x:v>
       </x:c>
       <x:c r="P194" s="4" t="str"/>
       <x:c r="Q194" s="4" t="str">
@@ -13089,10 +13089,10 @@
       <x:c r="S194" s="4" t="str"/>
       <x:c r="T194" s="4" t="str"/>
       <x:c r="U194" s="4" t="str">
-        <x:v>Figure P02-19：代码—产物—报告一致性验证图</x:v>
+        <x:v>Figure P02-16：P02 核心指标总览图</x:v>
       </x:c>
       <x:c r="V194" s="4" t="str">
-        <x:v>图 P02-19</x:v>
+        <x:v>图 P02-16</x:v>
       </x:c>
     </x:row>
     <x:row r="195">
@@ -13115,31 +13115,31 @@
         <x:v>docs/en/part14/p02_legal_sft.md</x:v>
       </x:c>
       <x:c r="G195" s="4" t="n">
-        <x:v>1132</x:v>
+        <x:v>912</x:v>
       </x:c>
       <x:c r="H195" s="4" t="str">
-        <x:v>P02-20</x:v>
+        <x:v>P02-17</x:v>
       </x:c>
       <x:c r="I195" s="4" t="str">
-        <x:v>Figure P02-20: Cross-Industry Transfer Methodology Chain Diagram</x:v>
+        <x:v>Figure P02-17: 50-Sample Validation Protocol Diagram</x:v>
       </x:c>
       <x:c r="J195" s="4" t="str">
-        <x:v>Figure P02-20</x:v>
+        <x:v>Figure P02-17</x:v>
       </x:c>
       <x:c r="K195" s="4" t="str">
-        <x:v>docs/images/part14/p02/p02_20_cross_domain_transfer.svg</x:v>
+        <x:v>docs/images/part14/p02/p02_17_eval_sampling_protocol.svg</x:v>
       </x:c>
       <x:c r="L195" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M195" s="4" t="str">
-        <x:v>1377x768</x:v>
+        <x:v>1380x752</x:v>
       </x:c>
       <x:c r="N195" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O195" s="4" t="str">
-        <x:v>Cross-Industry Transfer Methodology Chain Diagram.</x:v>
+        <x:v>50-Sample Validation Protocol Diagram.</x:v>
       </x:c>
       <x:c r="P195" s="4" t="str"/>
       <x:c r="Q195" s="4" t="str">
@@ -13151,10 +13151,10 @@
       <x:c r="S195" s="4" t="str"/>
       <x:c r="T195" s="4" t="str"/>
       <x:c r="U195" s="4" t="str">
-        <x:v>Figure P02-20：行业迁移方法链图</x:v>
+        <x:v>Figure P02-17：50 条抽样验证流程图</x:v>
       </x:c>
       <x:c r="V195" s="4" t="str">
-        <x:v>图 P02-20</x:v>
+        <x:v>图 P02-17</x:v>
       </x:c>
     </x:row>
     <x:row r="196">
@@ -13168,40 +13168,40 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D196" s="4" t="str">
-        <x:v>P03</x:v>
+        <x:v>P02</x:v>
       </x:c>
       <x:c r="E196" s="4" t="str">
-        <x:v>Project 3: LLaVA Multimodal Instruction Data Factory</x:v>
+        <x:v>Project 2: Vertical-domain Expert SFT for Law</x:v>
       </x:c>
       <x:c r="F196" s="4" t="str">
-        <x:v>docs/en/part14/p03_llava_instruct.md</x:v>
+        <x:v>docs/en/part14/p02_legal_sft.md</x:v>
       </x:c>
       <x:c r="G196" s="4" t="n">
-        <x:v>183</x:v>
+        <x:v>1011</x:v>
       </x:c>
       <x:c r="H196" s="4" t="str">
-        <x:v>P03-1</x:v>
+        <x:v>P02-18</x:v>
       </x:c>
       <x:c r="I196" s="4" t="str">
-        <x:v>Figure P03-1: LLaVA Multimodal Instruction Data Factory Overview</x:v>
+        <x:v>Figure P02-18: P02 Version Evolution Roadmap</x:v>
       </x:c>
       <x:c r="J196" s="4" t="str">
-        <x:v>Figure P03-1</x:v>
+        <x:v>Figure P02-18</x:v>
       </x:c>
       <x:c r="K196" s="4" t="str">
-        <x:v>docs/images/part14/p03/p03_01_llava_factory_overview.svg</x:v>
+        <x:v>docs/images/part14/p02/p02_18_version_timeline.svg</x:v>
       </x:c>
       <x:c r="L196" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M196" s="4" t="str">
-        <x:v>900x491</x:v>
+        <x:v>1377x768</x:v>
       </x:c>
       <x:c r="N196" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O196" s="4" t="str">
-        <x:v>LLaVA Multimodal Instruction Data Factory Overview.</x:v>
+        <x:v>P02 Version Evolution Roadmap.</x:v>
       </x:c>
       <x:c r="P196" s="4" t="str"/>
       <x:c r="Q196" s="4" t="str">
@@ -13213,10 +13213,10 @@
       <x:c r="S196" s="4" t="str"/>
       <x:c r="T196" s="4" t="str"/>
       <x:c r="U196" s="4" t="str">
-        <x:v>Figure P03-1：LLaVA 多模态指令数据工厂总览</x:v>
+        <x:v>Figure P02-18：P02 版本演进路线图</x:v>
       </x:c>
       <x:c r="V196" s="4" t="str">
-        <x:v>图 P03-1</x:v>
+        <x:v>图 P02-18</x:v>
       </x:c>
     </x:row>
     <x:row r="197">
@@ -13230,40 +13230,40 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D197" s="4" t="str">
-        <x:v>P03</x:v>
+        <x:v>P02</x:v>
       </x:c>
       <x:c r="E197" s="4" t="str">
-        <x:v>Project 3: LLaVA Multimodal Instruction Data Factory</x:v>
+        <x:v>Project 2: Vertical-domain Expert SFT for Law</x:v>
       </x:c>
       <x:c r="F197" s="4" t="str">
-        <x:v>docs/en/part14/p03_llava_instruct.md</x:v>
+        <x:v>docs/en/part14/p02_legal_sft.md</x:v>
       </x:c>
       <x:c r="G197" s="4" t="n">
-        <x:v>263</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="H197" s="4" t="str">
-        <x:v>P03-2</x:v>
+        <x:v>P02-19</x:v>
       </x:c>
       <x:c r="I197" s="4" t="str">
-        <x:v>Figure P03-2: Multimodal Data Factory Responsibility Collaboration Diagram</x:v>
+        <x:v>Figure P02-19: Code–Artifact–Report Consistency Validation Diagram</x:v>
       </x:c>
       <x:c r="J197" s="4" t="str">
-        <x:v>Figure P03-2</x:v>
+        <x:v>Figure P02-19</x:v>
       </x:c>
       <x:c r="K197" s="4" t="str">
-        <x:v>docs/images/part14/p03/p03_02_roles_and_responsibilities.svg</x:v>
+        <x:v>docs/images/part14/p02/p02_19_validation_chain.svg</x:v>
       </x:c>
       <x:c r="L197" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M197" s="4" t="str">
-        <x:v>1344x768</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N197" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O197" s="4" t="str">
-        <x:v>Multimodal Data Factory Responsibility Collaboration Diagram.</x:v>
+        <x:v>Code–Artifact–Report Consistency Validation Diagram.</x:v>
       </x:c>
       <x:c r="P197" s="4" t="str"/>
       <x:c r="Q197" s="4" t="str">
@@ -13275,10 +13275,10 @@
       <x:c r="S197" s="4" t="str"/>
       <x:c r="T197" s="4" t="str"/>
       <x:c r="U197" s="4" t="str">
-        <x:v>Figure P03-2：多模态数据工厂职责协同图</x:v>
+        <x:v>Figure P02-19：代码—产物—报告一致性验证图</x:v>
       </x:c>
       <x:c r="V197" s="4" t="str">
-        <x:v>图 P03-2</x:v>
+        <x:v>图 P02-19</x:v>
       </x:c>
     </x:row>
     <x:row r="198">
@@ -13292,40 +13292,40 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D198" s="4" t="str">
-        <x:v>P03</x:v>
+        <x:v>P02</x:v>
       </x:c>
       <x:c r="E198" s="4" t="str">
-        <x:v>Project 3: LLaVA Multimodal Instruction Data Factory</x:v>
+        <x:v>Project 2: Vertical-domain Expert SFT for Law</x:v>
       </x:c>
       <x:c r="F198" s="4" t="str">
-        <x:v>docs/en/part14/p03_llava_instruct.md</x:v>
+        <x:v>docs/en/part14/p02_legal_sft.md</x:v>
       </x:c>
       <x:c r="G198" s="4" t="n">
-        <x:v>304</x:v>
+        <x:v>1132</x:v>
       </x:c>
       <x:c r="H198" s="4" t="str">
-        <x:v>P03-3</x:v>
+        <x:v>P02-20</x:v>
       </x:c>
       <x:c r="I198" s="4" t="str">
-        <x:v>Figure P03-3: Multimodal Asset Layering Diagram</x:v>
+        <x:v>Figure P02-20: Cross-Industry Transfer Methodology Chain Diagram</x:v>
       </x:c>
       <x:c r="J198" s="4" t="str">
-        <x:v>Figure P03-3</x:v>
+        <x:v>Figure P02-20</x:v>
       </x:c>
       <x:c r="K198" s="4" t="str">
-        <x:v>docs/images/part14/p03/p03_03_asset_layers.svg</x:v>
+        <x:v>docs/images/part14/p02/p02_20_cross_domain_transfer.svg</x:v>
       </x:c>
       <x:c r="L198" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M198" s="4" t="str">
-        <x:v>1024x512</x:v>
+        <x:v>1377x768</x:v>
       </x:c>
       <x:c r="N198" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O198" s="4" t="str">
-        <x:v>Multimodal Asset Layering Diagram.</x:v>
+        <x:v>Cross-Industry Transfer Methodology Chain Diagram.</x:v>
       </x:c>
       <x:c r="P198" s="4" t="str"/>
       <x:c r="Q198" s="4" t="str">
@@ -13337,10 +13337,10 @@
       <x:c r="S198" s="4" t="str"/>
       <x:c r="T198" s="4" t="str"/>
       <x:c r="U198" s="4" t="str">
-        <x:v>Figure P03-3：多模态资产分层示意图</x:v>
+        <x:v>Figure P02-20：行业迁移方法链图</x:v>
       </x:c>
       <x:c r="V198" s="4" t="str">
-        <x:v>图 P03-3</x:v>
+        <x:v>图 P02-20</x:v>
       </x:c>
     </x:row>
     <x:row r="199">
@@ -13363,31 +13363,31 @@
         <x:v>docs/en/part14/p03_llava_instruct.md</x:v>
       </x:c>
       <x:c r="G199" s="4" t="n">
-        <x:v>442</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="H199" s="4" t="str">
-        <x:v>P03-4</x:v>
+        <x:v>P03-1</x:v>
       </x:c>
       <x:c r="I199" s="4" t="str">
-        <x:v>Figure P03-4: Document Image Task Layering Diagram</x:v>
+        <x:v>Figure P03-1: LLaVA Multimodal Instruction Data Factory Overview</x:v>
       </x:c>
       <x:c r="J199" s="4" t="str">
-        <x:v>Figure P03-4</x:v>
+        <x:v>Figure P03-1</x:v>
       </x:c>
       <x:c r="K199" s="4" t="str">
-        <x:v>docs/images/part14/p03/p03_04_document_tasks.svg</x:v>
+        <x:v>docs/images/part14/p03/p03_01_llava_factory_overview.svg</x:v>
       </x:c>
       <x:c r="L199" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M199" s="4" t="str">
-        <x:v>1280x720</x:v>
+        <x:v>900x491</x:v>
       </x:c>
       <x:c r="N199" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O199" s="4" t="str">
-        <x:v>Document Image Task Layering Diagram.</x:v>
+        <x:v>LLaVA Multimodal Instruction Data Factory Overview.</x:v>
       </x:c>
       <x:c r="P199" s="4" t="str"/>
       <x:c r="Q199" s="4" t="str">
@@ -13399,10 +13399,10 @@
       <x:c r="S199" s="4" t="str"/>
       <x:c r="T199" s="4" t="str"/>
       <x:c r="U199" s="4" t="str">
-        <x:v>Figure P03-4：文档图像任务分层图</x:v>
+        <x:v>Figure P03-1：LLaVA 多模态指令数据工厂总览</x:v>
       </x:c>
       <x:c r="V199" s="4" t="str">
-        <x:v>图 P03-4</x:v>
+        <x:v>图 P03-1</x:v>
       </x:c>
     </x:row>
     <x:row r="200">
@@ -13425,31 +13425,31 @@
         <x:v>docs/en/part14/p03_llava_instruct.md</x:v>
       </x:c>
       <x:c r="G200" s="4" t="n">
-        <x:v>542</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="H200" s="4" t="str">
-        <x:v>P03-5</x:v>
+        <x:v>P03-2</x:v>
       </x:c>
       <x:c r="I200" s="4" t="str">
-        <x:v>Figure P03-5: Bounding Box Coordinate Conversion and Normalization Diagram</x:v>
+        <x:v>Figure P03-2: Multimodal Data Factory Responsibility Collaboration Diagram</x:v>
       </x:c>
       <x:c r="J200" s="4" t="str">
-        <x:v>Figure P03-5</x:v>
+        <x:v>Figure P03-2</x:v>
       </x:c>
       <x:c r="K200" s="4" t="str">
-        <x:v>docs/images/part14/p03/p03_05_bbox_alignment.svg</x:v>
+        <x:v>docs/images/part14/p03/p03_02_roles_and_responsibilities.svg</x:v>
       </x:c>
       <x:c r="L200" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M200" s="4" t="str">
-        <x:v>1024x576</x:v>
+        <x:v>1344x768</x:v>
       </x:c>
       <x:c r="N200" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O200" s="4" t="str">
-        <x:v>Bounding Box Coordinate Conversion and Normalization Diagram.</x:v>
+        <x:v>Multimodal Data Factory Responsibility Collaboration Diagram.</x:v>
       </x:c>
       <x:c r="P200" s="4" t="str"/>
       <x:c r="Q200" s="4" t="str">
@@ -13461,10 +13461,10 @@
       <x:c r="S200" s="4" t="str"/>
       <x:c r="T200" s="4" t="str"/>
       <x:c r="U200" s="4" t="str">
-        <x:v>Figure P03-5：bbox 坐标转换与归一化示意图</x:v>
+        <x:v>Figure P03-2：多模态数据工厂职责协同图</x:v>
       </x:c>
       <x:c r="V200" s="4" t="str">
-        <x:v>图 P03-5</x:v>
+        <x:v>图 P03-2</x:v>
       </x:c>
     </x:row>
     <x:row r="201">
@@ -13487,31 +13487,31 @@
         <x:v>docs/en/part14/p03_llava_instruct.md</x:v>
       </x:c>
       <x:c r="G201" s="4" t="n">
-        <x:v>711</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="H201" s="4" t="str">
-        <x:v>P03-6</x:v>
+        <x:v>P03-3</x:v>
       </x:c>
       <x:c r="I201" s="4" t="str">
-        <x:v>Figure P03-6: Sample Quality Inspection and Rollback Closure Loop Diagram</x:v>
+        <x:v>Figure P03-3: Multimodal Asset Layering Diagram</x:v>
       </x:c>
       <x:c r="J201" s="4" t="str">
-        <x:v>Figure P03-6</x:v>
+        <x:v>Figure P03-3</x:v>
       </x:c>
       <x:c r="K201" s="4" t="str">
-        <x:v>docs/images/part14/p03/p03_06_quality_loop.svg</x:v>
+        <x:v>docs/images/part14/p03/p03_03_asset_layers.svg</x:v>
       </x:c>
       <x:c r="L201" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M201" s="4" t="str">
-        <x:v>900x491</x:v>
+        <x:v>1024x512</x:v>
       </x:c>
       <x:c r="N201" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O201" s="4" t="str">
-        <x:v>Sample Quality Inspection and Rollback Closure Loop Diagram.</x:v>
+        <x:v>Multimodal Asset Layering Diagram.</x:v>
       </x:c>
       <x:c r="P201" s="4" t="str"/>
       <x:c r="Q201" s="4" t="str">
@@ -13523,10 +13523,10 @@
       <x:c r="S201" s="4" t="str"/>
       <x:c r="T201" s="4" t="str"/>
       <x:c r="U201" s="4" t="str">
-        <x:v>Figure P03-6：样本质检与回退闭环图</x:v>
+        <x:v>Figure P03-3：多模态资产分层示意图</x:v>
       </x:c>
       <x:c r="V201" s="4" t="str">
-        <x:v>图 P03-6</x:v>
+        <x:v>图 P03-3</x:v>
       </x:c>
     </x:row>
     <x:row r="202">
@@ -13549,31 +13549,31 @@
         <x:v>docs/en/part14/p03_llava_instruct.md</x:v>
       </x:c>
       <x:c r="G202" s="4" t="n">
-        <x:v>925</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="H202" s="4" t="str">
-        <x:v>P03-7</x:v>
+        <x:v>P03-4</x:v>
       </x:c>
       <x:c r="I202" s="4" t="str">
-        <x:v>Figure P03-7: Failure Sample Attribution Diagram</x:v>
+        <x:v>Figure P03-4: Document Image Task Layering Diagram</x:v>
       </x:c>
       <x:c r="J202" s="4" t="str">
-        <x:v>Figure P03-7</x:v>
+        <x:v>Figure P03-4</x:v>
       </x:c>
       <x:c r="K202" s="4" t="str">
-        <x:v>docs/images/part14/p03/p03_07_failure_attribution.svg</x:v>
+        <x:v>docs/images/part14/p03/p03_04_document_tasks.svg</x:v>
       </x:c>
       <x:c r="L202" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M202" s="4" t="str">
-        <x:v>900x503</x:v>
+        <x:v>1280x720</x:v>
       </x:c>
       <x:c r="N202" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O202" s="4" t="str">
-        <x:v>Failure Sample Attribution Diagram.</x:v>
+        <x:v>Document Image Task Layering Diagram.</x:v>
       </x:c>
       <x:c r="P202" s="4" t="str"/>
       <x:c r="Q202" s="4" t="str">
@@ -13585,10 +13585,10 @@
       <x:c r="S202" s="4" t="str"/>
       <x:c r="T202" s="4" t="str"/>
       <x:c r="U202" s="4" t="str">
-        <x:v>Figure P03-7：失败样本归因示意图</x:v>
+        <x:v>Figure P03-4：文档图像任务分层图</x:v>
       </x:c>
       <x:c r="V202" s="4" t="str">
-        <x:v>图 P03-7</x:v>
+        <x:v>图 P03-4</x:v>
       </x:c>
     </x:row>
     <x:row r="203">
@@ -13611,31 +13611,31 @@
         <x:v>docs/en/part14/p03_llava_instruct.md</x:v>
       </x:c>
       <x:c r="G203" s="4" t="n">
-        <x:v>980</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="H203" s="4" t="str">
-        <x:v>P03-8</x:v>
+        <x:v>P03-5</x:v>
       </x:c>
       <x:c r="I203" s="4" t="str">
-        <x:v>Figure P03-8: Project Validation Closure Loop Diagram</x:v>
+        <x:v>Figure P03-5: Bounding Box Coordinate Conversion and Normalization Diagram</x:v>
       </x:c>
       <x:c r="J203" s="4" t="str">
-        <x:v>Figure P03-8</x:v>
+        <x:v>Figure P03-5</x:v>
       </x:c>
       <x:c r="K203" s="4" t="str">
-        <x:v>docs/images/part14/p03/p03_08_validation_loop.svg</x:v>
+        <x:v>docs/images/part14/p03/p03_05_bbox_alignment.svg</x:v>
       </x:c>
       <x:c r="L203" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M203" s="4" t="str">
-        <x:v>900x491</x:v>
+        <x:v>1024x576</x:v>
       </x:c>
       <x:c r="N203" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O203" s="4" t="str">
-        <x:v>Project Validation Closure Loop Diagram.</x:v>
+        <x:v>Bounding Box Coordinate Conversion and Normalization Diagram.</x:v>
       </x:c>
       <x:c r="P203" s="4" t="str"/>
       <x:c r="Q203" s="4" t="str">
@@ -13647,10 +13647,10 @@
       <x:c r="S203" s="4" t="str"/>
       <x:c r="T203" s="4" t="str"/>
       <x:c r="U203" s="4" t="str">
-        <x:v>Figure P03-8：项目验证闭环图</x:v>
+        <x:v>Figure P03-5：bbox 坐标转换与归一化示意图</x:v>
       </x:c>
       <x:c r="V203" s="4" t="str">
-        <x:v>图 P03-8</x:v>
+        <x:v>图 P03-5</x:v>
       </x:c>
     </x:row>
     <x:row r="204">
@@ -13664,28 +13664,28 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D204" s="4" t="str">
-        <x:v>P04</x:v>
+        <x:v>P03</x:v>
       </x:c>
       <x:c r="E204" s="4" t="str">
-        <x:v>Project 4: Synthetic Math and Code Textbook Factory</x:v>
+        <x:v>Project 3: LLaVA Multimodal Instruction Data Factory</x:v>
       </x:c>
       <x:c r="F204" s="4" t="str">
-        <x:v>docs/en/part14/p04_synthetic_textbook.md</x:v>
+        <x:v>docs/en/part14/p03_llava_instruct.md</x:v>
       </x:c>
       <x:c r="G204" s="4" t="n">
-        <x:v>84</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="H204" s="4" t="str">
-        <x:v>P04-1</x:v>
+        <x:v>P03-6</x:v>
       </x:c>
       <x:c r="I204" s="4" t="str">
-        <x:v>Figure P04-1: Synthetic Mathematics and Code Textbook Factory Project Positioning Diagram</x:v>
+        <x:v>Figure P03-6: Sample Quality Inspection and Rollback Closure Loop Diagram</x:v>
       </x:c>
       <x:c r="J204" s="4" t="str">
-        <x:v>Figure P04-1</x:v>
+        <x:v>Figure P03-6</x:v>
       </x:c>
       <x:c r="K204" s="4" t="str">
-        <x:v>docs/images/part14/p04/p04_01_project_positioning.svg</x:v>
+        <x:v>docs/images/part14/p03/p03_06_quality_loop.svg</x:v>
       </x:c>
       <x:c r="L204" s="4" t="str">
         <x:v>yes</x:v>
@@ -13697,7 +13697,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O204" s="4" t="str">
-        <x:v>Synthetic Mathematics and Code Textbook Factory Project Positioning Diagram.</x:v>
+        <x:v>Sample Quality Inspection and Rollback Closure Loop Diagram.</x:v>
       </x:c>
       <x:c r="P204" s="4" t="str"/>
       <x:c r="Q204" s="4" t="str">
@@ -13709,10 +13709,10 @@
       <x:c r="S204" s="4" t="str"/>
       <x:c r="T204" s="4" t="str"/>
       <x:c r="U204" s="4" t="str">
-        <x:v>Figure P04-1：合成数学与代码教材工厂项目定位图</x:v>
+        <x:v>Figure P03-6：样本质检与回退闭环图</x:v>
       </x:c>
       <x:c r="V204" s="4" t="str">
-        <x:v>图 P04-1</x:v>
+        <x:v>图 P03-6</x:v>
       </x:c>
     </x:row>
     <x:row r="205">
@@ -13726,40 +13726,40 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D205" s="4" t="str">
-        <x:v>P04</x:v>
+        <x:v>P03</x:v>
       </x:c>
       <x:c r="E205" s="4" t="str">
-        <x:v>Project 4: Synthetic Math and Code Textbook Factory</x:v>
+        <x:v>Project 3: LLaVA Multimodal Instruction Data Factory</x:v>
       </x:c>
       <x:c r="F205" s="4" t="str">
-        <x:v>docs/en/part14/p04_synthetic_textbook.md</x:v>
+        <x:v>docs/en/part14/p03_llava_instruct.md</x:v>
       </x:c>
       <x:c r="G205" s="4" t="n">
-        <x:v>109</x:v>
+        <x:v>925</x:v>
       </x:c>
       <x:c r="H205" s="4" t="str">
-        <x:v>P04-2</x:v>
+        <x:v>P03-7</x:v>
       </x:c>
       <x:c r="I205" s="4" t="str">
-        <x:v>Figure P04-2: P04 Project Objectives and Scope Diagram</x:v>
+        <x:v>Figure P03-7: Failure Sample Attribution Diagram</x:v>
       </x:c>
       <x:c r="J205" s="4" t="str">
-        <x:v>Figure P04-2</x:v>
+        <x:v>Figure P03-7</x:v>
       </x:c>
       <x:c r="K205" s="4" t="str">
-        <x:v>docs/images/part14/p04/p04_02_goals_and_scope.svg</x:v>
+        <x:v>docs/images/part14/p03/p03_07_failure_attribution.svg</x:v>
       </x:c>
       <x:c r="L205" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M205" s="4" t="str">
-        <x:v>900x491</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N205" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O205" s="4" t="str">
-        <x:v>P04 Project Objectives and Scope Diagram.</x:v>
+        <x:v>Failure Sample Attribution Diagram.</x:v>
       </x:c>
       <x:c r="P205" s="4" t="str"/>
       <x:c r="Q205" s="4" t="str">
@@ -13771,10 +13771,10 @@
       <x:c r="S205" s="4" t="str"/>
       <x:c r="T205" s="4" t="str"/>
       <x:c r="U205" s="4" t="str">
-        <x:v>Figure P04-2：P04 项目目标与边界示意图</x:v>
+        <x:v>Figure P03-7：失败样本归因示意图</x:v>
       </x:c>
       <x:c r="V205" s="4" t="str">
-        <x:v>图 P04-2</x:v>
+        <x:v>图 P03-7</x:v>
       </x:c>
     </x:row>
     <x:row r="206">
@@ -13788,28 +13788,28 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D206" s="4" t="str">
-        <x:v>P04</x:v>
+        <x:v>P03</x:v>
       </x:c>
       <x:c r="E206" s="4" t="str">
-        <x:v>Project 4: Synthetic Math and Code Textbook Factory</x:v>
+        <x:v>Project 3: LLaVA Multimodal Instruction Data Factory</x:v>
       </x:c>
       <x:c r="F206" s="4" t="str">
-        <x:v>docs/en/part14/p04_synthetic_textbook.md</x:v>
+        <x:v>docs/en/part14/p03_llava_instruct.md</x:v>
       </x:c>
       <x:c r="G206" s="4" t="n">
-        <x:v>189</x:v>
+        <x:v>980</x:v>
       </x:c>
       <x:c r="H206" s="4" t="str">
-        <x:v>P04-3</x:v>
+        <x:v>P03-8</x:v>
       </x:c>
       <x:c r="I206" s="4" t="str">
-        <x:v>Figure P04-3: P04 Overall Architecture Overview Diagram</x:v>
+        <x:v>Figure P03-8: Project Validation Closure Loop Diagram</x:v>
       </x:c>
       <x:c r="J206" s="4" t="str">
-        <x:v>Figure P04-3</x:v>
+        <x:v>Figure P03-8</x:v>
       </x:c>
       <x:c r="K206" s="4" t="str">
-        <x:v>docs/images/part14/p04/p04_03_pipeline_overview.svg</x:v>
+        <x:v>docs/images/part14/p03/p03_08_validation_loop.svg</x:v>
       </x:c>
       <x:c r="L206" s="4" t="str">
         <x:v>yes</x:v>
@@ -13821,11 +13821,9 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O206" s="4" t="str">
-        <x:v>P04 Overall Architecture Overview Diagram.</x:v>
-      </x:c>
-      <x:c r="P206" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Project 4: Synthetic Math and Code Textbook Factory; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>Project Validation Closure Loop Diagram.</x:v>
+      </x:c>
+      <x:c r="P206" s="4" t="str"/>
       <x:c r="Q206" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -13835,10 +13833,10 @@
       <x:c r="S206" s="4" t="str"/>
       <x:c r="T206" s="4" t="str"/>
       <x:c r="U206" s="4" t="str">
-        <x:v>Figure P04-3：P04 整体架构总览图</x:v>
+        <x:v>Figure P03-8：项目验证闭环图</x:v>
       </x:c>
       <x:c r="V206" s="4" t="str">
-        <x:v>图 P04-3</x:v>
+        <x:v>图 P03-8</x:v>
       </x:c>
     </x:row>
     <x:row r="207">
@@ -13861,19 +13859,19 @@
         <x:v>docs/en/part14/p04_synthetic_textbook.md</x:v>
       </x:c>
       <x:c r="G207" s="4" t="n">
-        <x:v>233</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H207" s="4" t="str">
-        <x:v>P04-4</x:v>
+        <x:v>P04-1</x:v>
       </x:c>
       <x:c r="I207" s="4" t="str">
-        <x:v>Figure P04-4: Textbook Factory Responsibility Collaboration Diagram</x:v>
+        <x:v>Figure P04-1: Synthetic Mathematics and Code Textbook Factory Project Positioning Diagram</x:v>
       </x:c>
       <x:c r="J207" s="4" t="str">
-        <x:v>Figure P04-4</x:v>
+        <x:v>Figure P04-1</x:v>
       </x:c>
       <x:c r="K207" s="4" t="str">
-        <x:v>docs/images/part14/p04/p04_04_roles_and_responsibilities.svg</x:v>
+        <x:v>docs/images/part14/p04/p04_01_project_positioning.svg</x:v>
       </x:c>
       <x:c r="L207" s="4" t="str">
         <x:v>yes</x:v>
@@ -13885,7 +13883,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O207" s="4" t="str">
-        <x:v>Textbook Factory Responsibility Collaboration Diagram.</x:v>
+        <x:v>Synthetic Mathematics and Code Textbook Factory Project Positioning Diagram.</x:v>
       </x:c>
       <x:c r="P207" s="4" t="str"/>
       <x:c r="Q207" s="4" t="str">
@@ -13897,10 +13895,10 @@
       <x:c r="S207" s="4" t="str"/>
       <x:c r="T207" s="4" t="str"/>
       <x:c r="U207" s="4" t="str">
-        <x:v>Figure P04-4：教材工厂职责协同图</x:v>
+        <x:v>Figure P04-1：合成数学与代码教材工厂项目定位图</x:v>
       </x:c>
       <x:c r="V207" s="4" t="str">
-        <x:v>图 P04-4</x:v>
+        <x:v>图 P04-1</x:v>
       </x:c>
     </x:row>
     <x:row r="208">
@@ -13923,31 +13921,31 @@
         <x:v>docs/en/part14/p04_synthetic_textbook.md</x:v>
       </x:c>
       <x:c r="G208" s="4" t="n">
-        <x:v>279</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="H208" s="4" t="str">
-        <x:v>P04-5</x:v>
+        <x:v>P04-2</x:v>
       </x:c>
       <x:c r="I208" s="4" t="str">
-        <x:v>Figure P04-5: Mapping from Seed Problems to Chapter Plans</x:v>
+        <x:v>Figure P04-2: P04 Project Objectives and Scope Diagram</x:v>
       </x:c>
       <x:c r="J208" s="4" t="str">
-        <x:v>Figure P04-5</x:v>
+        <x:v>Figure P04-2</x:v>
       </x:c>
       <x:c r="K208" s="4" t="str">
-        <x:v>docs/images/part14/p04/p04_05_seed_to_plan.svg</x:v>
+        <x:v>docs/images/part14/p04/p04_02_goals_and_scope.svg</x:v>
       </x:c>
       <x:c r="L208" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M208" s="4" t="str">
-        <x:v>1800x982</x:v>
+        <x:v>900x491</x:v>
       </x:c>
       <x:c r="N208" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O208" s="4" t="str">
-        <x:v>Mapping from Seed Problems to Chapter Plans.</x:v>
+        <x:v>P04 Project Objectives and Scope Diagram.</x:v>
       </x:c>
       <x:c r="P208" s="4" t="str"/>
       <x:c r="Q208" s="4" t="str">
@@ -13959,10 +13957,10 @@
       <x:c r="S208" s="4" t="str"/>
       <x:c r="T208" s="4" t="str"/>
       <x:c r="U208" s="4" t="str">
-        <x:v>Figure P04-5：种子题到章节计划的映射图</x:v>
+        <x:v>Figure P04-2：P04 项目目标与边界示意图</x:v>
       </x:c>
       <x:c r="V208" s="4" t="str">
-        <x:v>图 P04-5</x:v>
+        <x:v>图 P04-2</x:v>
       </x:c>
     </x:row>
     <x:row r="209">
@@ -13985,33 +13983,35 @@
         <x:v>docs/en/part14/p04_synthetic_textbook.md</x:v>
       </x:c>
       <x:c r="G209" s="4" t="n">
-        <x:v>318</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="H209" s="4" t="str">
-        <x:v>P04-6</x:v>
+        <x:v>P04-3</x:v>
       </x:c>
       <x:c r="I209" s="4" t="str">
-        <x:v>Figure P04-6: Evol-Instruct Evolution Path Diagram</x:v>
+        <x:v>Figure P04-3: P04 Overall Architecture Overview Diagram</x:v>
       </x:c>
       <x:c r="J209" s="4" t="str">
-        <x:v>Figure P04-6</x:v>
+        <x:v>Figure P04-3</x:v>
       </x:c>
       <x:c r="K209" s="4" t="str">
-        <x:v>docs/images/part14/p04/p04_06_evol_path.svg</x:v>
+        <x:v>docs/images/part14/p04/p04_03_pipeline_overview.svg</x:v>
       </x:c>
       <x:c r="L209" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M209" s="4" t="str">
-        <x:v>1672x941</x:v>
+        <x:v>900x491</x:v>
       </x:c>
       <x:c r="N209" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O209" s="4" t="str">
-        <x:v>Evol-Instruct Evolution Path Diagram.</x:v>
-      </x:c>
-      <x:c r="P209" s="4" t="str"/>
+        <x:v>P04 Overall Architecture Overview Diagram.</x:v>
+      </x:c>
+      <x:c r="P209" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Project 4: Synthetic Math and Code Textbook Factory; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q209" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -14021,10 +14021,10 @@
       <x:c r="S209" s="4" t="str"/>
       <x:c r="T209" s="4" t="str"/>
       <x:c r="U209" s="4" t="str">
-        <x:v>Figure P04-6：Evol-Instruct 进化路径图</x:v>
+        <x:v>Figure P04-3：P04 整体架构总览图</x:v>
       </x:c>
       <x:c r="V209" s="4" t="str">
-        <x:v>图 P04-6</x:v>
+        <x:v>图 P04-3</x:v>
       </x:c>
     </x:row>
     <x:row r="210">
@@ -14047,35 +14047,33 @@
         <x:v>docs/en/part14/p04_synthetic_textbook.md</x:v>
       </x:c>
       <x:c r="G210" s="4" t="n">
-        <x:v>357</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="H210" s="4" t="str">
-        <x:v>P04-7</x:v>
+        <x:v>P04-4</x:v>
       </x:c>
       <x:c r="I210" s="4" t="str">
-        <x:v>Figure P04-7: CoT vs. PoT Comparison Diagram</x:v>
+        <x:v>Figure P04-4: Textbook Factory Responsibility Collaboration Diagram</x:v>
       </x:c>
       <x:c r="J210" s="4" t="str">
-        <x:v>Figure P04-7</x:v>
+        <x:v>Figure P04-4</x:v>
       </x:c>
       <x:c r="K210" s="4" t="str">
-        <x:v>docs/images/part14/p04/p04_07_cot_vs_pot.svg</x:v>
+        <x:v>docs/images/part14/p04/p04_04_roles_and_responsibilities.svg</x:v>
       </x:c>
       <x:c r="L210" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M210" s="4" t="str">
-        <x:v>1672x941</x:v>
+        <x:v>900x491</x:v>
       </x:c>
       <x:c r="N210" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O210" s="4" t="str">
-        <x:v>CoT vs. PoT Comparison Diagram.</x:v>
-      </x:c>
-      <x:c r="P210" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Project 4: Synthetic Math and Code Textbook Factory; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>Textbook Factory Responsibility Collaboration Diagram.</x:v>
+      </x:c>
+      <x:c r="P210" s="4" t="str"/>
       <x:c r="Q210" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -14085,10 +14083,10 @@
       <x:c r="S210" s="4" t="str"/>
       <x:c r="T210" s="4" t="str"/>
       <x:c r="U210" s="4" t="str">
-        <x:v>Figure P04-7：CoT 与 PoT 对比图</x:v>
+        <x:v>Figure P04-4：教材工厂职责协同图</x:v>
       </x:c>
       <x:c r="V210" s="4" t="str">
-        <x:v>图 P04-7</x:v>
+        <x:v>图 P04-4</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
@@ -14111,35 +14109,33 @@
         <x:v>docs/en/part14/p04_synthetic_textbook.md</x:v>
       </x:c>
       <x:c r="G211" s="4" t="n">
-        <x:v>398</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H211" s="4" t="str">
-        <x:v>P04-8</x:v>
+        <x:v>P04-5</x:v>
       </x:c>
       <x:c r="I211" s="4" t="str">
-        <x:v>Figure P04-8: Generation Pipeline Detail Diagram</x:v>
+        <x:v>Figure P04-5: Mapping from Seed Problems to Chapter Plans</x:v>
       </x:c>
       <x:c r="J211" s="4" t="str">
-        <x:v>Figure P04-8</x:v>
+        <x:v>Figure P04-5</x:v>
       </x:c>
       <x:c r="K211" s="4" t="str">
-        <x:v>docs/images/part14/p04/p04_08_generation_chain.svg</x:v>
+        <x:v>docs/images/part14/p04/p04_05_seed_to_plan.svg</x:v>
       </x:c>
       <x:c r="L211" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M211" s="4" t="str">
-        <x:v>1296x724</x:v>
+        <x:v>1800x982</x:v>
       </x:c>
       <x:c r="N211" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O211" s="4" t="str">
-        <x:v>Generation Pipeline Detail Diagram.</x:v>
-      </x:c>
-      <x:c r="P211" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Project 4: Synthetic Math and Code Textbook Factory; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>Mapping from Seed Problems to Chapter Plans.</x:v>
+      </x:c>
+      <x:c r="P211" s="4" t="str"/>
       <x:c r="Q211" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -14149,10 +14145,10 @@
       <x:c r="S211" s="4" t="str"/>
       <x:c r="T211" s="4" t="str"/>
       <x:c r="U211" s="4" t="str">
-        <x:v>Figure P04-8：生成链路细化图</x:v>
+        <x:v>Figure P04-5：种子题到章节计划的映射图</x:v>
       </x:c>
       <x:c r="V211" s="4" t="str">
-        <x:v>图 P04-8</x:v>
+        <x:v>图 P04-5</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
@@ -14175,31 +14171,31 @@
         <x:v>docs/en/part14/p04_synthetic_textbook.md</x:v>
       </x:c>
       <x:c r="G212" s="4" t="n">
-        <x:v>428</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="H212" s="4" t="str">
-        <x:v>P04-9</x:v>
+        <x:v>P04-6</x:v>
       </x:c>
       <x:c r="I212" s="4" t="str">
-        <x:v>Figure P04-9: Sandbox Validation Execution Path Diagram</x:v>
+        <x:v>Figure P04-6: Evol-Instruct Evolution Path Diagram</x:v>
       </x:c>
       <x:c r="J212" s="4" t="str">
-        <x:v>Figure P04-9</x:v>
+        <x:v>Figure P04-6</x:v>
       </x:c>
       <x:c r="K212" s="4" t="str">
-        <x:v>docs/images/part14/p04/p04_09_sandbox_validation.svg</x:v>
+        <x:v>docs/images/part14/p04/p04_06_evol_path.svg</x:v>
       </x:c>
       <x:c r="L212" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M212" s="4" t="str">
-        <x:v>1296x707</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N212" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O212" s="4" t="str">
-        <x:v>Sandbox Validation Execution Path Diagram.</x:v>
+        <x:v>Evol-Instruct Evolution Path Diagram.</x:v>
       </x:c>
       <x:c r="P212" s="4" t="str"/>
       <x:c r="Q212" s="4" t="str">
@@ -14211,10 +14207,10 @@
       <x:c r="S212" s="4" t="str"/>
       <x:c r="T212" s="4" t="str"/>
       <x:c r="U212" s="4" t="str">
-        <x:v>Figure P04-9：沙箱验证执行路径图</x:v>
+        <x:v>Figure P04-6：Evol-Instruct 进化路径图</x:v>
       </x:c>
       <x:c r="V212" s="4" t="str">
-        <x:v>图 P04-9</x:v>
+        <x:v>图 P04-6</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
@@ -14237,33 +14233,35 @@
         <x:v>docs/en/part14/p04_synthetic_textbook.md</x:v>
       </x:c>
       <x:c r="G213" s="4" t="n">
-        <x:v>474</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="H213" s="4" t="str">
-        <x:v>P04-10</x:v>
+        <x:v>P04-7</x:v>
       </x:c>
       <x:c r="I213" s="4" t="str">
-        <x:v>Figure P04-10: Textbook Packaging Artifact Relationship Diagram</x:v>
+        <x:v>Figure P04-7: CoT vs. PoT Comparison Diagram</x:v>
       </x:c>
       <x:c r="J213" s="4" t="str">
-        <x:v>Figure P04-10</x:v>
+        <x:v>Figure P04-7</x:v>
       </x:c>
       <x:c r="K213" s="4" t="str">
-        <x:v>docs/images/part14/p04/p04_10_packaging_outputs.svg</x:v>
+        <x:v>docs/images/part14/p04/p04_07_cot_vs_pot.svg</x:v>
       </x:c>
       <x:c r="L213" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M213" s="4" t="str">
-        <x:v>900x503</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N213" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O213" s="4" t="str">
-        <x:v>Textbook Packaging Artifact Relationship Diagram.</x:v>
-      </x:c>
-      <x:c r="P213" s="4" t="str"/>
+        <x:v>CoT vs. PoT Comparison Diagram.</x:v>
+      </x:c>
+      <x:c r="P213" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Project 4: Synthetic Math and Code Textbook Factory; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q213" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -14273,10 +14271,10 @@
       <x:c r="S213" s="4" t="str"/>
       <x:c r="T213" s="4" t="str"/>
       <x:c r="U213" s="4" t="str">
-        <x:v>Figure P04-10：教材打包产物关系图</x:v>
+        <x:v>Figure P04-7：CoT 与 PoT 对比图</x:v>
       </x:c>
       <x:c r="V213" s="4" t="str">
-        <x:v>图 P04-10</x:v>
+        <x:v>图 P04-7</x:v>
       </x:c>
     </x:row>
     <x:row r="214">
@@ -14299,33 +14297,35 @@
         <x:v>docs/en/part14/p04_synthetic_textbook.md</x:v>
       </x:c>
       <x:c r="G214" s="4" t="n">
-        <x:v>518</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="H214" s="4" t="str">
-        <x:v>P04-11</x:v>
+        <x:v>P04-8</x:v>
       </x:c>
       <x:c r="I214" s="4" t="str">
-        <x:v>Figure P04-11: Training Encapsulation Interface Diagram</x:v>
+        <x:v>Figure P04-8: Generation Pipeline Detail Diagram</x:v>
       </x:c>
       <x:c r="J214" s="4" t="str">
-        <x:v>Figure P04-11</x:v>
+        <x:v>Figure P04-8</x:v>
       </x:c>
       <x:c r="K214" s="4" t="str">
-        <x:v>docs/images/part14/p04/p04_11_training_interface.svg</x:v>
+        <x:v>docs/images/part14/p04/p04_08_generation_chain.svg</x:v>
       </x:c>
       <x:c r="L214" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M214" s="4" t="str">
-        <x:v>1800x982</x:v>
+        <x:v>1296x724</x:v>
       </x:c>
       <x:c r="N214" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O214" s="4" t="str">
-        <x:v>Training Encapsulation Interface Diagram.</x:v>
-      </x:c>
-      <x:c r="P214" s="4" t="str"/>
+        <x:v>Generation Pipeline Detail Diagram.</x:v>
+      </x:c>
+      <x:c r="P214" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Project 4: Synthetic Math and Code Textbook Factory; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q214" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -14335,10 +14335,10 @@
       <x:c r="S214" s="4" t="str"/>
       <x:c r="T214" s="4" t="str"/>
       <x:c r="U214" s="4" t="str">
-        <x:v>Figure P04-11：训练封装接口图</x:v>
+        <x:v>Figure P04-8：生成链路细化图</x:v>
       </x:c>
       <x:c r="V214" s="4" t="str">
-        <x:v>图 P04-11</x:v>
+        <x:v>图 P04-8</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
@@ -14352,44 +14352,42 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D215" s="4" t="str">
-        <x:v>P05</x:v>
+        <x:v>P04</x:v>
       </x:c>
       <x:c r="E215" s="4" t="str">
-        <x:v>Project 5: Multimodal RAG Enterprise Financial Report Assistant</x:v>
+        <x:v>Project 4: Synthetic Math and Code Textbook Factory</x:v>
       </x:c>
       <x:c r="F215" s="4" t="str">
-        <x:v>docs/en/part14/p05_mm_rag.md</x:v>
+        <x:v>docs/en/part14/p04_synthetic_textbook.md</x:v>
       </x:c>
       <x:c r="G215" s="4" t="n">
-        <x:v>177</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="H215" s="4" t="str">
-        <x:v>P05-1</x:v>
+        <x:v>P04-9</x:v>
       </x:c>
       <x:c r="I215" s="4" t="str">
-        <x:v>Figure P05-1: Overall architecture diagram of the multimodal RAG financial report assistant</x:v>
+        <x:v>Figure P04-9: Sandbox Validation Execution Path Diagram</x:v>
       </x:c>
       <x:c r="J215" s="4" t="str">
-        <x:v>Figure P05-1</x:v>
+        <x:v>Figure P04-9</x:v>
       </x:c>
       <x:c r="K215" s="4" t="str">
-        <x:v>docs/images/part14/p05/p05_01_overall_architecture.svg</x:v>
+        <x:v>docs/images/part14/p04/p04_09_sandbox_validation.svg</x:v>
       </x:c>
       <x:c r="L215" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M215" s="4" t="str">
-        <x:v>1800x982</x:v>
+        <x:v>1296x707</x:v>
       </x:c>
       <x:c r="N215" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O215" s="4" t="str">
-        <x:v>Overall architecture diagram of the multimodal RAG financial report assistant.</x:v>
-      </x:c>
-      <x:c r="P215" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Project 5: Multimodal RAG Enterprise Financial Report Assistant; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>Sandbox Validation Execution Path Diagram.</x:v>
+      </x:c>
+      <x:c r="P215" s="4" t="str"/>
       <x:c r="Q215" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -14399,10 +14397,10 @@
       <x:c r="S215" s="4" t="str"/>
       <x:c r="T215" s="4" t="str"/>
       <x:c r="U215" s="4" t="str">
-        <x:v>Figure P05-1：多模态 RAG 财报助手总体架构图</x:v>
+        <x:v>Figure P04-9：沙箱验证执行路径图</x:v>
       </x:c>
       <x:c r="V215" s="4" t="str">
-        <x:v>图 P05-1</x:v>
+        <x:v>图 P04-9</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
@@ -14416,44 +14414,42 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D216" s="4" t="str">
-        <x:v>P05</x:v>
+        <x:v>P04</x:v>
       </x:c>
       <x:c r="E216" s="4" t="str">
-        <x:v>Project 5: Multimodal RAG Enterprise Financial Report Assistant</x:v>
+        <x:v>Project 4: Synthetic Math and Code Textbook Factory</x:v>
       </x:c>
       <x:c r="F216" s="4" t="str">
-        <x:v>docs/en/part14/p05_mm_rag.md</x:v>
+        <x:v>docs/en/part14/p04_synthetic_textbook.md</x:v>
       </x:c>
       <x:c r="G216" s="4" t="n">
-        <x:v>259</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="H216" s="4" t="str">
-        <x:v>P05-2</x:v>
+        <x:v>P04-10</x:v>
       </x:c>
       <x:c r="I216" s="4" t="str">
-        <x:v>Figure P05-2: Comparison of Vision-First and OCR-First approaches</x:v>
+        <x:v>Figure P04-10: Textbook Packaging Artifact Relationship Diagram</x:v>
       </x:c>
       <x:c r="J216" s="4" t="str">
-        <x:v>Figure P05-2</x:v>
+        <x:v>Figure P04-10</x:v>
       </x:c>
       <x:c r="K216" s="4" t="str">
-        <x:v>docs/images/part14/p05/p05_02_vision_vs_ocr.svg</x:v>
+        <x:v>docs/images/part14/p04/p04_10_packaging_outputs.svg</x:v>
       </x:c>
       <x:c r="L216" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M216" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N216" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O216" s="4" t="str">
-        <x:v>Comparison of Vision-First and OCR-First approaches.</x:v>
-      </x:c>
-      <x:c r="P216" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Project 5: Multimodal RAG Enterprise Financial Report Assistant; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>Textbook Packaging Artifact Relationship Diagram.</x:v>
+      </x:c>
+      <x:c r="P216" s="4" t="str"/>
       <x:c r="Q216" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -14463,10 +14459,10 @@
       <x:c r="S216" s="4" t="str"/>
       <x:c r="T216" s="4" t="str"/>
       <x:c r="U216" s="4" t="str">
-        <x:v>Figure P05-2：Vision-first 与 OCR-first 路线对比图</x:v>
+        <x:v>Figure P04-10：教材打包产物关系图</x:v>
       </x:c>
       <x:c r="V216" s="4" t="str">
-        <x:v>图 P05-2</x:v>
+        <x:v>图 P04-10</x:v>
       </x:c>
     </x:row>
     <x:row r="217">
@@ -14480,28 +14476,28 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D217" s="4" t="str">
-        <x:v>P05</x:v>
+        <x:v>P04</x:v>
       </x:c>
       <x:c r="E217" s="4" t="str">
-        <x:v>Project 5: Multimodal RAG Enterprise Financial Report Assistant</x:v>
+        <x:v>Project 4: Synthetic Math and Code Textbook Factory</x:v>
       </x:c>
       <x:c r="F217" s="4" t="str">
-        <x:v>docs/en/part14/p05_mm_rag.md</x:v>
+        <x:v>docs/en/part14/p04_synthetic_textbook.md</x:v>
       </x:c>
       <x:c r="G217" s="4" t="n">
-        <x:v>347</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="H217" s="4" t="str">
-        <x:v>P05-3</x:v>
+        <x:v>P04-11</x:v>
       </x:c>
       <x:c r="I217" s="4" t="str">
-        <x:v>Figure P05-3: Page assets and page number mapping diagram</x:v>
+        <x:v>Figure P04-11: Training Encapsulation Interface Diagram</x:v>
       </x:c>
       <x:c r="J217" s="4" t="str">
-        <x:v>Figure P05-3</x:v>
+        <x:v>Figure P04-11</x:v>
       </x:c>
       <x:c r="K217" s="4" t="str">
-        <x:v>docs/images/part14/p05/p05_03_page_assets.svg</x:v>
+        <x:v>docs/images/part14/p04/p04_11_training_interface.svg</x:v>
       </x:c>
       <x:c r="L217" s="4" t="str">
         <x:v>yes</x:v>
@@ -14513,7 +14509,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O217" s="4" t="str">
-        <x:v>Page assets and page number mapping diagram.</x:v>
+        <x:v>Training Encapsulation Interface Diagram.</x:v>
       </x:c>
       <x:c r="P217" s="4" t="str"/>
       <x:c r="Q217" s="4" t="str">
@@ -14525,10 +14521,10 @@
       <x:c r="S217" s="4" t="str"/>
       <x:c r="T217" s="4" t="str"/>
       <x:c r="U217" s="4" t="str">
-        <x:v>Figure P05-3：页面资产与页码映射示意图</x:v>
+        <x:v>Figure P04-11：训练封装接口图</x:v>
       </x:c>
       <x:c r="V217" s="4" t="str">
-        <x:v>图 P05-3</x:v>
+        <x:v>图 P04-11</x:v>
       </x:c>
     </x:row>
     <x:row r="218">
@@ -14551,19 +14547,19 @@
         <x:v>docs/en/part14/p05_mm_rag.md</x:v>
       </x:c>
       <x:c r="G218" s="4" t="n">
-        <x:v>380</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="H218" s="4" t="str">
-        <x:v>P05-4</x:v>
+        <x:v>P05-1</x:v>
       </x:c>
       <x:c r="I218" s="4" t="str">
-        <x:v>Figure P05-4: PDF page rendering and visual index construction diagram</x:v>
+        <x:v>Figure P05-1: Overall architecture diagram of the multimodal RAG financial report assistant</x:v>
       </x:c>
       <x:c r="J218" s="4" t="str">
-        <x:v>Figure P05-4</x:v>
+        <x:v>Figure P05-1</x:v>
       </x:c>
       <x:c r="K218" s="4" t="str">
-        <x:v>docs/images/part14/p05/p05_04_indexing_pipeline.svg</x:v>
+        <x:v>docs/images/part14/p05/p05_01_overall_architecture.svg</x:v>
       </x:c>
       <x:c r="L218" s="4" t="str">
         <x:v>yes</x:v>
@@ -14575,9 +14571,11 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O218" s="4" t="str">
-        <x:v>PDF page rendering and visual index construction diagram.</x:v>
-      </x:c>
-      <x:c r="P218" s="4" t="str"/>
+        <x:v>Overall architecture diagram of the multimodal RAG financial report assistant.</x:v>
+      </x:c>
+      <x:c r="P218" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Project 5: Multimodal RAG Enterprise Financial Report Assistant; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q218" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -14587,10 +14585,10 @@
       <x:c r="S218" s="4" t="str"/>
       <x:c r="T218" s="4" t="str"/>
       <x:c r="U218" s="4" t="str">
-        <x:v>Figure P05-4：PDF 页面渲染与视觉索引构建图</x:v>
+        <x:v>Figure P05-1：多模态 RAG 财报助手总体架构图</x:v>
       </x:c>
       <x:c r="V218" s="4" t="str">
-        <x:v>图 P05-4</x:v>
+        <x:v>图 P05-1</x:v>
       </x:c>
     </x:row>
     <x:row r="219">
@@ -14613,33 +14611,35 @@
         <x:v>docs/en/part14/p05_mm_rag.md</x:v>
       </x:c>
       <x:c r="G219" s="4" t="n">
-        <x:v>433</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="H219" s="4" t="str">
-        <x:v>P05-5</x:v>
+        <x:v>P05-2</x:v>
       </x:c>
       <x:c r="I219" s="4" t="str">
-        <x:v>Figure P05-5: Top-K multi-page recall and table-of-contents page filtering diagram</x:v>
+        <x:v>Figure P05-2: Comparison of Vision-First and OCR-First approaches</x:v>
       </x:c>
       <x:c r="J219" s="4" t="str">
-        <x:v>Figure P05-5</x:v>
+        <x:v>Figure P05-2</x:v>
       </x:c>
       <x:c r="K219" s="4" t="str">
-        <x:v>docs/images/part14/p05/p05_05_topk_filtering.svg</x:v>
+        <x:v>docs/images/part14/p05/p05_02_vision_vs_ocr.svg</x:v>
       </x:c>
       <x:c r="L219" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M219" s="4" t="str">
-        <x:v>1800x982</x:v>
+        <x:v>1800x1005</x:v>
       </x:c>
       <x:c r="N219" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O219" s="4" t="str">
-        <x:v>Top-K multi-page recall and table-of-contents page filtering diagram.</x:v>
-      </x:c>
-      <x:c r="P219" s="4" t="str"/>
+        <x:v>Comparison of Vision-First and OCR-First approaches.</x:v>
+      </x:c>
+      <x:c r="P219" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Project 5: Multimodal RAG Enterprise Financial Report Assistant; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q219" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -14649,10 +14649,10 @@
       <x:c r="S219" s="4" t="str"/>
       <x:c r="T219" s="4" t="str"/>
       <x:c r="U219" s="4" t="str">
-        <x:v>Figure P05-5：Top-K 多页召回与目录页过滤示意图</x:v>
+        <x:v>Figure P05-2：Vision-first 与 OCR-first 路线对比图</x:v>
       </x:c>
       <x:c r="V219" s="4" t="str">
-        <x:v>图 P05-5</x:v>
+        <x:v>图 P05-2</x:v>
       </x:c>
     </x:row>
     <x:row r="220">
@@ -14675,19 +14675,19 @@
         <x:v>docs/en/part14/p05_mm_rag.md</x:v>
       </x:c>
       <x:c r="G220" s="4" t="n">
-        <x:v>505</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="H220" s="4" t="str">
-        <x:v>P05-6</x:v>
+        <x:v>P05-3</x:v>
       </x:c>
       <x:c r="I220" s="4" t="str">
-        <x:v>Figure P05-6: Multi-image context injection and answer constraint diagram</x:v>
+        <x:v>Figure P05-3: Page assets and page number mapping diagram</x:v>
       </x:c>
       <x:c r="J220" s="4" t="str">
-        <x:v>Figure P05-6</x:v>
+        <x:v>Figure P05-3</x:v>
       </x:c>
       <x:c r="K220" s="4" t="str">
-        <x:v>docs/images/part14/p05/p05_06_multi_image_prompting.svg</x:v>
+        <x:v>docs/images/part14/p05/p05_03_page_assets.svg</x:v>
       </x:c>
       <x:c r="L220" s="4" t="str">
         <x:v>yes</x:v>
@@ -14699,7 +14699,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O220" s="4" t="str">
-        <x:v>Multi-image context injection and answer constraint diagram.</x:v>
+        <x:v>Page assets and page number mapping diagram.</x:v>
       </x:c>
       <x:c r="P220" s="4" t="str"/>
       <x:c r="Q220" s="4" t="str">
@@ -14711,10 +14711,10 @@
       <x:c r="S220" s="4" t="str"/>
       <x:c r="T220" s="4" t="str"/>
       <x:c r="U220" s="4" t="str">
-        <x:v>Figure P05-6：多图上下文注入与回答约束图</x:v>
+        <x:v>Figure P05-3：页面资产与页码映射示意图</x:v>
       </x:c>
       <x:c r="V220" s="4" t="str">
-        <x:v>图 P05-6</x:v>
+        <x:v>图 P05-3</x:v>
       </x:c>
     </x:row>
     <x:row r="221">
@@ -14737,31 +14737,31 @@
         <x:v>docs/en/part14/p05_mm_rag.md</x:v>
       </x:c>
       <x:c r="G221" s="4" t="n">
-        <x:v>665</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="H221" s="4" t="str">
-        <x:v>P05-7</x:v>
+        <x:v>P05-4</x:v>
       </x:c>
       <x:c r="I221" s="4" t="str">
-        <x:v>Figure P05-7: Dual-layer evaluation framework for retrieval and answer quality</x:v>
+        <x:v>Figure P05-4: PDF page rendering and visual index construction diagram</x:v>
       </x:c>
       <x:c r="J221" s="4" t="str">
-        <x:v>Figure P05-7</x:v>
+        <x:v>Figure P05-4</x:v>
       </x:c>
       <x:c r="K221" s="4" t="str">
-        <x:v>docs/images/part14/p05/p05_07_eval_framework.svg</x:v>
+        <x:v>docs/images/part14/p05/p05_04_indexing_pipeline.svg</x:v>
       </x:c>
       <x:c r="L221" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M221" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>1800x982</x:v>
       </x:c>
       <x:c r="N221" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O221" s="4" t="str">
-        <x:v>Dual-layer evaluation framework for retrieval and answer quality.</x:v>
+        <x:v>PDF page rendering and visual index construction diagram.</x:v>
       </x:c>
       <x:c r="P221" s="4" t="str"/>
       <x:c r="Q221" s="4" t="str">
@@ -14773,10 +14773,10 @@
       <x:c r="S221" s="4" t="str"/>
       <x:c r="T221" s="4" t="str"/>
       <x:c r="U221" s="4" t="str">
-        <x:v>Figure P05-7：检索与回答双层评测框架图</x:v>
+        <x:v>Figure P05-4：PDF 页面渲染与视觉索引构建图</x:v>
       </x:c>
       <x:c r="V221" s="4" t="str">
-        <x:v>图 P05-7</x:v>
+        <x:v>图 P05-4</x:v>
       </x:c>
     </x:row>
     <x:row r="222">
@@ -14799,31 +14799,31 @@
         <x:v>docs/en/part14/p05_mm_rag.md</x:v>
       </x:c>
       <x:c r="G222" s="4" t="n">
-        <x:v>812</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="H222" s="4" t="str">
-        <x:v>P05-8</x:v>
+        <x:v>P05-5</x:v>
       </x:c>
       <x:c r="I222" s="4" t="str">
-        <x:v>Figure P05-8: Multimodal RAG optimization roadmap</x:v>
+        <x:v>Figure P05-5: Top-K multi-page recall and table-of-contents page filtering diagram</x:v>
       </x:c>
       <x:c r="J222" s="4" t="str">
-        <x:v>Figure P05-8</x:v>
+        <x:v>Figure P05-5</x:v>
       </x:c>
       <x:c r="K222" s="4" t="str">
-        <x:v>docs/images/part14/p05/p05_08_optimization_roadmap.svg</x:v>
+        <x:v>docs/images/part14/p05/p05_05_topk_filtering.svg</x:v>
       </x:c>
       <x:c r="L222" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M222" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>1800x982</x:v>
       </x:c>
       <x:c r="N222" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O222" s="4" t="str">
-        <x:v>Multimodal RAG optimization roadmap.</x:v>
+        <x:v>Top-K multi-page recall and table-of-contents page filtering diagram.</x:v>
       </x:c>
       <x:c r="P222" s="4" t="str"/>
       <x:c r="Q222" s="4" t="str">
@@ -14835,10 +14835,10 @@
       <x:c r="S222" s="4" t="str"/>
       <x:c r="T222" s="4" t="str"/>
       <x:c r="U222" s="4" t="str">
-        <x:v>Figure P05-8：多模态 RAG 优化路径图</x:v>
+        <x:v>Figure P05-5：Top-K 多页召回与目录页过滤示意图</x:v>
       </x:c>
       <x:c r="V222" s="4" t="str">
-        <x:v>图 P05-8</x:v>
+        <x:v>图 P05-5</x:v>
       </x:c>
     </x:row>
     <x:row r="223">
@@ -14861,19 +14861,19 @@
         <x:v>docs/en/part14/p05_mm_rag.md</x:v>
       </x:c>
       <x:c r="G223" s="4" t="n">
-        <x:v>876</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="H223" s="4" t="str">
-        <x:v>P05-9</x:v>
+        <x:v>P05-6</x:v>
       </x:c>
       <x:c r="I223" s="4" t="str">
-        <x:v>Figure P05-9: Collaborative architecture of text RAG and multimodal RAG</x:v>
+        <x:v>Figure P05-6: Multi-image context injection and answer constraint diagram</x:v>
       </x:c>
       <x:c r="J223" s="4" t="str">
-        <x:v>Figure P05-9</x:v>
+        <x:v>Figure P05-6</x:v>
       </x:c>
       <x:c r="K223" s="4" t="str">
-        <x:v>docs/images/part14/p05/p05_09_hybrid_rag.svg</x:v>
+        <x:v>docs/images/part14/p05/p05_06_multi_image_prompting.svg</x:v>
       </x:c>
       <x:c r="L223" s="4" t="str">
         <x:v>yes</x:v>
@@ -14885,11 +14885,9 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O223" s="4" t="str">
-        <x:v>Collaborative architecture of text RAG and multimodal RAG.</x:v>
-      </x:c>
-      <x:c r="P223" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Project 5: Multimodal RAG Enterprise Financial Report Assistant; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>Multi-image context injection and answer constraint diagram.</x:v>
+      </x:c>
+      <x:c r="P223" s="4" t="str"/>
       <x:c r="Q223" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -14899,10 +14897,10 @@
       <x:c r="S223" s="4" t="str"/>
       <x:c r="T223" s="4" t="str"/>
       <x:c r="U223" s="4" t="str">
-        <x:v>Figure P05-9：文本 RAG 与多模态 RAG 协同架构图</x:v>
+        <x:v>Figure P05-6：多图上下文注入与回答约束图</x:v>
       </x:c>
       <x:c r="V223" s="4" t="str">
-        <x:v>图 P05-9</x:v>
+        <x:v>图 P05-6</x:v>
       </x:c>
     </x:row>
     <x:row r="224">
@@ -14916,40 +14914,40 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D224" s="4" t="str">
-        <x:v>P06</x:v>
+        <x:v>P05</x:v>
       </x:c>
       <x:c r="E224" s="4" t="str">
-        <x:v>Project 6: CoT Reasoning Dataset Construction and PRM Training</x:v>
+        <x:v>Project 5: Multimodal RAG Enterprise Financial Report Assistant</x:v>
       </x:c>
       <x:c r="F224" s="4" t="str">
-        <x:v>docs/en/part14/p06_prm.md</x:v>
+        <x:v>docs/en/part14/p05_mm_rag.md</x:v>
       </x:c>
       <x:c r="G224" s="4" t="n">
-        <x:v>182</x:v>
+        <x:v>665</x:v>
       </x:c>
       <x:c r="H224" s="4" t="str">
-        <x:v>P06-1</x:v>
+        <x:v>P05-7</x:v>
       </x:c>
       <x:c r="I224" s="4" t="str">
-        <x:v>Figure P06-1: CoT and PRM Data Factory Overview</x:v>
+        <x:v>Figure P05-7: Dual-layer evaluation framework for retrieval and answer quality</x:v>
       </x:c>
       <x:c r="J224" s="4" t="str">
-        <x:v>Figure P06-1</x:v>
+        <x:v>Figure P05-7</x:v>
       </x:c>
       <x:c r="K224" s="4" t="str">
-        <x:v>docs/images/part14/p06/p06_01_prm_factory_overview.svg</x:v>
+        <x:v>docs/images/part14/p05/p05_07_eval_framework.svg</x:v>
       </x:c>
       <x:c r="L224" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M224" s="4" t="str">
-        <x:v>1800x982</x:v>
+        <x:v>1800x1005</x:v>
       </x:c>
       <x:c r="N224" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O224" s="4" t="str">
-        <x:v>CoT and PRM Data Factory Overview.</x:v>
+        <x:v>Dual-layer evaluation framework for retrieval and answer quality.</x:v>
       </x:c>
       <x:c r="P224" s="4" t="str"/>
       <x:c r="Q224" s="4" t="str">
@@ -14961,10 +14959,10 @@
       <x:c r="S224" s="4" t="str"/>
       <x:c r="T224" s="4" t="str"/>
       <x:c r="U224" s="4" t="str">
-        <x:v>Figure P06-1：CoT 与 PRM 数据工厂总览</x:v>
+        <x:v>Figure P05-7：检索与回答双层评测框架图</x:v>
       </x:c>
       <x:c r="V224" s="4" t="str">
-        <x:v>图 P06-1</x:v>
+        <x:v>图 P05-7</x:v>
       </x:c>
     </x:row>
     <x:row r="225">
@@ -14978,40 +14976,40 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D225" s="4" t="str">
-        <x:v>P06</x:v>
+        <x:v>P05</x:v>
       </x:c>
       <x:c r="E225" s="4" t="str">
-        <x:v>Project 6: CoT Reasoning Dataset Construction and PRM Training</x:v>
+        <x:v>Project 5: Multimodal RAG Enterprise Financial Report Assistant</x:v>
       </x:c>
       <x:c r="F225" s="4" t="str">
-        <x:v>docs/en/part14/p06_prm.md</x:v>
+        <x:v>docs/en/part14/p05_mm_rag.md</x:v>
       </x:c>
       <x:c r="G225" s="4" t="n">
-        <x:v>229</x:v>
+        <x:v>812</x:v>
       </x:c>
       <x:c r="H225" s="4" t="str">
-        <x:v>P06-2</x:v>
+        <x:v>P05-8</x:v>
       </x:c>
       <x:c r="I225" s="4" t="str">
-        <x:v>Figure P06-2: Step-Level Validation and Training Feedback Loop</x:v>
+        <x:v>Figure P05-8: Multimodal RAG optimization roadmap</x:v>
       </x:c>
       <x:c r="J225" s="4" t="str">
-        <x:v>Figure P06-2</x:v>
+        <x:v>Figure P05-8</x:v>
       </x:c>
       <x:c r="K225" s="4" t="str">
-        <x:v>docs/images/part14/p06/p06_02_step_validation_loop.svg</x:v>
+        <x:v>docs/images/part14/p05/p05_08_optimization_roadmap.svg</x:v>
       </x:c>
       <x:c r="L225" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M225" s="4" t="str">
-        <x:v>1280x720</x:v>
+        <x:v>1800x1005</x:v>
       </x:c>
       <x:c r="N225" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O225" s="4" t="str">
-        <x:v>Step-Level Validation and Training Feedback Loop.</x:v>
+        <x:v>Multimodal RAG optimization roadmap.</x:v>
       </x:c>
       <x:c r="P225" s="4" t="str"/>
       <x:c r="Q225" s="4" t="str">
@@ -15023,10 +15021,10 @@
       <x:c r="S225" s="4" t="str"/>
       <x:c r="T225" s="4" t="str"/>
       <x:c r="U225" s="4" t="str">
-        <x:v>Figure P06-2：步骤级验证与训练闭环图</x:v>
+        <x:v>Figure P05-8：多模态 RAG 优化路径图</x:v>
       </x:c>
       <x:c r="V225" s="4" t="str">
-        <x:v>图 P06-2</x:v>
+        <x:v>图 P05-8</x:v>
       </x:c>
     </x:row>
     <x:row r="226">
@@ -15040,28 +15038,28 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D226" s="4" t="str">
-        <x:v>P06</x:v>
+        <x:v>P05</x:v>
       </x:c>
       <x:c r="E226" s="4" t="str">
-        <x:v>Project 6: CoT Reasoning Dataset Construction and PRM Training</x:v>
+        <x:v>Project 5: Multimodal RAG Enterprise Financial Report Assistant</x:v>
       </x:c>
       <x:c r="F226" s="4" t="str">
-        <x:v>docs/en/part14/p06_prm.md</x:v>
+        <x:v>docs/en/part14/p05_mm_rag.md</x:v>
       </x:c>
       <x:c r="G226" s="4" t="n">
-        <x:v>346</x:v>
+        <x:v>876</x:v>
       </x:c>
       <x:c r="H226" s="4" t="str">
-        <x:v>P06-3</x:v>
+        <x:v>P05-9</x:v>
       </x:c>
       <x:c r="I226" s="4" t="str">
-        <x:v>Figure P06-3: Task Sampling and Specification Generation Flowchart</x:v>
+        <x:v>Figure P05-9: Collaborative architecture of text RAG and multimodal RAG</x:v>
       </x:c>
       <x:c r="J226" s="4" t="str">
-        <x:v>Figure P06-3</x:v>
+        <x:v>Figure P05-9</x:v>
       </x:c>
       <x:c r="K226" s="4" t="str">
-        <x:v>docs/images/part14/p06/p06_03_task_sampling.svg</x:v>
+        <x:v>docs/images/part14/p05/p05_09_hybrid_rag.svg</x:v>
       </x:c>
       <x:c r="L226" s="4" t="str">
         <x:v>yes</x:v>
@@ -15073,9 +15071,11 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O226" s="4" t="str">
-        <x:v>Task Sampling and Specification Generation Flowchart.</x:v>
-      </x:c>
-      <x:c r="P226" s="4" t="str"/>
+        <x:v>Collaborative architecture of text RAG and multimodal RAG.</x:v>
+      </x:c>
+      <x:c r="P226" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Project 5: Multimodal RAG Enterprise Financial Report Assistant; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q226" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -15085,10 +15085,10 @@
       <x:c r="S226" s="4" t="str"/>
       <x:c r="T226" s="4" t="str"/>
       <x:c r="U226" s="4" t="str">
-        <x:v>Figure P06-3：任务采样与规格生成流程图</x:v>
+        <x:v>Figure P05-9：文本 RAG 与多模态 RAG 协同架构图</x:v>
       </x:c>
       <x:c r="V226" s="4" t="str">
-        <x:v>图 P06-3</x:v>
+        <x:v>图 P05-9</x:v>
       </x:c>
     </x:row>
     <x:row r="227">
@@ -15111,35 +15111,33 @@
         <x:v>docs/en/part14/p06_prm.md</x:v>
       </x:c>
       <x:c r="G227" s="4" t="n">
-        <x:v>419</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="H227" s="4" t="str">
-        <x:v>P06-4</x:v>
+        <x:v>P06-1</x:v>
       </x:c>
       <x:c r="I227" s="4" t="str">
-        <x:v>Figure P06-4: Schematic of the Three Trajectory Types</x:v>
+        <x:v>Figure P06-1: CoT and PRM Data Factory Overview</x:v>
       </x:c>
       <x:c r="J227" s="4" t="str">
-        <x:v>Figure P06-4</x:v>
+        <x:v>Figure P06-1</x:v>
       </x:c>
       <x:c r="K227" s="4" t="str">
-        <x:v>docs/images/part14/p06/p06_04_trace_types.svg</x:v>
+        <x:v>docs/images/part14/p06/p06_01_prm_factory_overview.svg</x:v>
       </x:c>
       <x:c r="L227" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M227" s="4" t="str">
-        <x:v>2752x1536</x:v>
+        <x:v>1800x982</x:v>
       </x:c>
       <x:c r="N227" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O227" s="4" t="str">
-        <x:v>Schematic of the Three Trajectory Types.</x:v>
-      </x:c>
-      <x:c r="P227" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Project 6: CoT Reasoning Dataset Construction and PRM Training; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>CoT and PRM Data Factory Overview.</x:v>
+      </x:c>
+      <x:c r="P227" s="4" t="str"/>
       <x:c r="Q227" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -15149,10 +15147,10 @@
       <x:c r="S227" s="4" t="str"/>
       <x:c r="T227" s="4" t="str"/>
       <x:c r="U227" s="4" t="str">
-        <x:v>Figure P06-4：三类轨迹关系示意图</x:v>
+        <x:v>Figure P06-1：CoT 与 PRM 数据工厂总览</x:v>
       </x:c>
       <x:c r="V227" s="4" t="str">
-        <x:v>图 P06-4</x:v>
+        <x:v>图 P06-1</x:v>
       </x:c>
     </x:row>
     <x:row r="228">
@@ -15175,35 +15173,33 @@
         <x:v>docs/en/part14/p06_prm.md</x:v>
       </x:c>
       <x:c r="G228" s="4" t="n">
-        <x:v>473</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="H228" s="4" t="str">
-        <x:v>P06-5</x:v>
+        <x:v>P06-2</x:v>
       </x:c>
       <x:c r="I228" s="4" t="str">
-        <x:v>Figure P06-5: PRM Step Schema Schematic</x:v>
+        <x:v>Figure P06-2: Step-Level Validation and Training Feedback Loop</x:v>
       </x:c>
       <x:c r="J228" s="4" t="str">
-        <x:v>Figure P06-5</x:v>
+        <x:v>Figure P06-2</x:v>
       </x:c>
       <x:c r="K228" s="4" t="str">
-        <x:v>docs/images/part14/p06/p06_05_step_schema.svg</x:v>
+        <x:v>docs/images/part14/p06/p06_02_step_validation_loop.svg</x:v>
       </x:c>
       <x:c r="L228" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M228" s="4" t="str">
-        <x:v>1344x734</x:v>
+        <x:v>1280x720</x:v>
       </x:c>
       <x:c r="N228" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O228" s="4" t="str">
-        <x:v>PRM Step Schema Schematic.</x:v>
-      </x:c>
-      <x:c r="P228" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Project 6: CoT Reasoning Dataset Construction and PRM Training; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>Step-Level Validation and Training Feedback Loop.</x:v>
+      </x:c>
+      <x:c r="P228" s="4" t="str"/>
       <x:c r="Q228" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -15213,10 +15209,10 @@
       <x:c r="S228" s="4" t="str"/>
       <x:c r="T228" s="4" t="str"/>
       <x:c r="U228" s="4" t="str">
-        <x:v>Figure P06-5：PRM step schema 示意图</x:v>
+        <x:v>Figure P06-2：步骤级验证与训练闭环图</x:v>
       </x:c>
       <x:c r="V228" s="4" t="str">
-        <x:v>图 P06-5</x:v>
+        <x:v>图 P06-2</x:v>
       </x:c>
     </x:row>
     <x:row r="229">
@@ -15239,35 +15235,33 @@
         <x:v>docs/en/part14/p06_prm.md</x:v>
       </x:c>
       <x:c r="G229" s="4" t="n">
-        <x:v>549</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="H229" s="4" t="str">
-        <x:v>P06-6</x:v>
+        <x:v>P06-3</x:v>
       </x:c>
       <x:c r="I229" s="4" t="str">
-        <x:v>Figure P06-6: Step Validation and Result Comparison Pipeline</x:v>
+        <x:v>Figure P06-3: Task Sampling and Specification Generation Flowchart</x:v>
       </x:c>
       <x:c r="J229" s="4" t="str">
-        <x:v>Figure P06-6</x:v>
+        <x:v>Figure P06-3</x:v>
       </x:c>
       <x:c r="K229" s="4" t="str">
-        <x:v>docs/images/part14/p06/p06_06_validation_pipeline.svg</x:v>
+        <x:v>docs/images/part14/p06/p06_03_task_sampling.svg</x:v>
       </x:c>
       <x:c r="L229" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M229" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1800x982</x:v>
       </x:c>
       <x:c r="N229" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O229" s="4" t="str">
-        <x:v>Step Validation and Result Comparison Pipeline.</x:v>
-      </x:c>
-      <x:c r="P229" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Project 6: CoT Reasoning Dataset Construction and PRM Training; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>Task Sampling and Specification Generation Flowchart.</x:v>
+      </x:c>
+      <x:c r="P229" s="4" t="str"/>
       <x:c r="Q229" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -15277,10 +15271,10 @@
       <x:c r="S229" s="4" t="str"/>
       <x:c r="T229" s="4" t="str"/>
       <x:c r="U229" s="4" t="str">
-        <x:v>Figure P06-6：步骤验证与结果比对流程图</x:v>
+        <x:v>Figure P06-3：任务采样与规格生成流程图</x:v>
       </x:c>
       <x:c r="V229" s="4" t="str">
-        <x:v>图 P06-6</x:v>
+        <x:v>图 P06-3</x:v>
       </x:c>
     </x:row>
     <x:row r="230">
@@ -15303,31 +15297,31 @@
         <x:v>docs/en/part14/p06_prm.md</x:v>
       </x:c>
       <x:c r="G230" s="4" t="n">
-        <x:v>583</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="H230" s="4" t="str">
-        <x:v>P06-7</x:v>
+        <x:v>P06-4</x:v>
       </x:c>
       <x:c r="I230" s="4" t="str">
-        <x:v>Figure P06-7: Step Labels and Process-Only Signal Schematic</x:v>
+        <x:v>Figure P06-4: Schematic of the Three Trajectory Types</x:v>
       </x:c>
       <x:c r="J230" s="4" t="str">
-        <x:v>Figure P06-7</x:v>
+        <x:v>Figure P06-4</x:v>
       </x:c>
       <x:c r="K230" s="4" t="str">
-        <x:v>docs/images/part14/p06/p06_07_step_labels.svg</x:v>
+        <x:v>docs/images/part14/p06/p06_04_trace_types.svg</x:v>
       </x:c>
       <x:c r="L230" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M230" s="4" t="str">
-        <x:v>1280x720</x:v>
+        <x:v>2752x1536</x:v>
       </x:c>
       <x:c r="N230" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O230" s="4" t="str">
-        <x:v>Step Labels and Process-Only Signal Schematic.</x:v>
+        <x:v>Schematic of the Three Trajectory Types.</x:v>
       </x:c>
       <x:c r="P230" s="4" t="str">
         <x:v>Review against the figure and surrounding text in Project 6: CoT Reasoning Dataset Construction and PRM Training; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
@@ -15341,10 +15335,10 @@
       <x:c r="S230" s="4" t="str"/>
       <x:c r="T230" s="4" t="str"/>
       <x:c r="U230" s="4" t="str">
-        <x:v>Figure P06-7：step 标签与 process-only signal 示意图</x:v>
+        <x:v>Figure P06-4：三类轨迹关系示意图</x:v>
       </x:c>
       <x:c r="V230" s="4" t="str">
-        <x:v>图 P06-7</x:v>
+        <x:v>图 P06-4</x:v>
       </x:c>
     </x:row>
     <x:row r="231">
@@ -15367,33 +15361,35 @@
         <x:v>docs/en/part14/p06_prm.md</x:v>
       </x:c>
       <x:c r="G231" s="4" t="n">
-        <x:v>682</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="H231" s="4" t="str">
-        <x:v>P06-8</x:v>
+        <x:v>P06-5</x:v>
       </x:c>
       <x:c r="I231" s="4" t="str">
-        <x:v>Figure P06-8: PRM Data Packaging and Training Interface</x:v>
+        <x:v>Figure P06-5: PRM Step Schema Schematic</x:v>
       </x:c>
       <x:c r="J231" s="4" t="str">
-        <x:v>Figure P06-8</x:v>
+        <x:v>Figure P06-5</x:v>
       </x:c>
       <x:c r="K231" s="4" t="str">
-        <x:v>docs/images/part14/p06/p06_08_training_interface.svg</x:v>
+        <x:v>docs/images/part14/p06/p06_05_step_schema.svg</x:v>
       </x:c>
       <x:c r="L231" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M231" s="4" t="str">
-        <x:v>1400x781</x:v>
+        <x:v>1344x734</x:v>
       </x:c>
       <x:c r="N231" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O231" s="4" t="str">
-        <x:v>PRM Data Packaging and Training Interface.</x:v>
-      </x:c>
-      <x:c r="P231" s="4" t="str"/>
+        <x:v>PRM Step Schema Schematic.</x:v>
+      </x:c>
+      <x:c r="P231" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Project 6: CoT Reasoning Dataset Construction and PRM Training; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q231" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -15403,10 +15399,10 @@
       <x:c r="S231" s="4" t="str"/>
       <x:c r="T231" s="4" t="str"/>
       <x:c r="U231" s="4" t="str">
-        <x:v>Figure P06-8：PRM 数据封装与训练接口图</x:v>
+        <x:v>Figure P06-5：PRM step schema 示意图</x:v>
       </x:c>
       <x:c r="V231" s="4" t="str">
-        <x:v>图 P06-8</x:v>
+        <x:v>图 P06-5</x:v>
       </x:c>
     </x:row>
     <x:row r="232">
@@ -15429,31 +15425,31 @@
         <x:v>docs/en/part14/p06_prm.md</x:v>
       </x:c>
       <x:c r="G232" s="4" t="n">
-        <x:v>755</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="H232" s="4" t="str">
-        <x:v>P06-9</x:v>
+        <x:v>P06-6</x:v>
       </x:c>
       <x:c r="I232" s="4" t="str">
-        <x:v>Figure P06-9: Validation Pass Rate vs. Trajectory Type Comparison</x:v>
+        <x:v>Figure P06-6: Step Validation and Result Comparison Pipeline</x:v>
       </x:c>
       <x:c r="J232" s="4" t="str">
-        <x:v>Figure P06-9</x:v>
+        <x:v>Figure P06-6</x:v>
       </x:c>
       <x:c r="K232" s="4" t="str">
-        <x:v>docs/images/part14/p06/p06_09_validation_metrics.svg</x:v>
+        <x:v>docs/images/part14/p06/p06_06_validation_pipeline.svg</x:v>
       </x:c>
       <x:c r="L232" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M232" s="4" t="str">
-        <x:v>1280x720</x:v>
+        <x:v>1400x764</x:v>
       </x:c>
       <x:c r="N232" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O232" s="4" t="str">
-        <x:v>Validation Pass Rate vs. Trajectory Type Comparison.</x:v>
+        <x:v>Step Validation and Result Comparison Pipeline.</x:v>
       </x:c>
       <x:c r="P232" s="4" t="str">
         <x:v>Review against the figure and surrounding text in Project 6: CoT Reasoning Dataset Construction and PRM Training; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
@@ -15467,10 +15463,10 @@
       <x:c r="S232" s="4" t="str"/>
       <x:c r="T232" s="4" t="str"/>
       <x:c r="U232" s="4" t="str">
-        <x:v>Figure P06-9：验证通过率与轨迹类型对照图</x:v>
+        <x:v>Figure P06-6：步骤验证与结果比对流程图</x:v>
       </x:c>
       <x:c r="V232" s="4" t="str">
-        <x:v>图 P06-9</x:v>
+        <x:v>图 P06-6</x:v>
       </x:c>
     </x:row>
     <x:row r="233">
@@ -15493,33 +15489,35 @@
         <x:v>docs/en/part14/p06_prm.md</x:v>
       </x:c>
       <x:c r="G233" s="4" t="n">
-        <x:v>854</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="H233" s="4" t="str">
-        <x:v>P06-10</x:v>
+        <x:v>P06-7</x:v>
       </x:c>
       <x:c r="I233" s="4" t="str">
-        <x:v>Figure P06-10: Noise Sources in Negative and Repair Trajectories</x:v>
+        <x:v>Figure P06-7: Step Labels and Process-Only Signal Schematic</x:v>
       </x:c>
       <x:c r="J233" s="4" t="str">
-        <x:v>Figure P06-10</x:v>
+        <x:v>Figure P06-7</x:v>
       </x:c>
       <x:c r="K233" s="4" t="str">
-        <x:v>docs/images/part14/p06/p06_10_noise_sources.svg</x:v>
+        <x:v>docs/images/part14/p06/p06_07_step_labels.svg</x:v>
       </x:c>
       <x:c r="L233" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M233" s="4" t="str">
-        <x:v>1672x941</x:v>
+        <x:v>1280x720</x:v>
       </x:c>
       <x:c r="N233" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O233" s="4" t="str">
-        <x:v>Noise Sources in Negative and Repair Trajectories.</x:v>
-      </x:c>
-      <x:c r="P233" s="4" t="str"/>
+        <x:v>Step Labels and Process-Only Signal Schematic.</x:v>
+      </x:c>
+      <x:c r="P233" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Project 6: CoT Reasoning Dataset Construction and PRM Training; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q233" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -15529,10 +15527,10 @@
       <x:c r="S233" s="4" t="str"/>
       <x:c r="T233" s="4" t="str"/>
       <x:c r="U233" s="4" t="str">
-        <x:v>Figure P06-10：negative / repair 噪声来源图</x:v>
+        <x:v>Figure P06-7：step 标签与 process-only signal 示意图</x:v>
       </x:c>
       <x:c r="V233" s="4" t="str">
-        <x:v>图 P06-10</x:v>
+        <x:v>图 P06-7</x:v>
       </x:c>
     </x:row>
     <x:row r="234">
@@ -15546,40 +15544,40 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D234" s="4" t="str">
-        <x:v>P07</x:v>
+        <x:v>P06</x:v>
       </x:c>
       <x:c r="E234" s="4" t="str">
-        <x:v>Project 7: Agent Tool-Use Data Factory</x:v>
+        <x:v>Project 6: CoT Reasoning Dataset Construction and PRM Training</x:v>
       </x:c>
       <x:c r="F234" s="4" t="str">
-        <x:v>docs/en/part14/p07_agent_tooluse.md</x:v>
+        <x:v>docs/en/part14/p06_prm.md</x:v>
       </x:c>
       <x:c r="G234" s="4" t="n">
-        <x:v>98</x:v>
+        <x:v>682</x:v>
       </x:c>
       <x:c r="H234" s="4" t="str">
-        <x:v>P07-1</x:v>
+        <x:v>P06-8</x:v>
       </x:c>
       <x:c r="I234" s="4" t="str">
-        <x:v>Figure P07-1: Agent Tool-Use Data Factory Overview</x:v>
+        <x:v>Figure P06-8: PRM Data Packaging and Training Interface</x:v>
       </x:c>
       <x:c r="J234" s="4" t="str">
-        <x:v>Figure P07-1</x:v>
+        <x:v>Figure P06-8</x:v>
       </x:c>
       <x:c r="K234" s="4" t="str">
-        <x:v>docs/images/part14/p07/p07_01_agent_tooluse_factory_overview.svg</x:v>
+        <x:v>docs/images/part14/p06/p06_08_training_interface.svg</x:v>
       </x:c>
       <x:c r="L234" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M234" s="4" t="str">
-        <x:v>1672x941</x:v>
+        <x:v>1400x781</x:v>
       </x:c>
       <x:c r="N234" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O234" s="4" t="str">
-        <x:v>Agent Tool-Use Data Factory Overview.</x:v>
+        <x:v>PRM Data Packaging and Training Interface.</x:v>
       </x:c>
       <x:c r="P234" s="4" t="str"/>
       <x:c r="Q234" s="4" t="str">
@@ -15591,10 +15589,10 @@
       <x:c r="S234" s="4" t="str"/>
       <x:c r="T234" s="4" t="str"/>
       <x:c r="U234" s="4" t="str">
-        <x:v>Figure P07-1：Agent Tool-Use 数据工厂总览</x:v>
+        <x:v>Figure P06-8：PRM 数据封装与训练接口图</x:v>
       </x:c>
       <x:c r="V234" s="4" t="str">
-        <x:v>图 P07-1</x:v>
+        <x:v>图 P06-8</x:v>
       </x:c>
     </x:row>
     <x:row r="235">
@@ -15608,43 +15606,43 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D235" s="4" t="str">
-        <x:v>P07</x:v>
+        <x:v>P06</x:v>
       </x:c>
       <x:c r="E235" s="4" t="str">
-        <x:v>Project 7: Agent Tool-Use Data Factory</x:v>
+        <x:v>Project 6: CoT Reasoning Dataset Construction and PRM Training</x:v>
       </x:c>
       <x:c r="F235" s="4" t="str">
-        <x:v>docs/en/part14/p07_agent_tooluse.md</x:v>
+        <x:v>docs/en/part14/p06_prm.md</x:v>
       </x:c>
       <x:c r="G235" s="4" t="n">
-        <x:v>214</x:v>
+        <x:v>755</x:v>
       </x:c>
       <x:c r="H235" s="4" t="str">
-        <x:v>P07-2</x:v>
+        <x:v>P06-9</x:v>
       </x:c>
       <x:c r="I235" s="4" t="str">
-        <x:v>Figure P07-2: Agent Tool-Use Three-Layer Architecture Diagram</x:v>
+        <x:v>Figure P06-9: Validation Pass Rate vs. Trajectory Type Comparison</x:v>
       </x:c>
       <x:c r="J235" s="4" t="str">
-        <x:v>Figure P07-2</x:v>
+        <x:v>Figure P06-9</x:v>
       </x:c>
       <x:c r="K235" s="4" t="str">
-        <x:v>docs/images/part14/p07/p07_02_three_layer_architecture.svg</x:v>
+        <x:v>docs/images/part14/p06/p06_09_validation_metrics.svg</x:v>
       </x:c>
       <x:c r="L235" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M235" s="4" t="str">
-        <x:v>1699x926</x:v>
+        <x:v>1280x720</x:v>
       </x:c>
       <x:c r="N235" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O235" s="4" t="str">
-        <x:v>Agent Tool-Use Three-Layer Architecture Diagram.</x:v>
+        <x:v>Validation Pass Rate vs. Trajectory Type Comparison.</x:v>
       </x:c>
       <x:c r="P235" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Project 7: Agent Tool-Use Data Factory; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+        <x:v>Review against the figure and surrounding text in Project 6: CoT Reasoning Dataset Construction and PRM Training; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
       </x:c>
       <x:c r="Q235" s="4" t="str">
         <x:v>no</x:v>
@@ -15655,10 +15653,10 @@
       <x:c r="S235" s="4" t="str"/>
       <x:c r="T235" s="4" t="str"/>
       <x:c r="U235" s="4" t="str">
-        <x:v>Figure P07-2：Agent Tool-Use 三层架构图</x:v>
+        <x:v>Figure P06-9：验证通过率与轨迹类型对照图</x:v>
       </x:c>
       <x:c r="V235" s="4" t="str">
-        <x:v>图 P07-2</x:v>
+        <x:v>图 P06-9</x:v>
       </x:c>
     </x:row>
     <x:row r="236">
@@ -15672,28 +15670,28 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D236" s="4" t="str">
-        <x:v>P07</x:v>
+        <x:v>P06</x:v>
       </x:c>
       <x:c r="E236" s="4" t="str">
-        <x:v>Project 7: Agent Tool-Use Data Factory</x:v>
+        <x:v>Project 6: CoT Reasoning Dataset Construction and PRM Training</x:v>
       </x:c>
       <x:c r="F236" s="4" t="str">
-        <x:v>docs/en/part14/p07_agent_tooluse.md</x:v>
+        <x:v>docs/en/part14/p06_prm.md</x:v>
       </x:c>
       <x:c r="G236" s="4" t="n">
-        <x:v>253</x:v>
+        <x:v>854</x:v>
       </x:c>
       <x:c r="H236" s="4" t="str">
-        <x:v>P07-3</x:v>
+        <x:v>P06-10</x:v>
       </x:c>
       <x:c r="I236" s="4" t="str">
-        <x:v>Figure P07-3: Key Engineering Facets of the Agent Data Factory</x:v>
+        <x:v>Figure P06-10: Noise Sources in Negative and Repair Trajectories</x:v>
       </x:c>
       <x:c r="J236" s="4" t="str">
-        <x:v>Figure P07-3</x:v>
+        <x:v>Figure P06-10</x:v>
       </x:c>
       <x:c r="K236" s="4" t="str">
-        <x:v>docs/images/part14/p07/p07_03_roles_and_responsibilities.svg</x:v>
+        <x:v>docs/images/part14/p06/p06_10_noise_sources.svg</x:v>
       </x:c>
       <x:c r="L236" s="4" t="str">
         <x:v>yes</x:v>
@@ -15705,7 +15703,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O236" s="4" t="str">
-        <x:v>Key Engineering Facets of the Agent Data Factory.</x:v>
+        <x:v>Noise Sources in Negative and Repair Trajectories.</x:v>
       </x:c>
       <x:c r="P236" s="4" t="str"/>
       <x:c r="Q236" s="4" t="str">
@@ -15717,10 +15715,10 @@
       <x:c r="S236" s="4" t="str"/>
       <x:c r="T236" s="4" t="str"/>
       <x:c r="U236" s="4" t="str">
-        <x:v>Figure P07-3：Agent 数据工厂关键工程面示意图</x:v>
+        <x:v>Figure P06-10：negative / repair 噪声来源图</x:v>
       </x:c>
       <x:c r="V236" s="4" t="str">
-        <x:v>图 P07-3</x:v>
+        <x:v>图 P06-10</x:v>
       </x:c>
     </x:row>
     <x:row r="237">
@@ -15743,19 +15741,19 @@
         <x:v>docs/en/part14/p07_agent_tooluse.md</x:v>
       </x:c>
       <x:c r="G237" s="4" t="n">
-        <x:v>327</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H237" s="4" t="str">
-        <x:v>P07-4</x:v>
+        <x:v>P07-1</x:v>
       </x:c>
       <x:c r="I237" s="4" t="str">
-        <x:v>Figure P07-4: Tool Schema Structure Diagram</x:v>
+        <x:v>Figure P07-1: Agent Tool-Use Data Factory Overview</x:v>
       </x:c>
       <x:c r="J237" s="4" t="str">
-        <x:v>Figure P07-4</x:v>
+        <x:v>Figure P07-1</x:v>
       </x:c>
       <x:c r="K237" s="4" t="str">
-        <x:v>docs/images/part14/p07/p07_04_tool_schema_structure.svg</x:v>
+        <x:v>docs/images/part14/p07/p07_01_agent_tooluse_factory_overview.svg</x:v>
       </x:c>
       <x:c r="L237" s="4" t="str">
         <x:v>yes</x:v>
@@ -15767,11 +15765,9 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O237" s="4" t="str">
-        <x:v>Tool Schema Structure Diagram.</x:v>
-      </x:c>
-      <x:c r="P237" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Project 7: Agent Tool-Use Data Factory; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>Agent Tool-Use Data Factory Overview.</x:v>
+      </x:c>
+      <x:c r="P237" s="4" t="str"/>
       <x:c r="Q237" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -15781,10 +15777,10 @@
       <x:c r="S237" s="4" t="str"/>
       <x:c r="T237" s="4" t="str"/>
       <x:c r="U237" s="4" t="str">
-        <x:v>Figure P07-4：工具 schema 结构示意图</x:v>
+        <x:v>Figure P07-1：Agent Tool-Use 数据工厂总览</x:v>
       </x:c>
       <x:c r="V237" s="4" t="str">
-        <x:v>图 P07-4</x:v>
+        <x:v>图 P07-1</x:v>
       </x:c>
     </x:row>
     <x:row r="238">
@@ -15807,33 +15803,35 @@
         <x:v>docs/en/part14/p07_agent_tooluse.md</x:v>
       </x:c>
       <x:c r="G238" s="4" t="n">
-        <x:v>402</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="H238" s="4" t="str">
-        <x:v>P07-5</x:v>
+        <x:v>P07-2</x:v>
       </x:c>
       <x:c r="I238" s="4" t="str">
-        <x:v>Figure P07-5: Relationship Diagram of Task Specifications and Trajectory Templates</x:v>
+        <x:v>Figure P07-2: Agent Tool-Use Three-Layer Architecture Diagram</x:v>
       </x:c>
       <x:c r="J238" s="4" t="str">
-        <x:v>Figure P07-5</x:v>
+        <x:v>Figure P07-2</x:v>
       </x:c>
       <x:c r="K238" s="4" t="str">
-        <x:v>docs/images/part14/p07/p07_05_task_specs_and_templates.svg</x:v>
+        <x:v>docs/images/part14/p07/p07_02_three_layer_architecture.svg</x:v>
       </x:c>
       <x:c r="L238" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M238" s="4" t="str">
-        <x:v>1700x925</x:v>
+        <x:v>1699x926</x:v>
       </x:c>
       <x:c r="N238" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O238" s="4" t="str">
-        <x:v>Relationship Diagram of Task Specifications and Trajectory Templates.</x:v>
-      </x:c>
-      <x:c r="P238" s="4" t="str"/>
+        <x:v>Agent Tool-Use Three-Layer Architecture Diagram.</x:v>
+      </x:c>
+      <x:c r="P238" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Project 7: Agent Tool-Use Data Factory; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q238" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -15843,10 +15841,10 @@
       <x:c r="S238" s="4" t="str"/>
       <x:c r="T238" s="4" t="str"/>
       <x:c r="U238" s="4" t="str">
-        <x:v>Figure P07-5：任务规格与轨迹模板关系图</x:v>
+        <x:v>Figure P07-2：Agent Tool-Use 三层架构图</x:v>
       </x:c>
       <x:c r="V238" s="4" t="str">
-        <x:v>图 P07-5</x:v>
+        <x:v>图 P07-2</x:v>
       </x:c>
     </x:row>
     <x:row r="239">
@@ -15869,31 +15867,31 @@
         <x:v>docs/en/part14/p07_agent_tooluse.md</x:v>
       </x:c>
       <x:c r="G239" s="4" t="n">
-        <x:v>492</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="H239" s="4" t="str">
-        <x:v>P07-6</x:v>
+        <x:v>P07-3</x:v>
       </x:c>
       <x:c r="I239" s="4" t="str">
-        <x:v>Figure P07-6: success / recovery / block Trajectory Taxonomy Diagram</x:v>
+        <x:v>Figure P07-3: Key Engineering Facets of the Agent Data Factory</x:v>
       </x:c>
       <x:c r="J239" s="4" t="str">
-        <x:v>Figure P07-6</x:v>
+        <x:v>Figure P07-3</x:v>
       </x:c>
       <x:c r="K239" s="4" t="str">
-        <x:v>docs/images/part14/p07/p07_06_trajectory_taxonomy.svg</x:v>
+        <x:v>docs/images/part14/p07/p07_03_roles_and_responsibilities.svg</x:v>
       </x:c>
       <x:c r="L239" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M239" s="4" t="str">
-        <x:v>1400x684</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N239" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O239" s="4" t="str">
-        <x:v>success / recovery / block Trajectory Taxonomy Diagram.</x:v>
+        <x:v>Key Engineering Facets of the Agent Data Factory.</x:v>
       </x:c>
       <x:c r="P239" s="4" t="str"/>
       <x:c r="Q239" s="4" t="str">
@@ -15905,10 +15903,10 @@
       <x:c r="S239" s="4" t="str"/>
       <x:c r="T239" s="4" t="str"/>
       <x:c r="U239" s="4" t="str">
-        <x:v>Figure P07-6：success / recovery / block 轨迹分层图</x:v>
+        <x:v>Figure P07-3：Agent 数据工厂关键工程面示意图</x:v>
       </x:c>
       <x:c r="V239" s="4" t="str">
-        <x:v>图 P07-6</x:v>
+        <x:v>图 P07-3</x:v>
       </x:c>
     </x:row>
     <x:row r="240">
@@ -15931,19 +15929,19 @@
         <x:v>docs/en/part14/p07_agent_tooluse.md</x:v>
       </x:c>
       <x:c r="G240" s="4" t="n">
-        <x:v>563</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="H240" s="4" t="str">
-        <x:v>P07-7</x:v>
+        <x:v>P07-4</x:v>
       </x:c>
       <x:c r="I240" s="4" t="str">
-        <x:v>Figure P07-7: Simulated Tool Environment Execution Closure Diagram</x:v>
+        <x:v>Figure P07-4: Tool Schema Structure Diagram</x:v>
       </x:c>
       <x:c r="J240" s="4" t="str">
-        <x:v>Figure P07-7</x:v>
+        <x:v>Figure P07-4</x:v>
       </x:c>
       <x:c r="K240" s="4" t="str">
-        <x:v>docs/images/part14/p07/p07_07_simulated_env_loop.svg</x:v>
+        <x:v>docs/images/part14/p07/p07_04_tool_schema_structure.svg</x:v>
       </x:c>
       <x:c r="L240" s="4" t="str">
         <x:v>yes</x:v>
@@ -15955,9 +15953,11 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O240" s="4" t="str">
-        <x:v>Simulated Tool Environment Execution Closure Diagram.</x:v>
-      </x:c>
-      <x:c r="P240" s="4" t="str"/>
+        <x:v>Tool Schema Structure Diagram.</x:v>
+      </x:c>
+      <x:c r="P240" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Project 7: Agent Tool-Use Data Factory; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q240" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -15967,10 +15967,10 @@
       <x:c r="S240" s="4" t="str"/>
       <x:c r="T240" s="4" t="str"/>
       <x:c r="U240" s="4" t="str">
-        <x:v>Figure P07-7：模拟工具环境执行闭环图</x:v>
+        <x:v>Figure P07-4：工具 schema 结构示意图</x:v>
       </x:c>
       <x:c r="V240" s="4" t="str">
-        <x:v>图 P07-7</x:v>
+        <x:v>图 P07-4</x:v>
       </x:c>
     </x:row>
     <x:row r="241">
@@ -15993,35 +15993,33 @@
         <x:v>docs/en/part14/p07_agent_tooluse.md</x:v>
       </x:c>
       <x:c r="G241" s="4" t="n">
-        <x:v>597</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="H241" s="4" t="str">
-        <x:v>P07-8</x:v>
+        <x:v>P07-5</x:v>
       </x:c>
       <x:c r="I241" s="4" t="str">
-        <x:v>Figure P07-8: P07 Six-Step Pipeline Diagram</x:v>
+        <x:v>Figure P07-5: Relationship Diagram of Task Specifications and Trajectory Templates</x:v>
       </x:c>
       <x:c r="J241" s="4" t="str">
-        <x:v>Figure P07-8</x:v>
+        <x:v>Figure P07-5</x:v>
       </x:c>
       <x:c r="K241" s="4" t="str">
-        <x:v>docs/images/part14/p07/p07_08_pipeline_steps.svg</x:v>
+        <x:v>docs/images/part14/p07/p07_05_task_specs_and_templates.svg</x:v>
       </x:c>
       <x:c r="L241" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M241" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1700x925</x:v>
       </x:c>
       <x:c r="N241" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O241" s="4" t="str">
-        <x:v>P07 Six-Step Pipeline Diagram.</x:v>
-      </x:c>
-      <x:c r="P241" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Project 7: Agent Tool-Use Data Factory; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>Relationship Diagram of Task Specifications and Trajectory Templates.</x:v>
+      </x:c>
+      <x:c r="P241" s="4" t="str"/>
       <x:c r="Q241" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -16031,10 +16029,10 @@
       <x:c r="S241" s="4" t="str"/>
       <x:c r="T241" s="4" t="str"/>
       <x:c r="U241" s="4" t="str">
-        <x:v>Figure P07-8：P07 六步流水线图</x:v>
+        <x:v>Figure P07-5：任务规格与轨迹模板关系图</x:v>
       </x:c>
       <x:c r="V241" s="4" t="str">
-        <x:v>图 P07-8</x:v>
+        <x:v>图 P07-5</x:v>
       </x:c>
     </x:row>
     <x:row r="242">
@@ -16057,31 +16055,31 @@
         <x:v>docs/en/part14/p07_agent_tooluse.md</x:v>
       </x:c>
       <x:c r="G242" s="4" t="n">
-        <x:v>627</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="H242" s="4" t="str">
-        <x:v>P07-9</x:v>
+        <x:v>P07-6</x:v>
       </x:c>
       <x:c r="I242" s="4" t="str">
-        <x:v>Figure P07-9: Parameter Correction and Retry Flow Diagram</x:v>
+        <x:v>Figure P07-6: success / recovery / block Trajectory Taxonomy Diagram</x:v>
       </x:c>
       <x:c r="J242" s="4" t="str">
-        <x:v>Figure P07-9</x:v>
+        <x:v>Figure P07-6</x:v>
       </x:c>
       <x:c r="K242" s="4" t="str">
-        <x:v>docs/images/part14/p07/p07_09_recovery_flow.svg</x:v>
+        <x:v>docs/images/part14/p07/p07_06_trajectory_taxonomy.svg</x:v>
       </x:c>
       <x:c r="L242" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M242" s="4" t="str">
-        <x:v>1672x941</x:v>
+        <x:v>1400x684</x:v>
       </x:c>
       <x:c r="N242" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O242" s="4" t="str">
-        <x:v>Parameter Correction and Retry Flow Diagram.</x:v>
+        <x:v>success / recovery / block Trajectory Taxonomy Diagram.</x:v>
       </x:c>
       <x:c r="P242" s="4" t="str"/>
       <x:c r="Q242" s="4" t="str">
@@ -16093,10 +16091,10 @@
       <x:c r="S242" s="4" t="str"/>
       <x:c r="T242" s="4" t="str"/>
       <x:c r="U242" s="4" t="str">
-        <x:v>Figure P07-9：参数修复与重试流程图</x:v>
+        <x:v>Figure P07-6：success / recovery / block 轨迹分层图</x:v>
       </x:c>
       <x:c r="V242" s="4" t="str">
-        <x:v>图 P07-9</x:v>
+        <x:v>图 P07-6</x:v>
       </x:c>
     </x:row>
     <x:row r="243">
@@ -16119,19 +16117,19 @@
         <x:v>docs/en/part14/p07_agent_tooluse.md</x:v>
       </x:c>
       <x:c r="G243" s="4" t="n">
-        <x:v>665</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="H243" s="4" t="str">
-        <x:v>P07-10</x:v>
+        <x:v>P07-7</x:v>
       </x:c>
       <x:c r="I243" s="4" t="str">
-        <x:v>Figure P07-10: Memory Read/Write Trajectory Diagram</x:v>
+        <x:v>Figure P07-7: Simulated Tool Environment Execution Closure Diagram</x:v>
       </x:c>
       <x:c r="J243" s="4" t="str">
-        <x:v>Figure P07-10</x:v>
+        <x:v>Figure P07-7</x:v>
       </x:c>
       <x:c r="K243" s="4" t="str">
-        <x:v>docs/images/part14/p07/p07_10_memory_trajectory.svg</x:v>
+        <x:v>docs/images/part14/p07/p07_07_simulated_env_loop.svg</x:v>
       </x:c>
       <x:c r="L243" s="4" t="str">
         <x:v>yes</x:v>
@@ -16143,7 +16141,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O243" s="4" t="str">
-        <x:v>Memory Read/Write Trajectory Diagram.</x:v>
+        <x:v>Simulated Tool Environment Execution Closure Diagram.</x:v>
       </x:c>
       <x:c r="P243" s="4" t="str"/>
       <x:c r="Q243" s="4" t="str">
@@ -16155,10 +16153,10 @@
       <x:c r="S243" s="4" t="str"/>
       <x:c r="T243" s="4" t="str"/>
       <x:c r="U243" s="4" t="str">
-        <x:v>Figure P07-10：Memory 读写轨迹示意图</x:v>
+        <x:v>Figure P07-7：模拟工具环境执行闭环图</x:v>
       </x:c>
       <x:c r="V243" s="4" t="str">
-        <x:v>图 P07-10</x:v>
+        <x:v>图 P07-7</x:v>
       </x:c>
     </x:row>
     <x:row r="244">
@@ -16181,33 +16179,35 @@
         <x:v>docs/en/part14/p07_agent_tooluse.md</x:v>
       </x:c>
       <x:c r="G244" s="4" t="n">
-        <x:v>700</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="H244" s="4" t="str">
-        <x:v>P07-11</x:v>
+        <x:v>P07-8</x:v>
       </x:c>
       <x:c r="I244" s="4" t="str">
-        <x:v>Figure P07-11: Unsafe Block Decision Flow Diagram</x:v>
+        <x:v>Figure P07-8: P07 Six-Step Pipeline Diagram</x:v>
       </x:c>
       <x:c r="J244" s="4" t="str">
-        <x:v>Figure P07-11</x:v>
+        <x:v>Figure P07-8</x:v>
       </x:c>
       <x:c r="K244" s="4" t="str">
-        <x:v>docs/images/part14/p07/p07_11_unsafe_block.svg</x:v>
+        <x:v>docs/images/part14/p07/p07_08_pipeline_steps.svg</x:v>
       </x:c>
       <x:c r="L244" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M244" s="4" t="str">
-        <x:v>1702x924</x:v>
+        <x:v>1400x764</x:v>
       </x:c>
       <x:c r="N244" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O244" s="4" t="str">
-        <x:v>Unsafe Block Decision Flow Diagram.</x:v>
-      </x:c>
-      <x:c r="P244" s="4" t="str"/>
+        <x:v>P07 Six-Step Pipeline Diagram.</x:v>
+      </x:c>
+      <x:c r="P244" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Project 7: Agent Tool-Use Data Factory; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q244" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -16217,10 +16217,10 @@
       <x:c r="S244" s="4" t="str"/>
       <x:c r="T244" s="4" t="str"/>
       <x:c r="U244" s="4" t="str">
-        <x:v>Figure P07-11：Unsafe block 决策分流图</x:v>
+        <x:v>Figure P07-8：P07 六步流水线图</x:v>
       </x:c>
       <x:c r="V244" s="4" t="str">
-        <x:v>图 P07-11</x:v>
+        <x:v>图 P07-8</x:v>
       </x:c>
     </x:row>
     <x:row r="245">
@@ -16243,19 +16243,19 @@
         <x:v>docs/en/part14/p07_agent_tooluse.md</x:v>
       </x:c>
       <x:c r="G245" s="4" t="n">
-        <x:v>762</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="H245" s="4" t="str">
-        <x:v>P07-12</x:v>
+        <x:v>P07-9</x:v>
       </x:c>
       <x:c r="I245" s="4" t="str">
-        <x:v>Figure P07-12: Event Log to Training Sample Reassembly Diagram</x:v>
+        <x:v>Figure P07-9: Parameter Correction and Retry Flow Diagram</x:v>
       </x:c>
       <x:c r="J245" s="4" t="str">
-        <x:v>Figure P07-12</x:v>
+        <x:v>Figure P07-9</x:v>
       </x:c>
       <x:c r="K245" s="4" t="str">
-        <x:v>docs/images/part14/p07/p07_12_dataset_repacking.svg</x:v>
+        <x:v>docs/images/part14/p07/p07_09_recovery_flow.svg</x:v>
       </x:c>
       <x:c r="L245" s="4" t="str">
         <x:v>yes</x:v>
@@ -16267,7 +16267,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O245" s="4" t="str">
-        <x:v>Event Log to Training Sample Reassembly Diagram.</x:v>
+        <x:v>Parameter Correction and Retry Flow Diagram.</x:v>
       </x:c>
       <x:c r="P245" s="4" t="str"/>
       <x:c r="Q245" s="4" t="str">
@@ -16279,10 +16279,10 @@
       <x:c r="S245" s="4" t="str"/>
       <x:c r="T245" s="4" t="str"/>
       <x:c r="U245" s="4" t="str">
-        <x:v>Figure P07-12：事件日志到训练样本重组图</x:v>
+        <x:v>Figure P07-9：参数修复与重试流程图</x:v>
       </x:c>
       <x:c r="V245" s="4" t="str">
-        <x:v>图 P07-12</x:v>
+        <x:v>图 P07-9</x:v>
       </x:c>
     </x:row>
     <x:row r="246">
@@ -16305,19 +16305,19 @@
         <x:v>docs/en/part14/p07_agent_tooluse.md</x:v>
       </x:c>
       <x:c r="G246" s="4" t="n">
-        <x:v>883</x:v>
+        <x:v>665</x:v>
       </x:c>
       <x:c r="H246" s="4" t="str">
-        <x:v>P07-13</x:v>
+        <x:v>P07-10</x:v>
       </x:c>
       <x:c r="I246" s="4" t="str">
-        <x:v>Figure P07-13: Evaluation and Inspection Dual-Closure Diagram</x:v>
+        <x:v>Figure P07-10: Memory Read/Write Trajectory Diagram</x:v>
       </x:c>
       <x:c r="J246" s="4" t="str">
-        <x:v>Figure P07-13</x:v>
+        <x:v>Figure P07-10</x:v>
       </x:c>
       <x:c r="K246" s="4" t="str">
-        <x:v>docs/images/part14/p07/p07_13_eval_and_checks.svg</x:v>
+        <x:v>docs/images/part14/p07/p07_10_memory_trajectory.svg</x:v>
       </x:c>
       <x:c r="L246" s="4" t="str">
         <x:v>yes</x:v>
@@ -16329,7 +16329,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O246" s="4" t="str">
-        <x:v>Evaluation and Inspection Dual-Closure Diagram.</x:v>
+        <x:v>Memory Read/Write Trajectory Diagram.</x:v>
       </x:c>
       <x:c r="P246" s="4" t="str"/>
       <x:c r="Q246" s="4" t="str">
@@ -16341,10 +16341,10 @@
       <x:c r="S246" s="4" t="str"/>
       <x:c r="T246" s="4" t="str"/>
       <x:c r="U246" s="4" t="str">
-        <x:v>Figure P07-13：评估与检查双闭环图</x:v>
+        <x:v>Figure P07-10：Memory 读写轨迹示意图</x:v>
       </x:c>
       <x:c r="V246" s="4" t="str">
-        <x:v>图 P07-13</x:v>
+        <x:v>图 P07-10</x:v>
       </x:c>
     </x:row>
     <x:row r="247">
@@ -16367,31 +16367,31 @@
         <x:v>docs/en/part14/p07_agent_tooluse.md</x:v>
       </x:c>
       <x:c r="G247" s="4" t="n">
-        <x:v>934</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="H247" s="4" t="str">
-        <x:v>P07-14</x:v>
+        <x:v>P07-11</x:v>
       </x:c>
       <x:c r="I247" s="4" t="str">
-        <x:v>Figure P07-14: P07 Future Evolution Roadmap</x:v>
+        <x:v>Figure P07-11: Unsafe Block Decision Flow Diagram</x:v>
       </x:c>
       <x:c r="J247" s="4" t="str">
-        <x:v>Figure P07-14</x:v>
+        <x:v>Figure P07-11</x:v>
       </x:c>
       <x:c r="K247" s="4" t="str">
-        <x:v>docs/images/part14/p07/p07_14_roadmap.svg</x:v>
+        <x:v>docs/images/part14/p07/p07_11_unsafe_block.svg</x:v>
       </x:c>
       <x:c r="L247" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M247" s="4" t="str">
-        <x:v>1672x941</x:v>
+        <x:v>1702x924</x:v>
       </x:c>
       <x:c r="N247" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O247" s="4" t="str">
-        <x:v>P07 Future Evolution Roadmap.</x:v>
+        <x:v>Unsafe Block Decision Flow Diagram.</x:v>
       </x:c>
       <x:c r="P247" s="4" t="str"/>
       <x:c r="Q247" s="4" t="str">
@@ -16403,10 +16403,10 @@
       <x:c r="S247" s="4" t="str"/>
       <x:c r="T247" s="4" t="str"/>
       <x:c r="U247" s="4" t="str">
-        <x:v>Figure P07-14：P07 后续演进路线图</x:v>
+        <x:v>Figure P07-11：Unsafe block 决策分流图</x:v>
       </x:c>
       <x:c r="V247" s="4" t="str">
-        <x:v>图 P07-14</x:v>
+        <x:v>图 P07-11</x:v>
       </x:c>
     </x:row>
     <x:row r="248">
@@ -16420,28 +16420,28 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D248" s="4" t="str">
-        <x:v>P08</x:v>
+        <x:v>P07</x:v>
       </x:c>
       <x:c r="E248" s="4" t="str">
-        <x:v>Project 8: Building an Enterprise DataOps Platform</x:v>
+        <x:v>Project 7: Agent Tool-Use Data Factory</x:v>
       </x:c>
       <x:c r="F248" s="4" t="str">
-        <x:v>docs/en/part14/p08_dataops.md</x:v>
+        <x:v>docs/en/part14/p07_agent_tooluse.md</x:v>
       </x:c>
       <x:c r="G248" s="4" t="n">
-        <x:v>272</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="H248" s="4" t="str">
-        <x:v>P08-1</x:v>
+        <x:v>P07-12</x:v>
       </x:c>
       <x:c r="I248" s="4" t="str">
-        <x:v>Figure 1: P08 DataOps platform overview</x:v>
+        <x:v>Figure P07-12: Event Log to Training Sample Reassembly Diagram</x:v>
       </x:c>
       <x:c r="J248" s="4" t="str">
-        <x:v>Figure 1: P08 DataOps platform overview</x:v>
+        <x:v>Figure P07-12</x:v>
       </x:c>
       <x:c r="K248" s="4" t="str">
-        <x:v>docs/images/part14/p08/p08_01_dataops_platform_overview.svg</x:v>
+        <x:v>docs/images/part14/p07/p07_12_dataset_repacking.svg</x:v>
       </x:c>
       <x:c r="L248" s="4" t="str">
         <x:v>yes</x:v>
@@ -16453,7 +16453,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O248" s="4" t="str">
-        <x:v>Figure 1: P08 DataOps platform overview.</x:v>
+        <x:v>Event Log to Training Sample Reassembly Diagram.</x:v>
       </x:c>
       <x:c r="P248" s="4" t="str"/>
       <x:c r="Q248" s="4" t="str">
@@ -16465,10 +16465,10 @@
       <x:c r="S248" s="4" t="str"/>
       <x:c r="T248" s="4" t="str"/>
       <x:c r="U248" s="4" t="str">
-        <x:v>Figure P08-1：P08 DataOps 平台总览图</x:v>
+        <x:v>Figure P07-12：事件日志到训练样本重组图</x:v>
       </x:c>
       <x:c r="V248" s="4" t="str">
-        <x:v>图 P08-1</x:v>
+        <x:v>图 P07-12</x:v>
       </x:c>
     </x:row>
     <x:row r="249">
@@ -16482,28 +16482,28 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D249" s="4" t="str">
-        <x:v>P08</x:v>
+        <x:v>P07</x:v>
       </x:c>
       <x:c r="E249" s="4" t="str">
-        <x:v>Project 8: Building an Enterprise DataOps Platform</x:v>
+        <x:v>Project 7: Agent Tool-Use Data Factory</x:v>
       </x:c>
       <x:c r="F249" s="4" t="str">
-        <x:v>docs/en/part14/p08_dataops.md</x:v>
+        <x:v>docs/en/part14/p07_agent_tooluse.md</x:v>
       </x:c>
       <x:c r="G249" s="4" t="n">
-        <x:v>328</x:v>
+        <x:v>883</x:v>
       </x:c>
       <x:c r="H249" s="4" t="str">
-        <x:v>P08-2</x:v>
+        <x:v>P07-13</x:v>
       </x:c>
       <x:c r="I249" s="4" t="str">
-        <x:v>Figure 2: Four-layer platform architecture</x:v>
+        <x:v>Figure P07-13: Evaluation and Inspection Dual-Closure Diagram</x:v>
       </x:c>
       <x:c r="J249" s="4" t="str">
-        <x:v>Figure 2: Four-layer platform architecture</x:v>
+        <x:v>Figure P07-13</x:v>
       </x:c>
       <x:c r="K249" s="4" t="str">
-        <x:v>docs/images/part14/p08/p08_02_four_layer_architecture.svg</x:v>
+        <x:v>docs/images/part14/p07/p07_13_eval_and_checks.svg</x:v>
       </x:c>
       <x:c r="L249" s="4" t="str">
         <x:v>yes</x:v>
@@ -16515,11 +16515,9 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O249" s="4" t="str">
-        <x:v>Figure 2: Four-layer platform architecture.</x:v>
-      </x:c>
-      <x:c r="P249" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Project 8: Building an Enterprise DataOps Platform; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>Evaluation and Inspection Dual-Closure Diagram.</x:v>
+      </x:c>
+      <x:c r="P249" s="4" t="str"/>
       <x:c r="Q249" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -16529,10 +16527,10 @@
       <x:c r="S249" s="4" t="str"/>
       <x:c r="T249" s="4" t="str"/>
       <x:c r="U249" s="4" t="str">
-        <x:v>Figure P08-2：平台四层架构图</x:v>
+        <x:v>Figure P07-13：评估与检查双闭环图</x:v>
       </x:c>
       <x:c r="V249" s="4" t="str">
-        <x:v>图 P08-2</x:v>
+        <x:v>图 P07-13</x:v>
       </x:c>
     </x:row>
     <x:row r="250">
@@ -16546,28 +16544,28 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D250" s="4" t="str">
-        <x:v>P08</x:v>
+        <x:v>P07</x:v>
       </x:c>
       <x:c r="E250" s="4" t="str">
-        <x:v>Project 8: Building an Enterprise DataOps Platform</x:v>
+        <x:v>Project 7: Agent Tool-Use Data Factory</x:v>
       </x:c>
       <x:c r="F250" s="4" t="str">
-        <x:v>docs/en/part14/p08_dataops.md</x:v>
+        <x:v>docs/en/part14/p07_agent_tooluse.md</x:v>
       </x:c>
       <x:c r="G250" s="4" t="n">
-        <x:v>362</x:v>
+        <x:v>934</x:v>
       </x:c>
       <x:c r="H250" s="4" t="str">
-        <x:v>P08-3</x:v>
+        <x:v>P07-14</x:v>
       </x:c>
       <x:c r="I250" s="4" t="str">
-        <x:v>Figure 3: Specification generation, simulated operation, evaluation, and check flow</x:v>
+        <x:v>Figure P07-14: P07 Future Evolution Roadmap</x:v>
       </x:c>
       <x:c r="J250" s="4" t="str">
-        <x:v>Figure 3: Spec generation, simulated run, evaluation, and check flow</x:v>
+        <x:v>Figure P07-14</x:v>
       </x:c>
       <x:c r="K250" s="4" t="str">
-        <x:v>docs/images/part14/p08/p08_03_specs_to_ops_pipeline.svg</x:v>
+        <x:v>docs/images/part14/p07/p07_14_roadmap.svg</x:v>
       </x:c>
       <x:c r="L250" s="4" t="str">
         <x:v>yes</x:v>
@@ -16579,7 +16577,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O250" s="4" t="str">
-        <x:v>Figure 3: Specification generation, simulated operation, evaluation, and check flow.</x:v>
+        <x:v>P07 Future Evolution Roadmap.</x:v>
       </x:c>
       <x:c r="P250" s="4" t="str"/>
       <x:c r="Q250" s="4" t="str">
@@ -16591,10 +16589,10 @@
       <x:c r="S250" s="4" t="str"/>
       <x:c r="T250" s="4" t="str"/>
       <x:c r="U250" s="4" t="str">
-        <x:v>Figure P08-3：规格生成—模拟运行—评估—检查流程图</x:v>
+        <x:v>Figure P07-14：P07 后续演进路线图</x:v>
       </x:c>
       <x:c r="V250" s="4" t="str">
-        <x:v>图 P08-3</x:v>
+        <x:v>图 P07-14</x:v>
       </x:c>
     </x:row>
     <x:row r="251">
@@ -16617,19 +16615,19 @@
         <x:v>docs/en/part14/p08_dataops.md</x:v>
       </x:c>
       <x:c r="G251" s="4" t="n">
-        <x:v>438</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="H251" s="4" t="str">
-        <x:v>P08-4</x:v>
+        <x:v>P08-1</x:v>
       </x:c>
       <x:c r="I251" s="4" t="str">
-        <x:v>Figure 4: Tenant, project, role, and API relationship</x:v>
+        <x:v>Figure 1: P08 DataOps platform overview</x:v>
       </x:c>
       <x:c r="J251" s="4" t="str">
-        <x:v>Figure 4: Tenant, project, role, and API relationship</x:v>
+        <x:v>Figure 1: P08 DataOps platform overview</x:v>
       </x:c>
       <x:c r="K251" s="4" t="str">
-        <x:v>docs/images/part14/p08/p08_04_object_model.svg</x:v>
+        <x:v>docs/images/part14/p08/p08_01_dataops_platform_overview.svg</x:v>
       </x:c>
       <x:c r="L251" s="4" t="str">
         <x:v>yes</x:v>
@@ -16641,7 +16639,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O251" s="4" t="str">
-        <x:v>Figure 4: Tenant, project, role, and API relationship.</x:v>
+        <x:v>Figure 1: P08 DataOps platform overview.</x:v>
       </x:c>
       <x:c r="P251" s="4" t="str"/>
       <x:c r="Q251" s="4" t="str">
@@ -16653,10 +16651,10 @@
       <x:c r="S251" s="4" t="str"/>
       <x:c r="T251" s="4" t="str"/>
       <x:c r="U251" s="4" t="str">
-        <x:v>Figure P08-4：租户—项目—角色—API 关系图</x:v>
+        <x:v>Figure P08-1：P08 DataOps 平台总览图</x:v>
       </x:c>
       <x:c r="V251" s="4" t="str">
-        <x:v>图 P08-4</x:v>
+        <x:v>图 P08-1</x:v>
       </x:c>
     </x:row>
     <x:row r="252">
@@ -16679,19 +16677,19 @@
         <x:v>docs/en/part14/p08_dataops.md</x:v>
       </x:c>
       <x:c r="G252" s="4" t="n">
-        <x:v>558</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="H252" s="4" t="str">
-        <x:v>P08-5</x:v>
+        <x:v>P08-2</x:v>
       </x:c>
       <x:c r="I252" s="4" t="str">
-        <x:v>Figure 5: Version lifecycle with release and rollback points</x:v>
+        <x:v>Figure 2: Four-layer platform architecture</x:v>
       </x:c>
       <x:c r="J252" s="4" t="str">
-        <x:v>Figure 5: Version lifecycle with release and rollback points</x:v>
+        <x:v>Figure 2: Four-layer platform architecture</x:v>
       </x:c>
       <x:c r="K252" s="4" t="str">
-        <x:v>docs/images/part14/p08/p08_05_version_lifecycle.svg</x:v>
+        <x:v>docs/images/part14/p08/p08_02_four_layer_architecture.svg</x:v>
       </x:c>
       <x:c r="L252" s="4" t="str">
         <x:v>yes</x:v>
@@ -16703,9 +16701,11 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O252" s="4" t="str">
-        <x:v>Figure 5: Version lifecycle with release and rollback points.</x:v>
-      </x:c>
-      <x:c r="P252" s="4" t="str"/>
+        <x:v>Figure 2: Four-layer platform architecture.</x:v>
+      </x:c>
+      <x:c r="P252" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Project 8: Building an Enterprise DataOps Platform; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q252" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -16715,10 +16715,10 @@
       <x:c r="S252" s="4" t="str"/>
       <x:c r="T252" s="4" t="str"/>
       <x:c r="U252" s="4" t="str">
-        <x:v>Figure P08-5：版本演进与发布/回滚点示意图</x:v>
+        <x:v>Figure P08-2：平台四层架构图</x:v>
       </x:c>
       <x:c r="V252" s="4" t="str">
-        <x:v>图 P08-5</x:v>
+        <x:v>图 P08-2</x:v>
       </x:c>
     </x:row>
     <x:row r="253">
@@ -16741,35 +16741,33 @@
         <x:v>docs/en/part14/p08_dataops.md</x:v>
       </x:c>
       <x:c r="G253" s="4" t="n">
-        <x:v>627</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="H253" s="4" t="str">
-        <x:v>P08-6</x:v>
+        <x:v>P08-3</x:v>
       </x:c>
       <x:c r="I253" s="4" t="str">
-        <x:v>Figure 6: Experiment status distribution and governance actions</x:v>
+        <x:v>Figure 3: Specification generation, simulated operation, evaluation, and check flow</x:v>
       </x:c>
       <x:c r="J253" s="4" t="str">
-        <x:v>Figure 6: Experiment status distribution and governance actions</x:v>
+        <x:v>Figure 3: Spec generation, simulated run, evaluation, and check flow</x:v>
       </x:c>
       <x:c r="K253" s="4" t="str">
-        <x:v>docs/images/part14/p08/p08_06_experiment_tracking.svg</x:v>
+        <x:v>docs/images/part14/p08/p08_03_specs_to_ops_pipeline.svg</x:v>
       </x:c>
       <x:c r="L253" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M253" s="4" t="str">
-        <x:v>1672x833</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N253" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O253" s="4" t="str">
-        <x:v>Figure 6: Experiment status distribution and governance actions.</x:v>
-      </x:c>
-      <x:c r="P253" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Project 8: Building an Enterprise DataOps Platform; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>Figure 3: Specification generation, simulated operation, evaluation, and check flow.</x:v>
+      </x:c>
+      <x:c r="P253" s="4" t="str"/>
       <x:c r="Q253" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -16779,10 +16777,10 @@
       <x:c r="S253" s="4" t="str"/>
       <x:c r="T253" s="4" t="str"/>
       <x:c r="U253" s="4" t="str">
-        <x:v>Figure P08-6：实验状态分布与治理动作图</x:v>
+        <x:v>Figure P08-3：规格生成—模拟运行—评估—检查流程图</x:v>
       </x:c>
       <x:c r="V253" s="4" t="str">
-        <x:v>图 P08-6</x:v>
+        <x:v>图 P08-3</x:v>
       </x:c>
     </x:row>
     <x:row r="254">
@@ -16805,19 +16803,19 @@
         <x:v>docs/en/part14/p08_dataops.md</x:v>
       </x:c>
       <x:c r="G254" s="4" t="n">
-        <x:v>679</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="H254" s="4" t="str">
-        <x:v>P08-7</x:v>
+        <x:v>P08-4</x:v>
       </x:c>
       <x:c r="I254" s="4" t="str">
-        <x:v>Figure 7: Version, experiment, result, and rollback lineage</x:v>
+        <x:v>Figure 4: Tenant, project, role, and API relationship</x:v>
       </x:c>
       <x:c r="J254" s="4" t="str">
-        <x:v>Figure 7: Version, experiment, result, and rollback lineage</x:v>
+        <x:v>Figure 4: Tenant, project, role, and API relationship</x:v>
       </x:c>
       <x:c r="K254" s="4" t="str">
-        <x:v>docs/images/part14/p08/p08_07_lineage_graph.svg</x:v>
+        <x:v>docs/images/part14/p08/p08_04_object_model.svg</x:v>
       </x:c>
       <x:c r="L254" s="4" t="str">
         <x:v>yes</x:v>
@@ -16829,7 +16827,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O254" s="4" t="str">
-        <x:v>Figure 7: Version, experiment, result, and rollback lineage.</x:v>
+        <x:v>Figure 4: Tenant, project, role, and API relationship.</x:v>
       </x:c>
       <x:c r="P254" s="4" t="str"/>
       <x:c r="Q254" s="4" t="str">
@@ -16841,10 +16839,10 @@
       <x:c r="S254" s="4" t="str"/>
       <x:c r="T254" s="4" t="str"/>
       <x:c r="U254" s="4" t="str">
-        <x:v>Figure P08-7：版本—实验—结果—回滚血缘图</x:v>
+        <x:v>Figure P08-4：租户—项目—角色—API 关系图</x:v>
       </x:c>
       <x:c r="V254" s="4" t="str">
-        <x:v>图 P08-7</x:v>
+        <x:v>图 P08-4</x:v>
       </x:c>
     </x:row>
     <x:row r="255">
@@ -16867,19 +16865,19 @@
         <x:v>docs/en/part14/p08_dataops.md</x:v>
       </x:c>
       <x:c r="G255" s="4" t="n">
-        <x:v>727</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="H255" s="4" t="str">
-        <x:v>P08-8</x:v>
+        <x:v>P08-5</x:v>
       </x:c>
       <x:c r="I255" s="4" t="str">
-        <x:v>Figure 8: Rollback trigger and recovery flow</x:v>
+        <x:v>Figure 5: Version lifecycle with release and rollback points</x:v>
       </x:c>
       <x:c r="J255" s="4" t="str">
-        <x:v>Figure 8: Rollback trigger and recovery flow</x:v>
+        <x:v>Figure 5: Version lifecycle with release and rollback points</x:v>
       </x:c>
       <x:c r="K255" s="4" t="str">
-        <x:v>docs/images/part14/p08/p08_08_rollback_flow.svg</x:v>
+        <x:v>docs/images/part14/p08/p08_05_version_lifecycle.svg</x:v>
       </x:c>
       <x:c r="L255" s="4" t="str">
         <x:v>yes</x:v>
@@ -16891,7 +16889,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O255" s="4" t="str">
-        <x:v>Figure 8: Rollback trigger and recovery flow.</x:v>
+        <x:v>Figure 5: Version lifecycle with release and rollback points.</x:v>
       </x:c>
       <x:c r="P255" s="4" t="str"/>
       <x:c r="Q255" s="4" t="str">
@@ -16903,10 +16901,10 @@
       <x:c r="S255" s="4" t="str"/>
       <x:c r="T255" s="4" t="str"/>
       <x:c r="U255" s="4" t="str">
-        <x:v>Figure P08-8：回滚触发与恢复流程图</x:v>
+        <x:v>Figure P08-5：版本演进与发布/回滚点示意图</x:v>
       </x:c>
       <x:c r="V255" s="4" t="str">
-        <x:v>图 P08-8</x:v>
+        <x:v>图 P08-5</x:v>
       </x:c>
     </x:row>
     <x:row r="256">
@@ -16929,33 +16927,35 @@
         <x:v>docs/en/part14/p08_dataops.md</x:v>
       </x:c>
       <x:c r="G256" s="4" t="n">
-        <x:v>795</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="H256" s="4" t="str">
-        <x:v>P08-9</x:v>
+        <x:v>P08-6</x:v>
       </x:c>
       <x:c r="I256" s="4" t="str">
-        <x:v>Figure 9: Metrics, logs, alerts, and audit loop</x:v>
+        <x:v>Figure 6: Experiment status distribution and governance actions</x:v>
       </x:c>
       <x:c r="J256" s="4" t="str">
-        <x:v>Figure 9: Metrics, logs, alerts, and audit loop</x:v>
+        <x:v>Figure 6: Experiment status distribution and governance actions</x:v>
       </x:c>
       <x:c r="K256" s="4" t="str">
-        <x:v>docs/images/part14/p08/p08_09_observability_loop.svg</x:v>
+        <x:v>docs/images/part14/p08/p08_06_experiment_tracking.svg</x:v>
       </x:c>
       <x:c r="L256" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M256" s="4" t="str">
-        <x:v>1254x1254</x:v>
+        <x:v>1672x833</x:v>
       </x:c>
       <x:c r="N256" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O256" s="4" t="str">
-        <x:v>Figure 9: Metrics, logs, alerts, and audit loop.</x:v>
-      </x:c>
-      <x:c r="P256" s="4" t="str"/>
+        <x:v>Figure 6: Experiment status distribution and governance actions.</x:v>
+      </x:c>
+      <x:c r="P256" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Project 8: Building an Enterprise DataOps Platform; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q256" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -16965,10 +16965,10 @@
       <x:c r="S256" s="4" t="str"/>
       <x:c r="T256" s="4" t="str"/>
       <x:c r="U256" s="4" t="str">
-        <x:v>Figure P08-9：指标—日志—告警—审计闭环图</x:v>
+        <x:v>Figure P08-6：实验状态分布与治理动作图</x:v>
       </x:c>
       <x:c r="V256" s="4" t="str">
-        <x:v>图 P08-9</x:v>
+        <x:v>图 P08-6</x:v>
       </x:c>
     </x:row>
     <x:row r="257">
@@ -16991,19 +16991,19 @@
         <x:v>docs/en/part14/p08_dataops.md</x:v>
       </x:c>
       <x:c r="G257" s="4" t="n">
-        <x:v>841</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="H257" s="4" t="str">
-        <x:v>P08-10</x:v>
+        <x:v>P08-7</x:v>
       </x:c>
       <x:c r="I257" s="4" t="str">
-        <x:v>Figure 10: Audit logs and incident review</x:v>
+        <x:v>Figure 7: Version, experiment, result, and rollback lineage</x:v>
       </x:c>
       <x:c r="J257" s="4" t="str">
-        <x:v>Figure 10: Audit logs and incident review</x:v>
+        <x:v>Figure 7: Version, experiment, result, and rollback lineage</x:v>
       </x:c>
       <x:c r="K257" s="4" t="str">
-        <x:v>docs/images/part14/p08/p08_10_audit_and_incident_review.svg</x:v>
+        <x:v>docs/images/part14/p08/p08_07_lineage_graph.svg</x:v>
       </x:c>
       <x:c r="L257" s="4" t="str">
         <x:v>yes</x:v>
@@ -17015,7 +17015,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O257" s="4" t="str">
-        <x:v>Figure 10: Audit logs and incident review.</x:v>
+        <x:v>Figure 7: Version, experiment, result, and rollback lineage.</x:v>
       </x:c>
       <x:c r="P257" s="4" t="str"/>
       <x:c r="Q257" s="4" t="str">
@@ -17027,10 +17027,10 @@
       <x:c r="S257" s="4" t="str"/>
       <x:c r="T257" s="4" t="str"/>
       <x:c r="U257" s="4" t="str">
-        <x:v>Figure P08-10：审计日志与事故复盘关联图</x:v>
+        <x:v>Figure P08-7：版本—实验—结果—回滚血缘图</x:v>
       </x:c>
       <x:c r="V257" s="4" t="str">
-        <x:v>图 P08-10</x:v>
+        <x:v>图 P08-7</x:v>
       </x:c>
     </x:row>
     <x:row r="258">
@@ -17053,19 +17053,19 @@
         <x:v>docs/en/part14/p08_dataops.md</x:v>
       </x:c>
       <x:c r="G258" s="4" t="n">
-        <x:v>935</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="H258" s="4" t="str">
-        <x:v>P08-11</x:v>
+        <x:v>P08-8</x:v>
       </x:c>
       <x:c r="I258" s="4" t="str">
-        <x:v>Figure 11: Check pipeline and consistency validation</x:v>
+        <x:v>Figure 8: Rollback trigger and recovery flow</x:v>
       </x:c>
       <x:c r="J258" s="4" t="str">
-        <x:v>Figure 11: Check pipeline and consistency validation</x:v>
+        <x:v>Figure 8: Rollback trigger and recovery flow</x:v>
       </x:c>
       <x:c r="K258" s="4" t="str">
-        <x:v>docs/images/part14/p08/p08_11_validation_pipeline.svg</x:v>
+        <x:v>docs/images/part14/p08/p08_08_rollback_flow.svg</x:v>
       </x:c>
       <x:c r="L258" s="4" t="str">
         <x:v>yes</x:v>
@@ -17077,11 +17077,9 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O258" s="4" t="str">
-        <x:v>Figure 11: Check pipeline and consistency validation.</x:v>
-      </x:c>
-      <x:c r="P258" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Project 8: Building an Enterprise DataOps Platform; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>Figure 8: Rollback trigger and recovery flow.</x:v>
+      </x:c>
+      <x:c r="P258" s="4" t="str"/>
       <x:c r="Q258" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -17091,10 +17089,10 @@
       <x:c r="S258" s="4" t="str"/>
       <x:c r="T258" s="4" t="str"/>
       <x:c r="U258" s="4" t="str">
-        <x:v>Figure P08-11：检查链路与一致性验证图</x:v>
+        <x:v>Figure P08-8：回滚触发与恢复流程图</x:v>
       </x:c>
       <x:c r="V258" s="4" t="str">
-        <x:v>图 P08-11</x:v>
+        <x:v>图 P08-8</x:v>
       </x:c>
     </x:row>
     <x:row r="259">
@@ -17108,44 +17106,42 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D259" s="4" t="str">
-        <x:v>P09</x:v>
+        <x:v>P08</x:v>
       </x:c>
       <x:c r="E259" s="4" t="str">
-        <x:v>Project 9: Privacy-preserving Data Pipeline</x:v>
+        <x:v>Project 8: Building an Enterprise DataOps Platform</x:v>
       </x:c>
       <x:c r="F259" s="4" t="str">
-        <x:v>docs/en/part14/p09_privacy_pipeline.md</x:v>
+        <x:v>docs/en/part14/p08_dataops.md</x:v>
       </x:c>
       <x:c r="G259" s="4" t="n">
-        <x:v>174</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="H259" s="4" t="str">
-        <x:v>P09-1</x:v>
+        <x:v>P08-9</x:v>
       </x:c>
       <x:c r="I259" s="4" t="str">
-        <x:v>Figure P09-1: P09 Privacy-Preserving Data Pipeline Overall Architecture</x:v>
+        <x:v>Figure 9: Metrics, logs, alerts, and audit loop</x:v>
       </x:c>
       <x:c r="J259" s="4" t="str">
-        <x:v>Figure P09-1</x:v>
+        <x:v>Figure 9: Metrics, logs, alerts, and audit loop</x:v>
       </x:c>
       <x:c r="K259" s="4" t="str">
-        <x:v>docs/images/part14/p09/p09_01_privacy_pipeline_overview.svg</x:v>
+        <x:v>docs/images/part14/p08/p08_09_observability_loop.svg</x:v>
       </x:c>
       <x:c r="L259" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M259" s="4" t="str">
-        <x:v>1536x1024</x:v>
+        <x:v>1254x1254</x:v>
       </x:c>
       <x:c r="N259" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O259" s="4" t="str">
-        <x:v>P09 Privacy-Preserving Data Pipeline Overall Architecture.</x:v>
-      </x:c>
-      <x:c r="P259" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Project 9: Privacy-preserving Data Pipeline; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>Figure 9: Metrics, logs, alerts, and audit loop.</x:v>
+      </x:c>
+      <x:c r="P259" s="4" t="str"/>
       <x:c r="Q259" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -17155,10 +17151,10 @@
       <x:c r="S259" s="4" t="str"/>
       <x:c r="T259" s="4" t="str"/>
       <x:c r="U259" s="4" t="str">
-        <x:v>Figure P09-1：P09 隐私保护数据流水线总体架构</x:v>
+        <x:v>Figure P08-9：指标—日志—告警—审计闭环图</x:v>
       </x:c>
       <x:c r="V259" s="4" t="str">
-        <x:v>图 P09-1</x:v>
+        <x:v>图 P08-9</x:v>
       </x:c>
     </x:row>
     <x:row r="260">
@@ -17172,44 +17168,42 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D260" s="4" t="str">
-        <x:v>P09</x:v>
+        <x:v>P08</x:v>
       </x:c>
       <x:c r="E260" s="4" t="str">
-        <x:v>Project 9: Privacy-preserving Data Pipeline</x:v>
+        <x:v>Project 8: Building an Enterprise DataOps Platform</x:v>
       </x:c>
       <x:c r="F260" s="4" t="str">
-        <x:v>docs/en/part14/p09_privacy_pipeline.md</x:v>
+        <x:v>docs/en/part14/p08_dataops.md</x:v>
       </x:c>
       <x:c r="G260" s="4" t="n">
-        <x:v>245</x:v>
+        <x:v>841</x:v>
       </x:c>
       <x:c r="H260" s="4" t="str">
-        <x:v>P09-2</x:v>
+        <x:v>P08-10</x:v>
       </x:c>
       <x:c r="I260" s="4" t="str">
-        <x:v>Figure P09-2: Key Engineering Dimensions of the P09 Privacy Pipeline</x:v>
+        <x:v>Figure 10: Audit logs and incident review</x:v>
       </x:c>
       <x:c r="J260" s="4" t="str">
-        <x:v>Figure P09-2</x:v>
+        <x:v>Figure 10: Audit logs and incident review</x:v>
       </x:c>
       <x:c r="K260" s="4" t="str">
-        <x:v>docs/images/part14/p09/p09_02_roles_and_responsibilities.svg</x:v>
+        <x:v>docs/images/part14/p08/p08_10_audit_and_incident_review.svg</x:v>
       </x:c>
       <x:c r="L260" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M260" s="4" t="str">
-        <x:v>1536x1024</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N260" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O260" s="4" t="str">
-        <x:v>Key Engineering Dimensions of the P09 Privacy Pipeline.</x:v>
-      </x:c>
-      <x:c r="P260" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Project 9: Privacy-preserving Data Pipeline; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>Figure 10: Audit logs and incident review.</x:v>
+      </x:c>
+      <x:c r="P260" s="4" t="str"/>
       <x:c r="Q260" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -17219,10 +17213,10 @@
       <x:c r="S260" s="4" t="str"/>
       <x:c r="T260" s="4" t="str"/>
       <x:c r="U260" s="4" t="str">
-        <x:v>Figure P09-2：P09 隐私流水线关键工程面图</x:v>
+        <x:v>Figure P08-10：审计日志与事故复盘关联图</x:v>
       </x:c>
       <x:c r="V260" s="4" t="str">
-        <x:v>图 P09-2</x:v>
+        <x:v>图 P08-10</x:v>
       </x:c>
     </x:row>
     <x:row r="261">
@@ -17236,28 +17230,28 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D261" s="4" t="str">
-        <x:v>P09</x:v>
+        <x:v>P08</x:v>
       </x:c>
       <x:c r="E261" s="4" t="str">
-        <x:v>Project 9: Privacy-preserving Data Pipeline</x:v>
+        <x:v>Project 8: Building an Enterprise DataOps Platform</x:v>
       </x:c>
       <x:c r="F261" s="4" t="str">
-        <x:v>docs/en/part14/p09_privacy_pipeline.md</x:v>
+        <x:v>docs/en/part14/p08_dataops.md</x:v>
       </x:c>
       <x:c r="G261" s="4" t="n">
-        <x:v>332</x:v>
+        <x:v>935</x:v>
       </x:c>
       <x:c r="H261" s="4" t="str">
-        <x:v>P09-3</x:v>
+        <x:v>P08-11</x:v>
       </x:c>
       <x:c r="I261" s="4" t="str">
-        <x:v>Figure P09-3: Relationships Among the Four Artifact Types in the Privacy Specification Layer</x:v>
+        <x:v>Figure 11: Check pipeline and consistency validation</x:v>
       </x:c>
       <x:c r="J261" s="4" t="str">
-        <x:v>Figure P09-3</x:v>
+        <x:v>Figure 11: Check pipeline and consistency validation</x:v>
       </x:c>
       <x:c r="K261" s="4" t="str">
-        <x:v>docs/images/part14/p09/p09_03_specs_layer.svg</x:v>
+        <x:v>docs/images/part14/p08/p08_11_validation_pipeline.svg</x:v>
       </x:c>
       <x:c r="L261" s="4" t="str">
         <x:v>yes</x:v>
@@ -17269,9 +17263,11 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O261" s="4" t="str">
-        <x:v>Relationships Among the Four Artifact Types in the Privacy Specification Layer.</x:v>
-      </x:c>
-      <x:c r="P261" s="4" t="str"/>
+        <x:v>Figure 11: Check pipeline and consistency validation.</x:v>
+      </x:c>
+      <x:c r="P261" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Project 8: Building an Enterprise DataOps Platform; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q261" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -17281,10 +17277,10 @@
       <x:c r="S261" s="4" t="str"/>
       <x:c r="T261" s="4" t="str"/>
       <x:c r="U261" s="4" t="str">
-        <x:v>Figure P09-3：隐私规格层四类产物关系图</x:v>
+        <x:v>Figure P08-11：检查链路与一致性验证图</x:v>
       </x:c>
       <x:c r="V261" s="4" t="str">
-        <x:v>图 P09-3</x:v>
+        <x:v>图 P08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="262">
@@ -17307,33 +17303,35 @@
         <x:v>docs/en/part14/p09_privacy_pipeline.md</x:v>
       </x:c>
       <x:c r="G262" s="4" t="n">
-        <x:v>392</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="H262" s="4" t="str">
-        <x:v>P09-4</x:v>
+        <x:v>P09-1</x:v>
       </x:c>
       <x:c r="I262" s="4" t="str">
-        <x:v>Figure P09-4: Scenario Coverage of Raw Sensitive Records</x:v>
+        <x:v>Figure P09-1: P09 Privacy-Preserving Data Pipeline Overall Architecture</x:v>
       </x:c>
       <x:c r="J262" s="4" t="str">
-        <x:v>Figure P09-4</x:v>
+        <x:v>Figure P09-1</x:v>
       </x:c>
       <x:c r="K262" s="4" t="str">
-        <x:v>docs/images/part14/p09/p09_04_raw_records_coverage.svg</x:v>
+        <x:v>docs/images/part14/p09/p09_01_privacy_pipeline_overview.svg</x:v>
       </x:c>
       <x:c r="L262" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M262" s="4" t="str">
-        <x:v>1672x941</x:v>
+        <x:v>1536x1024</x:v>
       </x:c>
       <x:c r="N262" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O262" s="4" t="str">
-        <x:v>Scenario Coverage of Raw Sensitive Records.</x:v>
-      </x:c>
-      <x:c r="P262" s="4" t="str"/>
+        <x:v>P09 Privacy-Preserving Data Pipeline Overall Architecture.</x:v>
+      </x:c>
+      <x:c r="P262" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Project 9: Privacy-preserving Data Pipeline; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q262" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -17343,10 +17341,10 @@
       <x:c r="S262" s="4" t="str"/>
       <x:c r="T262" s="4" t="str"/>
       <x:c r="U262" s="4" t="str">
-        <x:v>Figure P09-4：原始敏感记录场景覆盖图</x:v>
+        <x:v>Figure P09-1：P09 隐私保护数据流水线总体架构</x:v>
       </x:c>
       <x:c r="V262" s="4" t="str">
-        <x:v>图 P09-4</x:v>
+        <x:v>图 P09-1</x:v>
       </x:c>
     </x:row>
     <x:row r="263">
@@ -17369,31 +17367,31 @@
         <x:v>docs/en/part14/p09_privacy_pipeline.md</x:v>
       </x:c>
       <x:c r="G263" s="4" t="n">
-        <x:v>446</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="H263" s="4" t="str">
-        <x:v>P09-5</x:v>
+        <x:v>P09-2</x:v>
       </x:c>
       <x:c r="I263" s="4" t="str">
-        <x:v>Figure P09-5: PII Detection Rules and Hit Distribution</x:v>
+        <x:v>Figure P09-2: Key Engineering Dimensions of the P09 Privacy Pipeline</x:v>
       </x:c>
       <x:c r="J263" s="4" t="str">
-        <x:v>Figure P09-5</x:v>
+        <x:v>Figure P09-2</x:v>
       </x:c>
       <x:c r="K263" s="4" t="str">
-        <x:v>docs/images/part14/p09/p09_05_pii_detection_distribution.svg</x:v>
+        <x:v>docs/images/part14/p09/p09_02_roles_and_responsibilities.svg</x:v>
       </x:c>
       <x:c r="L263" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M263" s="4" t="str">
-        <x:v>1672x941</x:v>
+        <x:v>1536x1024</x:v>
       </x:c>
       <x:c r="N263" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O263" s="4" t="str">
-        <x:v>PII Detection Rules and Hit Distribution.</x:v>
+        <x:v>Key Engineering Dimensions of the P09 Privacy Pipeline.</x:v>
       </x:c>
       <x:c r="P263" s="4" t="str">
         <x:v>Review against the figure and surrounding text in Project 9: Privacy-preserving Data Pipeline; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
@@ -17407,10 +17405,10 @@
       <x:c r="S263" s="4" t="str"/>
       <x:c r="T263" s="4" t="str"/>
       <x:c r="U263" s="4" t="str">
-        <x:v>Figure P09-5：PII 检测规则与命中分布图</x:v>
+        <x:v>Figure P09-2：P09 隐私流水线关键工程面图</x:v>
       </x:c>
       <x:c r="V263" s="4" t="str">
-        <x:v>图 P09-5</x:v>
+        <x:v>图 P09-2</x:v>
       </x:c>
     </x:row>
     <x:row r="264">
@@ -17433,19 +17431,19 @@
         <x:v>docs/en/part14/p09_privacy_pipeline.md</x:v>
       </x:c>
       <x:c r="G264" s="4" t="n">
-        <x:v>496</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="H264" s="4" t="str">
-        <x:v>P09-6</x:v>
+        <x:v>P09-3</x:v>
       </x:c>
       <x:c r="I264" s="4" t="str">
-        <x:v>Figure P09-6: Classification Determination and Quarantine Trigger Relationship</x:v>
+        <x:v>Figure P09-3: Relationships Among the Four Artifact Types in the Privacy Specification Layer</x:v>
       </x:c>
       <x:c r="J264" s="4" t="str">
-        <x:v>Figure P09-6</x:v>
+        <x:v>Figure P09-3</x:v>
       </x:c>
       <x:c r="K264" s="4" t="str">
-        <x:v>docs/images/part14/p09/p09_06_classification_and_quarantine.svg</x:v>
+        <x:v>docs/images/part14/p09/p09_03_specs_layer.svg</x:v>
       </x:c>
       <x:c r="L264" s="4" t="str">
         <x:v>yes</x:v>
@@ -17457,7 +17455,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O264" s="4" t="str">
-        <x:v>Classification Determination and Quarantine Trigger Relationship.</x:v>
+        <x:v>Relationships Among the Four Artifact Types in the Privacy Specification Layer.</x:v>
       </x:c>
       <x:c r="P264" s="4" t="str"/>
       <x:c r="Q264" s="4" t="str">
@@ -17469,10 +17467,10 @@
       <x:c r="S264" s="4" t="str"/>
       <x:c r="T264" s="4" t="str"/>
       <x:c r="U264" s="4" t="str">
-        <x:v>Figure P09-6：分类判定与隔离触发关系图</x:v>
+        <x:v>Figure P09-3：隐私规格层四类产物关系图</x:v>
       </x:c>
       <x:c r="V264" s="4" t="str">
-        <x:v>图 P09-6</x:v>
+        <x:v>图 P09-3</x:v>
       </x:c>
     </x:row>
     <x:row r="265">
@@ -17495,19 +17493,19 @@
         <x:v>docs/en/part14/p09_privacy_pipeline.md</x:v>
       </x:c>
       <x:c r="G265" s="4" t="n">
-        <x:v>553</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="H265" s="4" t="str">
-        <x:v>P09-7</x:v>
+        <x:v>P09-4</x:v>
       </x:c>
       <x:c r="I265" s="4" t="str">
-        <x:v>Figure P09-7: De-identification Strategies for Different PII Types</x:v>
+        <x:v>Figure P09-4: Scenario Coverage of Raw Sensitive Records</x:v>
       </x:c>
       <x:c r="J265" s="4" t="str">
-        <x:v>Figure P09-7</x:v>
+        <x:v>Figure P09-4</x:v>
       </x:c>
       <x:c r="K265" s="4" t="str">
-        <x:v>docs/images/part14/p09/p09_07_redaction_strategies.svg</x:v>
+        <x:v>docs/images/part14/p09/p09_04_raw_records_coverage.svg</x:v>
       </x:c>
       <x:c r="L265" s="4" t="str">
         <x:v>yes</x:v>
@@ -17519,7 +17517,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O265" s="4" t="str">
-        <x:v>De-identification Strategies for Different PII Types.</x:v>
+        <x:v>Scenario Coverage of Raw Sensitive Records.</x:v>
       </x:c>
       <x:c r="P265" s="4" t="str"/>
       <x:c r="Q265" s="4" t="str">
@@ -17531,10 +17529,10 @@
       <x:c r="S265" s="4" t="str"/>
       <x:c r="T265" s="4" t="str"/>
       <x:c r="U265" s="4" t="str">
-        <x:v>Figure P09-7：不同 PII 类型的去标识化策略图</x:v>
+        <x:v>Figure P09-4：原始敏感记录场景覆盖图</x:v>
       </x:c>
       <x:c r="V265" s="4" t="str">
-        <x:v>图 P09-7</x:v>
+        <x:v>图 P09-4</x:v>
       </x:c>
     </x:row>
     <x:row r="266">
@@ -17557,19 +17555,19 @@
         <x:v>docs/en/part14/p09_privacy_pipeline.md</x:v>
       </x:c>
       <x:c r="G266" s="4" t="n">
-        <x:v>605</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="H266" s="4" t="str">
-        <x:v>P09-8</x:v>
+        <x:v>P09-5</x:v>
       </x:c>
       <x:c r="I266" s="4" t="str">
-        <x:v>Figure P09-8: Storage Zones and Role Access Boundaries</x:v>
+        <x:v>Figure P09-5: PII Detection Rules and Hit Distribution</x:v>
       </x:c>
       <x:c r="J266" s="4" t="str">
-        <x:v>Figure P09-8</x:v>
+        <x:v>Figure P09-5</x:v>
       </x:c>
       <x:c r="K266" s="4" t="str">
-        <x:v>docs/images/part14/p09/p09_08_storage_zones.svg</x:v>
+        <x:v>docs/images/part14/p09/p09_05_pii_detection_distribution.svg</x:v>
       </x:c>
       <x:c r="L266" s="4" t="str">
         <x:v>yes</x:v>
@@ -17581,9 +17579,11 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O266" s="4" t="str">
-        <x:v>Storage Zones and Role Access Boundaries.</x:v>
-      </x:c>
-      <x:c r="P266" s="4" t="str"/>
+        <x:v>PII Detection Rules and Hit Distribution.</x:v>
+      </x:c>
+      <x:c r="P266" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Project 9: Privacy-preserving Data Pipeline; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q266" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -17593,10 +17593,10 @@
       <x:c r="S266" s="4" t="str"/>
       <x:c r="T266" s="4" t="str"/>
       <x:c r="U266" s="4" t="str">
-        <x:v>Figure P09-8：存储分区与角色访问边界图</x:v>
+        <x:v>Figure P09-5：PII 检测规则与命中分布图</x:v>
       </x:c>
       <x:c r="V266" s="4" t="str">
-        <x:v>图 P09-8</x:v>
+        <x:v>图 P09-5</x:v>
       </x:c>
     </x:row>
     <x:row r="267">
@@ -17619,19 +17619,19 @@
         <x:v>docs/en/part14/p09_privacy_pipeline.md</x:v>
       </x:c>
       <x:c r="G267" s="4" t="n">
-        <x:v>651</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="H267" s="4" t="str">
-        <x:v>P09-9</x:v>
+        <x:v>P09-6</x:v>
       </x:c>
       <x:c r="I267" s="4" t="str">
-        <x:v>Figure P09-9: Relationships Among Alerts, Audit, and Incident Response</x:v>
+        <x:v>Figure P09-6: Classification Determination and Quarantine Trigger Relationship</x:v>
       </x:c>
       <x:c r="J267" s="4" t="str">
-        <x:v>Figure P09-9</x:v>
+        <x:v>Figure P09-6</x:v>
       </x:c>
       <x:c r="K267" s="4" t="str">
-        <x:v>docs/images/part14/p09/p09_09_alerts_and_audit.svg</x:v>
+        <x:v>docs/images/part14/p09/p09_06_classification_and_quarantine.svg</x:v>
       </x:c>
       <x:c r="L267" s="4" t="str">
         <x:v>yes</x:v>
@@ -17643,7 +17643,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O267" s="4" t="str">
-        <x:v>Relationships Among Alerts, Audit, and Incident Response.</x:v>
+        <x:v>Classification Determination and Quarantine Trigger Relationship.</x:v>
       </x:c>
       <x:c r="P267" s="4" t="str"/>
       <x:c r="Q267" s="4" t="str">
@@ -17655,10 +17655,10 @@
       <x:c r="S267" s="4" t="str"/>
       <x:c r="T267" s="4" t="str"/>
       <x:c r="U267" s="4" t="str">
-        <x:v>Figure P09-9：告警、审计与事件响应关系图</x:v>
+        <x:v>Figure P09-6：分类判定与隔离触发关系图</x:v>
       </x:c>
       <x:c r="V267" s="4" t="str">
-        <x:v>图 P09-9</x:v>
+        <x:v>图 P09-6</x:v>
       </x:c>
     </x:row>
     <x:row r="268">
@@ -17681,19 +17681,19 @@
         <x:v>docs/en/part14/p09_privacy_pipeline.md</x:v>
       </x:c>
       <x:c r="G268" s="4" t="n">
-        <x:v>697</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="H268" s="4" t="str">
-        <x:v>P09-10</x:v>
+        <x:v>P09-7</x:v>
       </x:c>
       <x:c r="I268" s="4" t="str">
-        <x:v>Figure P09-10: Preflight Check Process</x:v>
+        <x:v>Figure P09-7: De-identification Strategies for Different PII Types</x:v>
       </x:c>
       <x:c r="J268" s="4" t="str">
-        <x:v>Figure P09-10</x:v>
+        <x:v>Figure P09-7</x:v>
       </x:c>
       <x:c r="K268" s="4" t="str">
-        <x:v>docs/images/part14/p09/p09_10_preflight_checks.svg</x:v>
+        <x:v>docs/images/part14/p09/p09_07_redaction_strategies.svg</x:v>
       </x:c>
       <x:c r="L268" s="4" t="str">
         <x:v>yes</x:v>
@@ -17705,7 +17705,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O268" s="4" t="str">
-        <x:v>Preflight Check Process. Because it reflects a mature engineering practice: Not "run first, then observe," but "confirm that minimum conditions are met first, then proceed to higher-risk processing and exercise stages." Figure P09-10: Preflight Check Process.</x:v>
+        <x:v>De-identification Strategies for Different PII Types.</x:v>
       </x:c>
       <x:c r="P268" s="4" t="str"/>
       <x:c r="Q268" s="4" t="str">
@@ -17717,10 +17717,10 @@
       <x:c r="S268" s="4" t="str"/>
       <x:c r="T268" s="4" t="str"/>
       <x:c r="U268" s="4" t="str">
-        <x:v>Figure P09-10：preflight 检查流程图</x:v>
+        <x:v>Figure P09-7：不同 PII 类型的去标识化策略图</x:v>
       </x:c>
       <x:c r="V268" s="4" t="str">
-        <x:v>图 P09-10</x:v>
+        <x:v>图 P09-7</x:v>
       </x:c>
     </x:row>
     <x:row r="269">
@@ -17743,19 +17743,19 @@
         <x:v>docs/en/part14/p09_privacy_pipeline.md</x:v>
       </x:c>
       <x:c r="G269" s="4" t="n">
-        <x:v>745</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="H269" s="4" t="str">
-        <x:v>P09-11</x:v>
+        <x:v>P09-8</x:v>
       </x:c>
       <x:c r="I269" s="4" t="str">
-        <x:v>Figure P09-11: Incident Response and Postmortem Feedback Loop</x:v>
+        <x:v>Figure P09-8: Storage Zones and Role Access Boundaries</x:v>
       </x:c>
       <x:c r="J269" s="4" t="str">
-        <x:v>Figure P09-11</x:v>
+        <x:v>Figure P09-8</x:v>
       </x:c>
       <x:c r="K269" s="4" t="str">
-        <x:v>docs/images/part14/p09/p09_11_incident_postmortem.svg</x:v>
+        <x:v>docs/images/part14/p09/p09_08_storage_zones.svg</x:v>
       </x:c>
       <x:c r="L269" s="4" t="str">
         <x:v>yes</x:v>
@@ -17767,7 +17767,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O269" s="4" t="str">
-        <x:v>Incident Response and Postmortem Feedback Loop.</x:v>
+        <x:v>Storage Zones and Role Access Boundaries.</x:v>
       </x:c>
       <x:c r="P269" s="4" t="str"/>
       <x:c r="Q269" s="4" t="str">
@@ -17779,10 +17779,10 @@
       <x:c r="S269" s="4" t="str"/>
       <x:c r="T269" s="4" t="str"/>
       <x:c r="U269" s="4" t="str">
-        <x:v>Figure P09-11：事故响应与 postmortem 闭环图</x:v>
+        <x:v>Figure P09-8：存储分区与角色访问边界图</x:v>
       </x:c>
       <x:c r="V269" s="4" t="str">
-        <x:v>图 P09-11</x:v>
+        <x:v>图 P09-8</x:v>
       </x:c>
     </x:row>
     <x:row r="270">
@@ -17805,19 +17805,19 @@
         <x:v>docs/en/part14/p09_privacy_pipeline.md</x:v>
       </x:c>
       <x:c r="G270" s="4" t="n">
-        <x:v>986</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="H270" s="4" t="str">
-        <x:v>P09-12</x:v>
+        <x:v>P09-9</x:v>
       </x:c>
       <x:c r="I270" s="4" t="str">
-        <x:v>Figure P09-12: P09 Minimal Reproducible Execution Chain</x:v>
+        <x:v>Figure P09-9: Relationships Among Alerts, Audit, and Incident Response</x:v>
       </x:c>
       <x:c r="J270" s="4" t="str">
-        <x:v>Figure P09-12</x:v>
+        <x:v>Figure P09-9</x:v>
       </x:c>
       <x:c r="K270" s="4" t="str">
-        <x:v>docs/images/part14/p09/p09_12_execution_sequence.svg</x:v>
+        <x:v>docs/images/part14/p09/p09_09_alerts_and_audit.svg</x:v>
       </x:c>
       <x:c r="L270" s="4" t="str">
         <x:v>yes</x:v>
@@ -17829,7 +17829,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O270" s="4" t="str">
-        <x:v>P09 Minimal Reproducible Execution Chain.</x:v>
+        <x:v>Relationships Among Alerts, Audit, and Incident Response.</x:v>
       </x:c>
       <x:c r="P270" s="4" t="str"/>
       <x:c r="Q270" s="4" t="str">
@@ -17841,10 +17841,10 @@
       <x:c r="S270" s="4" t="str"/>
       <x:c r="T270" s="4" t="str"/>
       <x:c r="U270" s="4" t="str">
-        <x:v>Figure P09-12：P09 最小可复现运行链图</x:v>
+        <x:v>Figure P09-9：告警、审计与事件响应关系图</x:v>
       </x:c>
       <x:c r="V270" s="4" t="str">
-        <x:v>图 P09-12</x:v>
+        <x:v>图 P09-9</x:v>
       </x:c>
     </x:row>
     <x:row r="271">
@@ -17858,28 +17858,28 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D271" s="4" t="str">
-        <x:v>P10</x:v>
+        <x:v>P09</x:v>
       </x:c>
       <x:c r="E271" s="4" t="str">
-        <x:v>Project 10: End-to-End LLM Data Flywheel</x:v>
+        <x:v>Project 9: Privacy-preserving Data Pipeline</x:v>
       </x:c>
       <x:c r="F271" s="4" t="str">
-        <x:v>docs/en/part14/p10_flywheel.md</x:v>
+        <x:v>docs/en/part14/p09_privacy_pipeline.md</x:v>
       </x:c>
       <x:c r="G271" s="4" t="n">
-        <x:v>270</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="H271" s="4" t="str">
-        <x:v>P10-1</x:v>
+        <x:v>P09-10</x:v>
       </x:c>
       <x:c r="I271" s="4" t="str">
-        <x:v>From an engineering perspective, this project should be viewed as five layers instead of a linear data-input to model-output chain</x:v>
+        <x:v>Figure P09-10: Preflight Check Process</x:v>
       </x:c>
       <x:c r="J271" s="4" t="str">
-        <x:v>Figure 1: End-to-end LLM data flywheel overview</x:v>
+        <x:v>Figure P09-10</x:v>
       </x:c>
       <x:c r="K271" s="4" t="str">
-        <x:v>docs/images/part14/p10/p10_01_flywheel_overview.svg</x:v>
+        <x:v>docs/images/part14/p09/p09_10_preflight_checks.svg</x:v>
       </x:c>
       <x:c r="L271" s="4" t="str">
         <x:v>yes</x:v>
@@ -17891,7 +17891,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O271" s="4" t="str">
-        <x:v>From an engineering perspective, this project should be viewed as five layers instead of a linear data-input to model-output chain.</x:v>
+        <x:v>Preflight Check Process. Because it reflects a mature engineering practice: Not "run first, then observe," but "confirm that minimum conditions are met first, then proceed to higher-risk processing and exercise stages." Figure P09-10: Preflight Check Process.</x:v>
       </x:c>
       <x:c r="P271" s="4" t="str"/>
       <x:c r="Q271" s="4" t="str">
@@ -17903,10 +17903,10 @@
       <x:c r="S271" s="4" t="str"/>
       <x:c r="T271" s="4" t="str"/>
       <x:c r="U271" s="4" t="str">
-        <x:v>Figure P10-1：端到端 LLM 数据飞轮总览图</x:v>
+        <x:v>Figure P09-10：preflight 检查流程图</x:v>
       </x:c>
       <x:c r="V271" s="4" t="str">
-        <x:v>图 P10-1</x:v>
+        <x:v>图 P09-10</x:v>
       </x:c>
     </x:row>
     <x:row r="272">
@@ -17920,26 +17920,28 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D272" s="4" t="str">
-        <x:v>P10</x:v>
+        <x:v>P09</x:v>
       </x:c>
       <x:c r="E272" s="4" t="str">
-        <x:v>Project 10: End-to-End LLM Data Flywheel</x:v>
+        <x:v>Project 9: Privacy-preserving Data Pipeline</x:v>
       </x:c>
       <x:c r="F272" s="4" t="str">
-        <x:v>docs/en/part14/p10_flywheel.md</x:v>
+        <x:v>docs/en/part14/p09_privacy_pipeline.md</x:v>
       </x:c>
       <x:c r="G272" s="4" t="n">
-        <x:v>384</x:v>
+        <x:v>745</x:v>
       </x:c>
       <x:c r="H272" s="4" t="str">
-        <x:v>P10-2</x:v>
-      </x:c>
-      <x:c r="I272" s="4" t="str"/>
+        <x:v>P09-11</x:v>
+      </x:c>
+      <x:c r="I272" s="4" t="str">
+        <x:v>Figure P09-11: Incident Response and Postmortem Feedback Loop</x:v>
+      </x:c>
       <x:c r="J272" s="4" t="str">
-        <x:v>Figure 2: Upstream project registry and interface mapping</x:v>
+        <x:v>Figure P09-11</x:v>
       </x:c>
       <x:c r="K272" s="4" t="str">
-        <x:v>docs/images/part14/p10/p10_02_registry_and_interfaces.svg</x:v>
+        <x:v>docs/images/part14/p09/p09_11_incident_postmortem.svg</x:v>
       </x:c>
       <x:c r="L272" s="4" t="str">
         <x:v>yes</x:v>
@@ -17951,7 +17953,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O272" s="4" t="str">
-        <x:v>Figure 2: Upstream project registry and interface mapping.</x:v>
+        <x:v>Incident Response and Postmortem Feedback Loop.</x:v>
       </x:c>
       <x:c r="P272" s="4" t="str"/>
       <x:c r="Q272" s="4" t="str">
@@ -17963,10 +17965,10 @@
       <x:c r="S272" s="4" t="str"/>
       <x:c r="T272" s="4" t="str"/>
       <x:c r="U272" s="4" t="str">
-        <x:v>Figure P10-2：上游项目 registry 与接口映射图</x:v>
+        <x:v>Figure P09-11：事故响应与 postmortem 闭环图</x:v>
       </x:c>
       <x:c r="V272" s="4" t="str">
-        <x:v>图 P10-2</x:v>
+        <x:v>图 P09-11</x:v>
       </x:c>
     </x:row>
     <x:row r="273">
@@ -17980,26 +17982,28 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D273" s="4" t="str">
-        <x:v>P10</x:v>
+        <x:v>P09</x:v>
       </x:c>
       <x:c r="E273" s="4" t="str">
-        <x:v>Project 10: End-to-End LLM Data Flywheel</x:v>
+        <x:v>Project 9: Privacy-preserving Data Pipeline</x:v>
       </x:c>
       <x:c r="F273" s="4" t="str">
-        <x:v>docs/en/part14/p10_flywheel.md</x:v>
+        <x:v>docs/en/part14/p09_privacy_pipeline.md</x:v>
       </x:c>
       <x:c r="G273" s="4" t="n">
-        <x:v>438</x:v>
+        <x:v>986</x:v>
       </x:c>
       <x:c r="H273" s="4" t="str">
-        <x:v>P10-3</x:v>
-      </x:c>
-      <x:c r="I273" s="4" t="str"/>
+        <x:v>P09-12</x:v>
+      </x:c>
+      <x:c r="I273" s="4" t="str">
+        <x:v>Figure P09-12: P09 Minimal Reproducible Execution Chain</x:v>
+      </x:c>
       <x:c r="J273" s="4" t="str">
-        <x:v>Figure 3: Structured upstream project specs</x:v>
+        <x:v>Figure P09-12</x:v>
       </x:c>
       <x:c r="K273" s="4" t="str">
-        <x:v>docs/images/part14/p10/p10_03_project_specs.svg</x:v>
+        <x:v>docs/images/part14/p09/p09_12_execution_sequence.svg</x:v>
       </x:c>
       <x:c r="L273" s="4" t="str">
         <x:v>yes</x:v>
@@ -18011,7 +18015,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O273" s="4" t="str">
-        <x:v>Figure 3: Structured upstream project specs.</x:v>
+        <x:v>P09 Minimal Reproducible Execution Chain.</x:v>
       </x:c>
       <x:c r="P273" s="4" t="str"/>
       <x:c r="Q273" s="4" t="str">
@@ -18023,10 +18027,10 @@
       <x:c r="S273" s="4" t="str"/>
       <x:c r="T273" s="4" t="str"/>
       <x:c r="U273" s="4" t="str">
-        <x:v>Figure P10-3：上游项目结构化配置示意图</x:v>
+        <x:v>Figure P09-12：P09 最小可复现运行链图</x:v>
       </x:c>
       <x:c r="V273" s="4" t="str">
-        <x:v>图 P10-3</x:v>
+        <x:v>图 P09-12</x:v>
       </x:c>
     </x:row>
     <x:row r="274">
@@ -18049,29 +18053,31 @@
         <x:v>docs/en/part14/p10_flywheel.md</x:v>
       </x:c>
       <x:c r="G274" s="4" t="n">
-        <x:v>481</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="H274" s="4" t="str">
-        <x:v>P10-4</x:v>
-      </x:c>
-      <x:c r="I274" s="4" t="str"/>
+        <x:v>P10-1</x:v>
+      </x:c>
+      <x:c r="I274" s="4" t="str">
+        <x:v>From an engineering perspective, this project should be viewed as five layers instead of a linear data-input to model-output chain</x:v>
+      </x:c>
       <x:c r="J274" s="4" t="str">
-        <x:v>Figure 4: Five-stage plan and milestone relationships</x:v>
+        <x:v>Figure 1: End-to-end LLM data flywheel overview</x:v>
       </x:c>
       <x:c r="K274" s="4" t="str">
-        <x:v>docs/images/part14/p10/p10_04_stage_plan.svg</x:v>
+        <x:v>docs/images/part14/p10/p10_01_flywheel_overview.svg</x:v>
       </x:c>
       <x:c r="L274" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M274" s="4" t="str">
-        <x:v>1672x642</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N274" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O274" s="4" t="str">
-        <x:v>Figure 4: Five-stage plan and milestone relationships.</x:v>
+        <x:v>From an engineering perspective, this project should be viewed as five layers instead of a linear data-input to model-output chain.</x:v>
       </x:c>
       <x:c r="P274" s="4" t="str"/>
       <x:c r="Q274" s="4" t="str">
@@ -18083,10 +18089,10 @@
       <x:c r="S274" s="4" t="str"/>
       <x:c r="T274" s="4" t="str"/>
       <x:c r="U274" s="4" t="str">
-        <x:v>Figure P10-4：五阶段推进与里程碑关系图</x:v>
+        <x:v>Figure P10-1：端到端 LLM 数据飞轮总览图</x:v>
       </x:c>
       <x:c r="V274" s="4" t="str">
-        <x:v>图 P10-4</x:v>
+        <x:v>图 P10-1</x:v>
       </x:c>
     </x:row>
     <x:row r="275">
@@ -18109,17 +18115,17 @@
         <x:v>docs/en/part14/p10_flywheel.md</x:v>
       </x:c>
       <x:c r="G275" s="4" t="n">
-        <x:v>548</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="H275" s="4" t="str">
-        <x:v>P10-5</x:v>
+        <x:v>P10-2</x:v>
       </x:c>
       <x:c r="I275" s="4" t="str"/>
       <x:c r="J275" s="4" t="str">
-        <x:v>Figure 5: Five-layer flywheel code mapping</x:v>
+        <x:v>Figure 2: Upstream project registry and interface mapping</x:v>
       </x:c>
       <x:c r="K275" s="4" t="str">
-        <x:v>docs/images/part14/p10/p10_05_architecture_code_mapping.svg</x:v>
+        <x:v>docs/images/part14/p10/p10_02_registry_and_interfaces.svg</x:v>
       </x:c>
       <x:c r="L275" s="4" t="str">
         <x:v>yes</x:v>
@@ -18131,7 +18137,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O275" s="4" t="str">
-        <x:v>Figure 5: Five-layer flywheel code mapping.</x:v>
+        <x:v>Figure 2: Upstream project registry and interface mapping.</x:v>
       </x:c>
       <x:c r="P275" s="4" t="str"/>
       <x:c r="Q275" s="4" t="str">
@@ -18143,10 +18149,10 @@
       <x:c r="S275" s="4" t="str"/>
       <x:c r="T275" s="4" t="str"/>
       <x:c r="U275" s="4" t="str">
-        <x:v>Figure P10-5：飞轮五层结构代码映射图</x:v>
+        <x:v>Figure P10-2：上游项目 registry 与接口映射图</x:v>
       </x:c>
       <x:c r="V275" s="4" t="str">
-        <x:v>图 P10-5</x:v>
+        <x:v>图 P10-2</x:v>
       </x:c>
     </x:row>
     <x:row r="276">
@@ -18169,29 +18175,29 @@
         <x:v>docs/en/part14/p10_flywheel.md</x:v>
       </x:c>
       <x:c r="G276" s="4" t="n">
-        <x:v>593</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="H276" s="4" t="str">
-        <x:v>P10-6</x:v>
+        <x:v>P10-3</x:v>
       </x:c>
       <x:c r="I276" s="4" t="str"/>
       <x:c r="J276" s="4" t="str">
-        <x:v>Figure 6: System boundaries and control points</x:v>
+        <x:v>Figure 3: Structured upstream project specs</x:v>
       </x:c>
       <x:c r="K276" s="4" t="str">
-        <x:v>docs/images/part14/p10/p10_06_boundaries_and_control_points.svg</x:v>
+        <x:v>docs/images/part14/p10/p10_03_project_specs.svg</x:v>
       </x:c>
       <x:c r="L276" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M276" s="4" t="str">
-        <x:v>1586x992</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N276" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O276" s="4" t="str">
-        <x:v>Figure 6: System boundaries and control points.</x:v>
+        <x:v>Figure 3: Structured upstream project specs.</x:v>
       </x:c>
       <x:c r="P276" s="4" t="str"/>
       <x:c r="Q276" s="4" t="str">
@@ -18203,10 +18209,10 @@
       <x:c r="S276" s="4" t="str"/>
       <x:c r="T276" s="4" t="str"/>
       <x:c r="U276" s="4" t="str">
-        <x:v>Figure P10-6：系统边界与控制点示意图</x:v>
+        <x:v>Figure P10-3：上游项目结构化配置示意图</x:v>
       </x:c>
       <x:c r="V276" s="4" t="str">
-        <x:v>图 P10-6</x:v>
+        <x:v>图 P10-3</x:v>
       </x:c>
     </x:row>
     <x:row r="277">
@@ -18229,29 +18235,29 @@
         <x:v>docs/en/part14/p10_flywheel.md</x:v>
       </x:c>
       <x:c r="G277" s="4" t="n">
-        <x:v>624</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="H277" s="4" t="str">
-        <x:v>P10-7</x:v>
+        <x:v>P10-4</x:v>
       </x:c>
       <x:c r="I277" s="4" t="str"/>
       <x:c r="J277" s="4" t="str">
-        <x:v>Figure 7: Run records and milestone board</x:v>
+        <x:v>Figure 4: Five-stage plan and milestone relationships</x:v>
       </x:c>
       <x:c r="K277" s="4" t="str">
-        <x:v>docs/images/part14/p10/p10_07_runs_and_milestones.svg</x:v>
+        <x:v>docs/images/part14/p10/p10_04_stage_plan.svg</x:v>
       </x:c>
       <x:c r="L277" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M277" s="4" t="str">
-        <x:v>1672x941</x:v>
+        <x:v>1672x642</x:v>
       </x:c>
       <x:c r="N277" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O277" s="4" t="str">
-        <x:v>Figure 7: Run records and milestone board.</x:v>
+        <x:v>Figure 4: Five-stage plan and milestone relationships.</x:v>
       </x:c>
       <x:c r="P277" s="4" t="str"/>
       <x:c r="Q277" s="4" t="str">
@@ -18263,10 +18269,10 @@
       <x:c r="S277" s="4" t="str"/>
       <x:c r="T277" s="4" t="str"/>
       <x:c r="U277" s="4" t="str">
-        <x:v>Figure P10-7：运行记录与里程碑板示意图</x:v>
+        <x:v>Figure P10-4：五阶段推进与里程碑关系图</x:v>
       </x:c>
       <x:c r="V277" s="4" t="str">
-        <x:v>图 P10-7</x:v>
+        <x:v>图 P10-4</x:v>
       </x:c>
     </x:row>
     <x:row r="278">
@@ -18289,29 +18295,29 @@
         <x:v>docs/en/part14/p10_flywheel.md</x:v>
       </x:c>
       <x:c r="G278" s="4" t="n">
-        <x:v>722</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="H278" s="4" t="str">
-        <x:v>P10-8</x:v>
+        <x:v>P10-5</x:v>
       </x:c>
       <x:c r="I278" s="4" t="str"/>
       <x:c r="J278" s="4" t="str">
-        <x:v>Figure 8: Flywheel bottleneck map</x:v>
+        <x:v>Figure 5: Five-layer flywheel code mapping</x:v>
       </x:c>
       <x:c r="K278" s="4" t="str">
-        <x:v>docs/images/part14/p10/p10_08_bottleneck_map.svg</x:v>
+        <x:v>docs/images/part14/p10/p10_05_architecture_code_mapping.svg</x:v>
       </x:c>
       <x:c r="L278" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M278" s="4" t="str">
-        <x:v>1536x1024</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N278" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O278" s="4" t="str">
-        <x:v>Figure 8: Flywheel bottleneck map.</x:v>
+        <x:v>Figure 5: Five-layer flywheel code mapping.</x:v>
       </x:c>
       <x:c r="P278" s="4" t="str"/>
       <x:c r="Q278" s="4" t="str">
@@ -18323,10 +18329,10 @@
       <x:c r="S278" s="4" t="str"/>
       <x:c r="T278" s="4" t="str"/>
       <x:c r="U278" s="4" t="str">
-        <x:v>Figure P10-8：飞轮瓶颈定位图</x:v>
+        <x:v>Figure P10-5：飞轮五层结构代码映射图</x:v>
       </x:c>
       <x:c r="V278" s="4" t="str">
-        <x:v>图 P10-8</x:v>
+        <x:v>图 P10-5</x:v>
       </x:c>
     </x:row>
     <x:row r="279">
@@ -18349,29 +18355,29 @@
         <x:v>docs/en/part14/p10_flywheel.md</x:v>
       </x:c>
       <x:c r="G279" s="4" t="n">
-        <x:v>799</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="H279" s="4" t="str">
-        <x:v>P10-9</x:v>
+        <x:v>P10-6</x:v>
       </x:c>
       <x:c r="I279" s="4" t="str"/>
       <x:c r="J279" s="4" t="str">
-        <x:v>Figure 9: System-level metric generation logic</x:v>
+        <x:v>Figure 6: System boundaries and control points</x:v>
       </x:c>
       <x:c r="K279" s="4" t="str">
-        <x:v>docs/images/part14/p10/p10_09_metrics_codegen.svg</x:v>
+        <x:v>docs/images/part14/p10/p10_06_boundaries_and_control_points.svg</x:v>
       </x:c>
       <x:c r="L279" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M279" s="4" t="str">
-        <x:v>1672x941</x:v>
+        <x:v>1586x992</x:v>
       </x:c>
       <x:c r="N279" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O279" s="4" t="str">
-        <x:v>Figure 9: System-level metric generation logic.</x:v>
+        <x:v>Figure 6: System boundaries and control points.</x:v>
       </x:c>
       <x:c r="P279" s="4" t="str"/>
       <x:c r="Q279" s="4" t="str">
@@ -18383,10 +18389,10 @@
       <x:c r="S279" s="4" t="str"/>
       <x:c r="T279" s="4" t="str"/>
       <x:c r="U279" s="4" t="str">
-        <x:v>Figure P10-9：系统级指标生成逻辑图</x:v>
+        <x:v>Figure P10-6：系统边界与控制点示意图</x:v>
       </x:c>
       <x:c r="V279" s="4" t="str">
-        <x:v>图 P10-9</x:v>
+        <x:v>图 P10-6</x:v>
       </x:c>
     </x:row>
     <x:row r="280">
@@ -18409,17 +18415,17 @@
         <x:v>docs/en/part14/p10_flywheel.md</x:v>
       </x:c>
       <x:c r="G280" s="4" t="n">
-        <x:v>885</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="H280" s="4" t="str">
-        <x:v>P10-10</x:v>
+        <x:v>P10-7</x:v>
       </x:c>
       <x:c r="I280" s="4" t="str"/>
       <x:c r="J280" s="4" t="str">
-        <x:v>Figure 10: Check scripts and system contracts</x:v>
+        <x:v>Figure 7: Run records and milestone board</x:v>
       </x:c>
       <x:c r="K280" s="4" t="str">
-        <x:v>docs/images/part14/p10/p10_10_check_contracts.svg</x:v>
+        <x:v>docs/images/part14/p10/p10_07_runs_and_milestones.svg</x:v>
       </x:c>
       <x:c r="L280" s="4" t="str">
         <x:v>yes</x:v>
@@ -18431,7 +18437,7 @@
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O280" s="4" t="str">
-        <x:v>Figure 10: Check scripts and system contracts.</x:v>
+        <x:v>Figure 7: Run records and milestone board.</x:v>
       </x:c>
       <x:c r="P280" s="4" t="str"/>
       <x:c r="Q280" s="4" t="str">
@@ -18443,10 +18449,10 @@
       <x:c r="S280" s="4" t="str"/>
       <x:c r="T280" s="4" t="str"/>
       <x:c r="U280" s="4" t="str">
-        <x:v>Figure P10-10：检查脚本与系统契约图</x:v>
+        <x:v>Figure P10-7：运行记录与里程碑板示意图</x:v>
       </x:c>
       <x:c r="V280" s="4" t="str">
-        <x:v>图 P10-10</x:v>
+        <x:v>图 P10-7</x:v>
       </x:c>
     </x:row>
     <x:row r="281">
@@ -18460,44 +18466,40 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D281" s="4" t="str">
-        <x:v>P11</x:v>
+        <x:v>P10</x:v>
       </x:c>
       <x:c r="E281" s="4" t="str">
-        <x:v>Project 11: Reproducing Mini-DeepSeek Pre-training</x:v>
+        <x:v>Project 10: End-to-End LLM Data Flywheel</x:v>
       </x:c>
       <x:c r="F281" s="4" t="str">
-        <x:v>docs/en/part14/p11_mini_deepseek.md</x:v>
+        <x:v>docs/en/part14/p10_flywheel.md</x:v>
       </x:c>
       <x:c r="G281" s="4" t="n">
-        <x:v>79</x:v>
+        <x:v>722</x:v>
       </x:c>
       <x:c r="H281" s="4" t="str">
-        <x:v>P11-1</x:v>
-      </x:c>
-      <x:c r="I281" s="4" t="str">
-        <x:v>Figure P11-1: Mini-DeepSeek Multi-Source Pre-Training Data Pipeline Architecture</x:v>
-      </x:c>
+        <x:v>P10-8</x:v>
+      </x:c>
+      <x:c r="I281" s="4" t="str"/>
       <x:c r="J281" s="4" t="str">
-        <x:v>Mini-DeepSeek Data Pipeline</x:v>
+        <x:v>Figure 8: Flywheel bottleneck map</x:v>
       </x:c>
       <x:c r="K281" s="4" t="str">
-        <x:v>docs/images/part14/p11_mini_deepseek_arch_en.svg</x:v>
+        <x:v>docs/images/part14/p10/p10_08_bottleneck_map.svg</x:v>
       </x:c>
       <x:c r="L281" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M281" s="4" t="str">
-        <x:v>950x500</x:v>
+        <x:v>1536x1024</x:v>
       </x:c>
       <x:c r="N281" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O281" s="4" t="str">
-        <x:v>Mini-DeepSeek Multi-Source Pre-Training Data Pipeline Architecture.</x:v>
-      </x:c>
-      <x:c r="P281" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Project 11: Reproducing Mini-DeepSeek Pre-training; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>Figure 8: Flywheel bottleneck map.</x:v>
+      </x:c>
+      <x:c r="P281" s="4" t="str"/>
       <x:c r="Q281" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -18507,10 +18509,10 @@
       <x:c r="S281" s="4" t="str"/>
       <x:c r="T281" s="4" t="str"/>
       <x:c r="U281" s="4" t="str">
-        <x:v>Figure P11-1：Mini-DeepSeek 多源预训练数据流水线架构</x:v>
+        <x:v>Figure P10-8：飞轮瓶颈定位图</x:v>
       </x:c>
       <x:c r="V281" s="4" t="str">
-        <x:v>Mini-DeepSeek Data Pipeline</x:v>
+        <x:v>图 P10-8</x:v>
       </x:c>
     </x:row>
     <x:row r="282">
@@ -18524,40 +18526,38 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D282" s="4" t="str">
-        <x:v>P12</x:v>
+        <x:v>P10</x:v>
       </x:c>
       <x:c r="E282" s="4" t="str">
-        <x:v>Project 12: R1 Reasoning Flywheel</x:v>
+        <x:v>Project 10: End-to-End LLM Data Flywheel</x:v>
       </x:c>
       <x:c r="F282" s="4" t="str">
-        <x:v>docs/en/part14/p12_r1_reasoning_flywheel.md</x:v>
+        <x:v>docs/en/part14/p10_flywheel.md</x:v>
       </x:c>
       <x:c r="G282" s="4" t="n">
-        <x:v>97</x:v>
+        <x:v>799</x:v>
       </x:c>
       <x:c r="H282" s="4" t="str">
-        <x:v>P12-1</x:v>
-      </x:c>
-      <x:c r="I282" s="4" t="str">
-        <x:v>Figure P12-1: The closed-loop structure from cold-start data extraction, multi-path reasoning sampling, verifier pool, and rejection sampling to second-round SFT merging and training evaluation</x:v>
-      </x:c>
+        <x:v>P10-9</x:v>
+      </x:c>
+      <x:c r="I282" s="4" t="str"/>
       <x:c r="J282" s="4" t="str">
-        <x:v>Figure P12-1</x:v>
+        <x:v>Figure 9: System-level metric generation logic</x:v>
       </x:c>
       <x:c r="K282" s="4" t="str">
-        <x:v>docs/images/part14/p12/p12_r1_reasoning_flywheel_architecture.svg</x:v>
+        <x:v>docs/images/part14/p10/p10_09_metrics_codegen.svg</x:v>
       </x:c>
       <x:c r="L282" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M282" s="4" t="str">
-        <x:v>1774x887</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N282" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O282" s="4" t="str">
-        <x:v>The closed-loop structure from cold-start data extraction, multi-path reasoning sampling, verifier pool, and rejection sampling to second-round SFT merging and training evaluation.</x:v>
+        <x:v>Figure 9: System-level metric generation logic.</x:v>
       </x:c>
       <x:c r="P282" s="4" t="str"/>
       <x:c r="Q282" s="4" t="str">
@@ -18569,10 +18569,10 @@
       <x:c r="S282" s="4" t="str"/>
       <x:c r="T282" s="4" t="str"/>
       <x:c r="U282" s="4" t="str">
-        <x:v>Figure P12-1：从冷启动数据抽取、多路推理采样、verifier 池、拒绝采样到二轮 SFT 合并与训练评估的闭环结构</x:v>
+        <x:v>Figure P10-9：系统级指标生成逻辑图</x:v>
       </x:c>
       <x:c r="V282" s="4" t="str">
-        <x:v>图 P12-1</x:v>
+        <x:v>图 P10-9</x:v>
       </x:c>
     </x:row>
     <x:row r="283">
@@ -18586,44 +18586,40 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D283" s="4" t="str">
-        <x:v>P13</x:v>
+        <x:v>P10</x:v>
       </x:c>
       <x:c r="E283" s="4" t="str">
-        <x:v>Project 13: Multimodal Instruction Factory</x:v>
+        <x:v>Project 10: End-to-End LLM Data Flywheel</x:v>
       </x:c>
       <x:c r="F283" s="4" t="str">
-        <x:v>docs/en/part14/p13_multimodal_instruction_factory.md</x:v>
+        <x:v>docs/en/part14/p10_flywheel.md</x:v>
       </x:c>
       <x:c r="G283" s="4" t="n">
-        <x:v>84</x:v>
+        <x:v>885</x:v>
       </x:c>
       <x:c r="H283" s="4" t="str">
-        <x:v>13-1</x:v>
-      </x:c>
-      <x:c r="I283" s="4" t="str">
-        <x:v>Figure 13-1 Qwen-VL-style multimodal instruction synthesis pipeline</x:v>
-      </x:c>
+        <x:v>P10-10</x:v>
+      </x:c>
+      <x:c r="I283" s="4" t="str"/>
       <x:c r="J283" s="4" t="str">
-        <x:v>Multimodal Instruction Factory</x:v>
+        <x:v>Figure 10: Check scripts and system contracts</x:v>
       </x:c>
       <x:c r="K283" s="4" t="str">
-        <x:v>docs/images/part14/p13_mm_instruction_factory_arch_en.svg</x:v>
+        <x:v>docs/images/part14/p10/p10_10_check_contracts.svg</x:v>
       </x:c>
       <x:c r="L283" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M283" s="4" t="str">
-        <x:v>1000x730</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N283" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O283" s="4" t="str">
-        <x:v>Qwen-VL-style multimodal instruction synthesis pipeline.</x:v>
-      </x:c>
-      <x:c r="P283" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Project 13: Multimodal Instruction Factory; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>Figure 10: Check scripts and system contracts.</x:v>
+      </x:c>
+      <x:c r="P283" s="4" t="str"/>
       <x:c r="Q283" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -18633,10 +18629,10 @@
       <x:c r="S283" s="4" t="str"/>
       <x:c r="T283" s="4" t="str"/>
       <x:c r="U283" s="4" t="str">
-        <x:v>Figure P13-1：Qwen-VL 风格多模态指令合成流水线架构</x:v>
+        <x:v>Figure P10-10：检查脚本与系统契约图</x:v>
       </x:c>
       <x:c r="V283" s="4" t="str">
-        <x:v>Multimodal Instruction Factory</x:v>
+        <x:v>图 P10-10</x:v>
       </x:c>
     </x:row>
     <x:row r="284">
@@ -18650,43 +18646,43 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D284" s="4" t="str">
-        <x:v>P14</x:v>
+        <x:v>P11</x:v>
       </x:c>
       <x:c r="E284" s="4" t="str">
-        <x:v>Project 14: Video Generation Dataset: From Video Source to T2V-ready Data Pipeline</x:v>
+        <x:v>Project 11: Reproducing Mini-DeepSeek Pre-training</x:v>
       </x:c>
       <x:c r="F284" s="4" t="str">
-        <x:v>docs/en/part14/p14_video_generation.md</x:v>
+        <x:v>docs/en/part14/p11_mini_deepseek.md</x:v>
       </x:c>
       <x:c r="G284" s="4" t="n">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H284" s="4" t="str">
-        <x:v>P14-1</x:v>
+        <x:v>P11-1</x:v>
       </x:c>
       <x:c r="I284" s="4" t="str">
-        <x:v>Figure P14-1: English architecture diagram of the video generation data pipeline</x:v>
+        <x:v>Figure P11-1: Mini-DeepSeek Multi-Source Pre-Training Data Pipeline Architecture</x:v>
       </x:c>
       <x:c r="J284" s="4" t="str">
-        <x:v>P14 Video Generation Data Pipeline</x:v>
+        <x:v>Mini-DeepSeek Data Pipeline</x:v>
       </x:c>
       <x:c r="K284" s="4" t="str">
-        <x:v>docs/images/part14/p14_video_generation_pipeline_en.svg</x:v>
+        <x:v>docs/images/part14/p11_mini_deepseek_arch_en.svg</x:v>
       </x:c>
       <x:c r="L284" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M284" s="4" t="str">
-        <x:v>4401x1816</x:v>
+        <x:v>950x500</x:v>
       </x:c>
       <x:c r="N284" s="4" t="str">
         <x:v>svg</x:v>
       </x:c>
       <x:c r="O284" s="4" t="str">
-        <x:v>English architecture diagram of the video generation data pipeline.</x:v>
+        <x:v>Mini-DeepSeek Multi-Source Pre-Training Data Pipeline Architecture.</x:v>
       </x:c>
       <x:c r="P284" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Project 14: Video Generation Dataset: From Video Source to T2V-ready Data Pipeline; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+        <x:v>Review against the figure and surrounding text in Project 11: Reproducing Mini-DeepSeek Pre-training; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
       </x:c>
       <x:c r="Q284" s="4" t="str">
         <x:v>no</x:v>
@@ -18697,10 +18693,10 @@
       <x:c r="S284" s="4" t="str"/>
       <x:c r="T284" s="4" t="str"/>
       <x:c r="U284" s="4" t="str">
-        <x:v>Figure P14-1：视频生成数据流水线英文架构图</x:v>
+        <x:v>Figure P11-1：Mini-DeepSeek 多源预训练数据流水线架构</x:v>
       </x:c>
       <x:c r="V284" s="4" t="str">
-        <x:v>P14 Video Generation Data Pipeline</x:v>
+        <x:v>Mini-DeepSeek Data Pipeline</x:v>
       </x:c>
     </x:row>
     <x:row r="285">
@@ -18714,40 +18710,40 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D285" s="4" t="str">
-        <x:v>P14</x:v>
+        <x:v>P12</x:v>
       </x:c>
       <x:c r="E285" s="4" t="str">
-        <x:v>Project 14: Video Generation Dataset: From Video Source to T2V-ready Data Pipeline</x:v>
+        <x:v>Project 12: R1 Reasoning Flywheel</x:v>
       </x:c>
       <x:c r="F285" s="4" t="str">
-        <x:v>docs/en/part14/p14_video_generation.md</x:v>
+        <x:v>docs/en/part14/p12_r1_reasoning_flywheel.md</x:v>
       </x:c>
       <x:c r="G285" s="4" t="n">
-        <x:v>524</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H285" s="4" t="str">
-        <x:v>P14-2</x:v>
+        <x:v>P12-1</x:v>
       </x:c>
       <x:c r="I285" s="4" t="str">
-        <x:v>Table P14-12: Example of multi-frame sampling from a video clip The figure shows two sampled frames from the output data. The clip presents a coastal scene filmed from a high-altitude aerial perspective: deep blue water continuously crashes against rugged reef formations, white foam forms clearly at the edges of the dark rock faces, and sparse green vegetation distributed among the rocks preserves a degree of visual layering within the natural environment. The multi-frame caption covers the clip's subjects, scene, lighting, and atmosphere, describing natural illumination, cool-toned ocean surface, clear rock textures, and the dynamic quality imparted by wave motion. From the cinematic language annotation results, this shot is identified as extremewide shot size, highangle camera angle, ruleofthirds composition, natural lighting type, cool overall color tone, and cinematic style tag. The camera motion module classifies it as zoomin, indicating a noticeable push-in or scale change in the frame; motionstrength=0.8974 indicates that the clip carries a stable motion signal and is suitable for T2V training to learn natural scene motion, aerial perspectives, and coastal cinematic language</x:v>
+        <x:v>Figure P12-1: The closed-loop structure from cold-start data extraction, multi-path reasoning sampling, verifier pool, and rejection sampling to second-round SFT merging and training evaluation</x:v>
       </x:c>
       <x:c r="J285" s="4" t="str">
-        <x:v>frame1</x:v>
+        <x:v>Figure P12-1</x:v>
       </x:c>
       <x:c r="K285" s="4" t="str">
-        <x:v>docs/images/part14/p14_video_frame_0.jpg</x:v>
+        <x:v>docs/images/part14/p12/p12_r1_reasoning_flywheel_architecture.svg</x:v>
       </x:c>
       <x:c r="L285" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M285" s="4" t="str">
-        <x:v>448x252</x:v>
+        <x:v>1774x887</x:v>
       </x:c>
       <x:c r="N285" s="4" t="str">
-        <x:v>jpg</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O285" s="4" t="str">
-        <x:v>Table P14-12: Example of multi-frame sampling from a video clip The figure shows two sampled frames from the output data. The clip presents a coastal scene filmed from a high-altitude aerial perspective: deep blue water continuously crashes against rugged reef formations, white foam forms clearly at the edges of the dark rock faces, and sparse green vegetation distributed among the rocks preserves a degree of visual layering within the natural environment. The multi-frame...</x:v>
+        <x:v>The closed-loop structure from cold-start data extraction, multi-path reasoning sampling, verifier pool, and rejection sampling to second-round SFT merging and training evaluation.</x:v>
       </x:c>
       <x:c r="P285" s="4" t="str"/>
       <x:c r="Q285" s="4" t="str">
@@ -18759,10 +18755,10 @@
       <x:c r="S285" s="4" t="str"/>
       <x:c r="T285" s="4" t="str"/>
       <x:c r="U285" s="4" t="str">
-        <x:v>表 P14-12：视频片段多帧抽样示例 图中展示了产出数据中的两帧采样结果。该片段展示了一段从高空视角拍摄的海岸线画面：深蓝色海水不断冲击崎岖礁石，浪花在暗色岩壁边缘形成明显的白色泡沫，岩石间分布着少量绿色植被，使画面在自然环境中保留了一定层次感。多帧 caption 覆盖该片段的主体、场景、光照和氛围，描述自然光照、冷色调海面、清晰岩石纹理，以及海浪运动带来的动态感。从镜头语言标注结果看，该 shot 被识别为 extremewide 景别、highangle 高角度视角，构图方式为 ruleofthirds，光照类型为 natural，整体色彩倾向为 cool，风格标签为 cinematic。相机运动模块将其判定为 zoomin，说明画面存在较明显的推进或尺度变化；motionstrength=0.8974 表明该片段具有稳定运动信号，可用于 T2V 训练中学习自然场景运动、航拍视角和海岸镜头语言</x:v>
+        <x:v>Figure P12-1：从冷启动数据抽取、多路推理采样、verifier 池、拒绝采样到二轮 SFT 合并与训练评估的闭环结构</x:v>
       </x:c>
       <x:c r="V285" s="4" t="str">
-        <x:v>frame1</x:v>
+        <x:v>图 P12-1</x:v>
       </x:c>
     </x:row>
     <x:row r="286">
@@ -18776,42 +18772,44 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D286" s="4" t="str">
-        <x:v>P14</x:v>
+        <x:v>P13</x:v>
       </x:c>
       <x:c r="E286" s="4" t="str">
-        <x:v>Project 14: Video Generation Dataset: From Video Source to T2V-ready Data Pipeline</x:v>
+        <x:v>Project 13: Multimodal Instruction Factory</x:v>
       </x:c>
       <x:c r="F286" s="4" t="str">
-        <x:v>docs/en/part14/p14_video_generation.md</x:v>
+        <x:v>docs/en/part14/p13_multimodal_instruction_factory.md</x:v>
       </x:c>
       <x:c r="G286" s="4" t="n">
-        <x:v>524</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H286" s="4" t="str">
-        <x:v>P14-3</x:v>
+        <x:v>13-1</x:v>
       </x:c>
       <x:c r="I286" s="4" t="str">
-        <x:v>Table P14-12: Example of multi-frame sampling from a video clip The figure shows two sampled frames from the output data. The clip presents a coastal scene filmed from a high-altitude aerial perspective: deep blue water continuously crashes against rugged reef formations, white foam forms clearly at the edges of the dark rock faces, and sparse green vegetation distributed among the rocks preserves a degree of visual layering within the natural environment. The multi-frame caption covers the clip's subjects, scene, lighting, and atmosphere, describing natural illumination, cool-toned ocean surface, clear rock textures, and the dynamic quality imparted by wave motion. From the cinematic language annotation results, this shot is identified as extremewide shot size, highangle camera angle, ruleofthirds composition, natural lighting type, cool overall color tone, and cinematic style tag. The camera motion module classifies it as zoomin, indicating a noticeable push-in or scale change in the frame; motionstrength=0.8974 indicates that the clip carries a stable motion signal and is suitable for T2V training to learn natural scene motion, aerial perspectives, and coastal cinematic language</x:v>
+        <x:v>Figure 13-1 Qwen-VL-style multimodal instruction synthesis pipeline</x:v>
       </x:c>
       <x:c r="J286" s="4" t="str">
-        <x:v>frame2</x:v>
+        <x:v>Multimodal Instruction Factory</x:v>
       </x:c>
       <x:c r="K286" s="4" t="str">
-        <x:v>docs/images/part14/p14_video_frame_1.jpg</x:v>
+        <x:v>docs/images/part14/p13_mm_instruction_factory_arch_en.svg</x:v>
       </x:c>
       <x:c r="L286" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M286" s="4" t="str">
-        <x:v>448x252</x:v>
+        <x:v>1000x730</x:v>
       </x:c>
       <x:c r="N286" s="4" t="str">
-        <x:v>jpg</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O286" s="4" t="str">
-        <x:v>Table P14-12: Example of multi-frame sampling from a video clip The figure shows two sampled frames from the output data. The clip presents a coastal scene filmed from a high-altitude aerial perspective: deep blue water continuously crashes against rugged reef formations, white foam forms clearly at the edges of the dark rock faces, and sparse green vegetation distributed among the rocks preserves a degree of visual layering within the natural environment. The multi-frame...</x:v>
-      </x:c>
-      <x:c r="P286" s="4" t="str"/>
+        <x:v>Qwen-VL-style multimodal instruction synthesis pipeline.</x:v>
+      </x:c>
+      <x:c r="P286" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Project 13: Multimodal Instruction Factory; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q286" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -18820,8 +18818,12 @@
       </x:c>
       <x:c r="S286" s="4" t="str"/>
       <x:c r="T286" s="4" t="str"/>
-      <x:c r="U286" s="4" t="str"/>
-      <x:c r="V286" s="4" t="str"/>
+      <x:c r="U286" s="4" t="str">
+        <x:v>Figure P13-1：Qwen-VL 风格多模态指令合成流水线架构</x:v>
+      </x:c>
+      <x:c r="V286" s="4" t="str">
+        <x:v>Multimodal Instruction Factory</x:v>
+      </x:c>
     </x:row>
     <x:row r="287">
       <x:c r="A287" s="4" t="str">
@@ -18834,42 +18836,44 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D287" s="4" t="str">
-        <x:v>P15</x:v>
+        <x:v>P14</x:v>
       </x:c>
       <x:c r="E287" s="4" t="str">
-        <x:v>Project 15: Building an Enterprise Semantic BI Assistant with DataAgent</x:v>
+        <x:v>Project 14: Video Generation Dataset: From Video Source to T2V-ready Data Pipeline</x:v>
       </x:c>
       <x:c r="F287" s="4" t="str">
-        <x:v>docs/en/part14/p15_dataagent_semantic_nl2sql_agent.md</x:v>
+        <x:v>docs/en/part14/p14_video_generation.md</x:v>
       </x:c>
       <x:c r="G287" s="4" t="n">
-        <x:v>11</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H287" s="4" t="str">
-        <x:v>P15-1</x:v>
+        <x:v>P14-1</x:v>
       </x:c>
       <x:c r="I287" s="4" t="str">
-        <x:v>Figure P15-1: Engineering chain of the DataAgent semantic BI assistant</x:v>
+        <x:v>Figure P14-1: English architecture diagram of the video generation data pipeline</x:v>
       </x:c>
       <x:c r="J287" s="4" t="str">
-        <x:v>DataAgent semantic BI assistant engineering chain</x:v>
+        <x:v>P14 Video Generation Data Pipeline</x:v>
       </x:c>
       <x:c r="K287" s="4" t="str">
-        <x:v>docs/images/part14/p15_dataagent_engineering_chain_en.png</x:v>
+        <x:v>docs/images/part14/p14_video_generation_pipeline_en.svg</x:v>
       </x:c>
       <x:c r="L287" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M287" s="4" t="str">
-        <x:v>1536x1024</x:v>
+        <x:v>4401x1816</x:v>
       </x:c>
       <x:c r="N287" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O287" s="4" t="str">
-        <x:v>Engineering chain of the DataAgent semantic BI assistant.</x:v>
-      </x:c>
-      <x:c r="P287" s="4" t="str"/>
+        <x:v>English architecture diagram of the video generation data pipeline.</x:v>
+      </x:c>
+      <x:c r="P287" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Project 14: Video Generation Dataset: From Video Source to T2V-ready Data Pipeline; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
       <x:c r="Q287" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -18879,10 +18883,10 @@
       <x:c r="S287" s="4" t="str"/>
       <x:c r="T287" s="4" t="str"/>
       <x:c r="U287" s="4" t="str">
-        <x:v>Figure P15-1：DataAgent 语义问数助手工程链路</x:v>
+        <x:v>Figure P14-1：视频生成数据流水线英文架构图</x:v>
       </x:c>
       <x:c r="V287" s="4" t="str">
-        <x:v>DataAgent 语义问数助手工程链路</x:v>
+        <x:v>P14 Video Generation Data Pipeline</x:v>
       </x:c>
     </x:row>
     <x:row r="288">
@@ -18896,44 +18900,42 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D288" s="4" t="str">
-        <x:v>P15</x:v>
+        <x:v>P14</x:v>
       </x:c>
       <x:c r="E288" s="4" t="str">
-        <x:v>Project 15: Building an Enterprise Semantic BI Assistant with DataAgent</x:v>
+        <x:v>Project 14: Video Generation Dataset: From Video Source to T2V-ready Data Pipeline</x:v>
       </x:c>
       <x:c r="F288" s="4" t="str">
-        <x:v>docs/en/part14/p15_dataagent_semantic_nl2sql_agent.md</x:v>
+        <x:v>docs/en/part14/p14_video_generation.md</x:v>
       </x:c>
       <x:c r="G288" s="4" t="n">
-        <x:v>143</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="H288" s="4" t="str">
-        <x:v>P15-2</x:v>
+        <x:v>P14-2</x:v>
       </x:c>
       <x:c r="I288" s="4" t="str">
-        <x:v>Figure P15-2: DataGallery ecosystem architecture around DataAgent</x:v>
+        <x:v>Table P14-12: Example of multi-frame sampling from a video clip The figure shows two sampled frames from the output data. The clip presents a coastal scene filmed from a high-altitude aerial perspective: deep blue water continuously crashes against rugged reef formations, white foam forms clearly at the edges of the dark rock faces, and sparse green vegetation distributed among the rocks preserves a degree of visual layering within the natural environment. The multi-frame caption covers the clip's subjects, scene, lighting, and atmosphere, describing natural illumination, cool-toned ocean surface, clear rock textures, and the dynamic quality imparted by wave motion. From the cinematic language annotation results, this shot is identified as extremewide shot size, highangle camera angle, ruleofthirds composition, natural lighting type, cool overall color tone, and cinematic style tag. The camera motion module classifies it as zoomin, indicating a noticeable push-in or scale change in the frame; motionstrength=0.8974 indicates that the clip carries a stable motion signal and is suitable for T2V training to learn natural scene motion, aerial perspectives, and coastal cinematic language</x:v>
       </x:c>
       <x:c r="J288" s="4" t="str">
-        <x:v>DataGallery ecosystem architecture around DataAgent, Semantic Service, Data Studio, Data Ops, and foundation infrastructure</x:v>
+        <x:v>frame1</x:v>
       </x:c>
       <x:c r="K288" s="4" t="str">
-        <x:v>docs/images/part14/p15_datagallery_architecture_vector.svg</x:v>
+        <x:v>docs/images/part14/p14_video_frame_0.jpg</x:v>
       </x:c>
       <x:c r="L288" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M288" s="4" t="str">
-        <x:v>1536x1024</x:v>
+        <x:v>448x252</x:v>
       </x:c>
       <x:c r="N288" s="4" t="str">
-        <x:v>svg</x:v>
+        <x:v>jpg</x:v>
       </x:c>
       <x:c r="O288" s="4" t="str">
-        <x:v>DataGallery ecosystem architecture around DataAgent.</x:v>
-      </x:c>
-      <x:c r="P288" s="4" t="str">
-        <x:v>Review against the figure and surrounding text in Project 15: Building an Enterprise Semantic BI Assistant with DataAgent; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
-      </x:c>
+        <x:v>Table P14-12: Example of multi-frame sampling from a video clip The figure shows two sampled frames from the output data. The clip presents a coastal scene filmed from a high-altitude aerial perspective: deep blue water continuously crashes against rugged reef formations, white foam forms clearly at the edges of the dark rock faces, and sparse green vegetation distributed among the rocks preserves a degree of visual layering within the natural environment. The multi-frame...</x:v>
+      </x:c>
+      <x:c r="P288" s="4" t="str"/>
       <x:c r="Q288" s="4" t="str">
         <x:v>no</x:v>
       </x:c>
@@ -18943,10 +18945,10 @@
       <x:c r="S288" s="4" t="str"/>
       <x:c r="T288" s="4" t="str"/>
       <x:c r="U288" s="4" t="str">
-        <x:v>Figure P15-2：围绕 DataAgent 展开的 DataGallery 生态架构</x:v>
+        <x:v>表 P14-12：视频片段多帧抽样示例 图中展示了产出数据中的两帧采样结果。该片段展示了一段从高空视角拍摄的海岸线画面：深蓝色海水不断冲击崎岖礁石，浪花在暗色岩壁边缘形成明显的白色泡沫，岩石间分布着少量绿色植被，使画面在自然环境中保留了一定层次感。多帧 caption 覆盖该片段的主体、场景、光照和氛围，描述自然光照、冷色调海面、清晰岩石纹理，以及海浪运动带来的动态感。从镜头语言标注结果看，该 shot 被识别为 extremewide 景别、highangle 高角度视角，构图方式为 ruleofthirds，光照类型为 natural，整体色彩倾向为 cool，风格标签为 cinematic。相机运动模块将其判定为 zoomin，说明画面存在较明显的推进或尺度变化；motionstrength=0.8974 表明该片段具有稳定运动信号，可用于 T2V 训练中学习自然场景运动、航拍视角和海岸镜头语言</x:v>
       </x:c>
       <x:c r="V288" s="4" t="str">
-        <x:v>围绕 DataAgent、Semantic Service、Data Studio、Data Ops 与基础设施展开的 DataGallery 生态架构</x:v>
+        <x:v>frame1</x:v>
       </x:c>
     </x:row>
     <x:row r="289">
@@ -18960,40 +18962,40 @@
         <x:v>Part 14: Practical Projects</x:v>
       </x:c>
       <x:c r="D289" s="4" t="str">
-        <x:v>P15</x:v>
+        <x:v>P14</x:v>
       </x:c>
       <x:c r="E289" s="4" t="str">
-        <x:v>Project 15: Building an Enterprise Semantic BI Assistant with DataAgent</x:v>
+        <x:v>Project 14: Video Generation Dataset: From Video Source to T2V-ready Data Pipeline</x:v>
       </x:c>
       <x:c r="F289" s="4" t="str">
-        <x:v>docs/en/part14/p15_dataagent_semantic_nl2sql_agent.md</x:v>
+        <x:v>docs/en/part14/p14_video_generation.md</x:v>
       </x:c>
       <x:c r="G289" s="4" t="n">
-        <x:v>579</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="H289" s="4" t="str">
-        <x:v>P15-3</x:v>
+        <x:v>P14-3</x:v>
       </x:c>
       <x:c r="I289" s="4" t="str">
-        <x:v>Figure P15-3: Runtime flow of the DataAgent enterprise semantic BI assistant</x:v>
+        <x:v>Table P14-12: Example of multi-frame sampling from a video clip The figure shows two sampled frames from the output data. The clip presents a coastal scene filmed from a high-altitude aerial perspective: deep blue water continuously crashes against rugged reef formations, white foam forms clearly at the edges of the dark rock faces, and sparse green vegetation distributed among the rocks preserves a degree of visual layering within the natural environment. The multi-frame caption covers the clip's subjects, scene, lighting, and atmosphere, describing natural illumination, cool-toned ocean surface, clear rock textures, and the dynamic quality imparted by wave motion. From the cinematic language annotation results, this shot is identified as extremewide shot size, highangle camera angle, ruleofthirds composition, natural lighting type, cool overall color tone, and cinematic style tag. The camera motion module classifies it as zoomin, indicating a noticeable push-in or scale change in the frame; motionstrength=0.8974 indicates that the clip carries a stable motion signal and is suitable for T2V training to learn natural scene motion, aerial perspectives, and coastal cinematic language</x:v>
       </x:c>
       <x:c r="J289" s="4" t="str">
-        <x:v>Runtime flow of the DataAgent enterprise semantic BI assistant</x:v>
+        <x:v>frame2</x:v>
       </x:c>
       <x:c r="K289" s="4" t="str">
-        <x:v>docs/images/part14/p15_dataagent_semantic_bi_sequence_en.svg</x:v>
+        <x:v>docs/images/part14/p14_video_frame_1.jpg</x:v>
       </x:c>
       <x:c r="L289" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M289" s="4" t="str">
-        <x:v>1800x1120</x:v>
+        <x:v>448x252</x:v>
       </x:c>
       <x:c r="N289" s="4" t="str">
-        <x:v>svg</x:v>
+        <x:v>jpg</x:v>
       </x:c>
       <x:c r="O289" s="4" t="str">
-        <x:v>Runtime flow of the DataAgent enterprise semantic BI assistant.</x:v>
+        <x:v>Table P14-12: Example of multi-frame sampling from a video clip The figure shows two sampled frames from the output data. The clip presents a coastal scene filmed from a high-altitude aerial perspective: deep blue water continuously crashes against rugged reef formations, white foam forms clearly at the edges of the dark rock faces, and sparse green vegetation distributed among the rocks preserves a degree of visual layering within the natural environment. The multi-frame...</x:v>
       </x:c>
       <x:c r="P289" s="4" t="str"/>
       <x:c r="Q289" s="4" t="str">
@@ -19005,9 +19007,197 @@
       <x:c r="S289" s="4" t="str"/>
       <x:c r="T289" s="4" t="str"/>
       <x:c r="U289" s="4" t="str">
+        <x:v>表 P14-12：视频片段多帧抽样示例 图中展示了产出数据中的两帧采样结果。该片段展示了一段从高空视角拍摄的海岸线画面：深蓝色海水不断冲击崎岖礁石，浪花在暗色岩壁边缘形成明显的白色泡沫，岩石间分布着少量绿色植被，使画面在自然环境中保留了一定层次感。多帧 caption 覆盖该片段的主体、场景、光照和氛围，描述自然光照、冷色调海面、清晰岩石纹理，以及海浪运动带来的动态感。从镜头语言标注结果看，该 shot 被识别为 extremewide 景别、highangle 高角度视角，构图方式为 ruleofthirds，光照类型为 natural，整体色彩倾向为 cool，风格标签为 cinematic。相机运动模块将其判定为 zoomin，说明画面存在较明显的推进或尺度变化；motionstrength=0.8974 表明该片段具有稳定运动信号，可用于 T2V 训练中学习自然场景运动、航拍视角和海岸镜头语言</x:v>
+      </x:c>
+      <x:c r="V289" s="4" t="str">
+        <x:v>frame2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="290">
+      <x:c r="A290" s="4" t="str">
+        <x:v>ALT-0289</x:v>
+      </x:c>
+      <x:c r="B290" s="4" t="str">
+        <x:v>en</x:v>
+      </x:c>
+      <x:c r="C290" s="4" t="str">
+        <x:v>Part 14: Practical Projects</x:v>
+      </x:c>
+      <x:c r="D290" s="4" t="str">
+        <x:v>P15</x:v>
+      </x:c>
+      <x:c r="E290" s="4" t="str">
+        <x:v>Project 15: Building an Enterprise Semantic BI Assistant with DataAgent</x:v>
+      </x:c>
+      <x:c r="F290" s="4" t="str">
+        <x:v>docs/en/part14/p15_dataagent_semantic_nl2sql_agent.md</x:v>
+      </x:c>
+      <x:c r="G290" s="4" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H290" s="4" t="str">
+        <x:v>P15-1</x:v>
+      </x:c>
+      <x:c r="I290" s="4" t="str">
+        <x:v>Figure P15-1: Engineering chain of the DataAgent semantic BI assistant</x:v>
+      </x:c>
+      <x:c r="J290" s="4" t="str">
+        <x:v>DataAgent semantic BI assistant engineering chain</x:v>
+      </x:c>
+      <x:c r="K290" s="4" t="str">
+        <x:v>docs/images/part14/p15_dataagent_engineering_chain_en.png</x:v>
+      </x:c>
+      <x:c r="L290" s="4" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="M290" s="4" t="str">
+        <x:v>1536x1024</x:v>
+      </x:c>
+      <x:c r="N290" s="4" t="str">
+        <x:v>png</x:v>
+      </x:c>
+      <x:c r="O290" s="4" t="str">
+        <x:v>Engineering chain of the DataAgent semantic BI assistant.</x:v>
+      </x:c>
+      <x:c r="P290" s="4" t="str"/>
+      <x:c r="Q290" s="4" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="R290" s="4" t="str">
+        <x:v>Draft</x:v>
+      </x:c>
+      <x:c r="S290" s="4" t="str"/>
+      <x:c r="T290" s="4" t="str"/>
+      <x:c r="U290" s="4" t="str">
+        <x:v>Figure P15-1：DataAgent 语义问数助手工程链路</x:v>
+      </x:c>
+      <x:c r="V290" s="4" t="str">
+        <x:v>DataAgent 语义问数助手工程链路</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="291">
+      <x:c r="A291" s="4" t="str">
+        <x:v>ALT-0290</x:v>
+      </x:c>
+      <x:c r="B291" s="4" t="str">
+        <x:v>en</x:v>
+      </x:c>
+      <x:c r="C291" s="4" t="str">
+        <x:v>Part 14: Practical Projects</x:v>
+      </x:c>
+      <x:c r="D291" s="4" t="str">
+        <x:v>P15</x:v>
+      </x:c>
+      <x:c r="E291" s="4" t="str">
+        <x:v>Project 15: Building an Enterprise Semantic BI Assistant with DataAgent</x:v>
+      </x:c>
+      <x:c r="F291" s="4" t="str">
+        <x:v>docs/en/part14/p15_dataagent_semantic_nl2sql_agent.md</x:v>
+      </x:c>
+      <x:c r="G291" s="4" t="n">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="H291" s="4" t="str">
+        <x:v>P15-2</x:v>
+      </x:c>
+      <x:c r="I291" s="4" t="str">
+        <x:v>Figure P15-2: DataGallery ecosystem architecture around DataAgent</x:v>
+      </x:c>
+      <x:c r="J291" s="4" t="str">
+        <x:v>DataGallery ecosystem architecture around DataAgent, Semantic Service, Data Studio, Data Ops, and foundation infrastructure</x:v>
+      </x:c>
+      <x:c r="K291" s="4" t="str">
+        <x:v>docs/images/part14/p15_datagallery_architecture_vector.svg</x:v>
+      </x:c>
+      <x:c r="L291" s="4" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="M291" s="4" t="str">
+        <x:v>1536x1024</x:v>
+      </x:c>
+      <x:c r="N291" s="4" t="str">
+        <x:v>svg</x:v>
+      </x:c>
+      <x:c r="O291" s="4" t="str">
+        <x:v>DataGallery ecosystem architecture around DataAgent.</x:v>
+      </x:c>
+      <x:c r="P291" s="4" t="str">
+        <x:v>Review against the figure and surrounding text in Project 15: Building an Enterprise Semantic BI Assistant with DataAgent; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
+      </x:c>
+      <x:c r="Q291" s="4" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="R291" s="4" t="str">
+        <x:v>Draft</x:v>
+      </x:c>
+      <x:c r="S291" s="4" t="str"/>
+      <x:c r="T291" s="4" t="str"/>
+      <x:c r="U291" s="4" t="str">
+        <x:v>Figure P15-2：围绕 DataAgent 展开的 DataGallery 生态架构</x:v>
+      </x:c>
+      <x:c r="V291" s="4" t="str">
+        <x:v>围绕 DataAgent、Semantic Service、Data Studio、Data Ops 与基础设施展开的 DataGallery 生态架构</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="292">
+      <x:c r="A292" s="4" t="str">
+        <x:v>ALT-0291</x:v>
+      </x:c>
+      <x:c r="B292" s="4" t="str">
+        <x:v>en</x:v>
+      </x:c>
+      <x:c r="C292" s="4" t="str">
+        <x:v>Part 14: Practical Projects</x:v>
+      </x:c>
+      <x:c r="D292" s="4" t="str">
+        <x:v>P15</x:v>
+      </x:c>
+      <x:c r="E292" s="4" t="str">
+        <x:v>Project 15: Building an Enterprise Semantic BI Assistant with DataAgent</x:v>
+      </x:c>
+      <x:c r="F292" s="4" t="str">
+        <x:v>docs/en/part14/p15_dataagent_semantic_nl2sql_agent.md</x:v>
+      </x:c>
+      <x:c r="G292" s="4" t="n">
+        <x:v>579</x:v>
+      </x:c>
+      <x:c r="H292" s="4" t="str">
+        <x:v>P15-3</x:v>
+      </x:c>
+      <x:c r="I292" s="4" t="str">
+        <x:v>Figure P15-3: Runtime flow of the DataAgent enterprise semantic BI assistant</x:v>
+      </x:c>
+      <x:c r="J292" s="4" t="str">
+        <x:v>Runtime flow of the DataAgent enterprise semantic BI assistant</x:v>
+      </x:c>
+      <x:c r="K292" s="4" t="str">
+        <x:v>docs/images/part14/p15_dataagent_semantic_bi_sequence_en.svg</x:v>
+      </x:c>
+      <x:c r="L292" s="4" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="M292" s="4" t="str">
+        <x:v>1800x1120</x:v>
+      </x:c>
+      <x:c r="N292" s="4" t="str">
+        <x:v>svg</x:v>
+      </x:c>
+      <x:c r="O292" s="4" t="str">
+        <x:v>Runtime flow of the DataAgent enterprise semantic BI assistant.</x:v>
+      </x:c>
+      <x:c r="P292" s="4" t="str"/>
+      <x:c r="Q292" s="4" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="R292" s="4" t="str">
+        <x:v>Draft</x:v>
+      </x:c>
+      <x:c r="S292" s="4" t="str"/>
+      <x:c r="T292" s="4" t="str"/>
+      <x:c r="U292" s="4" t="str">
         <x:v>Figure P15-3：DataAgent 企业语义问数助手运行流程</x:v>
       </x:c>
-      <x:c r="V289" s="4" t="str">
+      <x:c r="V292" s="4" t="str">
         <x:v>DataAgent 企业语义问数助手运行流程</x:v>
       </x:c>
     </x:row>
